--- a/youzi/越王大道/index.xlsx
+++ b/youzi/越王大道/index.xlsx
@@ -39,6 +39,60 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF70C483"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAE202D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB8E1C1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAB1E2C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC4E7CC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED979F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8236"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
@@ -51,151 +105,3073 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA91E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218E3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDA3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAB1F2C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAC1F2C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC32938"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BDC2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC02836"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDE4150"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFA4AB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE2E4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD33140"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCF0F1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2FAA4B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFECF7EF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF3F4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED9BA3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFACDDB7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBE8EA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBF2836"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD53241"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9808A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3D4D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7130"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7DCA8F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC42A38"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC62B39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDB3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B2B8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF95D3A3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCA2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF67C07B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC969F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25866"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDA3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBB2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3B9BF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD2303F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9DFE1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEE9FA6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFDFD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A702F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8437"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BFC4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E7F35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBEDEE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7B33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5BBC71"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE3E5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFAE202D"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA91E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC4E7CC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218E3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF70C483"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED979F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAB1E2C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB8E1C1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8236"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFDC3545"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDA3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6AC27E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBEAEC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23943D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDE4251"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23943D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCFDFC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8437"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23953E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A443"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7B34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF46B35F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A712F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208838"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC3E6CB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218D3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8437"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF37AD52"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC52A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBC2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF63BF78"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7FCA90"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5FBD75"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23943D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8638"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7E35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23933D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8638"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8738"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218D3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7A33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8136"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2DFBC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2FA94B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6DC381"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF53B86A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B2B8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5EBD74"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF84CD95"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8738"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2DFBC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7CC98E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF46B35F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A644"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF249A3F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6CC280"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8638"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77580"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFCFC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77883"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBF2736"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22903C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7CC98E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF95D3A3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9DCDF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9858F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BAC0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFBFB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B3B9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF99D5A7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8337"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8538"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6CDD1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD43140"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDE4251"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24983F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196F2F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208839"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC929B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4C4C8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF54B96B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF37AD52"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCEEBD5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46672"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8036"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2CA848"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDE4554"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6727D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8538"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A544"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBB2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3949"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6D0D3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF37AD52"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7832"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE35E6B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC32A38"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6F4E9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAE202D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE35E6B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCEEEF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7ECA8F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBB2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD63242"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B4BA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCDEAD4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8537"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE04D5B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8638"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6FBF7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22923D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC12937"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3847"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB72432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA9DBB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8ED19D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8538"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC92C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC52A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF64BF79"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF269F42"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE5E7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3848"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A042"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD1303F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9DEE0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC72B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEE9DA4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B3B9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC939B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196D2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259E41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8136"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7E35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAD1F2D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D3D7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB3E0BD"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -213,7 +3189,157 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE3E6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC12937"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC72B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE4F4E8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7BC98D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7BC98D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7631"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBC2635"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE4F4E8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A142"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9838D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0DEBA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7BC98D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBC2635"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD63242"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE35D6A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAD1F2D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE04F5D"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -225,3151 +3351,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFAB1F2C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BDC2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFECF7EF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF3F4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE2E4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD33140"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2FAA4B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDE4150"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC02836"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCF0F1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFA4AB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD53241"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFACDDB7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7DCA8F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED9BA3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBE8EA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9808A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3D4D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC42A38"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7130"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBF2836"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC62B39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF67C07B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC969F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCA2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDB3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF95D3A3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B2B8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDA3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD2303F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25866"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEE9FA6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBB2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFDFD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9DFE1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3B9BF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BFC4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBEDEE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8437"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A702F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7B33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E7F35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBEAEC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAE202D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCFDFC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE3E5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23953E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5BBC71"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8437"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6AC27E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23943D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23943D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDE4251"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF46B35F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A712F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8437"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208838"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7B34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A443"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC3E6CB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218D3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC52A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF63BF78"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7FCA90"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23943D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF37AD52"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBC2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5FBD75"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8638"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8738"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218D3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23933D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7E35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8638"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7A33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8136"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2DFBC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7CC98E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF46B35F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8738"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5EBD74"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6DC381"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B2B8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2FA94B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF53B86A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF84CD95"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2DFBC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77580"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFCFC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A644"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6CC280"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8638"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF249A3F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77883"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7CC98E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF95D3A3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22903C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBF2736"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6CDD1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8538"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B3B9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8337"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BAC0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFBFB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9DCDF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF99D5A7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9858F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD43140"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDE4251"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196F2F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC929B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208839"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF37AD52"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4C4C8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF54B96B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCEEBD5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46672"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8036"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDE4554"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2CA848"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6727D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A544"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8538"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBB2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3949"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF37AD52"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7832"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6D0D3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC32A38"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6F4E9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAE202D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE35E6B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE35E6B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCEEEF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B4BA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCDEAD4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8537"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD63242"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBB2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE04D5B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7ECA8F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8638"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6FBF7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22923D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC12937"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3847"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB72432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF269F42"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8ED19D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA9DBB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF64BF79"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC52A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC92C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE5E7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8538"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A042"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3848"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEE9DA4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC72B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B3B9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD1303F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC939B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9DEE0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259E41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196D2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7E35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8136"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAD1F2D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE3E6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC12937"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC72B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB3E0BD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC32938"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D3D7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7631"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBC2635"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE4F4E8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7BC98D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD63242"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0DEBA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE4F4E8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7BC98D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBC2635"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9838D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7BC98D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A142"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAD1F2D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE35D6A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE04F5D"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFED9BA2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAC1F2C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -9306,7 +9306,7 @@
       <c r="C2" t="str">
         <v>002570</v>
       </c>
-      <c r="D2" s="2" t="str">
+      <c r="D2" s="11" t="str">
         <v>净卖: -1602.12万</v>
       </c>
       <c r="E2">
@@ -9321,40 +9321,40 @@
       <c r="H2">
         <v>0.15</v>
       </c>
-      <c r="I2" s="5">
+      <c r="I2" s="12">
         <v>9.77</v>
       </c>
-      <c r="J2" s="10">
+      <c r="J2" s="5">
         <v>9.62</v>
       </c>
       <c r="K2" s="6">
         <v>-1.35</v>
       </c>
-      <c r="L2" s="7">
+      <c r="L2" s="13">
         <v>-7.07</v>
       </c>
-      <c r="M2" s="8">
+      <c r="M2" s="1">
         <v>-3.31</v>
       </c>
-      <c r="N2" s="9">
+      <c r="N2" s="7">
         <v>2.56</v>
       </c>
-      <c r="O2" s="3">
+      <c r="O2" s="2">
         <v>9.32</v>
       </c>
-      <c r="P2" s="11">
+      <c r="P2" s="3">
         <v>-1.65</v>
       </c>
       <c r="Q2" s="4">
         <v>-11.43</v>
       </c>
-      <c r="R2" s="12">
+      <c r="R2" s="8">
         <v>-9.47</v>
       </c>
-      <c r="S2" s="13">
+      <c r="S2" s="9">
         <v>-8.12</v>
       </c>
-      <c r="T2" s="1">
+      <c r="T2" s="10">
         <v>-24.21</v>
       </c>
     </row>
@@ -9383,40 +9383,40 @@
       <c r="H3">
         <v>0.12</v>
       </c>
-      <c r="I3" s="25">
+      <c r="I3" s="22">
         <v>5.12</v>
       </c>
-      <c r="J3" s="22">
+      <c r="J3" s="23">
         <v>15.65</v>
       </c>
-      <c r="K3" s="23">
+      <c r="K3" s="18">
         <v>27.2</v>
       </c>
-      <c r="L3" s="16">
+      <c r="L3" s="15">
         <v>27.56</v>
       </c>
-      <c r="M3" s="26">
+      <c r="M3" s="19">
         <v>40.3</v>
       </c>
-      <c r="N3" s="14">
+      <c r="N3" s="24">
         <v>27.68</v>
       </c>
-      <c r="O3" s="17">
+      <c r="O3" s="25">
         <v>30.06</v>
       </c>
-      <c r="P3" s="18">
+      <c r="P3" s="26">
         <v>28.1</v>
       </c>
-      <c r="Q3" s="24">
+      <c r="Q3" s="16">
         <v>36.9</v>
       </c>
-      <c r="R3" s="19">
+      <c r="R3" s="17">
         <v>34.52</v>
       </c>
       <c r="S3" s="20">
         <v>21.07</v>
       </c>
-      <c r="T3" s="15">
+      <c r="T3" s="14">
         <v>26.67</v>
       </c>
     </row>
@@ -9430,7 +9430,7 @@
       <c r="C4" t="str">
         <v>002229</v>
       </c>
-      <c r="D4" s="37" t="str">
+      <c r="D4" s="35" t="str">
         <v>净买: 2135.02万</v>
       </c>
       <c r="E4">
@@ -9451,31 +9451,31 @@
       <c r="J4" s="39">
         <v>11.75</v>
       </c>
-      <c r="K4" s="33">
+      <c r="K4" s="31">
         <v>21.04</v>
       </c>
-      <c r="L4" s="34">
+      <c r="L4" s="27">
         <v>28.15</v>
       </c>
-      <c r="M4" s="27">
+      <c r="M4" s="28">
         <v>15.34</v>
       </c>
-      <c r="N4" s="35">
+      <c r="N4" s="32">
         <v>13.65</v>
       </c>
-      <c r="O4" s="28">
+      <c r="O4" s="33">
         <v>13.02</v>
       </c>
-      <c r="P4" s="29">
+      <c r="P4" s="36">
         <v>7.32</v>
       </c>
-      <c r="Q4" s="31">
+      <c r="Q4" s="34">
         <v>9.5</v>
       </c>
-      <c r="R4" s="32">
+      <c r="R4" s="29">
         <v>9.57</v>
       </c>
-      <c r="S4" s="36">
+      <c r="S4" s="37">
         <v>14.22</v>
       </c>
       <c r="T4" s="30">
@@ -9492,7 +9492,7 @@
       <c r="C5" t="str">
         <v>002915</v>
       </c>
-      <c r="D5" s="42" t="str">
+      <c r="D5" s="41" t="str">
         <v>净卖: -2747.73万</v>
       </c>
       <c r="E5">
@@ -9507,40 +9507,40 @@
       <c r="H5">
         <v>9.98</v>
       </c>
-      <c r="I5" s="48">
+      <c r="I5" s="51">
         <v>0</v>
       </c>
-      <c r="J5" s="43">
+      <c r="J5" s="52">
         <v>0.28</v>
       </c>
-      <c r="K5" s="40">
+      <c r="K5" s="42">
         <v>10.29</v>
       </c>
-      <c r="L5" s="50">
+      <c r="L5" s="48">
         <v>0.37</v>
       </c>
-      <c r="M5" s="51">
+      <c r="M5" s="45">
         <v>2.25</v>
       </c>
-      <c r="N5" s="44">
+      <c r="N5" s="46">
         <v>0.7</v>
       </c>
-      <c r="O5" s="49">
+      <c r="O5" s="43">
         <v>7.63</v>
       </c>
-      <c r="P5" s="45">
+      <c r="P5" s="47">
         <v>5.76</v>
       </c>
-      <c r="Q5" s="46">
+      <c r="Q5" s="49">
         <v>-4.82</v>
       </c>
-      <c r="R5" s="47">
+      <c r="R5" s="44">
         <v>4.68</v>
       </c>
-      <c r="S5" s="52">
+      <c r="S5" s="40">
         <v>11</v>
       </c>
-      <c r="T5" s="41">
+      <c r="T5" s="50">
         <v>-0.42</v>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       <c r="C6" t="str">
         <v>002177</v>
       </c>
-      <c r="D6" s="65" t="str">
+      <c r="D6" s="63" t="str">
         <v>净买: 3117.92万</v>
       </c>
       <c r="E6">
@@ -9575,34 +9575,34 @@
       <c r="J6" s="64">
         <v>10.79</v>
       </c>
-      <c r="K6" s="61">
+      <c r="K6" s="65">
         <v>7.24</v>
       </c>
-      <c r="L6" s="53">
+      <c r="L6" s="57">
         <v>12.3</v>
       </c>
-      <c r="M6" s="54">
+      <c r="M6" s="58">
         <v>5.6</v>
       </c>
-      <c r="N6" s="57">
+      <c r="N6" s="53">
         <v>2.46</v>
       </c>
-      <c r="O6" s="55">
+      <c r="O6" s="54">
         <v>-1.91</v>
       </c>
-      <c r="P6" s="62">
+      <c r="P6" s="61">
         <v>-9.56</v>
       </c>
-      <c r="Q6" s="56">
+      <c r="Q6" s="62">
         <v>-3.01</v>
       </c>
-      <c r="R6" s="58">
+      <c r="R6" s="55">
         <v>0.55</v>
       </c>
       <c r="S6" s="59">
         <v>3.14</v>
       </c>
-      <c r="T6" s="63">
+      <c r="T6" s="56">
         <v>7.65</v>
       </c>
     </row>
@@ -9616,7 +9616,7 @@
       <c r="C7" t="str">
         <v>002177</v>
       </c>
-      <c r="D7" s="77" t="str">
+      <c r="D7" s="71" t="str">
         <v>净卖: -2852.77万</v>
       </c>
       <c r="E7">
@@ -9631,40 +9631,40 @@
       <c r="H7">
         <v>-4.04</v>
       </c>
-      <c r="I7" s="73">
+      <c r="I7" s="77">
         <v>10.19</v>
       </c>
-      <c r="J7" s="74">
+      <c r="J7" s="72">
         <v>6.66</v>
       </c>
-      <c r="K7" s="70">
+      <c r="K7" s="73">
         <v>11.68</v>
       </c>
-      <c r="L7" s="75">
+      <c r="L7" s="67">
         <v>5.03</v>
       </c>
-      <c r="M7" s="78">
+      <c r="M7" s="68">
         <v>1.9</v>
       </c>
-      <c r="N7" s="76">
+      <c r="N7" s="69">
         <v>-2.45</v>
       </c>
-      <c r="O7" s="66">
+      <c r="O7" s="70">
         <v>-10.05</v>
       </c>
-      <c r="P7" s="71">
+      <c r="P7" s="74">
         <v>-3.53</v>
       </c>
-      <c r="Q7" s="68">
+      <c r="Q7" s="75">
         <v>0</v>
       </c>
-      <c r="R7" s="72">
+      <c r="R7" s="78">
         <v>2.58</v>
       </c>
-      <c r="S7" s="69">
+      <c r="S7" s="76">
         <v>-5.3</v>
       </c>
-      <c r="T7" s="67">
+      <c r="T7" s="66">
         <v>7.07</v>
       </c>
     </row>
@@ -9678,7 +9678,7 @@
       <c r="C8" t="str">
         <v>002882</v>
       </c>
-      <c r="D8" s="84" t="str">
+      <c r="D8" s="88" t="str">
         <v>净卖: -1459.92万</v>
       </c>
       <c r="E8">
@@ -9693,40 +9693,40 @@
       <c r="H8">
         <v>-0.92</v>
       </c>
-      <c r="I8" s="82">
+      <c r="I8" s="91">
         <v>11.01</v>
       </c>
-      <c r="J8" s="87">
+      <c r="J8" s="89">
         <v>11.21</v>
       </c>
-      <c r="K8" s="91">
+      <c r="K8" s="82">
         <v>1.71</v>
       </c>
-      <c r="L8" s="83">
+      <c r="L8" s="79">
         <v>4.11</v>
       </c>
-      <c r="M8" s="88">
+      <c r="M8" s="90">
         <v>0.04</v>
       </c>
-      <c r="N8" s="89">
+      <c r="N8" s="86">
         <v>0.78</v>
       </c>
-      <c r="O8" s="85">
+      <c r="O8" s="87">
         <v>2.37</v>
       </c>
-      <c r="P8" s="79">
+      <c r="P8" s="80">
         <v>5.12</v>
       </c>
-      <c r="Q8" s="80">
+      <c r="Q8" s="83">
         <v>5.93</v>
       </c>
-      <c r="R8" s="86">
+      <c r="R8" s="81">
         <v>8.07</v>
       </c>
-      <c r="S8" s="90">
+      <c r="S8" s="84">
         <v>18.88</v>
       </c>
-      <c r="T8" s="81">
+      <c r="T8" s="85">
         <v>18.88</v>
       </c>
     </row>
@@ -9740,7 +9740,7 @@
       <c r="C9" t="str">
         <v>003029</v>
       </c>
-      <c r="D9" s="92" t="str">
+      <c r="D9" s="98" t="str">
         <v>净卖: -276.02万</v>
       </c>
       <c r="E9">
@@ -9758,37 +9758,37 @@
       <c r="I9" s="99">
         <v>0</v>
       </c>
-      <c r="J9" s="101">
+      <c r="J9" s="94">
         <v>10.01</v>
       </c>
-      <c r="K9" s="93">
+      <c r="K9" s="100">
         <v>1.58</v>
       </c>
-      <c r="L9" s="94">
+      <c r="L9" s="102">
         <v>0.44</v>
       </c>
-      <c r="M9" s="102">
+      <c r="M9" s="92">
         <v>-9.6</v>
       </c>
-      <c r="N9" s="95">
+      <c r="N9" s="103">
         <v>-14.15</v>
       </c>
-      <c r="O9" s="96">
+      <c r="O9" s="95">
         <v>-11.05</v>
       </c>
-      <c r="P9" s="103">
+      <c r="P9" s="104">
         <v>-8.72</v>
       </c>
-      <c r="Q9" s="100">
+      <c r="Q9" s="96">
         <v>-7.3</v>
       </c>
-      <c r="R9" s="104">
+      <c r="R9" s="101">
         <v>-8.31</v>
       </c>
-      <c r="S9" s="97">
+      <c r="S9" s="93">
         <v>-7.9</v>
       </c>
-      <c r="T9" s="98">
+      <c r="T9" s="97">
         <v>-31.93</v>
       </c>
     </row>
@@ -9802,7 +9802,7 @@
       <c r="C10" t="str">
         <v>002017</v>
       </c>
-      <c r="D10" s="113" t="str">
+      <c r="D10" s="108" t="str">
         <v>净买: 6518.56万</v>
       </c>
       <c r="E10">
@@ -9817,40 +9817,40 @@
       <c r="H10">
         <v>5.13</v>
       </c>
-      <c r="I10" s="116">
+      <c r="I10" s="113">
         <v>4.66</v>
       </c>
-      <c r="J10" s="107">
+      <c r="J10" s="115">
         <v>-0.06</v>
       </c>
       <c r="K10" s="114">
         <v>-6.53</v>
       </c>
-      <c r="L10" s="117">
+      <c r="L10" s="109">
         <v>-5.79</v>
       </c>
-      <c r="M10" s="111">
+      <c r="M10" s="116">
         <v>-7.89</v>
       </c>
-      <c r="N10" s="112">
+      <c r="N10" s="110">
         <v>-3.46</v>
       </c>
-      <c r="O10" s="108">
+      <c r="O10" s="106">
         <v>0.68</v>
       </c>
-      <c r="P10" s="105">
+      <c r="P10" s="111">
         <v>0.51</v>
       </c>
-      <c r="Q10" s="109">
+      <c r="Q10" s="117">
         <v>-6.47</v>
       </c>
-      <c r="R10" s="110">
+      <c r="R10" s="105">
         <v>-3.8</v>
       </c>
-      <c r="S10" s="115">
+      <c r="S10" s="112">
         <v>-6.53</v>
       </c>
-      <c r="T10" s="106">
+      <c r="T10" s="107">
         <v>9.31</v>
       </c>
     </row>
@@ -9864,7 +9864,7 @@
       <c r="C11" t="str">
         <v>002670</v>
       </c>
-      <c r="D11" s="129" t="str">
+      <c r="D11" s="126" t="str">
         <v>净卖: -2720.58万</v>
       </c>
       <c r="E11">
@@ -9879,40 +9879,40 @@
       <c r="H11">
         <v>-0.81</v>
       </c>
-      <c r="I11" s="124">
+      <c r="I11" s="118">
         <v>-5.23</v>
       </c>
-      <c r="J11" s="125">
+      <c r="J11" s="127">
         <v>-1.39</v>
       </c>
-      <c r="K11" s="119">
+      <c r="K11" s="123">
         <v>-9.57</v>
       </c>
-      <c r="L11" s="126">
+      <c r="L11" s="129">
         <v>-7.18</v>
       </c>
-      <c r="M11" s="121">
+      <c r="M11" s="124">
         <v>-7.62</v>
       </c>
-      <c r="N11" s="122">
+      <c r="N11" s="119">
         <v>-8.69</v>
       </c>
-      <c r="O11" s="130">
+      <c r="O11" s="128">
         <v>-7.37</v>
       </c>
-      <c r="P11" s="127">
+      <c r="P11" s="120">
         <v>-8.56</v>
       </c>
-      <c r="Q11" s="128">
+      <c r="Q11" s="125">
         <v>-8.63</v>
       </c>
-      <c r="R11" s="118">
+      <c r="R11" s="121">
         <v>-4.28</v>
       </c>
-      <c r="S11" s="123">
+      <c r="S11" s="122">
         <v>-8.56</v>
       </c>
-      <c r="T11" s="120">
+      <c r="T11" s="130">
         <v>-7.93</v>
       </c>
     </row>
@@ -9926,7 +9926,7 @@
       <c r="C12" t="str">
         <v>002579</v>
       </c>
-      <c r="D12" s="143" t="str">
+      <c r="D12" s="136" t="str">
         <v>净买: 4403.72万</v>
       </c>
       <c r="E12">
@@ -9941,40 +9941,40 @@
       <c r="H12">
         <v>-2.68</v>
       </c>
-      <c r="I12" s="138">
+      <c r="I12" s="137">
         <v>13.04</v>
       </c>
-      <c r="J12" s="131">
+      <c r="J12" s="132">
         <v>12.54</v>
       </c>
-      <c r="K12" s="141">
+      <c r="K12" s="135">
         <v>7.97</v>
       </c>
-      <c r="L12" s="134">
+      <c r="L12" s="138">
         <v>12.54</v>
       </c>
-      <c r="M12" s="132">
+      <c r="M12" s="133">
         <v>7.1</v>
       </c>
-      <c r="N12" s="135">
+      <c r="N12" s="140">
         <v>-3.62</v>
       </c>
-      <c r="O12" s="136">
+      <c r="O12" s="141">
         <v>-2.97</v>
       </c>
-      <c r="P12" s="133">
+      <c r="P12" s="139">
         <v>-5.36</v>
       </c>
       <c r="Q12" s="142">
         <v>-3.7</v>
       </c>
-      <c r="R12" s="137">
+      <c r="R12" s="134">
         <v>-10.07</v>
       </c>
-      <c r="S12" s="139">
+      <c r="S12" s="143">
         <v>-6.59</v>
       </c>
-      <c r="T12" s="140">
+      <c r="T12" s="131">
         <v>-4.64</v>
       </c>
     </row>
@@ -9988,7 +9988,7 @@
       <c r="C13" t="str">
         <v>002229</v>
       </c>
-      <c r="D13" s="151" t="str">
+      <c r="D13" s="156" t="str">
         <v>净卖: -4629.75万</v>
       </c>
       <c r="E13">
@@ -10006,10 +10006,10 @@
       <c r="I13" s="144">
         <v>-7.78</v>
       </c>
-      <c r="J13" s="155">
+      <c r="J13" s="145">
         <v>-8.44</v>
       </c>
-      <c r="K13" s="145">
+      <c r="K13" s="154">
         <v>-11.23</v>
       </c>
       <c r="L13" s="152">
@@ -10018,25 +10018,25 @@
       <c r="M13" s="146">
         <v>-10.66</v>
       </c>
-      <c r="N13" s="149">
+      <c r="N13" s="147">
         <v>-6.65</v>
       </c>
-      <c r="O13" s="156">
+      <c r="O13" s="150">
         <v>-7.74</v>
       </c>
-      <c r="P13" s="147">
+      <c r="P13" s="151">
         <v>-7.69</v>
       </c>
-      <c r="Q13" s="153">
+      <c r="Q13" s="148">
         <v>-11.37</v>
       </c>
-      <c r="R13" s="154">
+      <c r="R13" s="149">
         <v>-10.8</v>
       </c>
-      <c r="S13" s="150">
+      <c r="S13" s="153">
         <v>-13.68</v>
       </c>
-      <c r="T13" s="148">
+      <c r="T13" s="155">
         <v>-7.17</v>
       </c>
     </row>
@@ -10050,7 +10050,7 @@
       <c r="C14" t="str">
         <v>000657</v>
       </c>
-      <c r="D14" s="162" t="str">
+      <c r="D14" s="159" t="str">
         <v>净卖: -6184.73万</v>
       </c>
       <c r="E14">
@@ -10065,40 +10065,40 @@
       <c r="H14">
         <v>-2</v>
       </c>
-      <c r="I14" s="167">
+      <c r="I14" s="166">
         <v>-8.16</v>
       </c>
-      <c r="J14" s="168">
+      <c r="J14" s="160">
         <v>-13.48</v>
       </c>
-      <c r="K14" s="163">
+      <c r="K14" s="161">
         <v>-14.93</v>
       </c>
-      <c r="L14" s="160">
+      <c r="L14" s="167">
         <v>-15.36</v>
       </c>
-      <c r="M14" s="165">
+      <c r="M14" s="162">
         <v>-15.2</v>
       </c>
-      <c r="N14" s="169">
+      <c r="N14" s="168">
         <v>-13.43</v>
       </c>
-      <c r="O14" s="157">
+      <c r="O14" s="163">
         <v>-13.1</v>
       </c>
-      <c r="P14" s="158">
+      <c r="P14" s="157">
         <v>-11.6</v>
       </c>
-      <c r="Q14" s="161">
+      <c r="Q14" s="169">
         <v>-10.74</v>
       </c>
-      <c r="R14" s="159">
+      <c r="R14" s="164">
         <v>-10.9</v>
       </c>
-      <c r="S14" s="166">
+      <c r="S14" s="158">
         <v>-8.81</v>
       </c>
-      <c r="T14" s="164">
+      <c r="T14" s="165">
         <v>201.4</v>
       </c>
     </row>
@@ -10112,7 +10112,7 @@
       <c r="C15" t="str">
         <v>002670</v>
       </c>
-      <c r="D15" s="171" t="str">
+      <c r="D15" s="179" t="str">
         <v>净卖: -7597.74万</v>
       </c>
       <c r="E15">
@@ -10127,37 +10127,37 @@
       <c r="H15">
         <v>0.45</v>
       </c>
-      <c r="I15" s="178">
+      <c r="I15" s="174">
         <v>1.89</v>
       </c>
-      <c r="J15" s="182">
+      <c r="J15" s="170">
         <v>-1.79</v>
       </c>
-      <c r="K15" s="170">
+      <c r="K15" s="180">
         <v>-1.79</v>
       </c>
-      <c r="L15" s="172">
+      <c r="L15" s="181">
         <v>-3.03</v>
       </c>
-      <c r="M15" s="179">
+      <c r="M15" s="171">
         <v>-4.83</v>
       </c>
       <c r="N15" s="175">
         <v>-3.73</v>
       </c>
-      <c r="O15" s="176">
+      <c r="O15" s="172">
         <v>-3.38</v>
       </c>
-      <c r="P15" s="173">
+      <c r="P15" s="182">
         <v>-4.28</v>
       </c>
-      <c r="Q15" s="174">
+      <c r="Q15" s="178">
         <v>-7.71</v>
       </c>
-      <c r="R15" s="180">
+      <c r="R15" s="173">
         <v>-3.98</v>
       </c>
-      <c r="S15" s="181">
+      <c r="S15" s="176">
         <v>-2.84</v>
       </c>
       <c r="T15" s="177">
@@ -10174,7 +10174,7 @@
       <c r="C16" t="str">
         <v>688039</v>
       </c>
-      <c r="D16" s="187" t="str">
+      <c r="D16" s="190" t="str">
         <v>净买: 3066.00万</v>
       </c>
       <c r="E16">
@@ -10189,40 +10189,40 @@
       <c r="H16">
         <v>7.16</v>
       </c>
-      <c r="I16" s="195">
+      <c r="I16" s="186">
         <v>11.98</v>
       </c>
-      <c r="J16" s="183">
+      <c r="J16" s="187">
         <v>16.69</v>
       </c>
-      <c r="K16" s="184">
+      <c r="K16" s="194">
         <v>3.41</v>
       </c>
-      <c r="L16" s="188">
+      <c r="L16" s="195">
         <v>0.07</v>
       </c>
-      <c r="M16" s="186">
+      <c r="M16" s="183">
         <v>-5.26</v>
       </c>
-      <c r="N16" s="192">
+      <c r="N16" s="191">
         <v>-3.41</v>
       </c>
-      <c r="O16" s="189">
+      <c r="O16" s="184">
         <v>-5.04</v>
       </c>
-      <c r="P16" s="185">
+      <c r="P16" s="189">
         <v>-10.52</v>
       </c>
-      <c r="Q16" s="193">
+      <c r="Q16" s="192">
         <v>-7.78</v>
       </c>
-      <c r="R16" s="194">
+      <c r="R16" s="185">
         <v>-6.1</v>
       </c>
-      <c r="S16" s="190">
+      <c r="S16" s="188">
         <v>-7.34</v>
       </c>
-      <c r="T16" s="191">
+      <c r="T16" s="193">
         <v>-20.42</v>
       </c>
     </row>
@@ -10236,7 +10236,7 @@
       <c r="C17" t="str">
         <v>600408</v>
       </c>
-      <c r="D17" s="202" t="str">
+      <c r="D17" s="201" t="str">
         <v>净买: 1877.05万</v>
       </c>
       <c r="E17">
@@ -10251,40 +10251,40 @@
       <c r="H17">
         <v>-4.45</v>
       </c>
-      <c r="I17" s="203">
+      <c r="I17" s="202">
         <v>15.2</v>
       </c>
-      <c r="J17" s="198">
+      <c r="J17" s="208">
         <v>26.72</v>
       </c>
-      <c r="K17" s="199">
+      <c r="K17" s="203">
         <v>39.46</v>
       </c>
-      <c r="L17" s="207">
+      <c r="L17" s="196">
         <v>53.43</v>
       </c>
-      <c r="M17" s="204">
+      <c r="M17" s="197">
         <v>68.87</v>
       </c>
-      <c r="N17" s="200">
+      <c r="N17" s="206">
         <v>52.7</v>
       </c>
-      <c r="O17" s="208">
+      <c r="O17" s="204">
         <v>37.5</v>
       </c>
       <c r="P17" s="205">
         <v>24.26</v>
       </c>
-      <c r="Q17" s="196">
+      <c r="Q17" s="198">
         <v>14.95</v>
       </c>
-      <c r="R17" s="201">
+      <c r="R17" s="199">
         <v>10.54</v>
       </c>
-      <c r="S17" s="197">
+      <c r="S17" s="200">
         <v>11.52</v>
       </c>
-      <c r="T17" s="206">
+      <c r="T17" s="207">
         <v>-23.28</v>
       </c>
     </row>
@@ -10298,7 +10298,7 @@
       <c r="C18" t="str">
         <v>601566</v>
       </c>
-      <c r="D18" s="214" t="str">
+      <c r="D18" s="220" t="str">
         <v>净买: 5226.66万</v>
       </c>
       <c r="E18">
@@ -10313,40 +10313,40 @@
       <c r="H18">
         <v>10.02</v>
       </c>
-      <c r="I18" s="215">
+      <c r="I18" s="221">
         <v>0</v>
       </c>
-      <c r="J18" s="211">
+      <c r="J18" s="214">
         <v>9.97</v>
       </c>
       <c r="K18" s="212">
         <v>20.95</v>
       </c>
-      <c r="L18" s="216">
+      <c r="L18" s="209">
         <v>33.02</v>
       </c>
-      <c r="M18" s="213">
+      <c r="M18" s="215">
         <v>19.73</v>
       </c>
-      <c r="N18" s="221">
+      <c r="N18" s="216">
         <v>7.73</v>
       </c>
-      <c r="O18" s="209">
+      <c r="O18" s="210">
         <v>3.32</v>
       </c>
-      <c r="P18" s="210">
+      <c r="P18" s="211">
         <v>-5.35</v>
       </c>
-      <c r="Q18" s="220">
+      <c r="Q18" s="217">
         <v>-6.94</v>
       </c>
-      <c r="R18" s="217">
+      <c r="R18" s="218">
         <v>-3.03</v>
       </c>
-      <c r="S18" s="218">
+      <c r="S18" s="219">
         <v>-2.46</v>
       </c>
-      <c r="T18" s="219">
+      <c r="T18" s="213">
         <v>-22.83</v>
       </c>
     </row>
@@ -10360,7 +10360,7 @@
       <c r="C19" t="str">
         <v>002029</v>
       </c>
-      <c r="D19" s="224" t="str">
+      <c r="D19" s="225" t="str">
         <v>净卖: -1276.40万</v>
       </c>
       <c r="E19">
@@ -10375,40 +10375,40 @@
       <c r="H19">
         <v>0</v>
       </c>
-      <c r="I19" s="232">
+      <c r="I19" s="226">
         <v>9.97</v>
       </c>
-      <c r="J19" s="225">
+      <c r="J19" s="229">
         <v>1.88</v>
       </c>
-      <c r="K19" s="233">
+      <c r="K19" s="230">
         <v>-2.35</v>
       </c>
-      <c r="L19" s="230">
+      <c r="L19" s="233">
         <v>-9.97</v>
       </c>
-      <c r="M19" s="226">
+      <c r="M19" s="227">
         <v>-11.67</v>
       </c>
-      <c r="N19" s="227">
+      <c r="N19" s="231">
         <v>-8</v>
       </c>
-      <c r="O19" s="222">
+      <c r="O19" s="234">
         <v>1.22</v>
       </c>
-      <c r="P19" s="231">
+      <c r="P19" s="222">
         <v>0.85</v>
       </c>
-      <c r="Q19" s="234">
+      <c r="Q19" s="223">
         <v>3.01</v>
       </c>
-      <c r="R19" s="228">
+      <c r="R19" s="224">
         <v>1.69</v>
       </c>
-      <c r="S19" s="229">
+      <c r="S19" s="228">
         <v>0.09</v>
       </c>
-      <c r="T19" s="223">
+      <c r="T19" s="232">
         <v>-7.81</v>
       </c>
     </row>
@@ -10422,7 +10422,7 @@
       <c r="C20" t="str">
         <v>601566</v>
       </c>
-      <c r="D20" s="239" t="str">
+      <c r="D20" s="240" t="str">
         <v>净卖: -2737.55万</v>
       </c>
       <c r="E20">
@@ -10440,37 +10440,37 @@
       <c r="I20" s="236">
         <v>5.75</v>
       </c>
-      <c r="J20" s="240">
+      <c r="J20" s="245">
         <v>16.3</v>
       </c>
-      <c r="K20" s="241">
+      <c r="K20" s="237">
         <v>4.67</v>
       </c>
-      <c r="L20" s="246">
+      <c r="L20" s="241">
         <v>-5.81</v>
       </c>
-      <c r="M20" s="242">
+      <c r="M20" s="246">
         <v>-9.67</v>
       </c>
-      <c r="N20" s="247">
+      <c r="N20" s="238">
         <v>-17.25</v>
       </c>
-      <c r="O20" s="237">
+      <c r="O20" s="239">
         <v>-18.64</v>
       </c>
-      <c r="P20" s="243">
+      <c r="P20" s="247">
         <v>-15.22</v>
       </c>
-      <c r="Q20" s="235">
+      <c r="Q20" s="242">
         <v>-14.72</v>
       </c>
-      <c r="R20" s="238">
+      <c r="R20" s="235">
         <v>-10.8</v>
       </c>
-      <c r="S20" s="244">
+      <c r="S20" s="243">
         <v>-6.19</v>
       </c>
-      <c r="T20" s="245">
+      <c r="T20" s="244">
         <v>-32.53</v>
       </c>
     </row>
@@ -10484,7 +10484,7 @@
       <c r="C21" t="str">
         <v>601566</v>
       </c>
-      <c r="D21" s="250" t="str">
+      <c r="D21" s="260" t="str">
         <v>净卖: -5218.09万</v>
       </c>
       <c r="E21">
@@ -10499,40 +10499,40 @@
       <c r="H21">
         <v>7.11</v>
       </c>
-      <c r="I21" s="251">
+      <c r="I21" s="257">
         <v>2.68</v>
       </c>
-      <c r="J21" s="257">
+      <c r="J21" s="248">
         <v>-7.59</v>
       </c>
-      <c r="K21" s="258">
+      <c r="K21" s="255">
         <v>-16.84</v>
       </c>
-      <c r="L21" s="259">
+      <c r="L21" s="258">
         <v>-20.25</v>
       </c>
-      <c r="M21" s="252">
+      <c r="M21" s="259">
         <v>-26.94</v>
       </c>
-      <c r="N21" s="260">
+      <c r="N21" s="249">
         <v>-28.17</v>
       </c>
-      <c r="O21" s="253">
+      <c r="O21" s="250">
         <v>-25.15</v>
       </c>
-      <c r="P21" s="254">
+      <c r="P21" s="256">
         <v>-24.71</v>
       </c>
-      <c r="Q21" s="248">
+      <c r="Q21" s="253">
         <v>-21.25</v>
       </c>
-      <c r="R21" s="255">
+      <c r="R21" s="251">
         <v>-17.18</v>
       </c>
-      <c r="S21" s="256">
+      <c r="S21" s="254">
         <v>-25.43</v>
       </c>
-      <c r="T21" s="249">
+      <c r="T21" s="252">
         <v>-40.44</v>
       </c>
     </row>
@@ -10546,7 +10546,7 @@
       <c r="C22" t="str">
         <v>600756</v>
       </c>
-      <c r="D22" s="263" t="str">
+      <c r="D22" s="265" t="str">
         <v>净卖: -2369.10万</v>
       </c>
       <c r="E22">
@@ -10561,40 +10561,40 @@
       <c r="H22">
         <v>-1.6</v>
       </c>
-      <c r="I22" s="267">
+      <c r="I22" s="266">
         <v>1.46</v>
       </c>
-      <c r="J22" s="264">
+      <c r="J22" s="272">
         <v>-4.63</v>
       </c>
-      <c r="K22" s="268">
+      <c r="K22" s="267">
         <v>-3.97</v>
       </c>
-      <c r="L22" s="265">
+      <c r="L22" s="273">
         <v>-13.57</v>
       </c>
-      <c r="M22" s="269">
+      <c r="M22" s="261">
         <v>-21.09</v>
       </c>
-      <c r="N22" s="270">
+      <c r="N22" s="268">
         <v>-19.75</v>
       </c>
-      <c r="O22" s="271">
+      <c r="O22" s="270">
         <v>-18.25</v>
       </c>
-      <c r="P22" s="272">
+      <c r="P22" s="263">
         <v>-20.84</v>
       </c>
-      <c r="Q22" s="273">
+      <c r="Q22" s="262">
         <v>-21.42</v>
       </c>
-      <c r="R22" s="266">
+      <c r="R22" s="269">
         <v>-23.17</v>
       </c>
-      <c r="S22" s="261">
+      <c r="S22" s="271">
         <v>-24.43</v>
       </c>
-      <c r="T22" s="262">
+      <c r="T22" s="264">
         <v>-31.15</v>
       </c>
     </row>
@@ -10608,7 +10608,7 @@
       <c r="C23" t="str">
         <v>603696</v>
       </c>
-      <c r="D23" s="284" t="str">
+      <c r="D23" s="274" t="str">
         <v>净买: 3978.78万</v>
       </c>
       <c r="E23">
@@ -10623,28 +10623,28 @@
       <c r="H23">
         <v>9.98</v>
       </c>
-      <c r="I23" s="281">
+      <c r="I23" s="284">
         <v>0</v>
       </c>
-      <c r="J23" s="279">
+      <c r="J23" s="286">
         <v>10.01</v>
       </c>
-      <c r="K23" s="285">
+      <c r="K23" s="275">
         <v>21.01</v>
       </c>
-      <c r="L23" s="280">
+      <c r="L23" s="276">
         <v>33.13</v>
       </c>
-      <c r="M23" s="286">
+      <c r="M23" s="277">
         <v>46.43</v>
       </c>
-      <c r="N23" s="274">
+      <c r="N23" s="285">
         <v>43.01</v>
       </c>
-      <c r="O23" s="275">
+      <c r="O23" s="280">
         <v>28.71</v>
       </c>
-      <c r="P23" s="276">
+      <c r="P23" s="281">
         <v>24.74</v>
       </c>
       <c r="Q23" s="278">
@@ -10653,7 +10653,7 @@
       <c r="R23" s="282">
         <v>40.71</v>
       </c>
-      <c r="S23" s="277">
+      <c r="S23" s="279">
         <v>26.66</v>
       </c>
       <c r="T23" s="283">
@@ -10670,7 +10670,7 @@
       <c r="C24" t="str">
         <v>002682</v>
       </c>
-      <c r="D24" s="294" t="str">
+      <c r="D24" s="298" t="str">
         <v>净买: 2499.06万</v>
       </c>
       <c r="E24">
@@ -10685,40 +10685,40 @@
       <c r="H24">
         <v>5.99</v>
       </c>
-      <c r="I24" s="289">
+      <c r="I24" s="299">
         <v>3.77</v>
       </c>
-      <c r="J24" s="290">
+      <c r="J24" s="287">
         <v>14.2</v>
       </c>
-      <c r="K24" s="295">
+      <c r="K24" s="291">
         <v>25.65</v>
       </c>
-      <c r="L24" s="296">
+      <c r="L24" s="292">
         <v>38.26</v>
       </c>
-      <c r="M24" s="291">
+      <c r="M24" s="293">
         <v>52.03</v>
       </c>
-      <c r="N24" s="297">
+      <c r="N24" s="288">
         <v>42.9</v>
       </c>
-      <c r="O24" s="293">
+      <c r="O24" s="296">
         <v>57.25</v>
       </c>
-      <c r="P24" s="298">
+      <c r="P24" s="294">
         <v>72.9</v>
       </c>
-      <c r="Q24" s="299">
+      <c r="Q24" s="289">
         <v>55.65</v>
       </c>
-      <c r="R24" s="287">
+      <c r="R24" s="297">
         <v>40.14</v>
       </c>
-      <c r="S24" s="288">
+      <c r="S24" s="295">
         <v>42.75</v>
       </c>
-      <c r="T24" s="292">
+      <c r="T24" s="290">
         <v>-13.91</v>
       </c>
     </row>
@@ -10732,7 +10732,7 @@
       <c r="C25" t="str">
         <v>603696</v>
       </c>
-      <c r="D25" s="305" t="str">
+      <c r="D25" s="303" t="str">
         <v>净卖: -1913.63万</v>
       </c>
       <c r="E25">
@@ -10747,40 +10747,40 @@
       <c r="H25">
         <v>-2.03</v>
       </c>
-      <c r="I25" s="306">
+      <c r="I25" s="307">
         <v>12.28</v>
       </c>
-      <c r="J25" s="312">
+      <c r="J25" s="304">
         <v>23.53</v>
       </c>
-      <c r="K25" s="302">
+      <c r="K25" s="300">
         <v>35.87</v>
       </c>
-      <c r="L25" s="307">
+      <c r="L25" s="306">
         <v>32.7</v>
       </c>
-      <c r="M25" s="300">
+      <c r="M25" s="308">
         <v>19.43</v>
       </c>
-      <c r="N25" s="308">
+      <c r="N25" s="309">
         <v>15.74</v>
       </c>
-      <c r="O25" s="309">
+      <c r="O25" s="310">
         <v>18.69</v>
       </c>
-      <c r="P25" s="310">
+      <c r="P25" s="311">
         <v>30.57</v>
       </c>
-      <c r="Q25" s="311">
+      <c r="Q25" s="301">
         <v>17.53</v>
       </c>
-      <c r="R25" s="301">
+      <c r="R25" s="302">
         <v>10.73</v>
       </c>
-      <c r="S25" s="303">
+      <c r="S25" s="312">
         <v>16.49</v>
       </c>
-      <c r="T25" s="304">
+      <c r="T25" s="305">
         <v>-8.25</v>
       </c>
     </row>
@@ -10794,7 +10794,7 @@
       <c r="C26" t="str">
         <v>603696</v>
       </c>
-      <c r="D26" s="323" t="str">
+      <c r="D26" s="316" t="str">
         <v>净卖: -3631.64万</v>
       </c>
       <c r="E26">
@@ -10809,40 +10809,40 @@
       <c r="H26">
         <v>9.08</v>
       </c>
-      <c r="I26" s="318">
+      <c r="I26" s="317">
         <v>-10.47</v>
       </c>
-      <c r="J26" s="315">
+      <c r="J26" s="321">
         <v>-19.42</v>
       </c>
-      <c r="K26" s="313">
+      <c r="K26" s="318">
         <v>-21.91</v>
       </c>
-      <c r="L26" s="319">
+      <c r="L26" s="313">
         <v>-19.92</v>
       </c>
-      <c r="M26" s="324">
+      <c r="M26" s="319">
         <v>-11.91</v>
       </c>
-      <c r="N26" s="320">
+      <c r="N26" s="322">
         <v>-20.7</v>
       </c>
-      <c r="O26" s="316">
+      <c r="O26" s="314">
         <v>-25.29</v>
       </c>
-      <c r="P26" s="325">
+      <c r="P26" s="320">
         <v>-21.4</v>
       </c>
-      <c r="Q26" s="321">
+      <c r="Q26" s="325">
         <v>-13.54</v>
       </c>
-      <c r="R26" s="322">
+      <c r="R26" s="315">
         <v>-4.9</v>
       </c>
-      <c r="S26" s="317">
+      <c r="S26" s="323">
         <v>4.59</v>
       </c>
-      <c r="T26" s="314">
+      <c r="T26" s="324">
         <v>-38.09</v>
       </c>
     </row>
@@ -10856,7 +10856,7 @@
       <c r="C27" t="str">
         <v>002682</v>
       </c>
-      <c r="D27" s="326" t="str">
+      <c r="D27" s="327" t="str">
         <v>净卖: -4674.28万</v>
       </c>
       <c r="E27">
@@ -10871,40 +10871,40 @@
       <c r="H27">
         <v>-4.33</v>
       </c>
-      <c r="I27" s="335">
+      <c r="I27" s="328">
         <v>14.93</v>
       </c>
-      <c r="J27" s="330">
+      <c r="J27" s="329">
         <v>3.47</v>
       </c>
-      <c r="K27" s="331">
+      <c r="K27" s="334">
         <v>-6.84</v>
       </c>
-      <c r="L27" s="333">
+      <c r="L27" s="335">
         <v>-5.11</v>
       </c>
-      <c r="M27" s="327">
+      <c r="M27" s="337">
         <v>-10.89</v>
       </c>
-      <c r="N27" s="328">
+      <c r="N27" s="336">
         <v>-19.36</v>
       </c>
-      <c r="O27" s="336">
+      <c r="O27" s="333">
         <v>-21</v>
       </c>
-      <c r="P27" s="332">
+      <c r="P27" s="338">
         <v>-20.33</v>
       </c>
-      <c r="Q27" s="337">
+      <c r="Q27" s="330">
         <v>-12.43</v>
       </c>
-      <c r="R27" s="334">
+      <c r="R27" s="331">
         <v>-14.26</v>
       </c>
-      <c r="S27" s="338">
+      <c r="S27" s="332">
         <v>-7.8</v>
       </c>
-      <c r="T27" s="329">
+      <c r="T27" s="326">
         <v>-42.77</v>
       </c>
     </row>
@@ -10918,7 +10918,7 @@
       <c r="C28" t="str">
         <v>600693</v>
       </c>
-      <c r="D28" s="343" t="str">
+      <c r="D28" s="348" t="str">
         <v>净买: 4441.53万</v>
       </c>
       <c r="E28">
@@ -10933,40 +10933,40 @@
       <c r="H28">
         <v>1.81</v>
       </c>
-      <c r="I28" s="348">
+      <c r="I28" s="344">
         <v>8.04</v>
       </c>
       <c r="J28" s="349">
         <v>15.95</v>
       </c>
-      <c r="K28" s="350">
+      <c r="K28" s="346">
         <v>10.22</v>
       </c>
-      <c r="L28" s="345">
+      <c r="L28" s="340">
         <v>13.45</v>
       </c>
-      <c r="M28" s="346">
+      <c r="M28" s="350">
         <v>12.33</v>
       </c>
-      <c r="N28" s="340">
+      <c r="N28" s="341">
         <v>23.53</v>
       </c>
-      <c r="O28" s="347">
+      <c r="O28" s="351">
         <v>28.54</v>
       </c>
-      <c r="P28" s="341">
+      <c r="P28" s="342">
         <v>41.4</v>
       </c>
-      <c r="Q28" s="342">
+      <c r="Q28" s="343">
         <v>37.84</v>
       </c>
-      <c r="R28" s="351">
+      <c r="R28" s="347">
         <v>44.23</v>
       </c>
-      <c r="S28" s="339">
+      <c r="S28" s="345">
         <v>30.52</v>
       </c>
-      <c r="T28" s="344">
+      <c r="T28" s="339">
         <v>-21.49</v>
       </c>
     </row>
@@ -10980,7 +10980,7 @@
       <c r="C29" t="str">
         <v>603696</v>
       </c>
-      <c r="D29" s="362" t="str">
+      <c r="D29" s="360" t="str">
         <v>净卖: -3147.63万</v>
       </c>
       <c r="E29">
@@ -10995,40 +10995,40 @@
       <c r="H29">
         <v>2.92</v>
       </c>
-      <c r="I29" s="352">
+      <c r="I29" s="356">
         <v>-12.53</v>
       </c>
-      <c r="J29" s="358">
+      <c r="J29" s="352">
         <v>-17.6</v>
       </c>
       <c r="K29" s="359">
         <v>-13.3</v>
       </c>
-      <c r="L29" s="355">
+      <c r="L29" s="357">
         <v>-4.64</v>
       </c>
       <c r="M29" s="353">
         <v>4.89</v>
       </c>
-      <c r="N29" s="356">
+      <c r="N29" s="354">
         <v>15.36</v>
       </c>
-      <c r="O29" s="363">
+      <c r="O29" s="361">
         <v>13.73</v>
       </c>
-      <c r="P29" s="357">
+      <c r="P29" s="362">
         <v>12.4</v>
       </c>
-      <c r="Q29" s="364">
+      <c r="Q29" s="355">
         <v>1.16</v>
       </c>
-      <c r="R29" s="360">
+      <c r="R29" s="358">
         <v>-8.97</v>
       </c>
-      <c r="S29" s="361">
+      <c r="S29" s="363">
         <v>-12.96</v>
       </c>
-      <c r="T29" s="354">
+      <c r="T29" s="364">
         <v>-31.72</v>
       </c>
     </row>
@@ -11042,7 +11042,7 @@
       <c r="C30" t="str">
         <v>600693</v>
       </c>
-      <c r="D30" s="376" t="str">
+      <c r="D30" s="370" t="str">
         <v>净卖: -5308.96万</v>
       </c>
       <c r="E30">
@@ -11057,40 +11057,40 @@
       <c r="H30">
         <v>2.51</v>
       </c>
-      <c r="I30" s="377">
+      <c r="I30" s="375">
         <v>0.41</v>
       </c>
-      <c r="J30" s="369">
+      <c r="J30" s="371">
         <v>-0.58</v>
       </c>
-      <c r="K30" s="370">
+      <c r="K30" s="372">
         <v>9.33</v>
       </c>
-      <c r="L30" s="371">
+      <c r="L30" s="369">
         <v>13.77</v>
       </c>
-      <c r="M30" s="372">
+      <c r="M30" s="376">
         <v>25.15</v>
       </c>
-      <c r="N30" s="366">
+      <c r="N30" s="377">
         <v>22</v>
       </c>
-      <c r="O30" s="367">
+      <c r="O30" s="373">
         <v>27.65</v>
       </c>
-      <c r="P30" s="373">
+      <c r="P30" s="365">
         <v>15.52</v>
       </c>
-      <c r="Q30" s="375">
+      <c r="Q30" s="374">
         <v>3.97</v>
       </c>
-      <c r="R30" s="374">
+      <c r="R30" s="366">
         <v>3.97</v>
       </c>
-      <c r="S30" s="368">
+      <c r="S30" s="367">
         <v>7.29</v>
       </c>
-      <c r="T30" s="365">
+      <c r="T30" s="368">
         <v>-30.51</v>
       </c>
     </row>
@@ -11104,7 +11104,7 @@
       <c r="C31" t="str">
         <v>600280</v>
       </c>
-      <c r="D31" s="386" t="str">
+      <c r="D31" s="385" t="str">
         <v>净买: 2343.21万</v>
       </c>
       <c r="E31">
@@ -11119,40 +11119,40 @@
       <c r="H31">
         <v>1.88</v>
       </c>
-      <c r="I31" s="387">
+      <c r="I31" s="379">
         <v>8.08</v>
       </c>
-      <c r="J31" s="383">
+      <c r="J31" s="388">
         <v>17.78</v>
       </c>
-      <c r="K31" s="384">
+      <c r="K31" s="389">
         <v>12.93</v>
       </c>
-      <c r="L31" s="388">
+      <c r="L31" s="390">
         <v>4.39</v>
       </c>
-      <c r="M31" s="385">
+      <c r="M31" s="380">
         <v>5.54</v>
       </c>
-      <c r="N31" s="378">
+      <c r="N31" s="381">
         <v>1.85</v>
       </c>
-      <c r="O31" s="379">
+      <c r="O31" s="383">
         <v>-1.15</v>
       </c>
-      <c r="P31" s="389">
+      <c r="P31" s="378">
         <v>-3</v>
       </c>
-      <c r="Q31" s="380">
+      <c r="Q31" s="384">
         <v>-7.85</v>
       </c>
-      <c r="R31" s="381">
+      <c r="R31" s="382">
         <v>-11.09</v>
       </c>
-      <c r="S31" s="390">
+      <c r="S31" s="386">
         <v>-10.16</v>
       </c>
-      <c r="T31" s="382">
+      <c r="T31" s="387">
         <v>-27.94</v>
       </c>
     </row>
@@ -11166,7 +11166,7 @@
       <c r="C32" t="str">
         <v>600280</v>
       </c>
-      <c r="D32" s="402" t="str">
+      <c r="D32" s="403" t="str">
         <v>净卖: -2545.17万</v>
       </c>
       <c r="E32">
@@ -11181,22 +11181,22 @@
       <c r="H32">
         <v>-3.92</v>
       </c>
-      <c r="I32" s="395">
+      <c r="I32" s="401">
         <v>-0.2</v>
       </c>
-      <c r="J32" s="391">
+      <c r="J32" s="398">
         <v>-7.76</v>
       </c>
-      <c r="K32" s="396">
+      <c r="K32" s="402">
         <v>-6.73</v>
       </c>
       <c r="L32" s="399">
         <v>-10</v>
       </c>
-      <c r="M32" s="400">
+      <c r="M32" s="396">
         <v>-12.65</v>
       </c>
-      <c r="N32" s="403">
+      <c r="N32" s="391">
         <v>-14.29</v>
       </c>
       <c r="O32" s="392">
@@ -11205,16 +11205,16 @@
       <c r="P32" s="397">
         <v>-21.43</v>
       </c>
-      <c r="Q32" s="393">
+      <c r="Q32" s="400">
         <v>-20.61</v>
       </c>
-      <c r="R32" s="394">
+      <c r="R32" s="393">
         <v>-16.33</v>
       </c>
-      <c r="S32" s="401">
+      <c r="S32" s="394">
         <v>-15.92</v>
       </c>
-      <c r="T32" s="398">
+      <c r="T32" s="395">
         <v>-36.33</v>
       </c>
     </row>
@@ -11228,7 +11228,7 @@
       <c r="C33" t="str">
         <v>002759</v>
       </c>
-      <c r="D33" s="409" t="str">
+      <c r="D33" s="408" t="str">
         <v>净买: 8490.49万</v>
       </c>
       <c r="E33">
@@ -11243,40 +11243,40 @@
       <c r="H33">
         <v>-3.82</v>
       </c>
-      <c r="I33" s="415">
+      <c r="I33" s="404">
         <v>11.08</v>
       </c>
-      <c r="J33" s="412">
+      <c r="J33" s="405">
         <v>22.19</v>
       </c>
-      <c r="K33" s="413">
+      <c r="K33" s="406">
         <v>22.69</v>
       </c>
-      <c r="L33" s="406">
+      <c r="L33" s="409">
         <v>13.63</v>
       </c>
-      <c r="M33" s="416">
+      <c r="M33" s="410">
         <v>14.61</v>
       </c>
-      <c r="N33" s="414">
+      <c r="N33" s="416">
         <v>26.07</v>
       </c>
-      <c r="O33" s="404">
+      <c r="O33" s="411">
         <v>26.51</v>
       </c>
-      <c r="P33" s="410">
+      <c r="P33" s="415">
         <v>18.86</v>
       </c>
-      <c r="Q33" s="407">
+      <c r="Q33" s="412">
         <v>15.77</v>
       </c>
-      <c r="R33" s="408">
+      <c r="R33" s="413">
         <v>13.87</v>
       </c>
-      <c r="S33" s="405">
+      <c r="S33" s="414">
         <v>15.03</v>
       </c>
-      <c r="T33" s="411">
+      <c r="T33" s="407">
         <v>-13.18</v>
       </c>
     </row>
@@ -11290,7 +11290,7 @@
       <c r="C34" t="str">
         <v>002792</v>
       </c>
-      <c r="D34" s="429" t="str">
+      <c r="D34" s="428" t="str">
         <v>净买: 8322.30万</v>
       </c>
       <c r="E34">
@@ -11305,40 +11305,40 @@
       <c r="H34">
         <v>0.05</v>
       </c>
-      <c r="I34" s="425">
+      <c r="I34" s="419">
         <v>7.5</v>
       </c>
-      <c r="J34" s="421">
+      <c r="J34" s="422">
         <v>15.33</v>
       </c>
-      <c r="K34" s="417">
+      <c r="K34" s="425">
         <v>19.23</v>
       </c>
-      <c r="L34" s="427">
+      <c r="L34" s="429">
         <v>31.17</v>
       </c>
-      <c r="M34" s="422">
+      <c r="M34" s="417">
         <v>44.28</v>
       </c>
-      <c r="N34" s="418">
+      <c r="N34" s="423">
         <v>53.02</v>
       </c>
-      <c r="O34" s="419">
+      <c r="O34" s="420">
         <v>68.33</v>
       </c>
-      <c r="P34" s="426">
+      <c r="P34" s="418">
         <v>76.16</v>
       </c>
-      <c r="Q34" s="423">
+      <c r="Q34" s="426">
         <v>58.53</v>
       </c>
       <c r="R34" s="424">
         <v>42.67</v>
       </c>
-      <c r="S34" s="420">
+      <c r="S34" s="427">
         <v>30.19</v>
       </c>
-      <c r="T34" s="428">
+      <c r="T34" s="421">
         <v>28.45</v>
       </c>
     </row>
@@ -11352,7 +11352,7 @@
       <c r="C35" t="str">
         <v>002792</v>
       </c>
-      <c r="D35" s="432" t="str">
+      <c r="D35" s="441" t="str">
         <v>净卖: -7684.69万</v>
       </c>
       <c r="E35">
@@ -11367,40 +11367,40 @@
       <c r="H35">
         <v>2.25</v>
       </c>
-      <c r="I35" s="430">
+      <c r="I35" s="438">
         <v>4.92</v>
       </c>
       <c r="J35" s="439">
         <v>8.47</v>
       </c>
-      <c r="K35" s="440">
+      <c r="K35" s="436">
         <v>19.33</v>
       </c>
-      <c r="L35" s="435">
+      <c r="L35" s="440">
         <v>31.26</v>
       </c>
-      <c r="M35" s="441">
+      <c r="M35" s="442">
         <v>39.21</v>
       </c>
-      <c r="N35" s="433">
+      <c r="N35" s="430">
         <v>53.14</v>
       </c>
-      <c r="O35" s="436">
+      <c r="O35" s="434">
         <v>60.26</v>
       </c>
-      <c r="P35" s="434">
+      <c r="P35" s="437">
         <v>44.23</v>
       </c>
-      <c r="Q35" s="442">
+      <c r="Q35" s="431">
         <v>29.8</v>
       </c>
-      <c r="R35" s="431">
+      <c r="R35" s="432">
         <v>18.44</v>
       </c>
-      <c r="S35" s="437">
+      <c r="S35" s="433">
         <v>17.43</v>
       </c>
-      <c r="T35" s="438">
+      <c r="T35" s="435">
         <v>16.86</v>
       </c>
     </row>
@@ -11414,7 +11414,7 @@
       <c r="C36" t="str">
         <v>002759</v>
       </c>
-      <c r="D36" s="447" t="str">
+      <c r="D36" s="453" t="str">
         <v>净买: 1.00亿</v>
       </c>
       <c r="E36">
@@ -11429,40 +11429,40 @@
       <c r="H36">
         <v>3.06</v>
       </c>
-      <c r="I36" s="453">
+      <c r="I36" s="446">
         <v>6.73</v>
       </c>
-      <c r="J36" s="452">
+      <c r="J36" s="447">
         <v>7.11</v>
       </c>
-      <c r="K36" s="454">
+      <c r="K36" s="451">
         <v>0.63</v>
       </c>
-      <c r="L36" s="448">
+      <c r="L36" s="443">
         <v>-1.99</v>
       </c>
-      <c r="M36" s="449">
+      <c r="M36" s="448">
         <v>-3.59</v>
       </c>
       <c r="N36" s="444">
         <v>-2.61</v>
       </c>
-      <c r="O36" s="455">
+      <c r="O36" s="445">
         <v>-7.82</v>
       </c>
-      <c r="P36" s="450">
+      <c r="P36" s="454">
         <v>-11.35</v>
       </c>
-      <c r="Q36" s="443">
+      <c r="Q36" s="449">
         <v>-5.64</v>
       </c>
-      <c r="R36" s="451">
+      <c r="R36" s="455">
         <v>-13.61</v>
       </c>
-      <c r="S36" s="445">
+      <c r="S36" s="450">
         <v>-12.5</v>
       </c>
-      <c r="T36" s="446">
+      <c r="T36" s="452">
         <v>-26.5</v>
       </c>
     </row>
@@ -11476,7 +11476,7 @@
       <c r="C37" t="str">
         <v>600776</v>
       </c>
-      <c r="D37" s="457" t="str">
+      <c r="D37" s="458" t="str">
         <v>净买: 5452.75万</v>
       </c>
       <c r="E37">
@@ -11491,40 +11491,40 @@
       <c r="H37">
         <v>10.02</v>
       </c>
-      <c r="I37" s="466">
+      <c r="I37" s="459">
         <v>0</v>
       </c>
-      <c r="J37" s="458">
+      <c r="J37" s="467">
         <v>10</v>
       </c>
       <c r="K37" s="462">
         <v>16.57</v>
       </c>
-      <c r="L37" s="463">
+      <c r="L37" s="464">
         <v>4.91</v>
       </c>
-      <c r="M37" s="459">
+      <c r="M37" s="465">
         <v>-5.58</v>
       </c>
-      <c r="N37" s="467">
+      <c r="N37" s="466">
         <v>-15.01</v>
       </c>
-      <c r="O37" s="464">
+      <c r="O37" s="468">
         <v>-17.91</v>
       </c>
-      <c r="P37" s="468">
+      <c r="P37" s="460">
         <v>-16.93</v>
       </c>
-      <c r="Q37" s="460">
+      <c r="Q37" s="456">
         <v>-15.19</v>
       </c>
-      <c r="R37" s="465">
+      <c r="R37" s="463">
         <v>-10.99</v>
       </c>
-      <c r="S37" s="456">
+      <c r="S37" s="461">
         <v>-15.27</v>
       </c>
-      <c r="T37" s="461">
+      <c r="T37" s="457">
         <v>-25.23</v>
       </c>
     </row>
@@ -11538,7 +11538,7 @@
       <c r="C38" t="str">
         <v>600410</v>
       </c>
-      <c r="D38" s="480" t="str">
+      <c r="D38" s="478" t="str">
         <v>净买: 1.26亿</v>
       </c>
       <c r="E38">
@@ -11553,40 +11553,40 @@
       <c r="H38">
         <v>-1.64</v>
       </c>
-      <c r="I38" s="476">
+      <c r="I38" s="472">
         <v>11.84</v>
       </c>
-      <c r="J38" s="481">
+      <c r="J38" s="473">
         <v>23.02</v>
       </c>
-      <c r="K38" s="479">
+      <c r="K38" s="474">
         <v>10.78</v>
       </c>
-      <c r="L38" s="469">
+      <c r="L38" s="479">
         <v>2.42</v>
       </c>
-      <c r="M38" s="471">
+      <c r="M38" s="475">
         <v>0</v>
       </c>
-      <c r="N38" s="472">
+      <c r="N38" s="480">
         <v>1.86</v>
       </c>
-      <c r="O38" s="477">
+      <c r="O38" s="481">
         <v>2.67</v>
       </c>
-      <c r="P38" s="473">
+      <c r="P38" s="469">
         <v>5.99</v>
       </c>
-      <c r="Q38" s="478">
+      <c r="Q38" s="476">
         <v>0.81</v>
       </c>
-      <c r="R38" s="470">
+      <c r="R38" s="477">
         <v>6.95</v>
       </c>
-      <c r="S38" s="474">
+      <c r="S38" s="470">
         <v>6.25</v>
       </c>
-      <c r="T38" s="475">
+      <c r="T38" s="471">
         <v>45.79</v>
       </c>
     </row>
@@ -11600,7 +11600,7 @@
       <c r="C39" t="str">
         <v>600410</v>
       </c>
-      <c r="D39" s="488" t="str">
+      <c r="D39" s="493" t="str">
         <v>净买: 1.26亿</v>
       </c>
       <c r="E39">
@@ -11615,40 +11615,40 @@
       <c r="H39">
         <v>10</v>
       </c>
-      <c r="I39" s="483">
+      <c r="I39" s="494">
         <v>0</v>
       </c>
-      <c r="J39" s="493">
+      <c r="J39" s="482">
         <v>-9.95</v>
       </c>
-      <c r="K39" s="484">
+      <c r="K39" s="487">
         <v>-16.75</v>
       </c>
-      <c r="L39" s="485">
+      <c r="L39" s="488">
         <v>-18.71</v>
       </c>
-      <c r="M39" s="494">
+      <c r="M39" s="489">
         <v>-17.2</v>
       </c>
-      <c r="N39" s="486">
+      <c r="N39" s="483">
         <v>-16.54</v>
       </c>
-      <c r="O39" s="489">
+      <c r="O39" s="484">
         <v>-13.84</v>
       </c>
-      <c r="P39" s="490">
+      <c r="P39" s="485">
         <v>-18.06</v>
       </c>
-      <c r="Q39" s="482">
+      <c r="Q39" s="486">
         <v>-13.06</v>
       </c>
       <c r="R39" s="491">
         <v>-13.64</v>
       </c>
-      <c r="S39" s="492">
+      <c r="S39" s="490">
         <v>-10.2</v>
       </c>
-      <c r="T39" s="487">
+      <c r="T39" s="492">
         <v>18.51</v>
       </c>
     </row>
@@ -11662,7 +11662,7 @@
       <c r="C40" t="str">
         <v>600776</v>
       </c>
-      <c r="D40" s="506" t="str">
+      <c r="D40" s="505" t="str">
         <v>净卖: -233.39万</v>
       </c>
       <c r="E40">
@@ -11677,40 +11677,40 @@
       <c r="H40">
         <v>-10</v>
       </c>
-      <c r="I40" s="507">
+      <c r="I40" s="500">
         <v>0</v>
       </c>
-      <c r="J40" s="501">
+      <c r="J40" s="506">
         <v>-9.98</v>
       </c>
-      <c r="K40" s="495">
+      <c r="K40" s="502">
         <v>-13.06</v>
       </c>
       <c r="L40" s="498">
         <v>-12.02</v>
       </c>
-      <c r="M40" s="502">
+      <c r="M40" s="501">
         <v>-10.17</v>
       </c>
-      <c r="N40" s="496">
+      <c r="N40" s="507">
         <v>-5.72</v>
       </c>
-      <c r="O40" s="499">
+      <c r="O40" s="495">
         <v>-10.26</v>
       </c>
       <c r="P40" s="503">
         <v>-9.89</v>
       </c>
-      <c r="Q40" s="505">
+      <c r="Q40" s="496">
         <v>-11.26</v>
       </c>
       <c r="R40" s="497">
         <v>-11.78</v>
       </c>
-      <c r="S40" s="504">
+      <c r="S40" s="499">
         <v>-12.49</v>
       </c>
-      <c r="T40" s="500">
+      <c r="T40" s="504">
         <v>-20.81</v>
       </c>
     </row>
@@ -11724,7 +11724,7 @@
       <c r="C41" t="str">
         <v>600410</v>
       </c>
-      <c r="D41" s="515" t="str">
+      <c r="D41" s="520" t="str">
         <v>净卖: -1.30亿</v>
       </c>
       <c r="E41">
@@ -11739,40 +11739,40 @@
       <c r="H41">
         <v>-1.97</v>
       </c>
-      <c r="I41" s="516">
+      <c r="I41" s="508">
         <v>-8.15</v>
       </c>
-      <c r="J41" s="509">
+      <c r="J41" s="515">
         <v>-15.08</v>
       </c>
-      <c r="K41" s="510">
+      <c r="K41" s="513">
         <v>-17.08</v>
       </c>
-      <c r="L41" s="511">
+      <c r="L41" s="509">
         <v>-15.54</v>
       </c>
-      <c r="M41" s="512">
+      <c r="M41" s="518">
         <v>-14.87</v>
       </c>
-      <c r="N41" s="517">
+      <c r="N41" s="510">
         <v>-12.11</v>
       </c>
-      <c r="O41" s="518">
+      <c r="O41" s="514">
         <v>-16.42</v>
       </c>
-      <c r="P41" s="519">
+      <c r="P41" s="511">
         <v>-11.32</v>
       </c>
-      <c r="Q41" s="520">
+      <c r="Q41" s="516">
         <v>-11.9</v>
       </c>
-      <c r="R41" s="513">
+      <c r="R41" s="512">
         <v>-8.4</v>
       </c>
-      <c r="S41" s="514">
+      <c r="S41" s="517">
         <v>-12.24</v>
       </c>
-      <c r="T41" s="508">
+      <c r="T41" s="519">
         <v>20.89</v>
       </c>
     </row>
@@ -11786,7 +11786,7 @@
       <c r="C42" t="str">
         <v>002792</v>
       </c>
-      <c r="D42" s="533" t="str">
+      <c r="D42" s="526" t="str">
         <v>净买: 5153.68万</v>
       </c>
       <c r="E42">
@@ -11804,37 +11804,37 @@
       <c r="I42" s="521">
         <v>9.39</v>
       </c>
-      <c r="J42" s="531">
+      <c r="J42" s="527">
         <v>15.85</v>
       </c>
-      <c r="K42" s="526">
+      <c r="K42" s="528">
         <v>10.51</v>
       </c>
-      <c r="L42" s="527">
+      <c r="L42" s="529">
         <v>6.31</v>
       </c>
-      <c r="M42" s="532">
+      <c r="M42" s="522">
         <v>1.07</v>
       </c>
-      <c r="N42" s="528">
+      <c r="N42" s="523">
         <v>-1.76</v>
       </c>
-      <c r="O42" s="522">
+      <c r="O42" s="530">
         <v>0.67</v>
       </c>
-      <c r="P42" s="529">
+      <c r="P42" s="524">
         <v>10.74</v>
       </c>
-      <c r="Q42" s="523">
+      <c r="Q42" s="532">
         <v>10.74</v>
       </c>
-      <c r="R42" s="524">
+      <c r="R42" s="531">
         <v>7.46</v>
       </c>
-      <c r="S42" s="530">
+      <c r="S42" s="525">
         <v>7.34</v>
       </c>
-      <c r="T42" s="525">
+      <c r="T42" s="533">
         <v>6.98</v>
       </c>
     </row>
@@ -11897,40 +11897,40 @@
       <c r="F44" t="str"/>
       <c r="G44" t="str"/>
       <c r="H44" t="str"/>
-      <c r="I44" s="535">
+      <c r="I44" s="538">
         <v>65.85</v>
       </c>
-      <c r="J44" s="542">
+      <c r="J44" s="544">
         <v>65.85</v>
       </c>
-      <c r="K44" s="538">
+      <c r="K44" s="545">
         <v>60.98</v>
       </c>
-      <c r="L44" s="543">
+      <c r="L44" s="541">
         <v>56.1</v>
       </c>
-      <c r="M44" s="536">
+      <c r="M44" s="539">
         <v>48.78</v>
       </c>
-      <c r="N44" s="539">
+      <c r="N44" s="542">
         <v>46.34</v>
       </c>
-      <c r="O44" s="540">
+      <c r="O44" s="534">
         <v>48.78</v>
       </c>
-      <c r="P44" s="544">
+      <c r="P44" s="535">
         <v>43.9</v>
       </c>
-      <c r="Q44" s="545">
+      <c r="Q44" s="540">
         <v>39.02</v>
       </c>
-      <c r="R44" s="541">
+      <c r="R44" s="543">
         <v>43.9</v>
       </c>
-      <c r="S44" s="537">
+      <c r="S44" s="536">
         <v>43.9</v>
       </c>
-      <c r="T44" s="534">
+      <c r="T44" s="537">
         <v>31.71</v>
       </c>
     </row>
@@ -11945,40 +11945,40 @@
       <c r="F45" t="str"/>
       <c r="G45" t="str"/>
       <c r="H45" t="str"/>
-      <c r="I45" s="554">
+      <c r="I45" s="552">
         <v>3.79</v>
       </c>
-      <c r="J45" s="555">
+      <c r="J45" s="553">
         <v>5.59</v>
       </c>
-      <c r="K45" s="549">
+      <c r="K45" s="557">
         <v>5.07</v>
       </c>
-      <c r="L45" s="556">
+      <c r="L45" s="549">
         <v>5.23</v>
       </c>
-      <c r="M45" s="557">
+      <c r="M45" s="548">
         <v>5.01</v>
       </c>
-      <c r="N45" s="552">
+      <c r="N45" s="554">
         <v>4.05</v>
       </c>
-      <c r="O45" s="553">
+      <c r="O45" s="555">
         <v>4.42</v>
       </c>
-      <c r="P45" s="547">
+      <c r="P45" s="550">
         <v>3.76</v>
       </c>
-      <c r="Q45" s="550">
+      <c r="Q45" s="551">
         <v>1.74</v>
       </c>
-      <c r="R45" s="548">
+      <c r="R45" s="546">
         <v>1.6</v>
       </c>
-      <c r="S45" s="551">
+      <c r="S45" s="556">
         <v>0.99</v>
       </c>
-      <c r="T45" s="546">
+      <c r="T45" s="547">
         <v>-4.22</v>
       </c>
     </row>

--- a/youzi/越王大道/index.xlsx
+++ b/youzi/越王大道/index.xlsx
@@ -39,18 +39,48 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFC4E7CC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF70C483"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFED979F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218E3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFAE202D"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF1A7230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFB8E1C1"/>
         <bgColor/>
       </patternFill>
@@ -63,72 +93,30 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA91E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFAB1E2C"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC4E7CC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED979F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF1E8236"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA91E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218E3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
@@ -207,6 +195,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFAC1F2C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFAB1F2C"/>
         <bgColor/>
       </patternFill>
@@ -225,6 +219,3108 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC32938"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BDC2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC02836"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD33140"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2FAA4B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDE4150"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFA4AB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE2E4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFECF7EF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF3F4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCF0F1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7130"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBF2836"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9808A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD53241"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED9BA3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7DCA8F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBE8EA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3D4D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC42A38"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFACDDB7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF67C07B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC969F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC62B39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF95D3A3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCA2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDB3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B2B8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3B9BF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEE9FA6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDA3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25866"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFDFD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBB2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9DFE1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD2303F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A702F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7B33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8437"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BFC4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBEDEE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E7F35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE3E5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBEAEC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDE4251"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23943D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8437"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6AC27E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5BBC71"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23943D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCFDFC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23953E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAE202D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC3E6CB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218D3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7B34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208838"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF46B35F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8437"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A712F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A443"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBC2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC52A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7FCA90"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23943D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF37AD52"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF63BF78"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5FBD75"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8638"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8738"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7E35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218D3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8638"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23933D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7A33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8136"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8738"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2DFBC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2FA94B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5EBD74"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6DC381"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B2B8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2DFBC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7CC98E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF46B35F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF53B86A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF84CD95"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77580"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFCFC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6CC280"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8638"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A644"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF249A3F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7CC98E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF95D3A3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBF2736"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77883"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22903C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B3B9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF99D5A7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8337"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6CDD1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9858F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFBFB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9DCDF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BAC0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8538"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDE4251"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196F2F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24983F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD43140"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208839"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC929B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4C4C8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF54B96B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF37AD52"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCEEBD5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46672"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8036"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2CA848"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDE4554"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6727D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8538"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A544"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBB2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3949"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7832"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6D0D3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF37AD52"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE35E6B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6F4E9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC32A38"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCEEEF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAE202D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE35E6B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD63242"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCDEAD4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBB2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE04D5B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B4BA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7ECA8F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8537"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22923D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8638"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6FBF7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC12937"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB72432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3847"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA9DBB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF64BF79"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8ED19D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF269F42"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC92C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC52A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE5E7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8538"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3848"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A042"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD1303F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9DEE0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B3B9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC939B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC72B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEE9DA4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259E41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196D2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7E35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8136"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC32938"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC72B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB3E0BD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC12937"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAD1F2D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D3D7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE3E6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE4F4E8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0DEBA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE4F4E8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7BC98D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBC2635"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A142"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD63242"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7BC98D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7631"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBC2635"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9838D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7BC98D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
@@ -243,2917 +3339,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC32938"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BDC2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC02836"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDE4150"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFA4AB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE2E4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD33140"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCF0F1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2FAA4B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFECF7EF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF3F4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED9BA3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFACDDB7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBE8EA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBF2836"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD53241"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9808A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3D4D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7130"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7DCA8F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC42A38"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC62B39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDB3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B2B8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF95D3A3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCA2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF67C07B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC969F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25866"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDA3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBB2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3B9BF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD2303F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9DFE1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEE9FA6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFDFD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A702F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8437"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BFC4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E7F35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBEDEE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7B33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5BBC71"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE3E5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAE202D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6AC27E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBEAEC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23943D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDE4251"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23943D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCFDFC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8437"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23953E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A443"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7B34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF46B35F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A712F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208838"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC3E6CB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218D3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8437"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF37AD52"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC52A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBC2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF63BF78"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7FCA90"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5FBD75"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23943D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8638"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7E35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23933D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8638"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8738"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218D3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7A33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8136"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2DFBC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2FA94B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6DC381"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF53B86A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B2B8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5EBD74"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF84CD95"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8738"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2DFBC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7CC98E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF46B35F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A644"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF249A3F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6CC280"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8638"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77580"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFCFC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77883"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBF2736"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22903C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7CC98E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF95D3A3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9DCDF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9858F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BAC0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFBFB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B3B9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF99D5A7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8337"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8538"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6CDD1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD43140"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDE4251"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196F2F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208839"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC929B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4C4C8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF54B96B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF37AD52"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCEEBD5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46672"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8036"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2CA848"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDE4554"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6727D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8538"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A544"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBB2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3949"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6D0D3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF37AD52"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7832"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE35E6B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC32A38"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6F4E9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAE202D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE35E6B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCEEEF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7ECA8F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBB2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD63242"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B4BA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCDEAD4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8537"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE04D5B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8638"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6FBF7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22923D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC12937"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3847"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB72432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA9DBB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8ED19D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8538"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC92C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC52A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF64BF79"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF269F42"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE5E7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3848"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A042"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD1303F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9DEE0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC72B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEE9DA4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B3B9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC939B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196D2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259E41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8136"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7E35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -3165,145 +3363,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF7D3D7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB3E0BD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC32938"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE3E6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC12937"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC72B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE4F4E8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7BC98D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7BC98D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7631"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBC2635"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE4F4E8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A142"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9838D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0DEBA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7BC98D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBC2635"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD63242"/>
+        <fgColor rgb="FFE04F5D"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -3315,67 +3375,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAD1F2D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE04F5D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAC1F2C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFED9BA2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -9306,7 +9306,7 @@
       <c r="C2" t="str">
         <v>002570</v>
       </c>
-      <c r="D2" s="11" t="str">
+      <c r="D2" s="13" t="str">
         <v>净卖: -1602.12万</v>
       </c>
       <c r="E2">
@@ -9321,40 +9321,40 @@
       <c r="H2">
         <v>0.15</v>
       </c>
-      <c r="I2" s="12">
+      <c r="I2" s="10">
         <v>9.77</v>
       </c>
-      <c r="J2" s="5">
+      <c r="J2" s="11">
         <v>9.62</v>
       </c>
-      <c r="K2" s="6">
+      <c r="K2" s="1">
         <v>-1.35</v>
       </c>
-      <c r="L2" s="13">
+      <c r="L2" s="5">
         <v>-7.07</v>
       </c>
-      <c r="M2" s="1">
+      <c r="M2" s="2">
         <v>-3.31</v>
       </c>
-      <c r="N2" s="7">
+      <c r="N2" s="3">
         <v>2.56</v>
       </c>
-      <c r="O2" s="2">
+      <c r="O2" s="6">
         <v>9.32</v>
       </c>
-      <c r="P2" s="3">
+      <c r="P2" s="8">
         <v>-1.65</v>
       </c>
-      <c r="Q2" s="4">
+      <c r="Q2" s="9">
         <v>-11.43</v>
       </c>
-      <c r="R2" s="8">
+      <c r="R2" s="7">
         <v>-9.47</v>
       </c>
-      <c r="S2" s="9">
+      <c r="S2" s="12">
         <v>-8.12</v>
       </c>
-      <c r="T2" s="10">
+      <c r="T2" s="4">
         <v>-24.21</v>
       </c>
     </row>
@@ -9368,7 +9368,7 @@
       <c r="C3" t="str">
         <v>002915</v>
       </c>
-      <c r="D3" s="21" t="str">
+      <c r="D3" s="19" t="str">
         <v>净买: 2039.94万</v>
       </c>
       <c r="E3">
@@ -9383,40 +9383,40 @@
       <c r="H3">
         <v>0.12</v>
       </c>
-      <c r="I3" s="22">
+      <c r="I3" s="20">
         <v>5.12</v>
       </c>
-      <c r="J3" s="23">
+      <c r="J3" s="25">
         <v>15.65</v>
       </c>
-      <c r="K3" s="18">
+      <c r="K3" s="26">
         <v>27.2</v>
       </c>
-      <c r="L3" s="15">
+      <c r="L3" s="17">
         <v>27.56</v>
       </c>
-      <c r="M3" s="19">
+      <c r="M3" s="21">
         <v>40.3</v>
       </c>
-      <c r="N3" s="24">
+      <c r="N3" s="18">
         <v>27.68</v>
       </c>
-      <c r="O3" s="25">
+      <c r="O3" s="14">
         <v>30.06</v>
       </c>
-      <c r="P3" s="26">
+      <c r="P3" s="22">
         <v>28.1</v>
       </c>
-      <c r="Q3" s="16">
+      <c r="Q3" s="15">
         <v>36.9</v>
       </c>
-      <c r="R3" s="17">
+      <c r="R3" s="23">
         <v>34.52</v>
       </c>
-      <c r="S3" s="20">
+      <c r="S3" s="24">
         <v>21.07</v>
       </c>
-      <c r="T3" s="14">
+      <c r="T3" s="16">
         <v>26.67</v>
       </c>
     </row>
@@ -9430,7 +9430,7 @@
       <c r="C4" t="str">
         <v>002229</v>
       </c>
-      <c r="D4" s="35" t="str">
+      <c r="D4" s="31" t="str">
         <v>净买: 2135.02万</v>
       </c>
       <c r="E4">
@@ -9445,40 +9445,40 @@
       <c r="H4">
         <v>8.23</v>
       </c>
-      <c r="I4" s="38">
+      <c r="I4" s="34">
         <v>1.62</v>
       </c>
-      <c r="J4" s="39">
+      <c r="J4" s="32">
         <v>11.75</v>
       </c>
-      <c r="K4" s="31">
+      <c r="K4" s="29">
         <v>21.04</v>
       </c>
-      <c r="L4" s="27">
+      <c r="L4" s="38">
         <v>28.15</v>
       </c>
-      <c r="M4" s="28">
+      <c r="M4" s="35">
         <v>15.34</v>
       </c>
-      <c r="N4" s="32">
+      <c r="N4" s="36">
         <v>13.65</v>
       </c>
-      <c r="O4" s="33">
+      <c r="O4" s="39">
         <v>13.02</v>
       </c>
-      <c r="P4" s="36">
+      <c r="P4" s="33">
         <v>7.32</v>
       </c>
-      <c r="Q4" s="34">
+      <c r="Q4" s="27">
         <v>9.5</v>
       </c>
-      <c r="R4" s="29">
+      <c r="R4" s="28">
         <v>9.57</v>
       </c>
-      <c r="S4" s="37">
+      <c r="S4" s="30">
         <v>14.22</v>
       </c>
-      <c r="T4" s="30">
+      <c r="T4" s="37">
         <v>38.49</v>
       </c>
     </row>
@@ -9492,7 +9492,7 @@
       <c r="C5" t="str">
         <v>002915</v>
       </c>
-      <c r="D5" s="41" t="str">
+      <c r="D5" s="50" t="str">
         <v>净卖: -2747.73万</v>
       </c>
       <c r="E5">
@@ -9510,37 +9510,37 @@
       <c r="I5" s="51">
         <v>0</v>
       </c>
-      <c r="J5" s="52">
+      <c r="J5" s="47">
         <v>0.28</v>
       </c>
-      <c r="K5" s="42">
+      <c r="K5" s="52">
         <v>10.29</v>
       </c>
       <c r="L5" s="48">
         <v>0.37</v>
       </c>
-      <c r="M5" s="45">
+      <c r="M5" s="44">
         <v>2.25</v>
       </c>
-      <c r="N5" s="46">
+      <c r="N5" s="45">
         <v>0.7</v>
       </c>
-      <c r="O5" s="43">
+      <c r="O5" s="40">
         <v>7.63</v>
       </c>
-      <c r="P5" s="47">
+      <c r="P5" s="41">
         <v>5.76</v>
       </c>
-      <c r="Q5" s="49">
+      <c r="Q5" s="42">
         <v>-4.82</v>
       </c>
-      <c r="R5" s="44">
+      <c r="R5" s="43">
         <v>4.68</v>
       </c>
-      <c r="S5" s="40">
+      <c r="S5" s="49">
         <v>11</v>
       </c>
-      <c r="T5" s="50">
+      <c r="T5" s="46">
         <v>-0.42</v>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       <c r="C6" t="str">
         <v>002177</v>
       </c>
-      <c r="D6" s="63" t="str">
+      <c r="D6" s="62" t="str">
         <v>净买: 3117.92万</v>
       </c>
       <c r="E6">
@@ -9569,40 +9569,40 @@
       <c r="H6">
         <v>5.02</v>
       </c>
-      <c r="I6" s="60">
+      <c r="I6" s="63">
         <v>4.78</v>
       </c>
-      <c r="J6" s="64">
+      <c r="J6" s="59">
         <v>10.79</v>
       </c>
-      <c r="K6" s="65">
+      <c r="K6" s="64">
         <v>7.24</v>
       </c>
-      <c r="L6" s="57">
+      <c r="L6" s="60">
         <v>12.3</v>
       </c>
-      <c r="M6" s="58">
+      <c r="M6" s="56">
         <v>5.6</v>
       </c>
-      <c r="N6" s="53">
+      <c r="N6" s="57">
         <v>2.46</v>
       </c>
-      <c r="O6" s="54">
+      <c r="O6" s="65">
         <v>-1.91</v>
       </c>
-      <c r="P6" s="61">
+      <c r="P6" s="53">
         <v>-9.56</v>
       </c>
-      <c r="Q6" s="62">
+      <c r="Q6" s="58">
         <v>-3.01</v>
       </c>
-      <c r="R6" s="55">
+      <c r="R6" s="61">
         <v>0.55</v>
       </c>
-      <c r="S6" s="59">
+      <c r="S6" s="55">
         <v>3.14</v>
       </c>
-      <c r="T6" s="56">
+      <c r="T6" s="54">
         <v>7.65</v>
       </c>
     </row>
@@ -9616,7 +9616,7 @@
       <c r="C7" t="str">
         <v>002177</v>
       </c>
-      <c r="D7" s="71" t="str">
+      <c r="D7" s="74" t="str">
         <v>净卖: -2852.77万</v>
       </c>
       <c r="E7">
@@ -9631,40 +9631,40 @@
       <c r="H7">
         <v>-4.04</v>
       </c>
-      <c r="I7" s="77">
+      <c r="I7" s="69">
         <v>10.19</v>
       </c>
-      <c r="J7" s="72">
+      <c r="J7" s="75">
         <v>6.66</v>
       </c>
-      <c r="K7" s="73">
+      <c r="K7" s="78">
         <v>11.68</v>
       </c>
-      <c r="L7" s="67">
+      <c r="L7" s="76">
         <v>5.03</v>
       </c>
-      <c r="M7" s="68">
+      <c r="M7" s="77">
         <v>1.9</v>
       </c>
-      <c r="N7" s="69">
+      <c r="N7" s="70">
         <v>-2.45</v>
       </c>
-      <c r="O7" s="70">
+      <c r="O7" s="71">
         <v>-10.05</v>
       </c>
-      <c r="P7" s="74">
+      <c r="P7" s="66">
         <v>-3.53</v>
       </c>
-      <c r="Q7" s="75">
+      <c r="Q7" s="72">
         <v>0</v>
       </c>
-      <c r="R7" s="78">
+      <c r="R7" s="67">
         <v>2.58</v>
       </c>
-      <c r="S7" s="76">
+      <c r="S7" s="73">
         <v>-5.3</v>
       </c>
-      <c r="T7" s="66">
+      <c r="T7" s="68">
         <v>7.07</v>
       </c>
     </row>
@@ -9693,40 +9693,40 @@
       <c r="H8">
         <v>-0.92</v>
       </c>
-      <c r="I8" s="91">
+      <c r="I8" s="89">
         <v>11.01</v>
       </c>
-      <c r="J8" s="89">
+      <c r="J8" s="80">
         <v>11.21</v>
       </c>
-      <c r="K8" s="82">
+      <c r="K8" s="81">
         <v>1.71</v>
       </c>
-      <c r="L8" s="79">
+      <c r="L8" s="84">
         <v>4.11</v>
       </c>
-      <c r="M8" s="90">
+      <c r="M8" s="85">
         <v>0.04</v>
       </c>
-      <c r="N8" s="86">
+      <c r="N8" s="90">
         <v>0.78</v>
       </c>
-      <c r="O8" s="87">
+      <c r="O8" s="82">
         <v>2.37</v>
       </c>
-      <c r="P8" s="80">
+      <c r="P8" s="83">
         <v>5.12</v>
       </c>
-      <c r="Q8" s="83">
+      <c r="Q8" s="91">
         <v>5.93</v>
       </c>
-      <c r="R8" s="81">
+      <c r="R8" s="86">
         <v>8.07</v>
       </c>
-      <c r="S8" s="84">
+      <c r="S8" s="87">
         <v>18.88</v>
       </c>
-      <c r="T8" s="85">
+      <c r="T8" s="79">
         <v>18.88</v>
       </c>
     </row>
@@ -9740,7 +9740,7 @@
       <c r="C9" t="str">
         <v>003029</v>
       </c>
-      <c r="D9" s="98" t="str">
+      <c r="D9" s="92" t="str">
         <v>净卖: -276.02万</v>
       </c>
       <c r="E9">
@@ -9755,37 +9755,37 @@
       <c r="H9">
         <v>10.01</v>
       </c>
-      <c r="I9" s="99">
+      <c r="I9" s="100">
         <v>0</v>
       </c>
-      <c r="J9" s="94">
+      <c r="J9" s="102">
         <v>10.01</v>
       </c>
-      <c r="K9" s="100">
+      <c r="K9" s="98">
         <v>1.58</v>
       </c>
-      <c r="L9" s="102">
+      <c r="L9" s="103">
         <v>0.44</v>
       </c>
-      <c r="M9" s="92">
+      <c r="M9" s="93">
         <v>-9.6</v>
       </c>
-      <c r="N9" s="103">
+      <c r="N9" s="101">
         <v>-14.15</v>
       </c>
-      <c r="O9" s="95">
+      <c r="O9" s="94">
         <v>-11.05</v>
       </c>
-      <c r="P9" s="104">
+      <c r="P9" s="95">
         <v>-8.72</v>
       </c>
-      <c r="Q9" s="96">
+      <c r="Q9" s="99">
         <v>-7.3</v>
       </c>
-      <c r="R9" s="101">
+      <c r="R9" s="104">
         <v>-8.31</v>
       </c>
-      <c r="S9" s="93">
+      <c r="S9" s="96">
         <v>-7.9</v>
       </c>
       <c r="T9" s="97">
@@ -9802,7 +9802,7 @@
       <c r="C10" t="str">
         <v>002017</v>
       </c>
-      <c r="D10" s="108" t="str">
+      <c r="D10" s="117" t="str">
         <v>净买: 6518.56万</v>
       </c>
       <c r="E10">
@@ -9817,40 +9817,40 @@
       <c r="H10">
         <v>5.13</v>
       </c>
-      <c r="I10" s="113">
+      <c r="I10" s="107">
         <v>4.66</v>
       </c>
-      <c r="J10" s="115">
+      <c r="J10" s="114">
         <v>-0.06</v>
       </c>
-      <c r="K10" s="114">
+      <c r="K10" s="108">
         <v>-6.53</v>
       </c>
       <c r="L10" s="109">
         <v>-5.79</v>
       </c>
-      <c r="M10" s="116">
+      <c r="M10" s="110">
         <v>-7.89</v>
       </c>
-      <c r="N10" s="110">
+      <c r="N10" s="111">
         <v>-3.46</v>
       </c>
-      <c r="O10" s="106">
+      <c r="O10" s="105">
         <v>0.68</v>
       </c>
-      <c r="P10" s="111">
+      <c r="P10" s="106">
         <v>0.51</v>
       </c>
-      <c r="Q10" s="117">
+      <c r="Q10" s="115">
         <v>-6.47</v>
       </c>
-      <c r="R10" s="105">
+      <c r="R10" s="112">
         <v>-3.8</v>
       </c>
-      <c r="S10" s="112">
+      <c r="S10" s="113">
         <v>-6.53</v>
       </c>
-      <c r="T10" s="107">
+      <c r="T10" s="116">
         <v>9.31</v>
       </c>
     </row>
@@ -9864,7 +9864,7 @@
       <c r="C11" t="str">
         <v>002670</v>
       </c>
-      <c r="D11" s="126" t="str">
+      <c r="D11" s="122" t="str">
         <v>净卖: -2720.58万</v>
       </c>
       <c r="E11">
@@ -9879,40 +9879,40 @@
       <c r="H11">
         <v>-0.81</v>
       </c>
-      <c r="I11" s="118">
+      <c r="I11" s="130">
         <v>-5.23</v>
       </c>
-      <c r="J11" s="127">
+      <c r="J11" s="118">
         <v>-1.39</v>
       </c>
-      <c r="K11" s="123">
+      <c r="K11" s="128">
         <v>-9.57</v>
       </c>
-      <c r="L11" s="129">
+      <c r="L11" s="119">
         <v>-7.18</v>
       </c>
-      <c r="M11" s="124">
+      <c r="M11" s="123">
         <v>-7.62</v>
       </c>
-      <c r="N11" s="119">
+      <c r="N11" s="120">
         <v>-8.69</v>
       </c>
-      <c r="O11" s="128">
+      <c r="O11" s="129">
         <v>-7.37</v>
       </c>
-      <c r="P11" s="120">
+      <c r="P11" s="124">
         <v>-8.56</v>
       </c>
-      <c r="Q11" s="125">
+      <c r="Q11" s="121">
         <v>-8.63</v>
       </c>
-      <c r="R11" s="121">
+      <c r="R11" s="125">
         <v>-4.28</v>
       </c>
-      <c r="S11" s="122">
+      <c r="S11" s="126">
         <v>-8.56</v>
       </c>
-      <c r="T11" s="130">
+      <c r="T11" s="127">
         <v>-7.93</v>
       </c>
     </row>
@@ -9926,7 +9926,7 @@
       <c r="C12" t="str">
         <v>002579</v>
       </c>
-      <c r="D12" s="136" t="str">
+      <c r="D12" s="131" t="str">
         <v>净买: 4403.72万</v>
       </c>
       <c r="E12">
@@ -9941,40 +9941,40 @@
       <c r="H12">
         <v>-2.68</v>
       </c>
-      <c r="I12" s="137">
+      <c r="I12" s="139">
         <v>13.04</v>
       </c>
       <c r="J12" s="132">
         <v>12.54</v>
       </c>
-      <c r="K12" s="135">
+      <c r="K12" s="133">
         <v>7.97</v>
       </c>
-      <c r="L12" s="138">
+      <c r="L12" s="134">
         <v>12.54</v>
       </c>
-      <c r="M12" s="133">
+      <c r="M12" s="135">
         <v>7.1</v>
       </c>
-      <c r="N12" s="140">
+      <c r="N12" s="141">
         <v>-3.62</v>
       </c>
-      <c r="O12" s="141">
+      <c r="O12" s="136">
         <v>-2.97</v>
       </c>
-      <c r="P12" s="139">
+      <c r="P12" s="142">
         <v>-5.36</v>
       </c>
-      <c r="Q12" s="142">
+      <c r="Q12" s="143">
         <v>-3.7</v>
       </c>
-      <c r="R12" s="134">
+      <c r="R12" s="140">
         <v>-10.07</v>
       </c>
-      <c r="S12" s="143">
+      <c r="S12" s="137">
         <v>-6.59</v>
       </c>
-      <c r="T12" s="131">
+      <c r="T12" s="138">
         <v>-4.64</v>
       </c>
     </row>
@@ -9988,7 +9988,7 @@
       <c r="C13" t="str">
         <v>002229</v>
       </c>
-      <c r="D13" s="156" t="str">
+      <c r="D13" s="152" t="str">
         <v>净卖: -4629.75万</v>
       </c>
       <c r="E13">
@@ -10003,40 +10003,40 @@
       <c r="H13">
         <v>3.11</v>
       </c>
-      <c r="I13" s="144">
+      <c r="I13" s="153">
         <v>-7.78</v>
       </c>
-      <c r="J13" s="145">
+      <c r="J13" s="148">
         <v>-8.44</v>
       </c>
-      <c r="K13" s="154">
+      <c r="K13" s="149">
         <v>-11.23</v>
       </c>
-      <c r="L13" s="152">
+      <c r="L13" s="150">
         <v>-12.22</v>
       </c>
-      <c r="M13" s="146">
+      <c r="M13" s="144">
         <v>-10.66</v>
       </c>
-      <c r="N13" s="147">
+      <c r="N13" s="154">
         <v>-6.65</v>
       </c>
-      <c r="O13" s="150">
+      <c r="O13" s="145">
         <v>-7.74</v>
       </c>
-      <c r="P13" s="151">
+      <c r="P13" s="146">
         <v>-7.69</v>
       </c>
-      <c r="Q13" s="148">
+      <c r="Q13" s="155">
         <v>-11.37</v>
       </c>
-      <c r="R13" s="149">
+      <c r="R13" s="147">
         <v>-10.8</v>
       </c>
-      <c r="S13" s="153">
+      <c r="S13" s="156">
         <v>-13.68</v>
       </c>
-      <c r="T13" s="155">
+      <c r="T13" s="151">
         <v>-7.17</v>
       </c>
     </row>
@@ -10050,7 +10050,7 @@
       <c r="C14" t="str">
         <v>000657</v>
       </c>
-      <c r="D14" s="159" t="str">
+      <c r="D14" s="162" t="str">
         <v>净卖: -6184.73万</v>
       </c>
       <c r="E14">
@@ -10065,40 +10065,40 @@
       <c r="H14">
         <v>-2</v>
       </c>
-      <c r="I14" s="166">
+      <c r="I14" s="165">
         <v>-8.16</v>
       </c>
       <c r="J14" s="160">
         <v>-13.48</v>
       </c>
-      <c r="K14" s="161">
+      <c r="K14" s="167">
         <v>-14.93</v>
       </c>
-      <c r="L14" s="167">
+      <c r="L14" s="161">
         <v>-15.36</v>
       </c>
-      <c r="M14" s="162">
+      <c r="M14" s="166">
         <v>-15.2</v>
       </c>
-      <c r="N14" s="168">
+      <c r="N14" s="163">
         <v>-13.43</v>
       </c>
-      <c r="O14" s="163">
+      <c r="O14" s="168">
         <v>-13.1</v>
       </c>
-      <c r="P14" s="157">
+      <c r="P14" s="169">
         <v>-11.6</v>
       </c>
-      <c r="Q14" s="169">
+      <c r="Q14" s="164">
         <v>-10.74</v>
       </c>
-      <c r="R14" s="164">
+      <c r="R14" s="157">
         <v>-10.9</v>
       </c>
       <c r="S14" s="158">
         <v>-8.81</v>
       </c>
-      <c r="T14" s="165">
+      <c r="T14" s="159">
         <v>201.4</v>
       </c>
     </row>
@@ -10112,7 +10112,7 @@
       <c r="C15" t="str">
         <v>002670</v>
       </c>
-      <c r="D15" s="179" t="str">
+      <c r="D15" s="182" t="str">
         <v>净卖: -7597.74万</v>
       </c>
       <c r="E15">
@@ -10127,40 +10127,40 @@
       <c r="H15">
         <v>0.45</v>
       </c>
-      <c r="I15" s="174">
+      <c r="I15" s="176">
         <v>1.89</v>
       </c>
-      <c r="J15" s="170">
+      <c r="J15" s="172">
         <v>-1.79</v>
       </c>
-      <c r="K15" s="180">
+      <c r="K15" s="177">
         <v>-1.79</v>
       </c>
-      <c r="L15" s="181">
+      <c r="L15" s="178">
         <v>-3.03</v>
       </c>
-      <c r="M15" s="171">
+      <c r="M15" s="173">
         <v>-4.83</v>
       </c>
-      <c r="N15" s="175">
+      <c r="N15" s="174">
         <v>-3.73</v>
       </c>
-      <c r="O15" s="172">
+      <c r="O15" s="175">
         <v>-3.38</v>
       </c>
-      <c r="P15" s="182">
+      <c r="P15" s="179">
         <v>-4.28</v>
       </c>
-      <c r="Q15" s="178">
+      <c r="Q15" s="170">
         <v>-7.71</v>
       </c>
-      <c r="R15" s="173">
+      <c r="R15" s="180">
         <v>-3.98</v>
       </c>
-      <c r="S15" s="176">
+      <c r="S15" s="181">
         <v>-2.84</v>
       </c>
-      <c r="T15" s="177">
+      <c r="T15" s="171">
         <v>-27.26</v>
       </c>
     </row>
@@ -10174,7 +10174,7 @@
       <c r="C16" t="str">
         <v>688039</v>
       </c>
-      <c r="D16" s="190" t="str">
+      <c r="D16" s="183" t="str">
         <v>净买: 3066.00万</v>
       </c>
       <c r="E16">
@@ -10189,40 +10189,40 @@
       <c r="H16">
         <v>7.16</v>
       </c>
-      <c r="I16" s="186">
+      <c r="I16" s="190">
         <v>11.98</v>
       </c>
-      <c r="J16" s="187">
+      <c r="J16" s="188">
         <v>16.69</v>
       </c>
-      <c r="K16" s="194">
+      <c r="K16" s="184">
         <v>3.41</v>
       </c>
-      <c r="L16" s="195">
+      <c r="L16" s="185">
         <v>0.07</v>
       </c>
-      <c r="M16" s="183">
+      <c r="M16" s="191">
         <v>-5.26</v>
       </c>
-      <c r="N16" s="191">
+      <c r="N16" s="186">
         <v>-3.41</v>
       </c>
-      <c r="O16" s="184">
+      <c r="O16" s="192">
         <v>-5.04</v>
       </c>
-      <c r="P16" s="189">
+      <c r="P16" s="193">
         <v>-10.52</v>
       </c>
-      <c r="Q16" s="192">
+      <c r="Q16" s="187">
         <v>-7.78</v>
       </c>
-      <c r="R16" s="185">
+      <c r="R16" s="194">
         <v>-6.1</v>
       </c>
-      <c r="S16" s="188">
+      <c r="S16" s="189">
         <v>-7.34</v>
       </c>
-      <c r="T16" s="193">
+      <c r="T16" s="195">
         <v>-20.42</v>
       </c>
     </row>
@@ -10236,7 +10236,7 @@
       <c r="C17" t="str">
         <v>600408</v>
       </c>
-      <c r="D17" s="201" t="str">
+      <c r="D17" s="205" t="str">
         <v>净买: 1877.05万</v>
       </c>
       <c r="E17">
@@ -10251,19 +10251,19 @@
       <c r="H17">
         <v>-4.45</v>
       </c>
-      <c r="I17" s="202">
+      <c r="I17" s="196">
         <v>15.2</v>
       </c>
-      <c r="J17" s="208">
+      <c r="J17" s="197">
         <v>26.72</v>
       </c>
-      <c r="K17" s="203">
+      <c r="K17" s="198">
         <v>39.46</v>
       </c>
-      <c r="L17" s="196">
+      <c r="L17" s="203">
         <v>53.43</v>
       </c>
-      <c r="M17" s="197">
+      <c r="M17" s="201">
         <v>68.87</v>
       </c>
       <c r="N17" s="206">
@@ -10272,19 +10272,19 @@
       <c r="O17" s="204">
         <v>37.5</v>
       </c>
-      <c r="P17" s="205">
+      <c r="P17" s="199">
         <v>24.26</v>
       </c>
-      <c r="Q17" s="198">
+      <c r="Q17" s="200">
         <v>14.95</v>
       </c>
-      <c r="R17" s="199">
+      <c r="R17" s="202">
         <v>10.54</v>
       </c>
-      <c r="S17" s="200">
+      <c r="S17" s="207">
         <v>11.52</v>
       </c>
-      <c r="T17" s="207">
+      <c r="T17" s="208">
         <v>-23.28</v>
       </c>
     </row>
@@ -10298,7 +10298,7 @@
       <c r="C18" t="str">
         <v>601566</v>
       </c>
-      <c r="D18" s="220" t="str">
+      <c r="D18" s="216" t="str">
         <v>净买: 5226.66万</v>
       </c>
       <c r="E18">
@@ -10313,37 +10313,37 @@
       <c r="H18">
         <v>10.02</v>
       </c>
-      <c r="I18" s="221">
+      <c r="I18" s="210">
         <v>0</v>
       </c>
-      <c r="J18" s="214">
+      <c r="J18" s="211">
         <v>9.97</v>
       </c>
-      <c r="K18" s="212">
+      <c r="K18" s="217">
         <v>20.95</v>
       </c>
-      <c r="L18" s="209">
+      <c r="L18" s="218">
         <v>33.02</v>
       </c>
-      <c r="M18" s="215">
+      <c r="M18" s="214">
         <v>19.73</v>
       </c>
-      <c r="N18" s="216">
+      <c r="N18" s="215">
         <v>7.73</v>
       </c>
-      <c r="O18" s="210">
+      <c r="O18" s="219">
         <v>3.32</v>
       </c>
-      <c r="P18" s="211">
+      <c r="P18" s="220">
         <v>-5.35</v>
       </c>
-      <c r="Q18" s="217">
+      <c r="Q18" s="221">
         <v>-6.94</v>
       </c>
-      <c r="R18" s="218">
+      <c r="R18" s="209">
         <v>-3.03</v>
       </c>
-      <c r="S18" s="219">
+      <c r="S18" s="212">
         <v>-2.46</v>
       </c>
       <c r="T18" s="213">
@@ -10360,7 +10360,7 @@
       <c r="C19" t="str">
         <v>002029</v>
       </c>
-      <c r="D19" s="225" t="str">
+      <c r="D19" s="227" t="str">
         <v>净卖: -1276.40万</v>
       </c>
       <c r="E19">
@@ -10375,40 +10375,40 @@
       <c r="H19">
         <v>0</v>
       </c>
-      <c r="I19" s="226">
+      <c r="I19" s="223">
         <v>9.97</v>
       </c>
-      <c r="J19" s="229">
+      <c r="J19" s="224">
         <v>1.88</v>
       </c>
-      <c r="K19" s="230">
+      <c r="K19" s="225">
         <v>-2.35</v>
       </c>
-      <c r="L19" s="233">
+      <c r="L19" s="226">
         <v>-9.97</v>
       </c>
-      <c r="M19" s="227">
+      <c r="M19" s="222">
         <v>-11.67</v>
       </c>
-      <c r="N19" s="231">
+      <c r="N19" s="228">
         <v>-8</v>
       </c>
-      <c r="O19" s="234">
+      <c r="O19" s="229">
         <v>1.22</v>
       </c>
-      <c r="P19" s="222">
+      <c r="P19" s="232">
         <v>0.85</v>
       </c>
-      <c r="Q19" s="223">
+      <c r="Q19" s="230">
         <v>3.01</v>
       </c>
-      <c r="R19" s="224">
+      <c r="R19" s="233">
         <v>1.69</v>
       </c>
-      <c r="S19" s="228">
+      <c r="S19" s="231">
         <v>0.09</v>
       </c>
-      <c r="T19" s="232">
+      <c r="T19" s="234">
         <v>-7.81</v>
       </c>
     </row>
@@ -10437,40 +10437,40 @@
       <c r="H20">
         <v>4.01</v>
       </c>
-      <c r="I20" s="236">
+      <c r="I20" s="241">
         <v>5.75</v>
       </c>
       <c r="J20" s="245">
         <v>16.3</v>
       </c>
-      <c r="K20" s="237">
+      <c r="K20" s="235">
         <v>4.67</v>
       </c>
-      <c r="L20" s="241">
+      <c r="L20" s="242">
         <v>-5.81</v>
       </c>
-      <c r="M20" s="246">
+      <c r="M20" s="236">
         <v>-9.67</v>
       </c>
-      <c r="N20" s="238">
+      <c r="N20" s="246">
         <v>-17.25</v>
       </c>
-      <c r="O20" s="239">
+      <c r="O20" s="243">
         <v>-18.64</v>
       </c>
-      <c r="P20" s="247">
+      <c r="P20" s="244">
         <v>-15.22</v>
       </c>
-      <c r="Q20" s="242">
+      <c r="Q20" s="239">
         <v>-14.72</v>
       </c>
-      <c r="R20" s="235">
+      <c r="R20" s="237">
         <v>-10.8</v>
       </c>
-      <c r="S20" s="243">
+      <c r="S20" s="238">
         <v>-6.19</v>
       </c>
-      <c r="T20" s="244">
+      <c r="T20" s="247">
         <v>-32.53</v>
       </c>
     </row>
@@ -10484,7 +10484,7 @@
       <c r="C21" t="str">
         <v>601566</v>
       </c>
-      <c r="D21" s="260" t="str">
+      <c r="D21" s="248" t="str">
         <v>净卖: -5218.09万</v>
       </c>
       <c r="E21">
@@ -10502,37 +10502,37 @@
       <c r="I21" s="257">
         <v>2.68</v>
       </c>
-      <c r="J21" s="248">
+      <c r="J21" s="255">
         <v>-7.59</v>
       </c>
-      <c r="K21" s="255">
+      <c r="K21" s="249">
         <v>-16.84</v>
       </c>
-      <c r="L21" s="258">
+      <c r="L21" s="250">
         <v>-20.25</v>
       </c>
       <c r="M21" s="259">
         <v>-26.94</v>
       </c>
-      <c r="N21" s="249">
+      <c r="N21" s="251">
         <v>-28.17</v>
       </c>
-      <c r="O21" s="250">
+      <c r="O21" s="252">
         <v>-25.15</v>
       </c>
-      <c r="P21" s="256">
+      <c r="P21" s="258">
         <v>-24.71</v>
       </c>
       <c r="Q21" s="253">
         <v>-21.25</v>
       </c>
-      <c r="R21" s="251">
+      <c r="R21" s="254">
         <v>-17.18</v>
       </c>
-      <c r="S21" s="254">
+      <c r="S21" s="260">
         <v>-25.43</v>
       </c>
-      <c r="T21" s="252">
+      <c r="T21" s="256">
         <v>-40.44</v>
       </c>
     </row>
@@ -10546,7 +10546,7 @@
       <c r="C22" t="str">
         <v>600756</v>
       </c>
-      <c r="D22" s="265" t="str">
+      <c r="D22" s="271" t="str">
         <v>净卖: -2369.10万</v>
       </c>
       <c r="E22">
@@ -10561,40 +10561,40 @@
       <c r="H22">
         <v>-1.6</v>
       </c>
-      <c r="I22" s="266">
+      <c r="I22" s="263">
         <v>1.46</v>
       </c>
       <c r="J22" s="272">
         <v>-4.63</v>
       </c>
-      <c r="K22" s="267">
+      <c r="K22" s="266">
         <v>-3.97</v>
       </c>
-      <c r="L22" s="273">
+      <c r="L22" s="267">
         <v>-13.57</v>
       </c>
-      <c r="M22" s="261">
+      <c r="M22" s="264">
         <v>-21.09</v>
       </c>
       <c r="N22" s="268">
         <v>-19.75</v>
       </c>
-      <c r="O22" s="270">
+      <c r="O22" s="273">
         <v>-18.25</v>
       </c>
-      <c r="P22" s="263">
+      <c r="P22" s="261">
         <v>-20.84</v>
       </c>
-      <c r="Q22" s="262">
+      <c r="Q22" s="269">
         <v>-21.42</v>
       </c>
-      <c r="R22" s="269">
+      <c r="R22" s="262">
         <v>-23.17</v>
       </c>
-      <c r="S22" s="271">
+      <c r="S22" s="265">
         <v>-24.43</v>
       </c>
-      <c r="T22" s="264">
+      <c r="T22" s="270">
         <v>-31.15</v>
       </c>
     </row>
@@ -10608,7 +10608,7 @@
       <c r="C23" t="str">
         <v>603696</v>
       </c>
-      <c r="D23" s="274" t="str">
+      <c r="D23" s="286" t="str">
         <v>净买: 3978.78万</v>
       </c>
       <c r="E23">
@@ -10623,40 +10623,40 @@
       <c r="H23">
         <v>9.98</v>
       </c>
-      <c r="I23" s="284">
+      <c r="I23" s="274">
         <v>0</v>
       </c>
-      <c r="J23" s="286">
+      <c r="J23" s="280">
         <v>10.01</v>
       </c>
-      <c r="K23" s="275">
+      <c r="K23" s="281">
         <v>21.01</v>
       </c>
-      <c r="L23" s="276">
+      <c r="L23" s="282">
         <v>33.13</v>
       </c>
-      <c r="M23" s="277">
+      <c r="M23" s="283">
         <v>46.43</v>
       </c>
-      <c r="N23" s="285">
+      <c r="N23" s="279">
         <v>43.01</v>
       </c>
-      <c r="O23" s="280">
+      <c r="O23" s="275">
         <v>28.71</v>
       </c>
-      <c r="P23" s="281">
+      <c r="P23" s="276">
         <v>24.74</v>
       </c>
-      <c r="Q23" s="278">
+      <c r="Q23" s="284">
         <v>27.91</v>
       </c>
-      <c r="R23" s="282">
+      <c r="R23" s="277">
         <v>40.71</v>
       </c>
-      <c r="S23" s="279">
+      <c r="S23" s="285">
         <v>26.66</v>
       </c>
-      <c r="T23" s="283">
+      <c r="T23" s="278">
         <v>-1.12</v>
       </c>
     </row>
@@ -10670,7 +10670,7 @@
       <c r="C24" t="str">
         <v>002682</v>
       </c>
-      <c r="D24" s="298" t="str">
+      <c r="D24" s="292" t="str">
         <v>净买: 2499.06万</v>
       </c>
       <c r="E24">
@@ -10691,34 +10691,34 @@
       <c r="J24" s="287">
         <v>14.2</v>
       </c>
-      <c r="K24" s="291">
+      <c r="K24" s="288">
         <v>25.65</v>
       </c>
-      <c r="L24" s="292">
+      <c r="L24" s="297">
         <v>38.26</v>
       </c>
-      <c r="M24" s="293">
+      <c r="M24" s="289">
         <v>52.03</v>
       </c>
-      <c r="N24" s="288">
+      <c r="N24" s="293">
         <v>42.9</v>
       </c>
-      <c r="O24" s="296">
+      <c r="O24" s="290">
         <v>57.25</v>
       </c>
       <c r="P24" s="294">
         <v>72.9</v>
       </c>
-      <c r="Q24" s="289">
+      <c r="Q24" s="295">
         <v>55.65</v>
       </c>
-      <c r="R24" s="297">
+      <c r="R24" s="296">
         <v>40.14</v>
       </c>
-      <c r="S24" s="295">
+      <c r="S24" s="291">
         <v>42.75</v>
       </c>
-      <c r="T24" s="290">
+      <c r="T24" s="298">
         <v>-13.91</v>
       </c>
     </row>
@@ -10732,7 +10732,7 @@
       <c r="C25" t="str">
         <v>603696</v>
       </c>
-      <c r="D25" s="303" t="str">
+      <c r="D25" s="301" t="str">
         <v>净卖: -1913.63万</v>
       </c>
       <c r="E25">
@@ -10747,34 +10747,34 @@
       <c r="H25">
         <v>-2.03</v>
       </c>
-      <c r="I25" s="307">
+      <c r="I25" s="309">
         <v>12.28</v>
       </c>
-      <c r="J25" s="304">
+      <c r="J25" s="300">
         <v>23.53</v>
       </c>
-      <c r="K25" s="300">
+      <c r="K25" s="310">
         <v>35.87</v>
       </c>
-      <c r="L25" s="306">
+      <c r="L25" s="311">
         <v>32.7</v>
       </c>
-      <c r="M25" s="308">
+      <c r="M25" s="306">
         <v>19.43</v>
       </c>
-      <c r="N25" s="309">
+      <c r="N25" s="302">
         <v>15.74</v>
       </c>
-      <c r="O25" s="310">
+      <c r="O25" s="303">
         <v>18.69</v>
       </c>
-      <c r="P25" s="311">
+      <c r="P25" s="307">
         <v>30.57</v>
       </c>
-      <c r="Q25" s="301">
+      <c r="Q25" s="304">
         <v>17.53</v>
       </c>
-      <c r="R25" s="302">
+      <c r="R25" s="308">
         <v>10.73</v>
       </c>
       <c r="S25" s="312">
@@ -10794,7 +10794,7 @@
       <c r="C26" t="str">
         <v>603696</v>
       </c>
-      <c r="D26" s="316" t="str">
+      <c r="D26" s="315" t="str">
         <v>净卖: -3631.64万</v>
       </c>
       <c r="E26">
@@ -10809,40 +10809,40 @@
       <c r="H26">
         <v>9.08</v>
       </c>
-      <c r="I26" s="317">
+      <c r="I26" s="316">
         <v>-10.47</v>
       </c>
-      <c r="J26" s="321">
+      <c r="J26" s="317">
         <v>-19.42</v>
       </c>
-      <c r="K26" s="318">
+      <c r="K26" s="321">
         <v>-21.91</v>
       </c>
-      <c r="L26" s="313">
+      <c r="L26" s="323">
         <v>-19.92</v>
       </c>
-      <c r="M26" s="319">
+      <c r="M26" s="324">
         <v>-11.91</v>
       </c>
-      <c r="N26" s="322">
+      <c r="N26" s="318">
         <v>-20.7</v>
       </c>
-      <c r="O26" s="314">
+      <c r="O26" s="319">
         <v>-25.29</v>
       </c>
-      <c r="P26" s="320">
+      <c r="P26" s="313">
         <v>-21.4</v>
       </c>
-      <c r="Q26" s="325">
+      <c r="Q26" s="322">
         <v>-13.54</v>
       </c>
-      <c r="R26" s="315">
+      <c r="R26" s="320">
         <v>-4.9</v>
       </c>
-      <c r="S26" s="323">
+      <c r="S26" s="325">
         <v>4.59</v>
       </c>
-      <c r="T26" s="324">
+      <c r="T26" s="314">
         <v>-38.09</v>
       </c>
     </row>
@@ -10856,7 +10856,7 @@
       <c r="C27" t="str">
         <v>002682</v>
       </c>
-      <c r="D27" s="327" t="str">
+      <c r="D27" s="330" t="str">
         <v>净卖: -4674.28万</v>
       </c>
       <c r="E27">
@@ -10871,13 +10871,13 @@
       <c r="H27">
         <v>-4.33</v>
       </c>
-      <c r="I27" s="328">
+      <c r="I27" s="331">
         <v>14.93</v>
       </c>
-      <c r="J27" s="329">
+      <c r="J27" s="332">
         <v>3.47</v>
       </c>
-      <c r="K27" s="334">
+      <c r="K27" s="336">
         <v>-6.84</v>
       </c>
       <c r="L27" s="335">
@@ -10886,25 +10886,25 @@
       <c r="M27" s="337">
         <v>-10.89</v>
       </c>
-      <c r="N27" s="336">
+      <c r="N27" s="338">
         <v>-19.36</v>
       </c>
-      <c r="O27" s="333">
+      <c r="O27" s="327">
         <v>-21</v>
       </c>
-      <c r="P27" s="338">
+      <c r="P27" s="326">
         <v>-20.33</v>
       </c>
-      <c r="Q27" s="330">
+      <c r="Q27" s="328">
         <v>-12.43</v>
       </c>
-      <c r="R27" s="331">
+      <c r="R27" s="329">
         <v>-14.26</v>
       </c>
-      <c r="S27" s="332">
+      <c r="S27" s="333">
         <v>-7.8</v>
       </c>
-      <c r="T27" s="326">
+      <c r="T27" s="334">
         <v>-42.77</v>
       </c>
     </row>
@@ -10918,7 +10918,7 @@
       <c r="C28" t="str">
         <v>600693</v>
       </c>
-      <c r="D28" s="348" t="str">
+      <c r="D28" s="345" t="str">
         <v>净买: 4441.53万</v>
       </c>
       <c r="E28">
@@ -10933,40 +10933,40 @@
       <c r="H28">
         <v>1.81</v>
       </c>
-      <c r="I28" s="344">
+      <c r="I28" s="346">
         <v>8.04</v>
       </c>
-      <c r="J28" s="349">
+      <c r="J28" s="347">
         <v>15.95</v>
       </c>
-      <c r="K28" s="346">
+      <c r="K28" s="348">
         <v>10.22</v>
       </c>
-      <c r="L28" s="340">
+      <c r="L28" s="343">
         <v>13.45</v>
       </c>
-      <c r="M28" s="350">
+      <c r="M28" s="351">
         <v>12.33</v>
       </c>
-      <c r="N28" s="341">
+      <c r="N28" s="349">
         <v>23.53</v>
       </c>
-      <c r="O28" s="351">
+      <c r="O28" s="340">
         <v>28.54</v>
       </c>
-      <c r="P28" s="342">
+      <c r="P28" s="341">
         <v>41.4</v>
       </c>
-      <c r="Q28" s="343">
+      <c r="Q28" s="350">
         <v>37.84</v>
       </c>
-      <c r="R28" s="347">
+      <c r="R28" s="342">
         <v>44.23</v>
       </c>
-      <c r="S28" s="345">
+      <c r="S28" s="339">
         <v>30.52</v>
       </c>
-      <c r="T28" s="339">
+      <c r="T28" s="344">
         <v>-21.49</v>
       </c>
     </row>
@@ -10980,7 +10980,7 @@
       <c r="C29" t="str">
         <v>603696</v>
       </c>
-      <c r="D29" s="360" t="str">
+      <c r="D29" s="363" t="str">
         <v>净卖: -3147.63万</v>
       </c>
       <c r="E29">
@@ -10998,37 +10998,37 @@
       <c r="I29" s="356">
         <v>-12.53</v>
       </c>
-      <c r="J29" s="352">
+      <c r="J29" s="357">
         <v>-17.6</v>
       </c>
-      <c r="K29" s="359">
+      <c r="K29" s="358">
         <v>-13.3</v>
       </c>
-      <c r="L29" s="357">
+      <c r="L29" s="364">
         <v>-4.64</v>
       </c>
-      <c r="M29" s="353">
+      <c r="M29" s="352">
         <v>4.89</v>
       </c>
-      <c r="N29" s="354">
+      <c r="N29" s="359">
         <v>15.36</v>
       </c>
-      <c r="O29" s="361">
+      <c r="O29" s="354">
         <v>13.73</v>
       </c>
-      <c r="P29" s="362">
+      <c r="P29" s="361">
         <v>12.4</v>
       </c>
-      <c r="Q29" s="355">
+      <c r="Q29" s="360">
         <v>1.16</v>
       </c>
-      <c r="R29" s="358">
+      <c r="R29" s="353">
         <v>-8.97</v>
       </c>
-      <c r="S29" s="363">
+      <c r="S29" s="362">
         <v>-12.96</v>
       </c>
-      <c r="T29" s="364">
+      <c r="T29" s="355">
         <v>-31.72</v>
       </c>
     </row>
@@ -11042,7 +11042,7 @@
       <c r="C30" t="str">
         <v>600693</v>
       </c>
-      <c r="D30" s="370" t="str">
+      <c r="D30" s="366" t="str">
         <v>净卖: -5308.96万</v>
       </c>
       <c r="E30">
@@ -11057,40 +11057,40 @@
       <c r="H30">
         <v>2.51</v>
       </c>
-      <c r="I30" s="375">
+      <c r="I30" s="371">
         <v>0.41</v>
       </c>
-      <c r="J30" s="371">
+      <c r="J30" s="367">
         <v>-0.58</v>
       </c>
-      <c r="K30" s="372">
+      <c r="K30" s="376">
         <v>9.33</v>
       </c>
-      <c r="L30" s="369">
+      <c r="L30" s="368">
         <v>13.77</v>
       </c>
-      <c r="M30" s="376">
+      <c r="M30" s="372">
         <v>25.15</v>
       </c>
-      <c r="N30" s="377">
+      <c r="N30" s="373">
         <v>22</v>
       </c>
-      <c r="O30" s="373">
+      <c r="O30" s="374">
         <v>27.65</v>
       </c>
-      <c r="P30" s="365">
+      <c r="P30" s="370">
         <v>15.52</v>
       </c>
-      <c r="Q30" s="374">
+      <c r="Q30" s="377">
         <v>3.97</v>
       </c>
-      <c r="R30" s="366">
+      <c r="R30" s="365">
         <v>3.97</v>
       </c>
-      <c r="S30" s="367">
+      <c r="S30" s="369">
         <v>7.29</v>
       </c>
-      <c r="T30" s="368">
+      <c r="T30" s="375">
         <v>-30.51</v>
       </c>
     </row>
@@ -11104,7 +11104,7 @@
       <c r="C31" t="str">
         <v>600280</v>
       </c>
-      <c r="D31" s="385" t="str">
+      <c r="D31" s="387" t="str">
         <v>净买: 2343.21万</v>
       </c>
       <c r="E31">
@@ -11119,40 +11119,40 @@
       <c r="H31">
         <v>1.88</v>
       </c>
-      <c r="I31" s="379">
+      <c r="I31" s="382">
         <v>8.08</v>
       </c>
       <c r="J31" s="388">
         <v>17.78</v>
       </c>
-      <c r="K31" s="389">
+      <c r="K31" s="379">
         <v>12.93</v>
       </c>
-      <c r="L31" s="390">
+      <c r="L31" s="383">
         <v>4.39</v>
       </c>
-      <c r="M31" s="380">
+      <c r="M31" s="378">
         <v>5.54</v>
       </c>
-      <c r="N31" s="381">
+      <c r="N31" s="384">
         <v>1.85</v>
       </c>
-      <c r="O31" s="383">
+      <c r="O31" s="380">
         <v>-1.15</v>
       </c>
-      <c r="P31" s="378">
+      <c r="P31" s="385">
         <v>-3</v>
       </c>
-      <c r="Q31" s="384">
+      <c r="Q31" s="389">
         <v>-7.85</v>
       </c>
-      <c r="R31" s="382">
+      <c r="R31" s="390">
         <v>-11.09</v>
       </c>
-      <c r="S31" s="386">
+      <c r="S31" s="381">
         <v>-10.16</v>
       </c>
-      <c r="T31" s="387">
+      <c r="T31" s="386">
         <v>-27.94</v>
       </c>
     </row>
@@ -11166,7 +11166,7 @@
       <c r="C32" t="str">
         <v>600280</v>
       </c>
-      <c r="D32" s="403" t="str">
+      <c r="D32" s="398" t="str">
         <v>净卖: -2545.17万</v>
       </c>
       <c r="E32">
@@ -11181,40 +11181,40 @@
       <c r="H32">
         <v>-3.92</v>
       </c>
-      <c r="I32" s="401">
+      <c r="I32" s="403">
         <v>-0.2</v>
       </c>
-      <c r="J32" s="398">
+      <c r="J32" s="399">
         <v>-7.76</v>
       </c>
-      <c r="K32" s="402">
+      <c r="K32" s="391">
         <v>-6.73</v>
       </c>
-      <c r="L32" s="399">
+      <c r="L32" s="395">
         <v>-10</v>
       </c>
       <c r="M32" s="396">
         <v>-12.65</v>
       </c>
-      <c r="N32" s="391">
+      <c r="N32" s="400">
         <v>-14.29</v>
       </c>
-      <c r="O32" s="392">
+      <c r="O32" s="401">
         <v>-18.57</v>
       </c>
-      <c r="P32" s="397">
+      <c r="P32" s="392">
         <v>-21.43</v>
       </c>
-      <c r="Q32" s="400">
+      <c r="Q32" s="393">
         <v>-20.61</v>
       </c>
-      <c r="R32" s="393">
+      <c r="R32" s="402">
         <v>-16.33</v>
       </c>
-      <c r="S32" s="394">
+      <c r="S32" s="397">
         <v>-15.92</v>
       </c>
-      <c r="T32" s="395">
+      <c r="T32" s="394">
         <v>-36.33</v>
       </c>
     </row>
@@ -11228,7 +11228,7 @@
       <c r="C33" t="str">
         <v>002759</v>
       </c>
-      <c r="D33" s="408" t="str">
+      <c r="D33" s="405" t="str">
         <v>净买: 8490.49万</v>
       </c>
       <c r="E33">
@@ -11243,40 +11243,40 @@
       <c r="H33">
         <v>-3.82</v>
       </c>
-      <c r="I33" s="404">
+      <c r="I33" s="407">
         <v>11.08</v>
       </c>
-      <c r="J33" s="405">
+      <c r="J33" s="409">
         <v>22.19</v>
       </c>
-      <c r="K33" s="406">
+      <c r="K33" s="408">
         <v>22.69</v>
       </c>
-      <c r="L33" s="409">
+      <c r="L33" s="410">
         <v>13.63</v>
       </c>
-      <c r="M33" s="410">
+      <c r="M33" s="411">
         <v>14.61</v>
       </c>
       <c r="N33" s="416">
         <v>26.07</v>
       </c>
-      <c r="O33" s="411">
+      <c r="O33" s="412">
         <v>26.51</v>
       </c>
-      <c r="P33" s="415">
+      <c r="P33" s="413">
         <v>18.86</v>
       </c>
-      <c r="Q33" s="412">
+      <c r="Q33" s="406">
         <v>15.77</v>
       </c>
-      <c r="R33" s="413">
+      <c r="R33" s="404">
         <v>13.87</v>
       </c>
       <c r="S33" s="414">
         <v>15.03</v>
       </c>
-      <c r="T33" s="407">
+      <c r="T33" s="415">
         <v>-13.18</v>
       </c>
     </row>
@@ -11290,7 +11290,7 @@
       <c r="C34" t="str">
         <v>002792</v>
       </c>
-      <c r="D34" s="428" t="str">
+      <c r="D34" s="423" t="str">
         <v>净买: 8322.30万</v>
       </c>
       <c r="E34">
@@ -11305,40 +11305,40 @@
       <c r="H34">
         <v>0.05</v>
       </c>
-      <c r="I34" s="419">
+      <c r="I34" s="428">
         <v>7.5</v>
       </c>
-      <c r="J34" s="422">
+      <c r="J34" s="417">
         <v>15.33</v>
       </c>
-      <c r="K34" s="425">
+      <c r="K34" s="421">
         <v>19.23</v>
       </c>
-      <c r="L34" s="429">
+      <c r="L34" s="418">
         <v>31.17</v>
       </c>
-      <c r="M34" s="417">
+      <c r="M34" s="424">
         <v>44.28</v>
       </c>
-      <c r="N34" s="423">
+      <c r="N34" s="425">
         <v>53.02</v>
       </c>
-      <c r="O34" s="420">
+      <c r="O34" s="429">
         <v>68.33</v>
       </c>
-      <c r="P34" s="418">
+      <c r="P34" s="426">
         <v>76.16</v>
       </c>
-      <c r="Q34" s="426">
+      <c r="Q34" s="419">
         <v>58.53</v>
       </c>
-      <c r="R34" s="424">
+      <c r="R34" s="422">
         <v>42.67</v>
       </c>
-      <c r="S34" s="427">
+      <c r="S34" s="420">
         <v>30.19</v>
       </c>
-      <c r="T34" s="421">
+      <c r="T34" s="427">
         <v>28.45</v>
       </c>
     </row>
@@ -11352,7 +11352,7 @@
       <c r="C35" t="str">
         <v>002792</v>
       </c>
-      <c r="D35" s="441" t="str">
+      <c r="D35" s="440" t="str">
         <v>净卖: -7684.69万</v>
       </c>
       <c r="E35">
@@ -11367,31 +11367,31 @@
       <c r="H35">
         <v>2.25</v>
       </c>
-      <c r="I35" s="438">
+      <c r="I35" s="441">
         <v>4.92</v>
       </c>
-      <c r="J35" s="439">
+      <c r="J35" s="434">
         <v>8.47</v>
       </c>
-      <c r="K35" s="436">
+      <c r="K35" s="438">
         <v>19.33</v>
       </c>
-      <c r="L35" s="440">
+      <c r="L35" s="442">
         <v>31.26</v>
       </c>
-      <c r="M35" s="442">
+      <c r="M35" s="436">
         <v>39.21</v>
       </c>
-      <c r="N35" s="430">
+      <c r="N35" s="437">
         <v>53.14</v>
       </c>
-      <c r="O35" s="434">
+      <c r="O35" s="430">
         <v>60.26</v>
       </c>
-      <c r="P35" s="437">
+      <c r="P35" s="431">
         <v>44.23</v>
       </c>
-      <c r="Q35" s="431">
+      <c r="Q35" s="435">
         <v>29.8</v>
       </c>
       <c r="R35" s="432">
@@ -11400,7 +11400,7 @@
       <c r="S35" s="433">
         <v>17.43</v>
       </c>
-      <c r="T35" s="435">
+      <c r="T35" s="439">
         <v>16.86</v>
       </c>
     </row>
@@ -11414,7 +11414,7 @@
       <c r="C36" t="str">
         <v>002759</v>
       </c>
-      <c r="D36" s="453" t="str">
+      <c r="D36" s="451" t="str">
         <v>净买: 1.00亿</v>
       </c>
       <c r="E36">
@@ -11429,40 +11429,40 @@
       <c r="H36">
         <v>3.06</v>
       </c>
-      <c r="I36" s="446">
+      <c r="I36" s="449">
         <v>6.73</v>
       </c>
-      <c r="J36" s="447">
+      <c r="J36" s="452">
         <v>7.11</v>
       </c>
-      <c r="K36" s="451">
+      <c r="K36" s="453">
         <v>0.63</v>
       </c>
-      <c r="L36" s="443">
+      <c r="L36" s="445">
         <v>-1.99</v>
       </c>
-      <c r="M36" s="448">
+      <c r="M36" s="446">
         <v>-3.59</v>
       </c>
-      <c r="N36" s="444">
+      <c r="N36" s="447">
         <v>-2.61</v>
       </c>
-      <c r="O36" s="445">
+      <c r="O36" s="454">
         <v>-7.82</v>
       </c>
-      <c r="P36" s="454">
+      <c r="P36" s="455">
         <v>-11.35</v>
       </c>
-      <c r="Q36" s="449">
+      <c r="Q36" s="448">
         <v>-5.64</v>
       </c>
-      <c r="R36" s="455">
+      <c r="R36" s="443">
         <v>-13.61</v>
       </c>
-      <c r="S36" s="450">
+      <c r="S36" s="444">
         <v>-12.5</v>
       </c>
-      <c r="T36" s="452">
+      <c r="T36" s="450">
         <v>-26.5</v>
       </c>
     </row>
@@ -11476,7 +11476,7 @@
       <c r="C37" t="str">
         <v>600776</v>
       </c>
-      <c r="D37" s="458" t="str">
+      <c r="D37" s="461" t="str">
         <v>净买: 5452.75万</v>
       </c>
       <c r="E37">
@@ -11491,40 +11491,40 @@
       <c r="H37">
         <v>10.02</v>
       </c>
-      <c r="I37" s="459">
+      <c r="I37" s="458">
         <v>0</v>
       </c>
-      <c r="J37" s="467">
+      <c r="J37" s="468">
         <v>10</v>
       </c>
       <c r="K37" s="462">
         <v>16.57</v>
       </c>
-      <c r="L37" s="464">
+      <c r="L37" s="463">
         <v>4.91</v>
       </c>
-      <c r="M37" s="465">
+      <c r="M37" s="464">
         <v>-5.58</v>
       </c>
-      <c r="N37" s="466">
+      <c r="N37" s="456">
         <v>-15.01</v>
       </c>
-      <c r="O37" s="468">
+      <c r="O37" s="457">
         <v>-17.91</v>
       </c>
-      <c r="P37" s="460">
+      <c r="P37" s="467">
         <v>-16.93</v>
       </c>
-      <c r="Q37" s="456">
+      <c r="Q37" s="459">
         <v>-15.19</v>
       </c>
-      <c r="R37" s="463">
+      <c r="R37" s="460">
         <v>-10.99</v>
       </c>
-      <c r="S37" s="461">
+      <c r="S37" s="465">
         <v>-15.27</v>
       </c>
-      <c r="T37" s="457">
+      <c r="T37" s="466">
         <v>-25.23</v>
       </c>
     </row>
@@ -11538,7 +11538,7 @@
       <c r="C38" t="str">
         <v>600410</v>
       </c>
-      <c r="D38" s="478" t="str">
+      <c r="D38" s="481" t="str">
         <v>净买: 1.26亿</v>
       </c>
       <c r="E38">
@@ -11553,40 +11553,40 @@
       <c r="H38">
         <v>-1.64</v>
       </c>
-      <c r="I38" s="472">
+      <c r="I38" s="476">
         <v>11.84</v>
       </c>
-      <c r="J38" s="473">
+      <c r="J38" s="477">
         <v>23.02</v>
       </c>
-      <c r="K38" s="474">
+      <c r="K38" s="469">
         <v>10.78</v>
       </c>
       <c r="L38" s="479">
         <v>2.42</v>
       </c>
-      <c r="M38" s="475">
+      <c r="M38" s="470">
         <v>0</v>
       </c>
-      <c r="N38" s="480">
+      <c r="N38" s="474">
         <v>1.86</v>
       </c>
-      <c r="O38" s="481">
+      <c r="O38" s="475">
         <v>2.67</v>
       </c>
-      <c r="P38" s="469">
+      <c r="P38" s="471">
         <v>5.99</v>
       </c>
-      <c r="Q38" s="476">
+      <c r="Q38" s="472">
         <v>0.81</v>
       </c>
-      <c r="R38" s="477">
+      <c r="R38" s="478">
         <v>6.95</v>
       </c>
-      <c r="S38" s="470">
+      <c r="S38" s="480">
         <v>6.25</v>
       </c>
-      <c r="T38" s="471">
+      <c r="T38" s="473">
         <v>45.79</v>
       </c>
     </row>
@@ -11600,7 +11600,7 @@
       <c r="C39" t="str">
         <v>600410</v>
       </c>
-      <c r="D39" s="493" t="str">
+      <c r="D39" s="488" t="str">
         <v>净买: 1.26亿</v>
       </c>
       <c r="E39">
@@ -11615,40 +11615,40 @@
       <c r="H39">
         <v>10</v>
       </c>
-      <c r="I39" s="494">
+      <c r="I39" s="489">
         <v>0</v>
       </c>
       <c r="J39" s="482">
         <v>-9.95</v>
       </c>
-      <c r="K39" s="487">
+      <c r="K39" s="492">
         <v>-16.75</v>
       </c>
-      <c r="L39" s="488">
+      <c r="L39" s="490">
         <v>-18.71</v>
       </c>
-      <c r="M39" s="489">
+      <c r="M39" s="487">
         <v>-17.2</v>
       </c>
-      <c r="N39" s="483">
+      <c r="N39" s="493">
         <v>-16.54</v>
       </c>
-      <c r="O39" s="484">
+      <c r="O39" s="491">
         <v>-13.84</v>
       </c>
-      <c r="P39" s="485">
+      <c r="P39" s="483">
         <v>-18.06</v>
       </c>
-      <c r="Q39" s="486">
+      <c r="Q39" s="484">
         <v>-13.06</v>
       </c>
-      <c r="R39" s="491">
+      <c r="R39" s="494">
         <v>-13.64</v>
       </c>
-      <c r="S39" s="490">
+      <c r="S39" s="485">
         <v>-10.2</v>
       </c>
-      <c r="T39" s="492">
+      <c r="T39" s="486">
         <v>18.51</v>
       </c>
     </row>
@@ -11662,7 +11662,7 @@
       <c r="C40" t="str">
         <v>600776</v>
       </c>
-      <c r="D40" s="505" t="str">
+      <c r="D40" s="502" t="str">
         <v>净卖: -233.39万</v>
       </c>
       <c r="E40">
@@ -11677,40 +11677,40 @@
       <c r="H40">
         <v>-10</v>
       </c>
-      <c r="I40" s="500">
+      <c r="I40" s="497">
         <v>0</v>
       </c>
-      <c r="J40" s="506">
+      <c r="J40" s="498">
         <v>-9.98</v>
       </c>
-      <c r="K40" s="502">
+      <c r="K40" s="503">
         <v>-13.06</v>
       </c>
-      <c r="L40" s="498">
+      <c r="L40" s="499">
         <v>-12.02</v>
       </c>
-      <c r="M40" s="501">
+      <c r="M40" s="507">
         <v>-10.17</v>
       </c>
-      <c r="N40" s="507">
+      <c r="N40" s="500">
         <v>-5.72</v>
       </c>
       <c r="O40" s="495">
         <v>-10.26</v>
       </c>
-      <c r="P40" s="503">
+      <c r="P40" s="506">
         <v>-9.89</v>
       </c>
-      <c r="Q40" s="496">
+      <c r="Q40" s="504">
         <v>-11.26</v>
       </c>
-      <c r="R40" s="497">
+      <c r="R40" s="496">
         <v>-11.78</v>
       </c>
-      <c r="S40" s="499">
+      <c r="S40" s="501">
         <v>-12.49</v>
       </c>
-      <c r="T40" s="504">
+      <c r="T40" s="505">
         <v>-20.81</v>
       </c>
     </row>
@@ -11724,7 +11724,7 @@
       <c r="C41" t="str">
         <v>600410</v>
       </c>
-      <c r="D41" s="520" t="str">
+      <c r="D41" s="515" t="str">
         <v>净卖: -1.30亿</v>
       </c>
       <c r="E41">
@@ -11739,40 +11739,40 @@
       <c r="H41">
         <v>-1.97</v>
       </c>
-      <c r="I41" s="508">
+      <c r="I41" s="509">
         <v>-8.15</v>
       </c>
-      <c r="J41" s="515">
+      <c r="J41" s="513">
         <v>-15.08</v>
       </c>
-      <c r="K41" s="513">
+      <c r="K41" s="518">
         <v>-17.08</v>
       </c>
-      <c r="L41" s="509">
+      <c r="L41" s="519">
         <v>-15.54</v>
       </c>
-      <c r="M41" s="518">
+      <c r="M41" s="516">
         <v>-14.87</v>
       </c>
-      <c r="N41" s="510">
+      <c r="N41" s="514">
         <v>-12.11</v>
       </c>
-      <c r="O41" s="514">
+      <c r="O41" s="520">
         <v>-16.42</v>
       </c>
-      <c r="P41" s="511">
+      <c r="P41" s="517">
         <v>-11.32</v>
       </c>
-      <c r="Q41" s="516">
+      <c r="Q41" s="510">
         <v>-11.9</v>
       </c>
-      <c r="R41" s="512">
+      <c r="R41" s="508">
         <v>-8.4</v>
       </c>
-      <c r="S41" s="517">
+      <c r="S41" s="511">
         <v>-12.24</v>
       </c>
-      <c r="T41" s="519">
+      <c r="T41" s="512">
         <v>20.89</v>
       </c>
     </row>
@@ -11786,7 +11786,7 @@
       <c r="C42" t="str">
         <v>002792</v>
       </c>
-      <c r="D42" s="526" t="str">
+      <c r="D42" s="524" t="str">
         <v>净买: 5153.68万</v>
       </c>
       <c r="E42">
@@ -11801,40 +11801,40 @@
       <c r="H42">
         <v>0.55</v>
       </c>
-      <c r="I42" s="521">
+      <c r="I42" s="530">
         <v>9.39</v>
       </c>
-      <c r="J42" s="527">
+      <c r="J42" s="531">
         <v>15.85</v>
       </c>
-      <c r="K42" s="528">
+      <c r="K42" s="527">
         <v>10.51</v>
       </c>
-      <c r="L42" s="529">
+      <c r="L42" s="525">
         <v>6.31</v>
       </c>
-      <c r="M42" s="522">
+      <c r="M42" s="532">
         <v>1.07</v>
       </c>
-      <c r="N42" s="523">
+      <c r="N42" s="528">
         <v>-1.76</v>
       </c>
-      <c r="O42" s="530">
+      <c r="O42" s="533">
         <v>0.67</v>
       </c>
-      <c r="P42" s="524">
+      <c r="P42" s="521">
         <v>10.74</v>
       </c>
-      <c r="Q42" s="532">
+      <c r="Q42" s="526">
         <v>10.74</v>
       </c>
-      <c r="R42" s="531">
+      <c r="R42" s="529">
         <v>7.46</v>
       </c>
-      <c r="S42" s="525">
+      <c r="S42" s="522">
         <v>7.34</v>
       </c>
-      <c r="T42" s="533">
+      <c r="T42" s="523">
         <v>6.98</v>
       </c>
     </row>
@@ -11897,40 +11897,40 @@
       <c r="F44" t="str"/>
       <c r="G44" t="str"/>
       <c r="H44" t="str"/>
-      <c r="I44" s="538">
+      <c r="I44" s="543">
         <v>65.85</v>
       </c>
-      <c r="J44" s="544">
+      <c r="J44" s="538">
         <v>65.85</v>
       </c>
-      <c r="K44" s="545">
+      <c r="K44" s="540">
         <v>60.98</v>
       </c>
-      <c r="L44" s="541">
+      <c r="L44" s="544">
         <v>56.1</v>
       </c>
-      <c r="M44" s="539">
+      <c r="M44" s="534">
         <v>48.78</v>
       </c>
-      <c r="N44" s="542">
+      <c r="N44" s="535">
         <v>46.34</v>
       </c>
-      <c r="O44" s="534">
+      <c r="O44" s="536">
         <v>48.78</v>
       </c>
-      <c r="P44" s="535">
+      <c r="P44" s="541">
         <v>43.9</v>
       </c>
-      <c r="Q44" s="540">
+      <c r="Q44" s="539">
         <v>39.02</v>
       </c>
-      <c r="R44" s="543">
+      <c r="R44" s="537">
         <v>43.9</v>
       </c>
-      <c r="S44" s="536">
+      <c r="S44" s="545">
         <v>43.9</v>
       </c>
-      <c r="T44" s="537">
+      <c r="T44" s="542">
         <v>31.71</v>
       </c>
     </row>
@@ -11945,40 +11945,40 @@
       <c r="F45" t="str"/>
       <c r="G45" t="str"/>
       <c r="H45" t="str"/>
-      <c r="I45" s="552">
+      <c r="I45" s="550">
         <v>3.79</v>
       </c>
       <c r="J45" s="553">
         <v>5.59</v>
       </c>
-      <c r="K45" s="557">
+      <c r="K45" s="548">
         <v>5.07</v>
       </c>
       <c r="L45" s="549">
         <v>5.23</v>
       </c>
-      <c r="M45" s="548">
+      <c r="M45" s="547">
         <v>5.01</v>
       </c>
-      <c r="N45" s="554">
+      <c r="N45" s="551">
         <v>4.05</v>
       </c>
-      <c r="O45" s="555">
+      <c r="O45" s="552">
         <v>4.42</v>
       </c>
-      <c r="P45" s="550">
+      <c r="P45" s="554">
         <v>3.76</v>
       </c>
-      <c r="Q45" s="551">
+      <c r="Q45" s="555">
         <v>1.74</v>
       </c>
-      <c r="R45" s="546">
+      <c r="R45" s="556">
         <v>1.6</v>
       </c>
-      <c r="S45" s="556">
+      <c r="S45" s="557">
         <v>0.99</v>
       </c>
-      <c r="T45" s="547">
+      <c r="T45" s="546">
         <v>-4.22</v>
       </c>
     </row>

--- a/youzi/越王大道/index.xlsx
+++ b/youzi/越王大道/index.xlsx
@@ -39,30 +39,72 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFB8E1C1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAB1E2C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFC4E7CC"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFED979F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8236"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA91E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF70C483"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFED979F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF218E3B"/>
         <bgColor/>
       </patternFill>
@@ -75,37 +117,175 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1A7230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB8E1C1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA91E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAB1E2C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8236"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDA3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAC1F2C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BDC2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAB1F2C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC32938"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCF0F1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2FAA4B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBECED"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -117,31 +297,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFEFA4AB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD33140"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF3F4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE2E4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC02836"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDE4150"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFACDDB7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBE8EA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBB2634"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -153,43 +375,2977 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFD53241"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED9BA3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7130"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3D4D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC42A38"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7DCA8F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9808A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF67C07B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC969F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC12937"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B2B8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF95D3A3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCA2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDB3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEE9FA6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25866"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFDA3444"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFD2303F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBB2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9DFE1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3B9BF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFDFD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A702F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BFC4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7B33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBEDEE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8437"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E7F35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDE4251"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23953E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE3E5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23943D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8437"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6AC27E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5BBC71"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23943D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCFDFC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBEAEC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208838"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A712F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7B34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC3E6CB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF46B35F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208839"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A443"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218D3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBC2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7FCA90"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5FBD75"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF63BF78"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC52A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23943D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF53B86A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8638"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7E35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23933D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8638"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8738"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7A33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8136"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2DFBC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7CC98E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2FA94B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6DC381"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF46B35F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5EBD74"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF53B86A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8738"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF84CD95"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B2B8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2DFBC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A644"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8638"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF249A3F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77580"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFCFC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6CC280"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77883"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22903C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBF2736"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7CC98E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF95D3A3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BAC0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF99D5A7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6CDD1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9DCDF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFBFB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8337"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B3B9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9858F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24983F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDE4251"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD43140"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196F2F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208839"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC929B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4C4C8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF37AD52"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF54B96B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDEF1E3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46672"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8437"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDE4554"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2CA848"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A544"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6727D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8538"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBB2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3949"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6D0D3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7832"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF37AD52"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6F4E9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAE202D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE35E6B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE35E6B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC32A38"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCEEEF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE04D5B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBB2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7ECA8F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8537"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD63242"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B4BA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCDEAD4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6FBF7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8638"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22923D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC12937"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3847"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB72432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC52A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE5E7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA9DBB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8ED19D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC92C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF64BF79"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8538"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF269F42"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3848"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A042"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEE9DA4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC939B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC72B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B3B9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD1303F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9DEE0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259E41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196D2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8136"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7E35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE3E6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC32938"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAD1F2D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB3E0BD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC12937"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D3D7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7BC98D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBC2635"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD63242"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE4F4E8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A142"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE4F4E8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0DEBA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7BC98D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7BC98D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8437"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBC2635"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9838D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE04F5D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE35D6A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED9BA2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAD1F2D"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -201,559 +3357,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFAB1F2C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC32938"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BDC2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC02836"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD33140"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2FAA4B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDE4150"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFA4AB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE2E4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFECF7EF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF3F4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCF0F1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7130"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBF2836"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9808A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD53241"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED9BA3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7DCA8F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBE8EA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3D4D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC42A38"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFACDDB7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF67C07B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC969F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC62B39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF95D3A3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCA2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDB3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B2B8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3B9BF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEE9FA6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDA3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25866"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFDFD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBB2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9DFE1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD2303F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A702F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7B33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8437"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BFC4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBEDEE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E7F35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE3E5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBEAEC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDE4251"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23943D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8437"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6AC27E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5BBC71"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23943D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCFDFC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23953E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAE202D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC3E6CB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218D3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7B34"/>
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -765,2617 +3369,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208838"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF46B35F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8437"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A712F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A443"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBC2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC52A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7FCA90"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23943D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF37AD52"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF63BF78"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5FBD75"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8638"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8738"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7E35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218D3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8638"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23933D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7A33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8136"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8738"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2DFBC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2FA94B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5EBD74"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6DC381"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B2B8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2DFBC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7CC98E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF46B35F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF53B86A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF84CD95"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77580"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFCFC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6CC280"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8638"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A644"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF249A3F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7CC98E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF95D3A3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBF2736"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77883"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22903C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B3B9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF99D5A7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8337"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6CDD1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9858F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFBFB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9DCDF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BAC0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8538"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDE4251"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196F2F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD43140"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208839"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC929B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4C4C8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF54B96B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF37AD52"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCEEBD5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46672"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8036"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2CA848"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDE4554"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6727D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8538"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A544"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBB2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3949"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7832"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6D0D3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF37AD52"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE35E6B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6F4E9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC32A38"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCEEEF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAE202D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE35E6B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD63242"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCDEAD4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBB2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE04D5B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B4BA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7ECA8F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8537"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22923D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8638"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6FBF7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC12937"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB72432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3847"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA9DBB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF64BF79"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8ED19D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF269F42"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC92C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC52A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE5E7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8538"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3848"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A042"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD1303F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9DEE0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B3B9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC939B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC72B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEE9DA4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259E41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196D2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7E35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8136"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC32938"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC72B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB3E0BD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC12937"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAD1F2D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D3D7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE3E6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE4F4E8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0DEBA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE4F4E8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7BC98D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBC2635"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A142"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD63242"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7BC98D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7631"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBC2635"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9838D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7BC98D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAC1F2C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAD1F2D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE04F5D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE35D6A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED9BA2"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -9306,7 +9306,7 @@
       <c r="C2" t="str">
         <v>002570</v>
       </c>
-      <c r="D2" s="13" t="str">
+      <c r="D2" s="5" t="str">
         <v>净卖: -1602.12万</v>
       </c>
       <c r="E2">
@@ -9324,37 +9324,37 @@
       <c r="I2" s="10">
         <v>9.77</v>
       </c>
-      <c r="J2" s="11">
+      <c r="J2" s="6">
         <v>9.62</v>
       </c>
-      <c r="K2" s="1">
+      <c r="K2" s="7">
         <v>-1.35</v>
       </c>
-      <c r="L2" s="5">
+      <c r="L2" s="12">
         <v>-7.07</v>
       </c>
-      <c r="M2" s="2">
+      <c r="M2" s="11">
         <v>-3.31</v>
       </c>
-      <c r="N2" s="3">
+      <c r="N2" s="8">
         <v>2.56</v>
       </c>
-      <c r="O2" s="6">
+      <c r="O2" s="13">
         <v>9.32</v>
       </c>
-      <c r="P2" s="8">
+      <c r="P2" s="1">
         <v>-1.65</v>
       </c>
-      <c r="Q2" s="9">
+      <c r="Q2" s="3">
         <v>-11.43</v>
       </c>
-      <c r="R2" s="7">
+      <c r="R2" s="4">
         <v>-9.47</v>
       </c>
-      <c r="S2" s="12">
+      <c r="S2" s="9">
         <v>-8.12</v>
       </c>
-      <c r="T2" s="4">
+      <c r="T2" s="2">
         <v>-24.21</v>
       </c>
     </row>
@@ -9368,7 +9368,7 @@
       <c r="C3" t="str">
         <v>002915</v>
       </c>
-      <c r="D3" s="19" t="str">
+      <c r="D3" s="22" t="str">
         <v>净买: 2039.94万</v>
       </c>
       <c r="E3">
@@ -9383,41 +9383,41 @@
       <c r="H3">
         <v>0.12</v>
       </c>
-      <c r="I3" s="20">
+      <c r="I3" s="19">
         <v>5.12</v>
       </c>
-      <c r="J3" s="25">
+      <c r="J3" s="14">
         <v>15.65</v>
       </c>
-      <c r="K3" s="26">
+      <c r="K3" s="15">
         <v>27.2</v>
       </c>
-      <c r="L3" s="17">
+      <c r="L3" s="23">
         <v>27.56</v>
       </c>
-      <c r="M3" s="21">
+      <c r="M3" s="17">
         <v>40.3</v>
       </c>
-      <c r="N3" s="18">
+      <c r="N3" s="24">
         <v>27.68</v>
       </c>
-      <c r="O3" s="14">
+      <c r="O3" s="20">
         <v>30.06</v>
       </c>
-      <c r="P3" s="22">
+      <c r="P3" s="25">
         <v>28.1</v>
       </c>
-      <c r="Q3" s="15">
+      <c r="Q3" s="21">
         <v>36.9</v>
       </c>
-      <c r="R3" s="23">
+      <c r="R3" s="26">
         <v>34.52</v>
       </c>
-      <c r="S3" s="24">
+      <c r="S3" s="18">
         <v>21.07</v>
       </c>
       <c r="T3" s="16">
-        <v>26.67</v>
+        <v>27.8</v>
       </c>
     </row>
     <row r="4">
@@ -9430,7 +9430,7 @@
       <c r="C4" t="str">
         <v>002229</v>
       </c>
-      <c r="D4" s="31" t="str">
+      <c r="D4" s="29" t="str">
         <v>净买: 2135.02万</v>
       </c>
       <c r="E4">
@@ -9445,41 +9445,41 @@
       <c r="H4">
         <v>8.23</v>
       </c>
-      <c r="I4" s="34">
+      <c r="I4" s="30">
         <v>1.62</v>
       </c>
-      <c r="J4" s="32">
+      <c r="J4" s="33">
         <v>11.75</v>
       </c>
-      <c r="K4" s="29">
+      <c r="K4" s="38">
         <v>21.04</v>
       </c>
-      <c r="L4" s="38">
+      <c r="L4" s="34">
         <v>28.15</v>
       </c>
-      <c r="M4" s="35">
+      <c r="M4" s="31">
         <v>15.34</v>
       </c>
-      <c r="N4" s="36">
+      <c r="N4" s="32">
         <v>13.65</v>
       </c>
-      <c r="O4" s="39">
+      <c r="O4" s="36">
         <v>13.02</v>
       </c>
-      <c r="P4" s="33">
+      <c r="P4" s="39">
         <v>7.32</v>
       </c>
       <c r="Q4" s="27">
         <v>9.5</v>
       </c>
-      <c r="R4" s="28">
+      <c r="R4" s="37">
         <v>9.57</v>
       </c>
-      <c r="S4" s="30">
+      <c r="S4" s="28">
         <v>14.22</v>
       </c>
-      <c r="T4" s="37">
-        <v>38.49</v>
+      <c r="T4" s="35">
+        <v>36.38</v>
       </c>
     </row>
     <row r="5">
@@ -9492,7 +9492,7 @@
       <c r="C5" t="str">
         <v>002915</v>
       </c>
-      <c r="D5" s="50" t="str">
+      <c r="D5" s="43" t="str">
         <v>净卖: -2747.73万</v>
       </c>
       <c r="E5">
@@ -9507,41 +9507,41 @@
       <c r="H5">
         <v>9.98</v>
       </c>
-      <c r="I5" s="51">
+      <c r="I5" s="47">
         <v>0</v>
       </c>
-      <c r="J5" s="47">
+      <c r="J5" s="48">
         <v>0.28</v>
       </c>
-      <c r="K5" s="52">
+      <c r="K5" s="49">
         <v>10.29</v>
       </c>
-      <c r="L5" s="48">
+      <c r="L5" s="40">
         <v>0.37</v>
       </c>
       <c r="M5" s="44">
         <v>2.25</v>
       </c>
-      <c r="N5" s="45">
+      <c r="N5" s="50">
         <v>0.7</v>
       </c>
-      <c r="O5" s="40">
+      <c r="O5" s="51">
         <v>7.63</v>
       </c>
-      <c r="P5" s="41">
+      <c r="P5" s="45">
         <v>5.76</v>
       </c>
-      <c r="Q5" s="42">
+      <c r="Q5" s="41">
         <v>-4.82</v>
       </c>
-      <c r="R5" s="43">
+      <c r="R5" s="52">
         <v>4.68</v>
       </c>
-      <c r="S5" s="49">
+      <c r="S5" s="46">
         <v>11</v>
       </c>
-      <c r="T5" s="46">
-        <v>-0.42</v>
+      <c r="T5" s="42">
+        <v>0.47</v>
       </c>
     </row>
     <row r="6">
@@ -9554,7 +9554,7 @@
       <c r="C6" t="str">
         <v>002177</v>
       </c>
-      <c r="D6" s="62" t="str">
+      <c r="D6" s="56" t="str">
         <v>净买: 3117.92万</v>
       </c>
       <c r="E6">
@@ -9569,41 +9569,41 @@
       <c r="H6">
         <v>5.02</v>
       </c>
-      <c r="I6" s="63">
+      <c r="I6" s="60">
         <v>4.78</v>
       </c>
-      <c r="J6" s="59">
+      <c r="J6" s="65">
         <v>10.79</v>
       </c>
-      <c r="K6" s="64">
+      <c r="K6" s="61">
         <v>7.24</v>
       </c>
-      <c r="L6" s="60">
+      <c r="L6" s="62">
         <v>12.3</v>
       </c>
-      <c r="M6" s="56">
+      <c r="M6" s="57">
         <v>5.6</v>
       </c>
-      <c r="N6" s="57">
+      <c r="N6" s="58">
         <v>2.46</v>
       </c>
-      <c r="O6" s="65">
+      <c r="O6" s="53">
         <v>-1.91</v>
       </c>
-      <c r="P6" s="53">
+      <c r="P6" s="59">
         <v>-9.56</v>
       </c>
-      <c r="Q6" s="58">
+      <c r="Q6" s="63">
         <v>-3.01</v>
       </c>
-      <c r="R6" s="61">
+      <c r="R6" s="54">
         <v>0.55</v>
       </c>
-      <c r="S6" s="55">
+      <c r="S6" s="64">
         <v>3.14</v>
       </c>
-      <c r="T6" s="54">
-        <v>7.65</v>
+      <c r="T6" s="55">
+        <v>8.06</v>
       </c>
     </row>
     <row r="7">
@@ -9616,7 +9616,7 @@
       <c r="C7" t="str">
         <v>002177</v>
       </c>
-      <c r="D7" s="74" t="str">
+      <c r="D7" s="73" t="str">
         <v>净卖: -2852.77万</v>
       </c>
       <c r="E7">
@@ -9631,41 +9631,41 @@
       <c r="H7">
         <v>-4.04</v>
       </c>
-      <c r="I7" s="69">
+      <c r="I7" s="70">
         <v>10.19</v>
       </c>
-      <c r="J7" s="75">
+      <c r="J7" s="77">
         <v>6.66</v>
       </c>
-      <c r="K7" s="78">
+      <c r="K7" s="74">
         <v>11.68</v>
       </c>
-      <c r="L7" s="76">
+      <c r="L7" s="78">
         <v>5.03</v>
       </c>
-      <c r="M7" s="77">
+      <c r="M7" s="75">
         <v>1.9</v>
       </c>
-      <c r="N7" s="70">
+      <c r="N7" s="76">
         <v>-2.45</v>
       </c>
-      <c r="O7" s="71">
+      <c r="O7" s="68">
         <v>-10.05</v>
       </c>
       <c r="P7" s="66">
         <v>-3.53</v>
       </c>
-      <c r="Q7" s="72">
+      <c r="Q7" s="67">
         <v>0</v>
       </c>
-      <c r="R7" s="67">
+      <c r="R7" s="69">
         <v>2.58</v>
       </c>
-      <c r="S7" s="73">
+      <c r="S7" s="71">
         <v>-5.3</v>
       </c>
-      <c r="T7" s="68">
-        <v>7.07</v>
+      <c r="T7" s="72">
+        <v>7.47</v>
       </c>
     </row>
     <row r="8">
@@ -9678,7 +9678,7 @@
       <c r="C8" t="str">
         <v>002882</v>
       </c>
-      <c r="D8" s="88" t="str">
+      <c r="D8" s="83" t="str">
         <v>净卖: -1459.92万</v>
       </c>
       <c r="E8">
@@ -9693,41 +9693,41 @@
       <c r="H8">
         <v>-0.92</v>
       </c>
-      <c r="I8" s="89">
+      <c r="I8" s="81">
         <v>11.01</v>
       </c>
-      <c r="J8" s="80">
+      <c r="J8" s="84">
         <v>11.21</v>
       </c>
-      <c r="K8" s="81">
+      <c r="K8" s="90">
         <v>1.71</v>
       </c>
-      <c r="L8" s="84">
+      <c r="L8" s="82">
         <v>4.11</v>
       </c>
-      <c r="M8" s="85">
+      <c r="M8" s="91">
         <v>0.04</v>
       </c>
-      <c r="N8" s="90">
+      <c r="N8" s="88">
         <v>0.78</v>
       </c>
-      <c r="O8" s="82">
+      <c r="O8" s="79">
         <v>2.37</v>
       </c>
-      <c r="P8" s="83">
+      <c r="P8" s="85">
         <v>5.12</v>
       </c>
-      <c r="Q8" s="91">
+      <c r="Q8" s="86">
         <v>5.93</v>
       </c>
-      <c r="R8" s="86">
+      <c r="R8" s="87">
         <v>8.07</v>
       </c>
-      <c r="S8" s="87">
+      <c r="S8" s="80">
         <v>18.88</v>
       </c>
-      <c r="T8" s="79">
-        <v>18.88</v>
+      <c r="T8" s="89">
+        <v>15.01</v>
       </c>
     </row>
     <row r="9">
@@ -9740,7 +9740,7 @@
       <c r="C9" t="str">
         <v>003029</v>
       </c>
-      <c r="D9" s="92" t="str">
+      <c r="D9" s="96" t="str">
         <v>净卖: -276.02万</v>
       </c>
       <c r="E9">
@@ -9755,41 +9755,41 @@
       <c r="H9">
         <v>10.01</v>
       </c>
-      <c r="I9" s="100">
+      <c r="I9" s="93">
         <v>0</v>
       </c>
-      <c r="J9" s="102">
+      <c r="J9" s="94">
         <v>10.01</v>
       </c>
-      <c r="K9" s="98">
+      <c r="K9" s="97">
         <v>1.58</v>
       </c>
-      <c r="L9" s="103">
+      <c r="L9" s="99">
         <v>0.44</v>
       </c>
-      <c r="M9" s="93">
+      <c r="M9" s="95">
         <v>-9.6</v>
       </c>
-      <c r="N9" s="101">
+      <c r="N9" s="103">
         <v>-14.15</v>
       </c>
-      <c r="O9" s="94">
+      <c r="O9" s="100">
         <v>-11.05</v>
       </c>
-      <c r="P9" s="95">
+      <c r="P9" s="98">
         <v>-8.72</v>
       </c>
-      <c r="Q9" s="99">
+      <c r="Q9" s="101">
         <v>-7.3</v>
       </c>
       <c r="R9" s="104">
         <v>-8.31</v>
       </c>
-      <c r="S9" s="96">
+      <c r="S9" s="102">
         <v>-7.9</v>
       </c>
-      <c r="T9" s="97">
-        <v>-31.93</v>
+      <c r="T9" s="92">
+        <v>-31.87</v>
       </c>
     </row>
     <row r="10">
@@ -9802,7 +9802,7 @@
       <c r="C10" t="str">
         <v>002017</v>
       </c>
-      <c r="D10" s="117" t="str">
+      <c r="D10" s="109" t="str">
         <v>净买: 6518.56万</v>
       </c>
       <c r="E10">
@@ -9817,41 +9817,41 @@
       <c r="H10">
         <v>5.13</v>
       </c>
-      <c r="I10" s="107">
+      <c r="I10" s="105">
         <v>4.66</v>
       </c>
-      <c r="J10" s="114">
+      <c r="J10" s="116">
         <v>-0.06</v>
       </c>
-      <c r="K10" s="108">
+      <c r="K10" s="110">
         <v>-6.53</v>
       </c>
-      <c r="L10" s="109">
+      <c r="L10" s="111">
         <v>-5.79</v>
       </c>
-      <c r="M10" s="110">
+      <c r="M10" s="112">
         <v>-7.89</v>
       </c>
-      <c r="N10" s="111">
+      <c r="N10" s="113">
         <v>-3.46</v>
       </c>
-      <c r="O10" s="105">
+      <c r="O10" s="107">
         <v>0.68</v>
       </c>
-      <c r="P10" s="106">
+      <c r="P10" s="117">
         <v>0.51</v>
       </c>
-      <c r="Q10" s="115">
+      <c r="Q10" s="106">
         <v>-6.47</v>
       </c>
-      <c r="R10" s="112">
+      <c r="R10" s="114">
         <v>-3.8</v>
       </c>
-      <c r="S10" s="113">
+      <c r="S10" s="115">
         <v>-6.53</v>
       </c>
-      <c r="T10" s="116">
-        <v>9.31</v>
+      <c r="T10" s="108">
+        <v>10.39</v>
       </c>
     </row>
     <row r="11">
@@ -9864,7 +9864,7 @@
       <c r="C11" t="str">
         <v>002670</v>
       </c>
-      <c r="D11" s="122" t="str">
+      <c r="D11" s="123" t="str">
         <v>净卖: -2720.58万</v>
       </c>
       <c r="E11">
@@ -9879,41 +9879,41 @@
       <c r="H11">
         <v>-0.81</v>
       </c>
-      <c r="I11" s="130">
+      <c r="I11" s="129">
         <v>-5.23</v>
       </c>
-      <c r="J11" s="118">
+      <c r="J11" s="124">
         <v>-1.39</v>
       </c>
-      <c r="K11" s="128">
+      <c r="K11" s="121">
         <v>-9.57</v>
       </c>
-      <c r="L11" s="119">
+      <c r="L11" s="130">
         <v>-7.18</v>
       </c>
-      <c r="M11" s="123">
+      <c r="M11" s="118">
         <v>-7.62</v>
       </c>
-      <c r="N11" s="120">
+      <c r="N11" s="122">
         <v>-8.69</v>
       </c>
-      <c r="O11" s="129">
+      <c r="O11" s="125">
         <v>-7.37</v>
       </c>
-      <c r="P11" s="124">
+      <c r="P11" s="126">
         <v>-8.56</v>
       </c>
-      <c r="Q11" s="121">
+      <c r="Q11" s="119">
         <v>-8.63</v>
       </c>
-      <c r="R11" s="125">
+      <c r="R11" s="127">
         <v>-4.28</v>
       </c>
-      <c r="S11" s="126">
+      <c r="S11" s="120">
         <v>-8.56</v>
       </c>
-      <c r="T11" s="127">
-        <v>-7.93</v>
+      <c r="T11" s="128">
+        <v>-7.56</v>
       </c>
     </row>
     <row r="12">
@@ -9926,7 +9926,7 @@
       <c r="C12" t="str">
         <v>002579</v>
       </c>
-      <c r="D12" s="131" t="str">
+      <c r="D12" s="143" t="str">
         <v>净买: 4403.72万</v>
       </c>
       <c r="E12">
@@ -9941,41 +9941,41 @@
       <c r="H12">
         <v>-2.68</v>
       </c>
-      <c r="I12" s="139">
+      <c r="I12" s="137">
         <v>13.04</v>
       </c>
-      <c r="J12" s="132">
+      <c r="J12" s="131">
         <v>12.54</v>
       </c>
-      <c r="K12" s="133">
+      <c r="K12" s="132">
         <v>7.97</v>
       </c>
-      <c r="L12" s="134">
+      <c r="L12" s="133">
         <v>12.54</v>
       </c>
-      <c r="M12" s="135">
+      <c r="M12" s="139">
         <v>7.1</v>
       </c>
-      <c r="N12" s="141">
+      <c r="N12" s="138">
         <v>-3.62</v>
       </c>
-      <c r="O12" s="136">
+      <c r="O12" s="134">
         <v>-2.97</v>
       </c>
-      <c r="P12" s="142">
+      <c r="P12" s="141">
         <v>-5.36</v>
       </c>
-      <c r="Q12" s="143">
+      <c r="Q12" s="135">
         <v>-3.7</v>
       </c>
-      <c r="R12" s="140">
+      <c r="R12" s="136">
         <v>-10.07</v>
       </c>
-      <c r="S12" s="137">
+      <c r="S12" s="140">
         <v>-6.59</v>
       </c>
-      <c r="T12" s="138">
-        <v>-4.64</v>
+      <c r="T12" s="142">
+        <v>-3.99</v>
       </c>
     </row>
     <row r="13">
@@ -9988,7 +9988,7 @@
       <c r="C13" t="str">
         <v>002229</v>
       </c>
-      <c r="D13" s="152" t="str">
+      <c r="D13" s="144" t="str">
         <v>净卖: -4629.75万</v>
       </c>
       <c r="E13">
@@ -10006,38 +10006,38 @@
       <c r="I13" s="153">
         <v>-7.78</v>
       </c>
-      <c r="J13" s="148">
+      <c r="J13" s="149">
         <v>-8.44</v>
       </c>
-      <c r="K13" s="149">
+      <c r="K13" s="154">
         <v>-11.23</v>
       </c>
-      <c r="L13" s="150">
+      <c r="L13" s="151">
         <v>-12.22</v>
       </c>
-      <c r="M13" s="144">
+      <c r="M13" s="145">
         <v>-10.66</v>
       </c>
-      <c r="N13" s="154">
+      <c r="N13" s="150">
         <v>-6.65</v>
       </c>
-      <c r="O13" s="145">
+      <c r="O13" s="146">
         <v>-7.74</v>
       </c>
-      <c r="P13" s="146">
+      <c r="P13" s="155">
         <v>-7.69</v>
       </c>
-      <c r="Q13" s="155">
+      <c r="Q13" s="156">
         <v>-11.37</v>
       </c>
       <c r="R13" s="147">
         <v>-10.8</v>
       </c>
-      <c r="S13" s="156">
+      <c r="S13" s="152">
         <v>-13.68</v>
       </c>
-      <c r="T13" s="151">
-        <v>-7.17</v>
+      <c r="T13" s="148">
+        <v>-8.58</v>
       </c>
     </row>
     <row r="14">
@@ -10050,7 +10050,7 @@
       <c r="C14" t="str">
         <v>000657</v>
       </c>
-      <c r="D14" s="162" t="str">
+      <c r="D14" s="161" t="str">
         <v>净卖: -6184.73万</v>
       </c>
       <c r="E14">
@@ -10065,41 +10065,41 @@
       <c r="H14">
         <v>-2</v>
       </c>
-      <c r="I14" s="165">
+      <c r="I14" s="169">
         <v>-8.16</v>
       </c>
-      <c r="J14" s="160">
+      <c r="J14" s="166">
         <v>-13.48</v>
       </c>
-      <c r="K14" s="167">
+      <c r="K14" s="157">
         <v>-14.93</v>
       </c>
-      <c r="L14" s="161">
+      <c r="L14" s="162">
         <v>-15.36</v>
       </c>
-      <c r="M14" s="166">
+      <c r="M14" s="158">
         <v>-15.2</v>
       </c>
       <c r="N14" s="163">
         <v>-13.43</v>
       </c>
-      <c r="O14" s="168">
+      <c r="O14" s="167">
         <v>-13.1</v>
       </c>
-      <c r="P14" s="169">
+      <c r="P14" s="159">
         <v>-11.6</v>
       </c>
       <c r="Q14" s="164">
         <v>-10.74</v>
       </c>
-      <c r="R14" s="157">
+      <c r="R14" s="165">
         <v>-10.9</v>
       </c>
-      <c r="S14" s="158">
+      <c r="S14" s="168">
         <v>-8.81</v>
       </c>
-      <c r="T14" s="159">
-        <v>201.4</v>
+      <c r="T14" s="160">
+        <v>214.39</v>
       </c>
     </row>
     <row r="15">
@@ -10112,7 +10112,7 @@
       <c r="C15" t="str">
         <v>002670</v>
       </c>
-      <c r="D15" s="182" t="str">
+      <c r="D15" s="176" t="str">
         <v>净卖: -7597.74万</v>
       </c>
       <c r="E15">
@@ -10127,41 +10127,41 @@
       <c r="H15">
         <v>0.45</v>
       </c>
-      <c r="I15" s="176">
+      <c r="I15" s="181">
         <v>1.89</v>
       </c>
-      <c r="J15" s="172">
+      <c r="J15" s="182">
         <v>-1.79</v>
       </c>
-      <c r="K15" s="177">
+      <c r="K15" s="170">
         <v>-1.79</v>
       </c>
-      <c r="L15" s="178">
+      <c r="L15" s="171">
         <v>-3.03</v>
       </c>
-      <c r="M15" s="173">
+      <c r="M15" s="172">
         <v>-4.83</v>
       </c>
-      <c r="N15" s="174">
+      <c r="N15" s="175">
         <v>-3.73</v>
       </c>
-      <c r="O15" s="175">
+      <c r="O15" s="173">
         <v>-3.38</v>
       </c>
-      <c r="P15" s="179">
+      <c r="P15" s="174">
         <v>-4.28</v>
       </c>
-      <c r="Q15" s="170">
+      <c r="Q15" s="178">
         <v>-7.71</v>
       </c>
-      <c r="R15" s="180">
+      <c r="R15" s="177">
         <v>-3.98</v>
       </c>
-      <c r="S15" s="181">
+      <c r="S15" s="179">
         <v>-2.84</v>
       </c>
-      <c r="T15" s="171">
-        <v>-27.26</v>
+      <c r="T15" s="180">
+        <v>-26.97</v>
       </c>
     </row>
     <row r="16">
@@ -10174,7 +10174,7 @@
       <c r="C16" t="str">
         <v>688039</v>
       </c>
-      <c r="D16" s="183" t="str">
+      <c r="D16" s="192" t="str">
         <v>净买: 3066.00万</v>
       </c>
       <c r="E16">
@@ -10189,41 +10189,41 @@
       <c r="H16">
         <v>7.16</v>
       </c>
-      <c r="I16" s="190">
+      <c r="I16" s="189">
         <v>11.98</v>
       </c>
-      <c r="J16" s="188">
+      <c r="J16" s="190">
         <v>16.69</v>
       </c>
-      <c r="K16" s="184">
+      <c r="K16" s="191">
         <v>3.41</v>
       </c>
-      <c r="L16" s="185">
+      <c r="L16" s="193">
         <v>0.07</v>
       </c>
-      <c r="M16" s="191">
+      <c r="M16" s="194">
         <v>-5.26</v>
       </c>
-      <c r="N16" s="186">
+      <c r="N16" s="195">
         <v>-3.41</v>
       </c>
-      <c r="O16" s="192">
+      <c r="O16" s="185">
         <v>-5.04</v>
       </c>
-      <c r="P16" s="193">
+      <c r="P16" s="184">
         <v>-10.52</v>
       </c>
-      <c r="Q16" s="187">
+      <c r="Q16" s="186">
         <v>-7.78</v>
       </c>
-      <c r="R16" s="194">
+      <c r="R16" s="187">
         <v>-6.1</v>
       </c>
-      <c r="S16" s="189">
+      <c r="S16" s="188">
         <v>-7.34</v>
       </c>
-      <c r="T16" s="195">
-        <v>-20.42</v>
+      <c r="T16" s="183">
+        <v>-19.45</v>
       </c>
     </row>
     <row r="17">
@@ -10236,7 +10236,7 @@
       <c r="C17" t="str">
         <v>600408</v>
       </c>
-      <c r="D17" s="205" t="str">
+      <c r="D17" s="200" t="str">
         <v>净买: 1877.05万</v>
       </c>
       <c r="E17">
@@ -10251,41 +10251,41 @@
       <c r="H17">
         <v>-4.45</v>
       </c>
-      <c r="I17" s="196">
+      <c r="I17" s="201">
         <v>15.2</v>
       </c>
-      <c r="J17" s="197">
+      <c r="J17" s="202">
         <v>26.72</v>
       </c>
-      <c r="K17" s="198">
+      <c r="K17" s="204">
         <v>39.46</v>
       </c>
       <c r="L17" s="203">
         <v>53.43</v>
       </c>
-      <c r="M17" s="201">
+      <c r="M17" s="205">
         <v>68.87</v>
       </c>
-      <c r="N17" s="206">
+      <c r="N17" s="197">
         <v>52.7</v>
       </c>
-      <c r="O17" s="204">
+      <c r="O17" s="206">
         <v>37.5</v>
       </c>
-      <c r="P17" s="199">
+      <c r="P17" s="207">
         <v>24.26</v>
       </c>
-      <c r="Q17" s="200">
+      <c r="Q17" s="208">
         <v>14.95</v>
       </c>
-      <c r="R17" s="202">
+      <c r="R17" s="198">
         <v>10.54</v>
       </c>
-      <c r="S17" s="207">
+      <c r="S17" s="199">
         <v>11.52</v>
       </c>
-      <c r="T17" s="208">
-        <v>-23.28</v>
+      <c r="T17" s="196">
+        <v>-22.3</v>
       </c>
     </row>
     <row r="18">
@@ -10298,7 +10298,7 @@
       <c r="C18" t="str">
         <v>601566</v>
       </c>
-      <c r="D18" s="216" t="str">
+      <c r="D18" s="219" t="str">
         <v>净买: 5226.66万</v>
       </c>
       <c r="E18">
@@ -10313,16 +10313,16 @@
       <c r="H18">
         <v>10.02</v>
       </c>
-      <c r="I18" s="210">
+      <c r="I18" s="220">
         <v>0</v>
       </c>
-      <c r="J18" s="211">
+      <c r="J18" s="221">
         <v>9.97</v>
       </c>
-      <c r="K18" s="217">
+      <c r="K18" s="209">
         <v>20.95</v>
       </c>
-      <c r="L18" s="218">
+      <c r="L18" s="217">
         <v>33.02</v>
       </c>
       <c r="M18" s="214">
@@ -10331,23 +10331,23 @@
       <c r="N18" s="215">
         <v>7.73</v>
       </c>
-      <c r="O18" s="219">
+      <c r="O18" s="210">
         <v>3.32</v>
       </c>
-      <c r="P18" s="220">
+      <c r="P18" s="212">
         <v>-5.35</v>
       </c>
-      <c r="Q18" s="221">
+      <c r="Q18" s="211">
         <v>-6.94</v>
       </c>
-      <c r="R18" s="209">
+      <c r="R18" s="216">
         <v>-3.03</v>
       </c>
-      <c r="S18" s="212">
+      <c r="S18" s="218">
         <v>-2.46</v>
       </c>
       <c r="T18" s="213">
-        <v>-22.83</v>
+        <v>-21.82</v>
       </c>
     </row>
     <row r="19">
@@ -10360,7 +10360,7 @@
       <c r="C19" t="str">
         <v>002029</v>
       </c>
-      <c r="D19" s="227" t="str">
+      <c r="D19" s="224" t="str">
         <v>净卖: -1276.40万</v>
       </c>
       <c r="E19">
@@ -10375,41 +10375,41 @@
       <c r="H19">
         <v>0</v>
       </c>
-      <c r="I19" s="223">
+      <c r="I19" s="230">
         <v>9.97</v>
       </c>
-      <c r="J19" s="224">
+      <c r="J19" s="233">
         <v>1.88</v>
       </c>
-      <c r="K19" s="225">
+      <c r="K19" s="223">
         <v>-2.35</v>
       </c>
-      <c r="L19" s="226">
+      <c r="L19" s="225">
         <v>-9.97</v>
       </c>
-      <c r="M19" s="222">
+      <c r="M19" s="226">
         <v>-11.67</v>
       </c>
-      <c r="N19" s="228">
+      <c r="N19" s="231">
         <v>-8</v>
       </c>
-      <c r="O19" s="229">
+      <c r="O19" s="227">
         <v>1.22</v>
       </c>
-      <c r="P19" s="232">
+      <c r="P19" s="228">
         <v>0.85</v>
       </c>
-      <c r="Q19" s="230">
+      <c r="Q19" s="234">
         <v>3.01</v>
       </c>
-      <c r="R19" s="233">
+      <c r="R19" s="222">
         <v>1.69</v>
       </c>
-      <c r="S19" s="231">
+      <c r="S19" s="229">
         <v>0.09</v>
       </c>
-      <c r="T19" s="234">
-        <v>-7.81</v>
+      <c r="T19" s="232">
+        <v>-7.34</v>
       </c>
     </row>
     <row r="20">
@@ -10422,7 +10422,7 @@
       <c r="C20" t="str">
         <v>601566</v>
       </c>
-      <c r="D20" s="240" t="str">
+      <c r="D20" s="244" t="str">
         <v>净卖: -2737.55万</v>
       </c>
       <c r="E20">
@@ -10437,41 +10437,41 @@
       <c r="H20">
         <v>4.01</v>
       </c>
-      <c r="I20" s="241">
+      <c r="I20" s="245">
         <v>5.75</v>
       </c>
-      <c r="J20" s="245">
+      <c r="J20" s="237">
         <v>16.3</v>
       </c>
-      <c r="K20" s="235">
+      <c r="K20" s="239">
         <v>4.67</v>
       </c>
-      <c r="L20" s="242">
+      <c r="L20" s="246">
         <v>-5.81</v>
       </c>
-      <c r="M20" s="236">
+      <c r="M20" s="247">
         <v>-9.67</v>
       </c>
-      <c r="N20" s="246">
+      <c r="N20" s="242">
         <v>-17.25</v>
       </c>
-      <c r="O20" s="243">
+      <c r="O20" s="235">
         <v>-18.64</v>
       </c>
-      <c r="P20" s="244">
+      <c r="P20" s="240">
         <v>-15.22</v>
       </c>
-      <c r="Q20" s="239">
+      <c r="Q20" s="243">
         <v>-14.72</v>
       </c>
-      <c r="R20" s="237">
+      <c r="R20" s="236">
         <v>-10.8</v>
       </c>
       <c r="S20" s="238">
         <v>-6.19</v>
       </c>
-      <c r="T20" s="247">
-        <v>-32.53</v>
+      <c r="T20" s="241">
+        <v>-31.65</v>
       </c>
     </row>
     <row r="21">
@@ -10484,7 +10484,7 @@
       <c r="C21" t="str">
         <v>601566</v>
       </c>
-      <c r="D21" s="248" t="str">
+      <c r="D21" s="254" t="str">
         <v>净卖: -5218.09万</v>
       </c>
       <c r="E21">
@@ -10499,41 +10499,41 @@
       <c r="H21">
         <v>7.11</v>
       </c>
-      <c r="I21" s="257">
+      <c r="I21" s="253">
         <v>2.68</v>
       </c>
-      <c r="J21" s="255">
+      <c r="J21" s="251">
         <v>-7.59</v>
       </c>
-      <c r="K21" s="249">
+      <c r="K21" s="258">
         <v>-16.84</v>
       </c>
-      <c r="L21" s="250">
+      <c r="L21" s="255">
         <v>-20.25</v>
       </c>
-      <c r="M21" s="259">
+      <c r="M21" s="256">
         <v>-26.94</v>
       </c>
-      <c r="N21" s="251">
+      <c r="N21" s="259">
         <v>-28.17</v>
       </c>
       <c r="O21" s="252">
         <v>-25.15</v>
       </c>
-      <c r="P21" s="258">
+      <c r="P21" s="257">
         <v>-24.71</v>
       </c>
-      <c r="Q21" s="253">
+      <c r="Q21" s="260">
         <v>-21.25</v>
       </c>
-      <c r="R21" s="254">
+      <c r="R21" s="248">
         <v>-17.18</v>
       </c>
-      <c r="S21" s="260">
+      <c r="S21" s="249">
         <v>-25.43</v>
       </c>
-      <c r="T21" s="256">
-        <v>-40.44</v>
+      <c r="T21" s="250">
+        <v>-39.65</v>
       </c>
     </row>
     <row r="22">
@@ -10546,7 +10546,7 @@
       <c r="C22" t="str">
         <v>600756</v>
       </c>
-      <c r="D22" s="271" t="str">
+      <c r="D22" s="272" t="str">
         <v>净卖: -2369.10万</v>
       </c>
       <c r="E22">
@@ -10561,41 +10561,41 @@
       <c r="H22">
         <v>-1.6</v>
       </c>
-      <c r="I22" s="263">
+      <c r="I22" s="268">
         <v>1.46</v>
       </c>
-      <c r="J22" s="272">
+      <c r="J22" s="271">
         <v>-4.63</v>
       </c>
-      <c r="K22" s="266">
+      <c r="K22" s="273">
         <v>-3.97</v>
       </c>
-      <c r="L22" s="267">
+      <c r="L22" s="269">
         <v>-13.57</v>
       </c>
-      <c r="M22" s="264">
+      <c r="M22" s="265">
         <v>-21.09</v>
       </c>
-      <c r="N22" s="268">
+      <c r="N22" s="261">
         <v>-19.75</v>
       </c>
-      <c r="O22" s="273">
+      <c r="O22" s="262">
         <v>-18.25</v>
       </c>
-      <c r="P22" s="261">
+      <c r="P22" s="270">
         <v>-20.84</v>
       </c>
-      <c r="Q22" s="269">
+      <c r="Q22" s="266">
         <v>-21.42</v>
       </c>
-      <c r="R22" s="262">
+      <c r="R22" s="263">
         <v>-23.17</v>
       </c>
-      <c r="S22" s="265">
+      <c r="S22" s="264">
         <v>-24.43</v>
       </c>
-      <c r="T22" s="270">
-        <v>-31.15</v>
+      <c r="T22" s="267">
+        <v>-29.94</v>
       </c>
     </row>
     <row r="23">
@@ -10626,38 +10626,38 @@
       <c r="I23" s="274">
         <v>0</v>
       </c>
-      <c r="J23" s="280">
+      <c r="J23" s="276">
         <v>10.01</v>
       </c>
-      <c r="K23" s="281">
+      <c r="K23" s="277">
         <v>21.01</v>
       </c>
-      <c r="L23" s="282">
+      <c r="L23" s="278">
         <v>33.13</v>
       </c>
-      <c r="M23" s="283">
+      <c r="M23" s="279">
         <v>46.43</v>
       </c>
-      <c r="N23" s="279">
+      <c r="N23" s="283">
         <v>43.01</v>
       </c>
-      <c r="O23" s="275">
+      <c r="O23" s="284">
         <v>28.71</v>
       </c>
-      <c r="P23" s="276">
+      <c r="P23" s="285">
         <v>24.74</v>
       </c>
-      <c r="Q23" s="284">
+      <c r="Q23" s="280">
         <v>27.91</v>
       </c>
-      <c r="R23" s="277">
+      <c r="R23" s="281">
         <v>40.71</v>
       </c>
-      <c r="S23" s="285">
+      <c r="S23" s="282">
         <v>26.66</v>
       </c>
-      <c r="T23" s="278">
-        <v>-1.12</v>
+      <c r="T23" s="275">
+        <v>-0.75</v>
       </c>
     </row>
     <row r="24">
@@ -10670,7 +10670,7 @@
       <c r="C24" t="str">
         <v>002682</v>
       </c>
-      <c r="D24" s="292" t="str">
+      <c r="D24" s="291" t="str">
         <v>净买: 2499.06万</v>
       </c>
       <c r="E24">
@@ -10685,41 +10685,41 @@
       <c r="H24">
         <v>5.99</v>
       </c>
-      <c r="I24" s="299">
+      <c r="I24" s="292">
         <v>3.77</v>
       </c>
-      <c r="J24" s="287">
+      <c r="J24" s="299">
         <v>14.2</v>
       </c>
-      <c r="K24" s="288">
+      <c r="K24" s="295">
         <v>25.65</v>
       </c>
-      <c r="L24" s="297">
+      <c r="L24" s="293">
         <v>38.26</v>
       </c>
-      <c r="M24" s="289">
+      <c r="M24" s="287">
         <v>52.03</v>
       </c>
-      <c r="N24" s="293">
+      <c r="N24" s="288">
         <v>42.9</v>
       </c>
-      <c r="O24" s="290">
+      <c r="O24" s="289">
         <v>57.25</v>
       </c>
       <c r="P24" s="294">
         <v>72.9</v>
       </c>
-      <c r="Q24" s="295">
+      <c r="Q24" s="296">
         <v>55.65</v>
       </c>
-      <c r="R24" s="296">
+      <c r="R24" s="297">
         <v>40.14</v>
       </c>
-      <c r="S24" s="291">
+      <c r="S24" s="290">
         <v>42.75</v>
       </c>
       <c r="T24" s="298">
-        <v>-13.91</v>
+        <v>-12.75</v>
       </c>
     </row>
     <row r="25">
@@ -10732,7 +10732,7 @@
       <c r="C25" t="str">
         <v>603696</v>
       </c>
-      <c r="D25" s="301" t="str">
+      <c r="D25" s="306" t="str">
         <v>净卖: -1913.63万</v>
       </c>
       <c r="E25">
@@ -10747,41 +10747,41 @@
       <c r="H25">
         <v>-2.03</v>
       </c>
-      <c r="I25" s="309">
+      <c r="I25" s="312">
         <v>12.28</v>
       </c>
-      <c r="J25" s="300">
+      <c r="J25" s="307">
         <v>23.53</v>
       </c>
-      <c r="K25" s="310">
+      <c r="K25" s="302">
         <v>35.87</v>
       </c>
-      <c r="L25" s="311">
+      <c r="L25" s="308">
         <v>32.7</v>
       </c>
-      <c r="M25" s="306">
+      <c r="M25" s="303">
         <v>19.43</v>
       </c>
-      <c r="N25" s="302">
+      <c r="N25" s="300">
         <v>15.74</v>
       </c>
-      <c r="O25" s="303">
+      <c r="O25" s="304">
         <v>18.69</v>
       </c>
-      <c r="P25" s="307">
+      <c r="P25" s="309">
         <v>30.57</v>
       </c>
-      <c r="Q25" s="304">
+      <c r="Q25" s="305">
         <v>17.53</v>
       </c>
-      <c r="R25" s="308">
+      <c r="R25" s="310">
         <v>10.73</v>
       </c>
-      <c r="S25" s="312">
+      <c r="S25" s="311">
         <v>16.49</v>
       </c>
-      <c r="T25" s="305">
-        <v>-8.25</v>
+      <c r="T25" s="301">
+        <v>-7.9</v>
       </c>
     </row>
     <row r="26">
@@ -10794,7 +10794,7 @@
       <c r="C26" t="str">
         <v>603696</v>
       </c>
-      <c r="D26" s="315" t="str">
+      <c r="D26" s="324" t="str">
         <v>净卖: -3631.64万</v>
       </c>
       <c r="E26">
@@ -10809,41 +10809,41 @@
       <c r="H26">
         <v>9.08</v>
       </c>
-      <c r="I26" s="316">
+      <c r="I26" s="313">
         <v>-10.47</v>
       </c>
-      <c r="J26" s="317">
+      <c r="J26" s="325">
         <v>-19.42</v>
       </c>
-      <c r="K26" s="321">
+      <c r="K26" s="314">
         <v>-21.91</v>
       </c>
-      <c r="L26" s="323">
+      <c r="L26" s="317">
         <v>-19.92</v>
       </c>
-      <c r="M26" s="324">
+      <c r="M26" s="315">
         <v>-11.91</v>
       </c>
-      <c r="N26" s="318">
+      <c r="N26" s="321">
         <v>-20.7</v>
       </c>
-      <c r="O26" s="319">
+      <c r="O26" s="318">
         <v>-25.29</v>
       </c>
-      <c r="P26" s="313">
+      <c r="P26" s="322">
         <v>-21.4</v>
       </c>
-      <c r="Q26" s="322">
+      <c r="Q26" s="319">
         <v>-13.54</v>
       </c>
       <c r="R26" s="320">
         <v>-4.9</v>
       </c>
-      <c r="S26" s="325">
+      <c r="S26" s="316">
         <v>4.59</v>
       </c>
-      <c r="T26" s="314">
-        <v>-38.09</v>
+      <c r="T26" s="323">
+        <v>-37.86</v>
       </c>
     </row>
     <row r="27">
@@ -10856,7 +10856,7 @@
       <c r="C27" t="str">
         <v>002682</v>
       </c>
-      <c r="D27" s="330" t="str">
+      <c r="D27" s="329" t="str">
         <v>净卖: -4674.28万</v>
       </c>
       <c r="E27">
@@ -10871,41 +10871,41 @@
       <c r="H27">
         <v>-4.33</v>
       </c>
-      <c r="I27" s="331">
+      <c r="I27" s="330">
         <v>14.93</v>
       </c>
-      <c r="J27" s="332">
+      <c r="J27" s="333">
         <v>3.47</v>
       </c>
-      <c r="K27" s="336">
+      <c r="K27" s="334">
         <v>-6.84</v>
       </c>
-      <c r="L27" s="335">
+      <c r="L27" s="331">
         <v>-5.11</v>
       </c>
-      <c r="M27" s="337">
+      <c r="M27" s="335">
         <v>-10.89</v>
       </c>
-      <c r="N27" s="338">
+      <c r="N27" s="326">
         <v>-19.36</v>
       </c>
-      <c r="O27" s="327">
+      <c r="O27" s="332">
         <v>-21</v>
       </c>
-      <c r="P27" s="326">
+      <c r="P27" s="336">
         <v>-20.33</v>
       </c>
-      <c r="Q27" s="328">
+      <c r="Q27" s="337">
         <v>-12.43</v>
       </c>
-      <c r="R27" s="329">
+      <c r="R27" s="328">
         <v>-14.26</v>
       </c>
-      <c r="S27" s="333">
+      <c r="S27" s="338">
         <v>-7.8</v>
       </c>
-      <c r="T27" s="334">
-        <v>-42.77</v>
+      <c r="T27" s="327">
+        <v>-42</v>
       </c>
     </row>
     <row r="28">
@@ -10918,7 +10918,7 @@
       <c r="C28" t="str">
         <v>600693</v>
       </c>
-      <c r="D28" s="345" t="str">
+      <c r="D28" s="342" t="str">
         <v>净买: 4441.53万</v>
       </c>
       <c r="E28">
@@ -10933,41 +10933,41 @@
       <c r="H28">
         <v>1.81</v>
       </c>
-      <c r="I28" s="346">
+      <c r="I28" s="343">
         <v>8.04</v>
       </c>
-      <c r="J28" s="347">
+      <c r="J28" s="351">
         <v>15.95</v>
       </c>
-      <c r="K28" s="348">
+      <c r="K28" s="344">
         <v>10.22</v>
       </c>
-      <c r="L28" s="343">
+      <c r="L28" s="340">
         <v>13.45</v>
       </c>
-      <c r="M28" s="351">
+      <c r="M28" s="347">
         <v>12.33</v>
       </c>
-      <c r="N28" s="349">
+      <c r="N28" s="341">
         <v>23.53</v>
       </c>
-      <c r="O28" s="340">
+      <c r="O28" s="345">
         <v>28.54</v>
       </c>
-      <c r="P28" s="341">
+      <c r="P28" s="348">
         <v>41.4</v>
       </c>
-      <c r="Q28" s="350">
+      <c r="Q28" s="339">
         <v>37.84</v>
       </c>
-      <c r="R28" s="342">
+      <c r="R28" s="349">
         <v>44.23</v>
       </c>
-      <c r="S28" s="339">
+      <c r="S28" s="350">
         <v>30.52</v>
       </c>
-      <c r="T28" s="344">
-        <v>-21.49</v>
+      <c r="T28" s="346">
+        <v>-20.9</v>
       </c>
     </row>
     <row r="29">
@@ -10980,7 +10980,7 @@
       <c r="C29" t="str">
         <v>603696</v>
       </c>
-      <c r="D29" s="363" t="str">
+      <c r="D29" s="358" t="str">
         <v>净卖: -3147.63万</v>
       </c>
       <c r="E29">
@@ -10995,13 +10995,13 @@
       <c r="H29">
         <v>2.92</v>
       </c>
-      <c r="I29" s="356">
+      <c r="I29" s="363">
         <v>-12.53</v>
       </c>
-      <c r="J29" s="357">
+      <c r="J29" s="359">
         <v>-17.6</v>
       </c>
-      <c r="K29" s="358">
+      <c r="K29" s="355">
         <v>-13.3</v>
       </c>
       <c r="L29" s="364">
@@ -11010,26 +11010,26 @@
       <c r="M29" s="352">
         <v>4.89</v>
       </c>
-      <c r="N29" s="359">
+      <c r="N29" s="356">
         <v>15.36</v>
       </c>
-      <c r="O29" s="354">
+      <c r="O29" s="361">
         <v>13.73</v>
       </c>
-      <c r="P29" s="361">
+      <c r="P29" s="353">
         <v>12.4</v>
       </c>
-      <c r="Q29" s="360">
+      <c r="Q29" s="357">
         <v>1.16</v>
       </c>
-      <c r="R29" s="353">
+      <c r="R29" s="362">
         <v>-8.97</v>
       </c>
-      <c r="S29" s="362">
+      <c r="S29" s="354">
         <v>-12.96</v>
       </c>
-      <c r="T29" s="355">
-        <v>-31.72</v>
+      <c r="T29" s="360">
+        <v>-31.46</v>
       </c>
     </row>
     <row r="30">
@@ -11042,7 +11042,7 @@
       <c r="C30" t="str">
         <v>600693</v>
       </c>
-      <c r="D30" s="366" t="str">
+      <c r="D30" s="377" t="str">
         <v>净卖: -5308.96万</v>
       </c>
       <c r="E30">
@@ -11057,41 +11057,41 @@
       <c r="H30">
         <v>2.51</v>
       </c>
-      <c r="I30" s="371">
+      <c r="I30" s="374">
         <v>0.41</v>
       </c>
-      <c r="J30" s="367">
+      <c r="J30" s="365">
         <v>-0.58</v>
       </c>
-      <c r="K30" s="376">
+      <c r="K30" s="366">
         <v>9.33</v>
       </c>
-      <c r="L30" s="368">
+      <c r="L30" s="367">
         <v>13.77</v>
       </c>
-      <c r="M30" s="372">
+      <c r="M30" s="375">
         <v>25.15</v>
       </c>
-      <c r="N30" s="373">
+      <c r="N30" s="372">
         <v>22</v>
       </c>
-      <c r="O30" s="374">
+      <c r="O30" s="368">
         <v>27.65</v>
       </c>
-      <c r="P30" s="370">
+      <c r="P30" s="373">
         <v>15.52</v>
       </c>
-      <c r="Q30" s="377">
+      <c r="Q30" s="369">
         <v>3.97</v>
       </c>
-      <c r="R30" s="365">
+      <c r="R30" s="370">
         <v>3.97</v>
       </c>
-      <c r="S30" s="369">
+      <c r="S30" s="371">
         <v>7.29</v>
       </c>
-      <c r="T30" s="375">
-        <v>-30.51</v>
+      <c r="T30" s="376">
+        <v>-29.99</v>
       </c>
     </row>
     <row r="31">
@@ -11104,7 +11104,7 @@
       <c r="C31" t="str">
         <v>600280</v>
       </c>
-      <c r="D31" s="387" t="str">
+      <c r="D31" s="385" t="str">
         <v>净买: 2343.21万</v>
       </c>
       <c r="E31">
@@ -11119,41 +11119,41 @@
       <c r="H31">
         <v>1.88</v>
       </c>
-      <c r="I31" s="382">
+      <c r="I31" s="380">
         <v>8.08</v>
       </c>
-      <c r="J31" s="388">
+      <c r="J31" s="389">
         <v>17.78</v>
       </c>
-      <c r="K31" s="379">
+      <c r="K31" s="390">
         <v>12.93</v>
       </c>
-      <c r="L31" s="383">
+      <c r="L31" s="378">
         <v>4.39</v>
       </c>
-      <c r="M31" s="378">
+      <c r="M31" s="384">
         <v>5.54</v>
       </c>
-      <c r="N31" s="384">
+      <c r="N31" s="386">
         <v>1.85</v>
       </c>
-      <c r="O31" s="380">
+      <c r="O31" s="387">
         <v>-1.15</v>
       </c>
-      <c r="P31" s="385">
+      <c r="P31" s="381">
         <v>-3</v>
       </c>
-      <c r="Q31" s="389">
+      <c r="Q31" s="382">
         <v>-7.85</v>
       </c>
-      <c r="R31" s="390">
+      <c r="R31" s="388">
         <v>-11.09</v>
       </c>
-      <c r="S31" s="381">
+      <c r="S31" s="383">
         <v>-10.16</v>
       </c>
-      <c r="T31" s="386">
-        <v>-27.94</v>
+      <c r="T31" s="379">
+        <v>-28.18</v>
       </c>
     </row>
     <row r="32">
@@ -11166,7 +11166,7 @@
       <c r="C32" t="str">
         <v>600280</v>
       </c>
-      <c r="D32" s="398" t="str">
+      <c r="D32" s="401" t="str">
         <v>净卖: -2545.17万</v>
       </c>
       <c r="E32">
@@ -11181,41 +11181,41 @@
       <c r="H32">
         <v>-3.92</v>
       </c>
-      <c r="I32" s="403">
+      <c r="I32" s="393">
         <v>-0.2</v>
       </c>
-      <c r="J32" s="399">
+      <c r="J32" s="395">
         <v>-7.76</v>
       </c>
-      <c r="K32" s="391">
+      <c r="K32" s="399">
         <v>-6.73</v>
       </c>
-      <c r="L32" s="395">
+      <c r="L32" s="402">
         <v>-10</v>
       </c>
       <c r="M32" s="396">
         <v>-12.65</v>
       </c>
-      <c r="N32" s="400">
+      <c r="N32" s="403">
         <v>-14.29</v>
       </c>
-      <c r="O32" s="401">
+      <c r="O32" s="391">
         <v>-18.57</v>
       </c>
       <c r="P32" s="392">
         <v>-21.43</v>
       </c>
-      <c r="Q32" s="393">
+      <c r="Q32" s="397">
         <v>-20.61</v>
       </c>
-      <c r="R32" s="402">
+      <c r="R32" s="398">
         <v>-16.33</v>
       </c>
-      <c r="S32" s="397">
+      <c r="S32" s="400">
         <v>-15.92</v>
       </c>
       <c r="T32" s="394">
-        <v>-36.33</v>
+        <v>-36.53</v>
       </c>
     </row>
     <row r="33">
@@ -11228,7 +11228,7 @@
       <c r="C33" t="str">
         <v>002759</v>
       </c>
-      <c r="D33" s="405" t="str">
+      <c r="D33" s="408" t="str">
         <v>净买: 8490.49万</v>
       </c>
       <c r="E33">
@@ -11243,41 +11243,41 @@
       <c r="H33">
         <v>-3.82</v>
       </c>
-      <c r="I33" s="407">
+      <c r="I33" s="414">
         <v>11.08</v>
       </c>
       <c r="J33" s="409">
         <v>22.19</v>
       </c>
-      <c r="K33" s="408">
+      <c r="K33" s="412">
         <v>22.69</v>
       </c>
-      <c r="L33" s="410">
+      <c r="L33" s="415">
         <v>13.63</v>
       </c>
-      <c r="M33" s="411">
+      <c r="M33" s="404">
         <v>14.61</v>
       </c>
       <c r="N33" s="416">
         <v>26.07</v>
       </c>
-      <c r="O33" s="412">
+      <c r="O33" s="405">
         <v>26.51</v>
       </c>
-      <c r="P33" s="413">
+      <c r="P33" s="410">
         <v>18.86</v>
       </c>
       <c r="Q33" s="406">
         <v>15.77</v>
       </c>
-      <c r="R33" s="404">
+      <c r="R33" s="413">
         <v>13.87</v>
       </c>
-      <c r="S33" s="414">
+      <c r="S33" s="411">
         <v>15.03</v>
       </c>
-      <c r="T33" s="415">
-        <v>-13.18</v>
+      <c r="T33" s="407">
+        <v>-14.86</v>
       </c>
     </row>
     <row r="34">
@@ -11290,7 +11290,7 @@
       <c r="C34" t="str">
         <v>002792</v>
       </c>
-      <c r="D34" s="423" t="str">
+      <c r="D34" s="425" t="str">
         <v>净买: 8322.30万</v>
       </c>
       <c r="E34">
@@ -11305,41 +11305,41 @@
       <c r="H34">
         <v>0.05</v>
       </c>
-      <c r="I34" s="428">
+      <c r="I34" s="417">
         <v>7.5</v>
       </c>
-      <c r="J34" s="417">
+      <c r="J34" s="426">
         <v>15.33</v>
       </c>
-      <c r="K34" s="421">
+      <c r="K34" s="418">
         <v>19.23</v>
       </c>
-      <c r="L34" s="418">
+      <c r="L34" s="427">
         <v>31.17</v>
       </c>
-      <c r="M34" s="424">
+      <c r="M34" s="428">
         <v>44.28</v>
       </c>
-      <c r="N34" s="425">
+      <c r="N34" s="420">
         <v>53.02</v>
       </c>
-      <c r="O34" s="429">
+      <c r="O34" s="421">
         <v>68.33</v>
       </c>
-      <c r="P34" s="426">
+      <c r="P34" s="424">
         <v>76.16</v>
       </c>
-      <c r="Q34" s="419">
+      <c r="Q34" s="422">
         <v>58.53</v>
       </c>
-      <c r="R34" s="422">
+      <c r="R34" s="429">
         <v>42.67</v>
       </c>
-      <c r="S34" s="420">
+      <c r="S34" s="423">
         <v>30.19</v>
       </c>
-      <c r="T34" s="427">
-        <v>28.45</v>
+      <c r="T34" s="419">
+        <v>33.13</v>
       </c>
     </row>
     <row r="35">
@@ -11352,7 +11352,7 @@
       <c r="C35" t="str">
         <v>002792</v>
       </c>
-      <c r="D35" s="440" t="str">
+      <c r="D35" s="436" t="str">
         <v>净卖: -7684.69万</v>
       </c>
       <c r="E35">
@@ -11367,41 +11367,41 @@
       <c r="H35">
         <v>2.25</v>
       </c>
-      <c r="I35" s="441">
+      <c r="I35" s="431">
         <v>4.92</v>
       </c>
-      <c r="J35" s="434">
+      <c r="J35" s="432">
         <v>8.47</v>
       </c>
-      <c r="K35" s="438">
+      <c r="K35" s="437">
         <v>19.33</v>
       </c>
-      <c r="L35" s="442">
+      <c r="L35" s="438">
         <v>31.26</v>
       </c>
-      <c r="M35" s="436">
+      <c r="M35" s="439">
         <v>39.21</v>
       </c>
-      <c r="N35" s="437">
+      <c r="N35" s="440">
         <v>53.14</v>
       </c>
-      <c r="O35" s="430">
+      <c r="O35" s="433">
         <v>60.26</v>
       </c>
-      <c r="P35" s="431">
+      <c r="P35" s="441">
         <v>44.23</v>
       </c>
-      <c r="Q35" s="435">
+      <c r="Q35" s="434">
         <v>29.8</v>
       </c>
-      <c r="R35" s="432">
+      <c r="R35" s="442">
         <v>18.44</v>
       </c>
-      <c r="S35" s="433">
+      <c r="S35" s="430">
         <v>17.43</v>
       </c>
-      <c r="T35" s="439">
-        <v>16.86</v>
+      <c r="T35" s="435">
+        <v>21.12</v>
       </c>
     </row>
     <row r="36">
@@ -11414,7 +11414,7 @@
       <c r="C36" t="str">
         <v>002759</v>
       </c>
-      <c r="D36" s="451" t="str">
+      <c r="D36" s="453" t="str">
         <v>净买: 1.00亿</v>
       </c>
       <c r="E36">
@@ -11429,41 +11429,41 @@
       <c r="H36">
         <v>3.06</v>
       </c>
-      <c r="I36" s="449">
+      <c r="I36" s="448">
         <v>6.73</v>
       </c>
-      <c r="J36" s="452">
+      <c r="J36" s="443">
         <v>7.11</v>
       </c>
-      <c r="K36" s="453">
+      <c r="K36" s="444">
         <v>0.63</v>
       </c>
       <c r="L36" s="445">
         <v>-1.99</v>
       </c>
-      <c r="M36" s="446">
+      <c r="M36" s="449">
         <v>-3.59</v>
       </c>
-      <c r="N36" s="447">
+      <c r="N36" s="446">
         <v>-2.61</v>
       </c>
-      <c r="O36" s="454">
+      <c r="O36" s="451">
         <v>-7.82</v>
       </c>
-      <c r="P36" s="455">
+      <c r="P36" s="450">
         <v>-11.35</v>
       </c>
-      <c r="Q36" s="448">
+      <c r="Q36" s="452">
         <v>-5.64</v>
       </c>
-      <c r="R36" s="443">
+      <c r="R36" s="454">
         <v>-13.61</v>
       </c>
-      <c r="S36" s="444">
+      <c r="S36" s="447">
         <v>-12.5</v>
       </c>
-      <c r="T36" s="450">
-        <v>-26.5</v>
+      <c r="T36" s="455">
+        <v>-27.92</v>
       </c>
     </row>
     <row r="37">
@@ -11476,7 +11476,7 @@
       <c r="C37" t="str">
         <v>600776</v>
       </c>
-      <c r="D37" s="461" t="str">
+      <c r="D37" s="458" t="str">
         <v>净买: 5452.75万</v>
       </c>
       <c r="E37">
@@ -11491,41 +11491,41 @@
       <c r="H37">
         <v>10.02</v>
       </c>
-      <c r="I37" s="458">
+      <c r="I37" s="465">
         <v>0</v>
       </c>
-      <c r="J37" s="468">
+      <c r="J37" s="459">
         <v>10</v>
       </c>
-      <c r="K37" s="462">
+      <c r="K37" s="468">
         <v>16.57</v>
       </c>
-      <c r="L37" s="463">
+      <c r="L37" s="461">
         <v>4.91</v>
       </c>
-      <c r="M37" s="464">
+      <c r="M37" s="462">
         <v>-5.58</v>
       </c>
       <c r="N37" s="456">
         <v>-15.01</v>
       </c>
-      <c r="O37" s="457">
+      <c r="O37" s="463">
         <v>-17.91</v>
       </c>
-      <c r="P37" s="467">
+      <c r="P37" s="466">
         <v>-16.93</v>
       </c>
-      <c r="Q37" s="459">
+      <c r="Q37" s="464">
         <v>-15.19</v>
       </c>
       <c r="R37" s="460">
         <v>-10.99</v>
       </c>
-      <c r="S37" s="465">
+      <c r="S37" s="457">
         <v>-15.27</v>
       </c>
-      <c r="T37" s="466">
-        <v>-25.23</v>
+      <c r="T37" s="467">
+        <v>-25.01</v>
       </c>
     </row>
     <row r="38">
@@ -11538,7 +11538,7 @@
       <c r="C38" t="str">
         <v>600410</v>
       </c>
-      <c r="D38" s="481" t="str">
+      <c r="D38" s="469" t="str">
         <v>净买: 1.26亿</v>
       </c>
       <c r="E38">
@@ -11553,41 +11553,41 @@
       <c r="H38">
         <v>-1.64</v>
       </c>
-      <c r="I38" s="476">
+      <c r="I38" s="477">
         <v>11.84</v>
       </c>
-      <c r="J38" s="477">
+      <c r="J38" s="478">
         <v>23.02</v>
       </c>
-      <c r="K38" s="469">
+      <c r="K38" s="473">
         <v>10.78</v>
       </c>
-      <c r="L38" s="479">
+      <c r="L38" s="471">
         <v>2.42</v>
       </c>
       <c r="M38" s="470">
         <v>0</v>
       </c>
-      <c r="N38" s="474">
+      <c r="N38" s="479">
         <v>1.86</v>
       </c>
-      <c r="O38" s="475">
+      <c r="O38" s="474">
         <v>2.67</v>
       </c>
-      <c r="P38" s="471">
+      <c r="P38" s="480">
         <v>5.99</v>
       </c>
-      <c r="Q38" s="472">
+      <c r="Q38" s="481">
         <v>0.81</v>
       </c>
-      <c r="R38" s="478">
+      <c r="R38" s="475">
         <v>6.95</v>
       </c>
-      <c r="S38" s="480">
+      <c r="S38" s="476">
         <v>6.25</v>
       </c>
-      <c r="T38" s="473">
-        <v>45.79</v>
+      <c r="T38" s="472">
+        <v>46.05</v>
       </c>
     </row>
     <row r="39">
@@ -11600,7 +11600,7 @@
       <c r="C39" t="str">
         <v>600410</v>
       </c>
-      <c r="D39" s="488" t="str">
+      <c r="D39" s="491" t="str">
         <v>净买: 1.26亿</v>
       </c>
       <c r="E39">
@@ -11615,41 +11615,41 @@
       <c r="H39">
         <v>10</v>
       </c>
-      <c r="I39" s="489">
+      <c r="I39" s="492">
         <v>0</v>
       </c>
-      <c r="J39" s="482">
+      <c r="J39" s="483">
         <v>-9.95</v>
       </c>
-      <c r="K39" s="492">
+      <c r="K39" s="484">
         <v>-16.75</v>
       </c>
-      <c r="L39" s="490">
+      <c r="L39" s="493">
         <v>-18.71</v>
       </c>
-      <c r="M39" s="487">
+      <c r="M39" s="485">
         <v>-17.2</v>
       </c>
-      <c r="N39" s="493">
+      <c r="N39" s="494">
         <v>-16.54</v>
       </c>
-      <c r="O39" s="491">
+      <c r="O39" s="486">
         <v>-13.84</v>
       </c>
-      <c r="P39" s="483">
+      <c r="P39" s="490">
         <v>-18.06</v>
       </c>
-      <c r="Q39" s="484">
+      <c r="Q39" s="487">
         <v>-13.06</v>
       </c>
-      <c r="R39" s="494">
+      <c r="R39" s="488">
         <v>-13.64</v>
       </c>
-      <c r="S39" s="485">
+      <c r="S39" s="482">
         <v>-10.2</v>
       </c>
-      <c r="T39" s="486">
-        <v>18.51</v>
+      <c r="T39" s="489">
+        <v>18.71</v>
       </c>
     </row>
     <row r="40">
@@ -11662,7 +11662,7 @@
       <c r="C40" t="str">
         <v>600776</v>
       </c>
-      <c r="D40" s="502" t="str">
+      <c r="D40" s="496" t="str">
         <v>净卖: -233.39万</v>
       </c>
       <c r="E40">
@@ -11677,41 +11677,41 @@
       <c r="H40">
         <v>-10</v>
       </c>
-      <c r="I40" s="497">
+      <c r="I40" s="503">
         <v>0</v>
       </c>
-      <c r="J40" s="498">
+      <c r="J40" s="499">
         <v>-9.98</v>
       </c>
-      <c r="K40" s="503">
+      <c r="K40" s="504">
         <v>-13.06</v>
       </c>
-      <c r="L40" s="499">
+      <c r="L40" s="500">
         <v>-12.02</v>
       </c>
-      <c r="M40" s="507">
+      <c r="M40" s="497">
         <v>-10.17</v>
       </c>
-      <c r="N40" s="500">
+      <c r="N40" s="501">
         <v>-5.72</v>
       </c>
-      <c r="O40" s="495">
+      <c r="O40" s="502">
         <v>-10.26</v>
       </c>
-      <c r="P40" s="506">
+      <c r="P40" s="507">
         <v>-9.89</v>
       </c>
-      <c r="Q40" s="504">
+      <c r="Q40" s="498">
         <v>-11.26</v>
       </c>
-      <c r="R40" s="496">
+      <c r="R40" s="505">
         <v>-11.78</v>
       </c>
-      <c r="S40" s="501">
+      <c r="S40" s="506">
         <v>-12.49</v>
       </c>
-      <c r="T40" s="505">
-        <v>-20.81</v>
+      <c r="T40" s="495">
+        <v>-20.58</v>
       </c>
     </row>
     <row r="41">
@@ -11724,7 +11724,7 @@
       <c r="C41" t="str">
         <v>600410</v>
       </c>
-      <c r="D41" s="515" t="str">
+      <c r="D41" s="517" t="str">
         <v>净卖: -1.30亿</v>
       </c>
       <c r="E41">
@@ -11739,41 +11739,41 @@
       <c r="H41">
         <v>-1.97</v>
       </c>
-      <c r="I41" s="509">
+      <c r="I41" s="512">
         <v>-8.15</v>
       </c>
-      <c r="J41" s="513">
+      <c r="J41" s="508">
         <v>-15.08</v>
       </c>
-      <c r="K41" s="518">
+      <c r="K41" s="509">
         <v>-17.08</v>
       </c>
-      <c r="L41" s="519">
+      <c r="L41" s="513">
         <v>-15.54</v>
       </c>
-      <c r="M41" s="516">
+      <c r="M41" s="518">
         <v>-14.87</v>
       </c>
-      <c r="N41" s="514">
+      <c r="N41" s="515">
         <v>-12.11</v>
       </c>
-      <c r="O41" s="520">
+      <c r="O41" s="519">
         <v>-16.42</v>
       </c>
-      <c r="P41" s="517">
+      <c r="P41" s="510">
         <v>-11.32</v>
       </c>
-      <c r="Q41" s="510">
+      <c r="Q41" s="516">
         <v>-11.9</v>
       </c>
-      <c r="R41" s="508">
+      <c r="R41" s="514">
         <v>-8.4</v>
       </c>
       <c r="S41" s="511">
         <v>-12.24</v>
       </c>
-      <c r="T41" s="512">
-        <v>20.89</v>
+      <c r="T41" s="520">
+        <v>21.09</v>
       </c>
     </row>
     <row r="42">
@@ -11786,7 +11786,7 @@
       <c r="C42" t="str">
         <v>002792</v>
       </c>
-      <c r="D42" s="524" t="str">
+      <c r="D42" s="531" t="str">
         <v>净买: 5153.68万</v>
       </c>
       <c r="E42">
@@ -11801,41 +11801,41 @@
       <c r="H42">
         <v>0.55</v>
       </c>
-      <c r="I42" s="530">
+      <c r="I42" s="523">
         <v>9.39</v>
       </c>
-      <c r="J42" s="531">
+      <c r="J42" s="524">
         <v>15.85</v>
       </c>
-      <c r="K42" s="527">
+      <c r="K42" s="525">
         <v>10.51</v>
       </c>
-      <c r="L42" s="525">
+      <c r="L42" s="532">
         <v>6.31</v>
       </c>
-      <c r="M42" s="532">
+      <c r="M42" s="533">
         <v>1.07</v>
       </c>
-      <c r="N42" s="528">
+      <c r="N42" s="526">
         <v>-1.76</v>
       </c>
-      <c r="O42" s="533">
+      <c r="O42" s="521">
         <v>0.67</v>
       </c>
-      <c r="P42" s="521">
+      <c r="P42" s="529">
         <v>10.74</v>
       </c>
-      <c r="Q42" s="526">
+      <c r="Q42" s="527">
         <v>10.74</v>
       </c>
-      <c r="R42" s="529">
+      <c r="R42" s="530">
         <v>7.46</v>
       </c>
       <c r="S42" s="522">
         <v>7.34</v>
       </c>
-      <c r="T42" s="523">
-        <v>6.98</v>
+      <c r="T42" s="528">
+        <v>10.88</v>
       </c>
     </row>
     <row r="43">
@@ -11897,41 +11897,41 @@
       <c r="F44" t="str"/>
       <c r="G44" t="str"/>
       <c r="H44" t="str"/>
-      <c r="I44" s="543">
+      <c r="I44" s="535">
         <v>65.85</v>
       </c>
-      <c r="J44" s="538">
+      <c r="J44" s="544">
         <v>65.85</v>
       </c>
-      <c r="K44" s="540">
+      <c r="K44" s="536">
         <v>60.98</v>
       </c>
-      <c r="L44" s="544">
+      <c r="L44" s="545">
         <v>56.1</v>
       </c>
-      <c r="M44" s="534">
+      <c r="M44" s="539">
         <v>48.78</v>
       </c>
-      <c r="N44" s="535">
+      <c r="N44" s="540">
         <v>46.34</v>
       </c>
-      <c r="O44" s="536">
+      <c r="O44" s="537">
         <v>48.78</v>
       </c>
-      <c r="P44" s="541">
+      <c r="P44" s="534">
         <v>43.9</v>
       </c>
-      <c r="Q44" s="539">
+      <c r="Q44" s="538">
         <v>39.02</v>
       </c>
-      <c r="R44" s="537">
+      <c r="R44" s="541">
         <v>43.9</v>
       </c>
-      <c r="S44" s="545">
+      <c r="S44" s="542">
         <v>43.9</v>
       </c>
-      <c r="T44" s="542">
-        <v>31.71</v>
+      <c r="T44" s="543">
+        <v>34.15</v>
       </c>
     </row>
     <row r="45">
@@ -11945,41 +11945,41 @@
       <c r="F45" t="str"/>
       <c r="G45" t="str"/>
       <c r="H45" t="str"/>
-      <c r="I45" s="550">
+      <c r="I45" s="553">
         <v>3.79</v>
       </c>
-      <c r="J45" s="553">
+      <c r="J45" s="554">
         <v>5.59</v>
       </c>
-      <c r="K45" s="548">
+      <c r="K45" s="549">
         <v>5.07</v>
       </c>
-      <c r="L45" s="549">
+      <c r="L45" s="556">
         <v>5.23</v>
       </c>
-      <c r="M45" s="547">
+      <c r="M45" s="557">
         <v>5.01</v>
       </c>
-      <c r="N45" s="551">
+      <c r="N45" s="550">
         <v>4.05</v>
       </c>
-      <c r="O45" s="552">
+      <c r="O45" s="551">
         <v>4.42</v>
       </c>
-      <c r="P45" s="554">
+      <c r="P45" s="552">
         <v>3.76</v>
       </c>
-      <c r="Q45" s="555">
+      <c r="Q45" s="546">
         <v>1.74</v>
       </c>
-      <c r="R45" s="556">
+      <c r="R45" s="547">
         <v>1.6</v>
       </c>
-      <c r="S45" s="557">
+      <c r="S45" s="548">
         <v>0.99</v>
       </c>
-      <c r="T45" s="546">
-        <v>-4.22</v>
+      <c r="T45" s="555">
+        <v>-3.44</v>
       </c>
     </row>
   </sheetData>

--- a/youzi/越王大道/index.xlsx
+++ b/youzi/越王大道/index.xlsx
@@ -39,19 +39,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF218E3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA91E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAB1E2C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC4E7CC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF70C483"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAE202D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFB8E1C1"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FFED979F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8236"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -63,49 +117,2179 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDA3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAC1F2C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC32938"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAB1F2C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BDC2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF3F4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE2E4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC02836"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2FAA4B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDE4150"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCF0F1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFA4AB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD33140"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE6E8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFAB1E2C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC4E7CC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED979F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8236"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA91E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF70C483"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218E3B"/>
+        <fgColor rgb="FFDD3D4D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7DCA8F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD53241"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE35F6B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC42A38"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFACDDB7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7130"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBE8EA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9808A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED9BA3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF95D3A3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDB3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B2B8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCA2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC969F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77580"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF67C07B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25866"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9DFE1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEE9FA6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBB2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3B9BF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDA3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD2303F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFDFD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BFC4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E7F35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7B33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8437"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBEDEE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A702F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCFDFC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6AC27E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE3E5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDE4251"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBEAEC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23943D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23943D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8437"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23953E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5BBC71"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB72432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A712F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218D3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC3E6CB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208838"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7B34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF46B35F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A443"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBC2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5FBD75"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC52A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF63BF78"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7FCA90"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23943D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF40B15A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8638"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8638"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8738"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7E35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23933D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7A33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8136"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2DFBC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5EBD74"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8738"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF84CD95"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7CC98E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF46B35F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6DC381"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B2B8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2DFBC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2FA94B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF53B86A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A644"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8638"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFCFC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77580"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6CC280"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF249A3F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77883"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF95D3A3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBF2736"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7CC98E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22903C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6CDD1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BAC0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9DCDF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9858F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B3B9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF99D5A7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8337"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFBFB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7531"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196F2F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD43140"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDE4251"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24983F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC929B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208839"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4C4C8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF37AD52"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF54B96B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFACDDB7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46672"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7732"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2CA848"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDE4554"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A544"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8538"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6727D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBB2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6D0D3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7832"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF37AD52"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3949"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC32A38"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE35E6B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCEEEF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6F4E9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE35E6B"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -129,37 +2313,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDA3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FF7ECA8F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8537"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -171,25 +2337,997 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFE04D5B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD63242"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B4BA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCDEAD4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBB2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22923D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6FBF7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8638"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC12937"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB72432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3847"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF269F42"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC92C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC52A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE5E7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA9DBB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF64BF79"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8ED19D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8538"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3848"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A042"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD1303F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9DEE0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC72B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC939B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEE9DA4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B3B9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196D2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259E41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8136"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7E35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAD1F2D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D3D7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC12937"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB3E0BD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE3E6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC32938"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC32938"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBC2635"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9838D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE4F4E8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE4F4E8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7BC98D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBC2635"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD63242"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A142"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0DEBA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7BC98D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7BC98D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8437"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE04F5D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAD1F2D"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -207,3109 +3345,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BDC2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAB1F2C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC32938"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCF0F1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2FAA4B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBECED"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFA4AB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD33140"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF3F4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE2E4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC02836"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDE4150"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFACDDB7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBE8EA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBB2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD53241"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED9BA3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7130"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3D4D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC42A38"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7DCA8F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9808A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF67C07B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC969F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC12937"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B2B8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF95D3A3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCA2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDB3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEE9FA6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25866"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDA3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD2303F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBB2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9DFE1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3B9BF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFDFD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A702F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BFC4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7B33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBEDEE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8437"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E7F35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDE4251"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23953E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE3E5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23943D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8437"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6AC27E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5BBC71"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23943D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCFDFC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBEAEC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208838"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A712F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7B34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC3E6CB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF46B35F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208839"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A443"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218D3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBC2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7FCA90"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5FBD75"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF63BF78"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC52A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23943D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF53B86A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8638"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7E35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23933D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8638"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8738"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7A33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8136"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2DFBC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7CC98E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2FA94B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6DC381"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF46B35F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5EBD74"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF53B86A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8738"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF84CD95"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B2B8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2DFBC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A644"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8638"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF249A3F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77580"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFCFC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6CC280"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77883"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22903C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBF2736"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7CC98E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF95D3A3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BAC0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF99D5A7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6CDD1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9DCDF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFBFB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8337"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B3B9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9858F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDE4251"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD43140"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196F2F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208839"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC929B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4C4C8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF37AD52"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF54B96B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDEF1E3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46672"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8437"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDE4554"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2CA848"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A544"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6727D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8538"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBB2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3949"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6D0D3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7832"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF37AD52"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6F4E9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAE202D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE35E6B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE35E6B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC32A38"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCEEEF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE04D5B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBB2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7ECA8F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8537"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD63242"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B4BA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCDEAD4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6FBF7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8638"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22923D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC12937"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3847"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB72432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC52A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE5E7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA9DBB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8ED19D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC92C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF64BF79"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8538"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF269F42"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3848"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A042"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEE9DA4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC939B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC72B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B3B9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD1303F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9DEE0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259E41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196D2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8136"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7E35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE3E6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC32938"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAD1F2D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB3E0BD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC12937"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D3D7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7BC98D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBC2635"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD63242"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE4F4E8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A142"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE4F4E8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0DEBA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7BC98D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7BC98D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8437"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBC2635"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9838D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE04F5D"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -3327,49 +3369,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAD1F2D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAC1F2C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -9306,7 +9306,7 @@
       <c r="C2" t="str">
         <v>002570</v>
       </c>
-      <c r="D2" s="5" t="str">
+      <c r="D2" s="3" t="str">
         <v>净卖: -1602.12万</v>
       </c>
       <c r="E2">
@@ -9321,41 +9321,41 @@
       <c r="H2">
         <v>0.15</v>
       </c>
-      <c r="I2" s="10">
+      <c r="I2" s="4">
         <v>9.77</v>
       </c>
-      <c r="J2" s="6">
+      <c r="J2" s="5">
         <v>9.62</v>
       </c>
-      <c r="K2" s="7">
+      <c r="K2" s="6">
         <v>-1.35</v>
       </c>
-      <c r="L2" s="12">
+      <c r="L2" s="1">
         <v>-7.07</v>
       </c>
-      <c r="M2" s="11">
+      <c r="M2" s="7">
         <v>-3.31</v>
       </c>
-      <c r="N2" s="8">
+      <c r="N2" s="10">
         <v>2.56</v>
       </c>
-      <c r="O2" s="13">
+      <c r="O2" s="8">
         <v>9.32</v>
       </c>
-      <c r="P2" s="1">
+      <c r="P2" s="9">
         <v>-1.65</v>
       </c>
-      <c r="Q2" s="3">
+      <c r="Q2" s="11">
         <v>-11.43</v>
       </c>
-      <c r="R2" s="4">
+      <c r="R2" s="13">
         <v>-9.47</v>
       </c>
-      <c r="S2" s="9">
+      <c r="S2" s="12">
         <v>-8.12</v>
       </c>
       <c r="T2" s="2">
-        <v>-24.21</v>
+        <v>-25.41</v>
       </c>
     </row>
     <row r="3">
@@ -9368,7 +9368,7 @@
       <c r="C3" t="str">
         <v>002915</v>
       </c>
-      <c r="D3" s="22" t="str">
+      <c r="D3" s="17" t="str">
         <v>净买: 2039.94万</v>
       </c>
       <c r="E3">
@@ -9383,41 +9383,41 @@
       <c r="H3">
         <v>0.12</v>
       </c>
-      <c r="I3" s="19">
+      <c r="I3" s="18">
         <v>5.12</v>
       </c>
-      <c r="J3" s="14">
+      <c r="J3" s="24">
         <v>15.65</v>
       </c>
       <c r="K3" s="15">
         <v>27.2</v>
       </c>
-      <c r="L3" s="23">
+      <c r="L3" s="25">
         <v>27.56</v>
       </c>
-      <c r="M3" s="17">
+      <c r="M3" s="16">
         <v>40.3</v>
       </c>
-      <c r="N3" s="24">
+      <c r="N3" s="26">
         <v>27.68</v>
       </c>
-      <c r="O3" s="20">
+      <c r="O3" s="19">
         <v>30.06</v>
       </c>
-      <c r="P3" s="25">
+      <c r="P3" s="20">
         <v>28.1</v>
       </c>
       <c r="Q3" s="21">
         <v>36.9</v>
       </c>
-      <c r="R3" s="26">
+      <c r="R3" s="22">
         <v>34.52</v>
       </c>
-      <c r="S3" s="18">
+      <c r="S3" s="23">
         <v>21.07</v>
       </c>
-      <c r="T3" s="16">
-        <v>27.8</v>
+      <c r="T3" s="14">
+        <v>27.98</v>
       </c>
     </row>
     <row r="4">
@@ -9430,7 +9430,7 @@
       <c r="C4" t="str">
         <v>002229</v>
       </c>
-      <c r="D4" s="29" t="str">
+      <c r="D4" s="37" t="str">
         <v>净买: 2135.02万</v>
       </c>
       <c r="E4">
@@ -9445,41 +9445,41 @@
       <c r="H4">
         <v>8.23</v>
       </c>
-      <c r="I4" s="30">
+      <c r="I4" s="32">
         <v>1.62</v>
       </c>
-      <c r="J4" s="33">
+      <c r="J4" s="38">
         <v>11.75</v>
       </c>
-      <c r="K4" s="38">
+      <c r="K4" s="29">
         <v>21.04</v>
       </c>
-      <c r="L4" s="34">
+      <c r="L4" s="33">
         <v>28.15</v>
       </c>
-      <c r="M4" s="31">
+      <c r="M4" s="34">
         <v>15.34</v>
       </c>
-      <c r="N4" s="32">
+      <c r="N4" s="36">
         <v>13.65</v>
       </c>
-      <c r="O4" s="36">
+      <c r="O4" s="39">
         <v>13.02</v>
       </c>
-      <c r="P4" s="39">
+      <c r="P4" s="30">
         <v>7.32</v>
       </c>
       <c r="Q4" s="27">
         <v>9.5</v>
       </c>
-      <c r="R4" s="37">
+      <c r="R4" s="31">
         <v>9.57</v>
       </c>
-      <c r="S4" s="28">
+      <c r="S4" s="35">
         <v>14.22</v>
       </c>
-      <c r="T4" s="35">
-        <v>36.38</v>
+      <c r="T4" s="28">
+        <v>33.29</v>
       </c>
     </row>
     <row r="5">
@@ -9492,7 +9492,7 @@
       <c r="C5" t="str">
         <v>002915</v>
       </c>
-      <c r="D5" s="43" t="str">
+      <c r="D5" s="52" t="str">
         <v>净卖: -2747.73万</v>
       </c>
       <c r="E5">
@@ -9507,41 +9507,41 @@
       <c r="H5">
         <v>9.98</v>
       </c>
-      <c r="I5" s="47">
+      <c r="I5" s="40">
         <v>0</v>
       </c>
-      <c r="J5" s="48">
+      <c r="J5" s="41">
         <v>0.28</v>
       </c>
-      <c r="K5" s="49">
+      <c r="K5" s="42">
         <v>10.29</v>
       </c>
-      <c r="L5" s="40">
+      <c r="L5" s="48">
         <v>0.37</v>
       </c>
-      <c r="M5" s="44">
+      <c r="M5" s="49">
         <v>2.25</v>
       </c>
-      <c r="N5" s="50">
+      <c r="N5" s="43">
         <v>0.7</v>
       </c>
-      <c r="O5" s="51">
+      <c r="O5" s="44">
         <v>7.63</v>
       </c>
-      <c r="P5" s="45">
+      <c r="P5" s="50">
         <v>5.76</v>
       </c>
-      <c r="Q5" s="41">
+      <c r="Q5" s="45">
         <v>-4.82</v>
       </c>
-      <c r="R5" s="52">
+      <c r="R5" s="46">
         <v>4.68</v>
       </c>
-      <c r="S5" s="46">
+      <c r="S5" s="47">
         <v>11</v>
       </c>
-      <c r="T5" s="42">
-        <v>0.47</v>
+      <c r="T5" s="51">
+        <v>0.61</v>
       </c>
     </row>
     <row r="6">
@@ -9554,7 +9554,7 @@
       <c r="C6" t="str">
         <v>002177</v>
       </c>
-      <c r="D6" s="56" t="str">
+      <c r="D6" s="64" t="str">
         <v>净买: 3117.92万</v>
       </c>
       <c r="E6">
@@ -9569,41 +9569,41 @@
       <c r="H6">
         <v>5.02</v>
       </c>
-      <c r="I6" s="60">
+      <c r="I6" s="53">
         <v>4.78</v>
       </c>
-      <c r="J6" s="65">
+      <c r="J6" s="55">
         <v>10.79</v>
       </c>
-      <c r="K6" s="61">
+      <c r="K6" s="59">
         <v>7.24</v>
       </c>
-      <c r="L6" s="62">
+      <c r="L6" s="56">
         <v>12.3</v>
       </c>
       <c r="M6" s="57">
         <v>5.6</v>
       </c>
-      <c r="N6" s="58">
+      <c r="N6" s="65">
         <v>2.46</v>
       </c>
-      <c r="O6" s="53">
+      <c r="O6" s="60">
         <v>-1.91</v>
       </c>
-      <c r="P6" s="59">
+      <c r="P6" s="61">
         <v>-9.56</v>
       </c>
-      <c r="Q6" s="63">
+      <c r="Q6" s="54">
         <v>-3.01</v>
       </c>
-      <c r="R6" s="54">
+      <c r="R6" s="62">
         <v>0.55</v>
       </c>
-      <c r="S6" s="64">
+      <c r="S6" s="63">
         <v>3.14</v>
       </c>
-      <c r="T6" s="55">
-        <v>8.06</v>
+      <c r="T6" s="58">
+        <v>3.96</v>
       </c>
     </row>
     <row r="7">
@@ -9616,7 +9616,7 @@
       <c r="C7" t="str">
         <v>002177</v>
       </c>
-      <c r="D7" s="73" t="str">
+      <c r="D7" s="68" t="str">
         <v>净卖: -2852.77万</v>
       </c>
       <c r="E7">
@@ -9631,41 +9631,41 @@
       <c r="H7">
         <v>-4.04</v>
       </c>
-      <c r="I7" s="70">
+      <c r="I7" s="66">
         <v>10.19</v>
       </c>
-      <c r="J7" s="77">
+      <c r="J7" s="71">
         <v>6.66</v>
       </c>
-      <c r="K7" s="74">
+      <c r="K7" s="72">
         <v>11.68</v>
       </c>
-      <c r="L7" s="78">
+      <c r="L7" s="69">
         <v>5.03</v>
       </c>
-      <c r="M7" s="75">
+      <c r="M7" s="70">
         <v>1.9</v>
       </c>
-      <c r="N7" s="76">
+      <c r="N7" s="67">
         <v>-2.45</v>
       </c>
-      <c r="O7" s="68">
+      <c r="O7" s="75">
         <v>-10.05</v>
       </c>
-      <c r="P7" s="66">
+      <c r="P7" s="76">
         <v>-3.53</v>
       </c>
-      <c r="Q7" s="67">
+      <c r="Q7" s="77">
         <v>0</v>
       </c>
-      <c r="R7" s="69">
+      <c r="R7" s="73">
         <v>2.58</v>
       </c>
-      <c r="S7" s="71">
+      <c r="S7" s="78">
         <v>-5.3</v>
       </c>
-      <c r="T7" s="72">
-        <v>7.47</v>
+      <c r="T7" s="74">
+        <v>3.4</v>
       </c>
     </row>
     <row r="8">
@@ -9678,7 +9678,7 @@
       <c r="C8" t="str">
         <v>002882</v>
       </c>
-      <c r="D8" s="83" t="str">
+      <c r="D8" s="90" t="str">
         <v>净卖: -1459.92万</v>
       </c>
       <c r="E8">
@@ -9693,41 +9693,41 @@
       <c r="H8">
         <v>-0.92</v>
       </c>
-      <c r="I8" s="81">
+      <c r="I8" s="91">
         <v>11.01</v>
       </c>
-      <c r="J8" s="84">
+      <c r="J8" s="79">
         <v>11.21</v>
       </c>
-      <c r="K8" s="90">
+      <c r="K8" s="85">
         <v>1.71</v>
       </c>
-      <c r="L8" s="82">
+      <c r="L8" s="80">
         <v>4.11</v>
       </c>
-      <c r="M8" s="91">
+      <c r="M8" s="88">
         <v>0.04</v>
       </c>
-      <c r="N8" s="88">
+      <c r="N8" s="81">
         <v>0.78</v>
       </c>
-      <c r="O8" s="79">
+      <c r="O8" s="82">
         <v>2.37</v>
       </c>
-      <c r="P8" s="85">
+      <c r="P8" s="86">
         <v>5.12</v>
       </c>
-      <c r="Q8" s="86">
+      <c r="Q8" s="87">
         <v>5.93</v>
       </c>
-      <c r="R8" s="87">
+      <c r="R8" s="83">
         <v>8.07</v>
       </c>
-      <c r="S8" s="80">
+      <c r="S8" s="84">
         <v>18.88</v>
       </c>
       <c r="T8" s="89">
-        <v>15.01</v>
+        <v>12.56</v>
       </c>
     </row>
     <row r="9">
@@ -9755,41 +9755,41 @@
       <c r="H9">
         <v>10.01</v>
       </c>
-      <c r="I9" s="93">
+      <c r="I9" s="92">
         <v>0</v>
       </c>
-      <c r="J9" s="94">
+      <c r="J9" s="101">
         <v>10.01</v>
       </c>
-      <c r="K9" s="97">
+      <c r="K9" s="93">
         <v>1.58</v>
       </c>
-      <c r="L9" s="99">
+      <c r="L9" s="102">
         <v>0.44</v>
       </c>
-      <c r="M9" s="95">
+      <c r="M9" s="103">
         <v>-9.6</v>
       </c>
-      <c r="N9" s="103">
+      <c r="N9" s="98">
         <v>-14.15</v>
       </c>
-      <c r="O9" s="100">
+      <c r="O9" s="99">
         <v>-11.05</v>
       </c>
-      <c r="P9" s="98">
+      <c r="P9" s="97">
         <v>-8.72</v>
       </c>
-      <c r="Q9" s="101">
+      <c r="Q9" s="104">
         <v>-7.3</v>
       </c>
-      <c r="R9" s="104">
+      <c r="R9" s="94">
         <v>-8.31</v>
       </c>
-      <c r="S9" s="102">
+      <c r="S9" s="100">
         <v>-7.9</v>
       </c>
-      <c r="T9" s="92">
-        <v>-31.87</v>
+      <c r="T9" s="95">
+        <v>-33.7</v>
       </c>
     </row>
     <row r="10">
@@ -9802,7 +9802,7 @@
       <c r="C10" t="str">
         <v>002017</v>
       </c>
-      <c r="D10" s="109" t="str">
+      <c r="D10" s="111" t="str">
         <v>净买: 6518.56万</v>
       </c>
       <c r="E10">
@@ -9817,41 +9817,41 @@
       <c r="H10">
         <v>5.13</v>
       </c>
-      <c r="I10" s="105">
+      <c r="I10" s="108">
         <v>4.66</v>
       </c>
-      <c r="J10" s="116">
+      <c r="J10" s="105">
         <v>-0.06</v>
       </c>
-      <c r="K10" s="110">
+      <c r="K10" s="112">
         <v>-6.53</v>
       </c>
-      <c r="L10" s="111">
+      <c r="L10" s="116">
         <v>-5.79</v>
       </c>
-      <c r="M10" s="112">
+      <c r="M10" s="113">
         <v>-7.89</v>
       </c>
-      <c r="N10" s="113">
+      <c r="N10" s="106">
         <v>-3.46</v>
       </c>
       <c r="O10" s="107">
         <v>0.68</v>
       </c>
-      <c r="P10" s="117">
+      <c r="P10" s="109">
         <v>0.51</v>
       </c>
-      <c r="Q10" s="106">
+      <c r="Q10" s="114">
         <v>-6.47</v>
       </c>
-      <c r="R10" s="114">
+      <c r="R10" s="115">
         <v>-3.8</v>
       </c>
-      <c r="S10" s="115">
+      <c r="S10" s="110">
         <v>-6.53</v>
       </c>
-      <c r="T10" s="108">
-        <v>10.39</v>
+      <c r="T10" s="117">
+        <v>8.46</v>
       </c>
     </row>
     <row r="11">
@@ -9864,7 +9864,7 @@
       <c r="C11" t="str">
         <v>002670</v>
       </c>
-      <c r="D11" s="123" t="str">
+      <c r="D11" s="124" t="str">
         <v>净卖: -2720.58万</v>
       </c>
       <c r="E11">
@@ -9879,41 +9879,41 @@
       <c r="H11">
         <v>-0.81</v>
       </c>
-      <c r="I11" s="129">
+      <c r="I11" s="130">
         <v>-5.23</v>
       </c>
-      <c r="J11" s="124">
+      <c r="J11" s="121">
         <v>-1.39</v>
       </c>
-      <c r="K11" s="121">
+      <c r="K11" s="118">
         <v>-9.57</v>
       </c>
-      <c r="L11" s="130">
+      <c r="L11" s="119">
         <v>-7.18</v>
       </c>
-      <c r="M11" s="118">
+      <c r="M11" s="122">
         <v>-7.62</v>
       </c>
-      <c r="N11" s="122">
+      <c r="N11" s="125">
         <v>-8.69</v>
       </c>
-      <c r="O11" s="125">
+      <c r="O11" s="129">
         <v>-7.37</v>
       </c>
-      <c r="P11" s="126">
+      <c r="P11" s="123">
         <v>-8.56</v>
       </c>
-      <c r="Q11" s="119">
+      <c r="Q11" s="120">
         <v>-8.63</v>
       </c>
-      <c r="R11" s="127">
+      <c r="R11" s="126">
         <v>-4.28</v>
       </c>
-      <c r="S11" s="120">
+      <c r="S11" s="127">
         <v>-8.56</v>
       </c>
       <c r="T11" s="128">
-        <v>-7.56</v>
+        <v>-16.81</v>
       </c>
     </row>
     <row r="12">
@@ -9926,7 +9926,7 @@
       <c r="C12" t="str">
         <v>002579</v>
       </c>
-      <c r="D12" s="143" t="str">
+      <c r="D12" s="135" t="str">
         <v>净买: 4403.72万</v>
       </c>
       <c r="E12">
@@ -9941,41 +9941,41 @@
       <c r="H12">
         <v>-2.68</v>
       </c>
-      <c r="I12" s="137">
+      <c r="I12" s="136">
         <v>13.04</v>
       </c>
-      <c r="J12" s="131">
+      <c r="J12" s="143">
         <v>12.54</v>
       </c>
-      <c r="K12" s="132">
+      <c r="K12" s="131">
         <v>7.97</v>
       </c>
       <c r="L12" s="133">
         <v>12.54</v>
       </c>
-      <c r="M12" s="139">
+      <c r="M12" s="134">
         <v>7.1</v>
       </c>
-      <c r="N12" s="138">
+      <c r="N12" s="137">
         <v>-3.62</v>
       </c>
-      <c r="O12" s="134">
+      <c r="O12" s="138">
         <v>-2.97</v>
       </c>
-      <c r="P12" s="141">
+      <c r="P12" s="140">
         <v>-5.36</v>
       </c>
-      <c r="Q12" s="135">
+      <c r="Q12" s="132">
         <v>-3.7</v>
       </c>
-      <c r="R12" s="136">
+      <c r="R12" s="141">
         <v>-10.07</v>
       </c>
-      <c r="S12" s="140">
+      <c r="S12" s="139">
         <v>-6.59</v>
       </c>
       <c r="T12" s="142">
-        <v>-3.99</v>
+        <v>-4.42</v>
       </c>
     </row>
     <row r="13">
@@ -9988,7 +9988,7 @@
       <c r="C13" t="str">
         <v>002229</v>
       </c>
-      <c r="D13" s="144" t="str">
+      <c r="D13" s="145" t="str">
         <v>净卖: -4629.75万</v>
       </c>
       <c r="E13">
@@ -10003,41 +10003,41 @@
       <c r="H13">
         <v>3.11</v>
       </c>
-      <c r="I13" s="153">
+      <c r="I13" s="146">
         <v>-7.78</v>
       </c>
-      <c r="J13" s="149">
+      <c r="J13" s="151">
         <v>-8.44</v>
       </c>
       <c r="K13" s="154">
         <v>-11.23</v>
       </c>
-      <c r="L13" s="151">
+      <c r="L13" s="147">
         <v>-12.22</v>
       </c>
-      <c r="M13" s="145">
+      <c r="M13" s="155">
         <v>-10.66</v>
       </c>
-      <c r="N13" s="150">
+      <c r="N13" s="152">
         <v>-6.65</v>
       </c>
-      <c r="O13" s="146">
+      <c r="O13" s="144">
         <v>-7.74</v>
       </c>
-      <c r="P13" s="155">
+      <c r="P13" s="148">
         <v>-7.69</v>
       </c>
-      <c r="Q13" s="156">
+      <c r="Q13" s="149">
         <v>-11.37</v>
       </c>
-      <c r="R13" s="147">
+      <c r="R13" s="150">
         <v>-10.8</v>
       </c>
-      <c r="S13" s="152">
+      <c r="S13" s="156">
         <v>-13.68</v>
       </c>
-      <c r="T13" s="148">
-        <v>-8.58</v>
+      <c r="T13" s="153">
+        <v>-10.66</v>
       </c>
     </row>
     <row r="14">
@@ -10050,7 +10050,7 @@
       <c r="C14" t="str">
         <v>000657</v>
       </c>
-      <c r="D14" s="161" t="str">
+      <c r="D14" s="160" t="str">
         <v>净卖: -6184.73万</v>
       </c>
       <c r="E14">
@@ -10065,41 +10065,41 @@
       <c r="H14">
         <v>-2</v>
       </c>
-      <c r="I14" s="169">
+      <c r="I14" s="161">
         <v>-8.16</v>
       </c>
-      <c r="J14" s="166">
+      <c r="J14" s="169">
         <v>-13.48</v>
       </c>
-      <c r="K14" s="157">
+      <c r="K14" s="162">
         <v>-14.93</v>
       </c>
-      <c r="L14" s="162">
+      <c r="L14" s="165">
         <v>-15.36</v>
       </c>
-      <c r="M14" s="158">
+      <c r="M14" s="166">
         <v>-15.2</v>
       </c>
-      <c r="N14" s="163">
+      <c r="N14" s="167">
         <v>-13.43</v>
       </c>
-      <c r="O14" s="167">
+      <c r="O14" s="168">
         <v>-13.1</v>
       </c>
-      <c r="P14" s="159">
+      <c r="P14" s="163">
         <v>-11.6</v>
       </c>
-      <c r="Q14" s="164">
+      <c r="Q14" s="157">
         <v>-10.74</v>
       </c>
-      <c r="R14" s="165">
+      <c r="R14" s="164">
         <v>-10.9</v>
       </c>
-      <c r="S14" s="168">
+      <c r="S14" s="159">
         <v>-8.81</v>
       </c>
-      <c r="T14" s="160">
-        <v>214.39</v>
+      <c r="T14" s="158">
+        <v>210.47</v>
       </c>
     </row>
     <row r="15">
@@ -10112,7 +10112,7 @@
       <c r="C15" t="str">
         <v>002670</v>
       </c>
-      <c r="D15" s="176" t="str">
+      <c r="D15" s="175" t="str">
         <v>净卖: -7597.74万</v>
       </c>
       <c r="E15">
@@ -10127,41 +10127,41 @@
       <c r="H15">
         <v>0.45</v>
       </c>
-      <c r="I15" s="181">
+      <c r="I15" s="179">
         <v>1.89</v>
       </c>
-      <c r="J15" s="182">
+      <c r="J15" s="170">
         <v>-1.79</v>
       </c>
-      <c r="K15" s="170">
+      <c r="K15" s="180">
         <v>-1.79</v>
       </c>
-      <c r="L15" s="171">
+      <c r="L15" s="176">
         <v>-3.03</v>
       </c>
-      <c r="M15" s="172">
+      <c r="M15" s="181">
         <v>-4.83</v>
       </c>
-      <c r="N15" s="175">
+      <c r="N15" s="171">
         <v>-3.73</v>
       </c>
-      <c r="O15" s="173">
+      <c r="O15" s="178">
         <v>-3.38</v>
       </c>
-      <c r="P15" s="174">
+      <c r="P15" s="177">
         <v>-4.28</v>
       </c>
-      <c r="Q15" s="178">
+      <c r="Q15" s="172">
         <v>-7.71</v>
       </c>
-      <c r="R15" s="177">
+      <c r="R15" s="182">
         <v>-3.98</v>
       </c>
-      <c r="S15" s="179">
+      <c r="S15" s="173">
         <v>-2.84</v>
       </c>
-      <c r="T15" s="180">
-        <v>-26.97</v>
+      <c r="T15" s="174">
+        <v>-34.28</v>
       </c>
     </row>
     <row r="16">
@@ -10174,7 +10174,7 @@
       <c r="C16" t="str">
         <v>688039</v>
       </c>
-      <c r="D16" s="192" t="str">
+      <c r="D16" s="195" t="str">
         <v>净买: 3066.00万</v>
       </c>
       <c r="E16">
@@ -10189,41 +10189,41 @@
       <c r="H16">
         <v>7.16</v>
       </c>
-      <c r="I16" s="189">
+      <c r="I16" s="185">
         <v>11.98</v>
       </c>
-      <c r="J16" s="190">
+      <c r="J16" s="193">
         <v>16.69</v>
       </c>
-      <c r="K16" s="191">
+      <c r="K16" s="188">
         <v>3.41</v>
       </c>
-      <c r="L16" s="193">
+      <c r="L16" s="186">
         <v>0.07</v>
       </c>
-      <c r="M16" s="194">
+      <c r="M16" s="189">
         <v>-5.26</v>
       </c>
-      <c r="N16" s="195">
+      <c r="N16" s="190">
         <v>-3.41</v>
       </c>
-      <c r="O16" s="185">
+      <c r="O16" s="183">
         <v>-5.04</v>
       </c>
-      <c r="P16" s="184">
+      <c r="P16" s="187">
         <v>-10.52</v>
       </c>
-      <c r="Q16" s="186">
+      <c r="Q16" s="184">
         <v>-7.78</v>
       </c>
-      <c r="R16" s="187">
+      <c r="R16" s="191">
         <v>-6.1</v>
       </c>
-      <c r="S16" s="188">
+      <c r="S16" s="194">
         <v>-7.34</v>
       </c>
-      <c r="T16" s="183">
-        <v>-19.45</v>
+      <c r="T16" s="192">
+        <v>-21.69</v>
       </c>
     </row>
     <row r="17">
@@ -10236,7 +10236,7 @@
       <c r="C17" t="str">
         <v>600408</v>
       </c>
-      <c r="D17" s="200" t="str">
+      <c r="D17" s="197" t="str">
         <v>净买: 1877.05万</v>
       </c>
       <c r="E17">
@@ -10251,22 +10251,22 @@
       <c r="H17">
         <v>-4.45</v>
       </c>
-      <c r="I17" s="201">
+      <c r="I17" s="204">
         <v>15.2</v>
       </c>
-      <c r="J17" s="202">
+      <c r="J17" s="198">
         <v>26.72</v>
       </c>
-      <c r="K17" s="204">
+      <c r="K17" s="201">
         <v>39.46</v>
       </c>
-      <c r="L17" s="203">
+      <c r="L17" s="196">
         <v>53.43</v>
       </c>
-      <c r="M17" s="205">
+      <c r="M17" s="199">
         <v>68.87</v>
       </c>
-      <c r="N17" s="197">
+      <c r="N17" s="205">
         <v>52.7</v>
       </c>
       <c r="O17" s="206">
@@ -10275,17 +10275,17 @@
       <c r="P17" s="207">
         <v>24.26</v>
       </c>
-      <c r="Q17" s="208">
+      <c r="Q17" s="200">
         <v>14.95</v>
       </c>
-      <c r="R17" s="198">
+      <c r="R17" s="208">
         <v>10.54</v>
       </c>
-      <c r="S17" s="199">
+      <c r="S17" s="202">
         <v>11.52</v>
       </c>
-      <c r="T17" s="196">
-        <v>-22.3</v>
+      <c r="T17" s="203">
+        <v>-21.81</v>
       </c>
     </row>
     <row r="18">
@@ -10298,7 +10298,7 @@
       <c r="C18" t="str">
         <v>601566</v>
       </c>
-      <c r="D18" s="219" t="str">
+      <c r="D18" s="211" t="str">
         <v>净买: 5226.66万</v>
       </c>
       <c r="E18">
@@ -10313,41 +10313,41 @@
       <c r="H18">
         <v>10.02</v>
       </c>
-      <c r="I18" s="220">
+      <c r="I18" s="214">
         <v>0</v>
       </c>
       <c r="J18" s="221">
         <v>9.97</v>
       </c>
-      <c r="K18" s="209">
+      <c r="K18" s="218">
         <v>20.95</v>
       </c>
-      <c r="L18" s="217">
+      <c r="L18" s="215">
         <v>33.02</v>
       </c>
-      <c r="M18" s="214">
+      <c r="M18" s="219">
         <v>19.73</v>
       </c>
-      <c r="N18" s="215">
+      <c r="N18" s="212">
         <v>7.73</v>
       </c>
-      <c r="O18" s="210">
+      <c r="O18" s="209">
         <v>3.32</v>
       </c>
-      <c r="P18" s="212">
+      <c r="P18" s="220">
         <v>-5.35</v>
       </c>
-      <c r="Q18" s="211">
+      <c r="Q18" s="216">
         <v>-6.94</v>
       </c>
-      <c r="R18" s="216">
+      <c r="R18" s="213">
         <v>-3.03</v>
       </c>
-      <c r="S18" s="218">
+      <c r="S18" s="210">
         <v>-2.46</v>
       </c>
-      <c r="T18" s="213">
-        <v>-21.82</v>
+      <c r="T18" s="217">
+        <v>-21.17</v>
       </c>
     </row>
     <row r="19">
@@ -10360,7 +10360,7 @@
       <c r="C19" t="str">
         <v>002029</v>
       </c>
-      <c r="D19" s="224" t="str">
+      <c r="D19" s="232" t="str">
         <v>净卖: -1276.40万</v>
       </c>
       <c r="E19">
@@ -10375,41 +10375,41 @@
       <c r="H19">
         <v>0</v>
       </c>
-      <c r="I19" s="230">
+      <c r="I19" s="224">
         <v>9.97</v>
       </c>
-      <c r="J19" s="233">
+      <c r="J19" s="227">
         <v>1.88</v>
       </c>
-      <c r="K19" s="223">
+      <c r="K19" s="228">
         <v>-2.35</v>
       </c>
-      <c r="L19" s="225">
+      <c r="L19" s="233">
         <v>-9.97</v>
       </c>
-      <c r="M19" s="226">
+      <c r="M19" s="234">
         <v>-11.67</v>
       </c>
-      <c r="N19" s="231">
+      <c r="N19" s="229">
         <v>-8</v>
       </c>
-      <c r="O19" s="227">
+      <c r="O19" s="222">
         <v>1.22</v>
       </c>
-      <c r="P19" s="228">
+      <c r="P19" s="225">
         <v>0.85</v>
       </c>
-      <c r="Q19" s="234">
+      <c r="Q19" s="226">
         <v>3.01</v>
       </c>
-      <c r="R19" s="222">
+      <c r="R19" s="223">
         <v>1.69</v>
       </c>
-      <c r="S19" s="229">
+      <c r="S19" s="230">
         <v>0.09</v>
       </c>
-      <c r="T19" s="232">
-        <v>-7.34</v>
+      <c r="T19" s="231">
+        <v>-9.22</v>
       </c>
     </row>
     <row r="20">
@@ -10422,7 +10422,7 @@
       <c r="C20" t="str">
         <v>601566</v>
       </c>
-      <c r="D20" s="244" t="str">
+      <c r="D20" s="243" t="str">
         <v>净卖: -2737.55万</v>
       </c>
       <c r="E20">
@@ -10437,41 +10437,41 @@
       <c r="H20">
         <v>4.01</v>
       </c>
-      <c r="I20" s="245">
+      <c r="I20" s="240">
         <v>5.75</v>
       </c>
-      <c r="J20" s="237">
+      <c r="J20" s="244">
         <v>16.3</v>
       </c>
-      <c r="K20" s="239">
+      <c r="K20" s="245">
         <v>4.67</v>
       </c>
-      <c r="L20" s="246">
+      <c r="L20" s="235">
         <v>-5.81</v>
       </c>
-      <c r="M20" s="247">
+      <c r="M20" s="236">
         <v>-9.67</v>
       </c>
-      <c r="N20" s="242">
+      <c r="N20" s="237">
         <v>-17.25</v>
       </c>
-      <c r="O20" s="235">
+      <c r="O20" s="241">
         <v>-18.64</v>
       </c>
-      <c r="P20" s="240">
+      <c r="P20" s="238">
         <v>-15.22</v>
       </c>
-      <c r="Q20" s="243">
+      <c r="Q20" s="242">
         <v>-14.72</v>
       </c>
-      <c r="R20" s="236">
+      <c r="R20" s="239">
         <v>-10.8</v>
       </c>
-      <c r="S20" s="238">
+      <c r="S20" s="246">
         <v>-6.19</v>
       </c>
-      <c r="T20" s="241">
-        <v>-31.65</v>
+      <c r="T20" s="247">
+        <v>-31.08</v>
       </c>
     </row>
     <row r="21">
@@ -10484,7 +10484,7 @@
       <c r="C21" t="str">
         <v>601566</v>
       </c>
-      <c r="D21" s="254" t="str">
+      <c r="D21" s="252" t="str">
         <v>净卖: -5218.09万</v>
       </c>
       <c r="E21">
@@ -10499,13 +10499,13 @@
       <c r="H21">
         <v>7.11</v>
       </c>
-      <c r="I21" s="253">
+      <c r="I21" s="248">
         <v>2.68</v>
       </c>
-      <c r="J21" s="251">
+      <c r="J21" s="249">
         <v>-7.59</v>
       </c>
-      <c r="K21" s="258">
+      <c r="K21" s="250">
         <v>-16.84</v>
       </c>
       <c r="L21" s="255">
@@ -10514,26 +10514,26 @@
       <c r="M21" s="256">
         <v>-26.94</v>
       </c>
-      <c r="N21" s="259">
+      <c r="N21" s="257">
         <v>-28.17</v>
       </c>
-      <c r="O21" s="252">
+      <c r="O21" s="253">
         <v>-25.15</v>
       </c>
-      <c r="P21" s="257">
+      <c r="P21" s="254">
         <v>-24.71</v>
       </c>
-      <c r="Q21" s="260">
+      <c r="Q21" s="258">
         <v>-21.25</v>
       </c>
-      <c r="R21" s="248">
+      <c r="R21" s="259">
         <v>-17.18</v>
       </c>
-      <c r="S21" s="249">
+      <c r="S21" s="260">
         <v>-25.43</v>
       </c>
-      <c r="T21" s="250">
-        <v>-39.65</v>
+      <c r="T21" s="251">
+        <v>-39.15</v>
       </c>
     </row>
     <row r="22">
@@ -10546,7 +10546,7 @@
       <c r="C22" t="str">
         <v>600756</v>
       </c>
-      <c r="D22" s="272" t="str">
+      <c r="D22" s="271" t="str">
         <v>净卖: -2369.10万</v>
       </c>
       <c r="E22">
@@ -10561,41 +10561,41 @@
       <c r="H22">
         <v>-1.6</v>
       </c>
-      <c r="I22" s="268">
+      <c r="I22" s="267">
         <v>1.46</v>
       </c>
-      <c r="J22" s="271">
+      <c r="J22" s="268">
         <v>-4.63</v>
       </c>
-      <c r="K22" s="273">
+      <c r="K22" s="269">
         <v>-3.97</v>
       </c>
-      <c r="L22" s="269">
+      <c r="L22" s="273">
         <v>-13.57</v>
       </c>
-      <c r="M22" s="265">
+      <c r="M22" s="272">
         <v>-21.09</v>
       </c>
-      <c r="N22" s="261">
+      <c r="N22" s="263">
         <v>-19.75</v>
       </c>
-      <c r="O22" s="262">
+      <c r="O22" s="261">
         <v>-18.25</v>
       </c>
-      <c r="P22" s="270">
+      <c r="P22" s="264">
         <v>-20.84</v>
       </c>
-      <c r="Q22" s="266">
+      <c r="Q22" s="265">
         <v>-21.42</v>
       </c>
-      <c r="R22" s="263">
+      <c r="R22" s="270">
         <v>-23.17</v>
       </c>
-      <c r="S22" s="264">
+      <c r="S22" s="262">
         <v>-24.43</v>
       </c>
-      <c r="T22" s="267">
-        <v>-29.94</v>
+      <c r="T22" s="266">
+        <v>-32.03</v>
       </c>
     </row>
     <row r="23">
@@ -10608,7 +10608,7 @@
       <c r="C23" t="str">
         <v>603696</v>
       </c>
-      <c r="D23" s="286" t="str">
+      <c r="D23" s="276" t="str">
         <v>净买: 3978.78万</v>
       </c>
       <c r="E23">
@@ -10623,41 +10623,41 @@
       <c r="H23">
         <v>9.98</v>
       </c>
-      <c r="I23" s="274">
+      <c r="I23" s="285">
         <v>0</v>
       </c>
-      <c r="J23" s="276">
+      <c r="J23" s="277">
         <v>10.01</v>
       </c>
-      <c r="K23" s="277">
+      <c r="K23" s="282">
         <v>21.01</v>
       </c>
       <c r="L23" s="278">
         <v>33.13</v>
       </c>
-      <c r="M23" s="279">
+      <c r="M23" s="286">
         <v>46.43</v>
       </c>
-      <c r="N23" s="283">
+      <c r="N23" s="279">
         <v>43.01</v>
       </c>
-      <c r="O23" s="284">
+      <c r="O23" s="283">
         <v>28.71</v>
       </c>
-      <c r="P23" s="285">
+      <c r="P23" s="280">
         <v>24.74</v>
       </c>
-      <c r="Q23" s="280">
+      <c r="Q23" s="274">
         <v>27.91</v>
       </c>
-      <c r="R23" s="281">
+      <c r="R23" s="284">
         <v>40.71</v>
       </c>
-      <c r="S23" s="282">
+      <c r="S23" s="275">
         <v>26.66</v>
       </c>
-      <c r="T23" s="275">
-        <v>-0.75</v>
+      <c r="T23" s="281">
+        <v>-1.93</v>
       </c>
     </row>
     <row r="24">
@@ -10670,7 +10670,7 @@
       <c r="C24" t="str">
         <v>002682</v>
       </c>
-      <c r="D24" s="291" t="str">
+      <c r="D24" s="293" t="str">
         <v>净买: 2499.06万</v>
       </c>
       <c r="E24">
@@ -10685,41 +10685,41 @@
       <c r="H24">
         <v>5.99</v>
       </c>
-      <c r="I24" s="292">
+      <c r="I24" s="290">
         <v>3.77</v>
       </c>
       <c r="J24" s="299">
         <v>14.2</v>
       </c>
-      <c r="K24" s="295">
+      <c r="K24" s="287">
         <v>25.65</v>
       </c>
-      <c r="L24" s="293">
+      <c r="L24" s="298">
         <v>38.26</v>
       </c>
-      <c r="M24" s="287">
+      <c r="M24" s="294">
         <v>52.03</v>
       </c>
-      <c r="N24" s="288">
+      <c r="N24" s="295">
         <v>42.9</v>
       </c>
-      <c r="O24" s="289">
+      <c r="O24" s="291">
         <v>57.25</v>
       </c>
-      <c r="P24" s="294">
+      <c r="P24" s="288">
         <v>72.9</v>
       </c>
       <c r="Q24" s="296">
         <v>55.65</v>
       </c>
-      <c r="R24" s="297">
+      <c r="R24" s="289">
         <v>40.14</v>
       </c>
-      <c r="S24" s="290">
+      <c r="S24" s="292">
         <v>42.75</v>
       </c>
-      <c r="T24" s="298">
-        <v>-12.75</v>
+      <c r="T24" s="297">
+        <v>-13.91</v>
       </c>
     </row>
     <row r="25">
@@ -10750,38 +10750,38 @@
       <c r="I25" s="312">
         <v>12.28</v>
       </c>
-      <c r="J25" s="307">
+      <c r="J25" s="305">
         <v>23.53</v>
       </c>
-      <c r="K25" s="302">
+      <c r="K25" s="309">
         <v>35.87</v>
       </c>
-      <c r="L25" s="308">
+      <c r="L25" s="300">
         <v>32.7</v>
       </c>
-      <c r="M25" s="303">
+      <c r="M25" s="307">
         <v>19.43</v>
       </c>
-      <c r="N25" s="300">
+      <c r="N25" s="308">
         <v>15.74</v>
       </c>
-      <c r="O25" s="304">
+      <c r="O25" s="310">
         <v>18.69</v>
       </c>
-      <c r="P25" s="309">
+      <c r="P25" s="301">
         <v>30.57</v>
       </c>
-      <c r="Q25" s="305">
+      <c r="Q25" s="302">
         <v>17.53</v>
       </c>
-      <c r="R25" s="310">
+      <c r="R25" s="311">
         <v>10.73</v>
       </c>
-      <c r="S25" s="311">
+      <c r="S25" s="303">
         <v>16.49</v>
       </c>
-      <c r="T25" s="301">
-        <v>-7.9</v>
+      <c r="T25" s="304">
+        <v>-9</v>
       </c>
     </row>
     <row r="26">
@@ -10794,7 +10794,7 @@
       <c r="C26" t="str">
         <v>603696</v>
       </c>
-      <c r="D26" s="324" t="str">
+      <c r="D26" s="319" t="str">
         <v>净卖: -3631.64万</v>
       </c>
       <c r="E26">
@@ -10809,41 +10809,41 @@
       <c r="H26">
         <v>9.08</v>
       </c>
-      <c r="I26" s="313">
+      <c r="I26" s="320">
         <v>-10.47</v>
       </c>
-      <c r="J26" s="325">
+      <c r="J26" s="321">
         <v>-19.42</v>
       </c>
-      <c r="K26" s="314">
+      <c r="K26" s="313">
         <v>-21.91</v>
       </c>
-      <c r="L26" s="317">
+      <c r="L26" s="314">
         <v>-19.92</v>
       </c>
-      <c r="M26" s="315">
+      <c r="M26" s="324">
         <v>-11.91</v>
       </c>
-      <c r="N26" s="321">
+      <c r="N26" s="325">
         <v>-20.7</v>
       </c>
-      <c r="O26" s="318">
+      <c r="O26" s="322">
         <v>-25.29</v>
       </c>
-      <c r="P26" s="322">
+      <c r="P26" s="315">
         <v>-21.4</v>
       </c>
-      <c r="Q26" s="319">
+      <c r="Q26" s="323">
         <v>-13.54</v>
       </c>
-      <c r="R26" s="320">
+      <c r="R26" s="316">
         <v>-4.9</v>
       </c>
-      <c r="S26" s="316">
+      <c r="S26" s="317">
         <v>4.59</v>
       </c>
-      <c r="T26" s="323">
-        <v>-37.86</v>
+      <c r="T26" s="318">
+        <v>-38.6</v>
       </c>
     </row>
     <row r="27">
@@ -10856,7 +10856,7 @@
       <c r="C27" t="str">
         <v>002682</v>
       </c>
-      <c r="D27" s="329" t="str">
+      <c r="D27" s="338" t="str">
         <v>净卖: -4674.28万</v>
       </c>
       <c r="E27">
@@ -10871,41 +10871,41 @@
       <c r="H27">
         <v>-4.33</v>
       </c>
-      <c r="I27" s="330">
+      <c r="I27" s="336">
         <v>14.93</v>
       </c>
       <c r="J27" s="333">
         <v>3.47</v>
       </c>
-      <c r="K27" s="334">
+      <c r="K27" s="326">
         <v>-6.84</v>
       </c>
-      <c r="L27" s="331">
+      <c r="L27" s="327">
         <v>-5.11</v>
       </c>
-      <c r="M27" s="335">
+      <c r="M27" s="334">
         <v>-10.89</v>
       </c>
-      <c r="N27" s="326">
+      <c r="N27" s="337">
         <v>-19.36</v>
       </c>
-      <c r="O27" s="332">
+      <c r="O27" s="330">
         <v>-21</v>
       </c>
-      <c r="P27" s="336">
+      <c r="P27" s="335">
         <v>-20.33</v>
       </c>
-      <c r="Q27" s="337">
+      <c r="Q27" s="331">
         <v>-12.43</v>
       </c>
       <c r="R27" s="328">
         <v>-14.26</v>
       </c>
-      <c r="S27" s="338">
+      <c r="S27" s="329">
         <v>-7.8</v>
       </c>
-      <c r="T27" s="327">
-        <v>-42</v>
+      <c r="T27" s="332">
+        <v>-42.77</v>
       </c>
     </row>
     <row r="28">
@@ -10918,7 +10918,7 @@
       <c r="C28" t="str">
         <v>600693</v>
       </c>
-      <c r="D28" s="342" t="str">
+      <c r="D28" s="340" t="str">
         <v>净买: 4441.53万</v>
       </c>
       <c r="E28">
@@ -10933,41 +10933,41 @@
       <c r="H28">
         <v>1.81</v>
       </c>
-      <c r="I28" s="343">
+      <c r="I28" s="348">
         <v>8.04</v>
       </c>
-      <c r="J28" s="351">
+      <c r="J28" s="341">
         <v>15.95</v>
       </c>
-      <c r="K28" s="344">
+      <c r="K28" s="342">
         <v>10.22</v>
       </c>
-      <c r="L28" s="340">
+      <c r="L28" s="345">
         <v>13.45</v>
       </c>
-      <c r="M28" s="347">
+      <c r="M28" s="339">
         <v>12.33</v>
       </c>
-      <c r="N28" s="341">
+      <c r="N28" s="343">
         <v>23.53</v>
       </c>
-      <c r="O28" s="345">
+      <c r="O28" s="349">
         <v>28.54</v>
       </c>
-      <c r="P28" s="348">
+      <c r="P28" s="350">
         <v>41.4</v>
       </c>
-      <c r="Q28" s="339">
+      <c r="Q28" s="344">
         <v>37.84</v>
       </c>
-      <c r="R28" s="349">
+      <c r="R28" s="351">
         <v>44.23</v>
       </c>
-      <c r="S28" s="350">
+      <c r="S28" s="346">
         <v>30.52</v>
       </c>
-      <c r="T28" s="346">
-        <v>-20.9</v>
+      <c r="T28" s="347">
+        <v>-22.87</v>
       </c>
     </row>
     <row r="29">
@@ -10980,7 +10980,7 @@
       <c r="C29" t="str">
         <v>603696</v>
       </c>
-      <c r="D29" s="358" t="str">
+      <c r="D29" s="361" t="str">
         <v>净卖: -3147.63万</v>
       </c>
       <c r="E29">
@@ -10995,41 +10995,41 @@
       <c r="H29">
         <v>2.92</v>
       </c>
-      <c r="I29" s="363">
+      <c r="I29" s="359">
         <v>-12.53</v>
       </c>
-      <c r="J29" s="359">
+      <c r="J29" s="354">
         <v>-17.6</v>
       </c>
       <c r="K29" s="355">
         <v>-13.3</v>
       </c>
-      <c r="L29" s="364">
+      <c r="L29" s="362">
         <v>-4.64</v>
       </c>
-      <c r="M29" s="352">
+      <c r="M29" s="363">
         <v>4.89</v>
       </c>
-      <c r="N29" s="356">
+      <c r="N29" s="364">
         <v>15.36</v>
       </c>
-      <c r="O29" s="361">
+      <c r="O29" s="356">
         <v>13.73</v>
       </c>
-      <c r="P29" s="353">
+      <c r="P29" s="352">
         <v>12.4</v>
       </c>
       <c r="Q29" s="357">
         <v>1.16</v>
       </c>
-      <c r="R29" s="362">
+      <c r="R29" s="358">
         <v>-8.97</v>
       </c>
-      <c r="S29" s="354">
+      <c r="S29" s="353">
         <v>-12.96</v>
       </c>
       <c r="T29" s="360">
-        <v>-31.46</v>
+        <v>-32.27</v>
       </c>
     </row>
     <row r="30">
@@ -11042,7 +11042,7 @@
       <c r="C30" t="str">
         <v>600693</v>
       </c>
-      <c r="D30" s="377" t="str">
+      <c r="D30" s="368" t="str">
         <v>净卖: -5308.96万</v>
       </c>
       <c r="E30">
@@ -11057,41 +11057,41 @@
       <c r="H30">
         <v>2.51</v>
       </c>
-      <c r="I30" s="374">
+      <c r="I30" s="372">
         <v>0.41</v>
       </c>
-      <c r="J30" s="365">
+      <c r="J30" s="373">
         <v>-0.58</v>
       </c>
-      <c r="K30" s="366">
+      <c r="K30" s="377">
         <v>9.33</v>
       </c>
-      <c r="L30" s="367">
+      <c r="L30" s="374">
         <v>13.77</v>
       </c>
-      <c r="M30" s="375">
+      <c r="M30" s="365">
         <v>25.15</v>
       </c>
-      <c r="N30" s="372">
+      <c r="N30" s="366">
         <v>22</v>
       </c>
-      <c r="O30" s="368">
+      <c r="O30" s="375">
         <v>27.65</v>
       </c>
-      <c r="P30" s="373">
+      <c r="P30" s="371">
         <v>15.52</v>
       </c>
-      <c r="Q30" s="369">
+      <c r="Q30" s="376">
         <v>3.97</v>
       </c>
-      <c r="R30" s="370">
+      <c r="R30" s="369">
         <v>3.97</v>
       </c>
-      <c r="S30" s="371">
+      <c r="S30" s="367">
         <v>7.29</v>
       </c>
-      <c r="T30" s="376">
-        <v>-29.99</v>
+      <c r="T30" s="370">
+        <v>-31.74</v>
       </c>
     </row>
     <row r="31">
@@ -11104,7 +11104,7 @@
       <c r="C31" t="str">
         <v>600280</v>
       </c>
-      <c r="D31" s="385" t="str">
+      <c r="D31" s="383" t="str">
         <v>净买: 2343.21万</v>
       </c>
       <c r="E31">
@@ -11119,41 +11119,41 @@
       <c r="H31">
         <v>1.88</v>
       </c>
-      <c r="I31" s="380">
+      <c r="I31" s="390">
         <v>8.08</v>
       </c>
-      <c r="J31" s="389">
+      <c r="J31" s="378">
         <v>17.78</v>
       </c>
-      <c r="K31" s="390">
+      <c r="K31" s="379">
         <v>12.93</v>
       </c>
-      <c r="L31" s="378">
+      <c r="L31" s="384">
         <v>4.39</v>
       </c>
-      <c r="M31" s="384">
+      <c r="M31" s="385">
         <v>5.54</v>
       </c>
-      <c r="N31" s="386">
+      <c r="N31" s="387">
         <v>1.85</v>
       </c>
-      <c r="O31" s="387">
+      <c r="O31" s="388">
         <v>-1.15</v>
       </c>
-      <c r="P31" s="381">
+      <c r="P31" s="380">
         <v>-3</v>
       </c>
       <c r="Q31" s="382">
         <v>-7.85</v>
       </c>
-      <c r="R31" s="388">
+      <c r="R31" s="381">
         <v>-11.09</v>
       </c>
-      <c r="S31" s="383">
+      <c r="S31" s="389">
         <v>-10.16</v>
       </c>
-      <c r="T31" s="379">
-        <v>-28.18</v>
+      <c r="T31" s="386">
+        <v>-29.1</v>
       </c>
     </row>
     <row r="32">
@@ -11181,41 +11181,41 @@
       <c r="H32">
         <v>-3.92</v>
       </c>
-      <c r="I32" s="393">
+      <c r="I32" s="398">
         <v>-0.2</v>
       </c>
-      <c r="J32" s="395">
+      <c r="J32" s="403">
         <v>-7.76</v>
       </c>
-      <c r="K32" s="399">
+      <c r="K32" s="394">
         <v>-6.73</v>
       </c>
       <c r="L32" s="402">
         <v>-10</v>
       </c>
-      <c r="M32" s="396">
+      <c r="M32" s="391">
         <v>-12.65</v>
       </c>
-      <c r="N32" s="403">
+      <c r="N32" s="399">
         <v>-14.29</v>
       </c>
-      <c r="O32" s="391">
+      <c r="O32" s="395">
         <v>-18.57</v>
       </c>
-      <c r="P32" s="392">
+      <c r="P32" s="400">
         <v>-21.43</v>
       </c>
-      <c r="Q32" s="397">
+      <c r="Q32" s="396">
         <v>-20.61</v>
       </c>
-      <c r="R32" s="398">
+      <c r="R32" s="392">
         <v>-16.33</v>
       </c>
-      <c r="S32" s="400">
+      <c r="S32" s="393">
         <v>-15.92</v>
       </c>
-      <c r="T32" s="394">
-        <v>-36.53</v>
+      <c r="T32" s="397">
+        <v>-37.35</v>
       </c>
     </row>
     <row r="33">
@@ -11228,7 +11228,7 @@
       <c r="C33" t="str">
         <v>002759</v>
       </c>
-      <c r="D33" s="408" t="str">
+      <c r="D33" s="407" t="str">
         <v>净买: 8490.49万</v>
       </c>
       <c r="E33">
@@ -11243,41 +11243,41 @@
       <c r="H33">
         <v>-3.82</v>
       </c>
-      <c r="I33" s="414">
+      <c r="I33" s="408">
         <v>11.08</v>
       </c>
-      <c r="J33" s="409">
+      <c r="J33" s="416">
         <v>22.19</v>
       </c>
-      <c r="K33" s="412">
+      <c r="K33" s="413">
         <v>22.69</v>
       </c>
-      <c r="L33" s="415">
+      <c r="L33" s="409">
         <v>13.63</v>
       </c>
       <c r="M33" s="404">
         <v>14.61</v>
       </c>
-      <c r="N33" s="416">
+      <c r="N33" s="414">
         <v>26.07</v>
       </c>
-      <c r="O33" s="405">
+      <c r="O33" s="415">
         <v>26.51</v>
       </c>
       <c r="P33" s="410">
         <v>18.86</v>
       </c>
-      <c r="Q33" s="406">
+      <c r="Q33" s="411">
         <v>15.77</v>
       </c>
-      <c r="R33" s="413">
+      <c r="R33" s="412">
         <v>13.87</v>
       </c>
-      <c r="S33" s="411">
+      <c r="S33" s="406">
         <v>15.03</v>
       </c>
-      <c r="T33" s="407">
-        <v>-14.86</v>
+      <c r="T33" s="405">
+        <v>-13.9</v>
       </c>
     </row>
     <row r="34">
@@ -11290,7 +11290,7 @@
       <c r="C34" t="str">
         <v>002792</v>
       </c>
-      <c r="D34" s="425" t="str">
+      <c r="D34" s="420" t="str">
         <v>净买: 8322.30万</v>
       </c>
       <c r="E34">
@@ -11305,41 +11305,41 @@
       <c r="H34">
         <v>0.05</v>
       </c>
-      <c r="I34" s="417">
+      <c r="I34" s="421">
         <v>7.5</v>
       </c>
-      <c r="J34" s="426">
+      <c r="J34" s="422">
         <v>15.33</v>
       </c>
-      <c r="K34" s="418">
+      <c r="K34" s="423">
         <v>19.23</v>
       </c>
-      <c r="L34" s="427">
+      <c r="L34" s="424">
         <v>31.17</v>
       </c>
-      <c r="M34" s="428">
+      <c r="M34" s="418">
         <v>44.28</v>
       </c>
-      <c r="N34" s="420">
+      <c r="N34" s="426">
         <v>53.02</v>
       </c>
-      <c r="O34" s="421">
+      <c r="O34" s="419">
         <v>68.33</v>
       </c>
-      <c r="P34" s="424">
+      <c r="P34" s="427">
         <v>76.16</v>
       </c>
-      <c r="Q34" s="422">
+      <c r="Q34" s="428">
         <v>58.53</v>
       </c>
       <c r="R34" s="429">
         <v>42.67</v>
       </c>
-      <c r="S34" s="423">
+      <c r="S34" s="425">
         <v>30.19</v>
       </c>
-      <c r="T34" s="419">
-        <v>33.13</v>
+      <c r="T34" s="417">
+        <v>28.85</v>
       </c>
     </row>
     <row r="35">
@@ -11352,7 +11352,7 @@
       <c r="C35" t="str">
         <v>002792</v>
       </c>
-      <c r="D35" s="436" t="str">
+      <c r="D35" s="441" t="str">
         <v>净卖: -7684.69万</v>
       </c>
       <c r="E35">
@@ -11367,41 +11367,41 @@
       <c r="H35">
         <v>2.25</v>
       </c>
-      <c r="I35" s="431">
+      <c r="I35" s="436">
         <v>4.92</v>
       </c>
-      <c r="J35" s="432">
+      <c r="J35" s="433">
         <v>8.47</v>
       </c>
-      <c r="K35" s="437">
+      <c r="K35" s="442">
         <v>19.33</v>
       </c>
-      <c r="L35" s="438">
+      <c r="L35" s="437">
         <v>31.26</v>
       </c>
-      <c r="M35" s="439">
+      <c r="M35" s="434">
         <v>39.21</v>
       </c>
-      <c r="N35" s="440">
+      <c r="N35" s="430">
         <v>53.14</v>
       </c>
-      <c r="O35" s="433">
+      <c r="O35" s="431">
         <v>60.26</v>
       </c>
-      <c r="P35" s="441">
+      <c r="P35" s="432">
         <v>44.23</v>
       </c>
-      <c r="Q35" s="434">
+      <c r="Q35" s="435">
         <v>29.8</v>
       </c>
-      <c r="R35" s="442">
+      <c r="R35" s="438">
         <v>18.44</v>
       </c>
-      <c r="S35" s="430">
+      <c r="S35" s="439">
         <v>17.43</v>
       </c>
-      <c r="T35" s="435">
-        <v>21.12</v>
+      <c r="T35" s="440">
+        <v>17.22</v>
       </c>
     </row>
     <row r="36">
@@ -11414,7 +11414,7 @@
       <c r="C36" t="str">
         <v>002759</v>
       </c>
-      <c r="D36" s="453" t="str">
+      <c r="D36" s="447" t="str">
         <v>净买: 1.00亿</v>
       </c>
       <c r="E36">
@@ -11432,38 +11432,38 @@
       <c r="I36" s="448">
         <v>6.73</v>
       </c>
-      <c r="J36" s="443">
+      <c r="J36" s="450">
         <v>7.11</v>
       </c>
-      <c r="K36" s="444">
+      <c r="K36" s="451">
         <v>0.63</v>
       </c>
-      <c r="L36" s="445">
+      <c r="L36" s="452">
         <v>-1.99</v>
       </c>
-      <c r="M36" s="449">
+      <c r="M36" s="453">
         <v>-3.59</v>
       </c>
-      <c r="N36" s="446">
+      <c r="N36" s="454">
         <v>-2.61</v>
       </c>
-      <c r="O36" s="451">
+      <c r="O36" s="455">
         <v>-7.82</v>
       </c>
-      <c r="P36" s="450">
+      <c r="P36" s="443">
         <v>-11.35</v>
       </c>
-      <c r="Q36" s="452">
+      <c r="Q36" s="445">
         <v>-5.64</v>
       </c>
-      <c r="R36" s="454">
+      <c r="R36" s="444">
         <v>-13.61</v>
       </c>
-      <c r="S36" s="447">
+      <c r="S36" s="449">
         <v>-12.5</v>
       </c>
-      <c r="T36" s="455">
-        <v>-27.92</v>
+      <c r="T36" s="446">
+        <v>-27.11</v>
       </c>
     </row>
     <row r="37">
@@ -11476,7 +11476,7 @@
       <c r="C37" t="str">
         <v>600776</v>
       </c>
-      <c r="D37" s="458" t="str">
+      <c r="D37" s="463" t="str">
         <v>净买: 5452.75万</v>
       </c>
       <c r="E37">
@@ -11491,41 +11491,41 @@
       <c r="H37">
         <v>10.02</v>
       </c>
-      <c r="I37" s="465">
+      <c r="I37" s="464">
         <v>0</v>
       </c>
-      <c r="J37" s="459">
+      <c r="J37" s="468">
         <v>10</v>
       </c>
-      <c r="K37" s="468">
+      <c r="K37" s="456">
         <v>16.57</v>
       </c>
-      <c r="L37" s="461">
+      <c r="L37" s="457">
         <v>4.91</v>
       </c>
-      <c r="M37" s="462">
+      <c r="M37" s="465">
         <v>-5.58</v>
       </c>
-      <c r="N37" s="456">
+      <c r="N37" s="466">
         <v>-15.01</v>
       </c>
-      <c r="O37" s="463">
+      <c r="O37" s="467">
         <v>-17.91</v>
       </c>
-      <c r="P37" s="466">
+      <c r="P37" s="458">
         <v>-16.93</v>
       </c>
-      <c r="Q37" s="464">
+      <c r="Q37" s="459">
         <v>-15.19</v>
       </c>
       <c r="R37" s="460">
         <v>-10.99</v>
       </c>
-      <c r="S37" s="457">
+      <c r="S37" s="461">
         <v>-15.27</v>
       </c>
-      <c r="T37" s="467">
-        <v>-25.01</v>
+      <c r="T37" s="462">
+        <v>-26.75</v>
       </c>
     </row>
     <row r="38">
@@ -11538,7 +11538,7 @@
       <c r="C38" t="str">
         <v>600410</v>
       </c>
-      <c r="D38" s="469" t="str">
+      <c r="D38" s="477" t="str">
         <v>净买: 1.26亿</v>
       </c>
       <c r="E38">
@@ -11553,41 +11553,41 @@
       <c r="H38">
         <v>-1.64</v>
       </c>
-      <c r="I38" s="477">
+      <c r="I38" s="474">
         <v>11.84</v>
       </c>
-      <c r="J38" s="478">
+      <c r="J38" s="475">
         <v>23.02</v>
       </c>
-      <c r="K38" s="473">
+      <c r="K38" s="472">
         <v>10.78</v>
       </c>
-      <c r="L38" s="471">
+      <c r="L38" s="476">
         <v>2.42</v>
       </c>
-      <c r="M38" s="470">
+      <c r="M38" s="478">
         <v>0</v>
       </c>
       <c r="N38" s="479">
         <v>1.86</v>
       </c>
-      <c r="O38" s="474">
+      <c r="O38" s="473">
         <v>2.67</v>
       </c>
-      <c r="P38" s="480">
+      <c r="P38" s="469">
         <v>5.99</v>
       </c>
-      <c r="Q38" s="481">
+      <c r="Q38" s="470">
         <v>0.81</v>
       </c>
-      <c r="R38" s="475">
+      <c r="R38" s="471">
         <v>6.95</v>
       </c>
-      <c r="S38" s="476">
+      <c r="S38" s="480">
         <v>6.25</v>
       </c>
-      <c r="T38" s="472">
-        <v>46.05</v>
+      <c r="T38" s="481">
+        <v>40.55</v>
       </c>
     </row>
     <row r="39">
@@ -11600,7 +11600,7 @@
       <c r="C39" t="str">
         <v>600410</v>
       </c>
-      <c r="D39" s="491" t="str">
+      <c r="D39" s="487" t="str">
         <v>净买: 1.26亿</v>
       </c>
       <c r="E39">
@@ -11615,41 +11615,41 @@
       <c r="H39">
         <v>10</v>
       </c>
-      <c r="I39" s="492">
+      <c r="I39" s="488">
         <v>0</v>
       </c>
-      <c r="J39" s="483">
+      <c r="J39" s="482">
         <v>-9.95</v>
       </c>
-      <c r="K39" s="484">
+      <c r="K39" s="486">
         <v>-16.75</v>
       </c>
-      <c r="L39" s="493">
+      <c r="L39" s="483">
         <v>-18.71</v>
       </c>
-      <c r="M39" s="485">
+      <c r="M39" s="484">
         <v>-17.2</v>
       </c>
-      <c r="N39" s="494">
+      <c r="N39" s="489">
         <v>-16.54</v>
       </c>
-      <c r="O39" s="486">
+      <c r="O39" s="492">
         <v>-13.84</v>
       </c>
-      <c r="P39" s="490">
+      <c r="P39" s="493">
         <v>-18.06</v>
       </c>
-      <c r="Q39" s="487">
+      <c r="Q39" s="490">
         <v>-13.06</v>
       </c>
-      <c r="R39" s="488">
+      <c r="R39" s="494">
         <v>-13.64</v>
       </c>
-      <c r="S39" s="482">
+      <c r="S39" s="491">
         <v>-10.2</v>
       </c>
-      <c r="T39" s="489">
-        <v>18.71</v>
+      <c r="T39" s="485">
+        <v>14.25</v>
       </c>
     </row>
     <row r="40">
@@ -11662,7 +11662,7 @@
       <c r="C40" t="str">
         <v>600776</v>
       </c>
-      <c r="D40" s="496" t="str">
+      <c r="D40" s="500" t="str">
         <v>净卖: -233.39万</v>
       </c>
       <c r="E40">
@@ -11677,41 +11677,41 @@
       <c r="H40">
         <v>-10</v>
       </c>
-      <c r="I40" s="503">
+      <c r="I40" s="495">
         <v>0</v>
       </c>
-      <c r="J40" s="499">
+      <c r="J40" s="501">
         <v>-9.98</v>
       </c>
-      <c r="K40" s="504">
+      <c r="K40" s="496">
         <v>-13.06</v>
       </c>
-      <c r="L40" s="500">
+      <c r="L40" s="497">
         <v>-12.02</v>
       </c>
-      <c r="M40" s="497">
+      <c r="M40" s="502">
         <v>-10.17</v>
       </c>
-      <c r="N40" s="501">
+      <c r="N40" s="505">
         <v>-5.72</v>
       </c>
-      <c r="O40" s="502">
+      <c r="O40" s="503">
         <v>-10.26</v>
       </c>
-      <c r="P40" s="507">
+      <c r="P40" s="504">
         <v>-9.89</v>
       </c>
       <c r="Q40" s="498">
         <v>-11.26</v>
       </c>
-      <c r="R40" s="505">
+      <c r="R40" s="506">
         <v>-11.78</v>
       </c>
-      <c r="S40" s="506">
+      <c r="S40" s="499">
         <v>-12.49</v>
       </c>
-      <c r="T40" s="495">
-        <v>-20.58</v>
+      <c r="T40" s="507">
+        <v>-22.42</v>
       </c>
     </row>
     <row r="41">
@@ -11724,7 +11724,7 @@
       <c r="C41" t="str">
         <v>600410</v>
       </c>
-      <c r="D41" s="517" t="str">
+      <c r="D41" s="516" t="str">
         <v>净卖: -1.30亿</v>
       </c>
       <c r="E41">
@@ -11739,41 +11739,41 @@
       <c r="H41">
         <v>-1.97</v>
       </c>
-      <c r="I41" s="512">
+      <c r="I41" s="508">
         <v>-8.15</v>
       </c>
-      <c r="J41" s="508">
+      <c r="J41" s="512">
         <v>-15.08</v>
       </c>
-      <c r="K41" s="509">
+      <c r="K41" s="514">
         <v>-17.08</v>
       </c>
-      <c r="L41" s="513">
+      <c r="L41" s="509">
         <v>-15.54</v>
       </c>
-      <c r="M41" s="518">
+      <c r="M41" s="517">
         <v>-14.87</v>
       </c>
-      <c r="N41" s="515">
+      <c r="N41" s="518">
         <v>-12.11</v>
       </c>
-      <c r="O41" s="519">
+      <c r="O41" s="510">
         <v>-16.42</v>
       </c>
-      <c r="P41" s="510">
+      <c r="P41" s="515">
         <v>-11.32</v>
       </c>
-      <c r="Q41" s="516">
+      <c r="Q41" s="513">
         <v>-11.9</v>
       </c>
-      <c r="R41" s="514">
+      <c r="R41" s="519">
         <v>-8.4</v>
       </c>
       <c r="S41" s="511">
         <v>-12.24</v>
       </c>
       <c r="T41" s="520">
-        <v>21.09</v>
+        <v>16.54</v>
       </c>
     </row>
     <row r="42">
@@ -11786,7 +11786,7 @@
       <c r="C42" t="str">
         <v>002792</v>
       </c>
-      <c r="D42" s="531" t="str">
+      <c r="D42" s="533" t="str">
         <v>净买: 5153.68万</v>
       </c>
       <c r="E42">
@@ -11801,41 +11801,41 @@
       <c r="H42">
         <v>0.55</v>
       </c>
-      <c r="I42" s="523">
+      <c r="I42" s="521">
         <v>9.39</v>
       </c>
-      <c r="J42" s="524">
+      <c r="J42" s="530">
         <v>15.85</v>
       </c>
-      <c r="K42" s="525">
+      <c r="K42" s="527">
         <v>10.51</v>
       </c>
-      <c r="L42" s="532">
+      <c r="L42" s="522">
         <v>6.31</v>
       </c>
-      <c r="M42" s="533">
+      <c r="M42" s="523">
         <v>1.07</v>
       </c>
-      <c r="N42" s="526">
+      <c r="N42" s="525">
         <v>-1.76</v>
       </c>
-      <c r="O42" s="521">
+      <c r="O42" s="526">
         <v>0.67</v>
       </c>
-      <c r="P42" s="529">
+      <c r="P42" s="528">
         <v>10.74</v>
       </c>
-      <c r="Q42" s="527">
+      <c r="Q42" s="531">
         <v>10.74</v>
       </c>
-      <c r="R42" s="530">
+      <c r="R42" s="524">
         <v>7.46</v>
       </c>
-      <c r="S42" s="522">
+      <c r="S42" s="532">
         <v>7.34</v>
       </c>
-      <c r="T42" s="528">
-        <v>10.88</v>
+      <c r="T42" s="529">
+        <v>7.32</v>
       </c>
     </row>
     <row r="43">
@@ -11897,40 +11897,40 @@
       <c r="F44" t="str"/>
       <c r="G44" t="str"/>
       <c r="H44" t="str"/>
-      <c r="I44" s="535">
+      <c r="I44" s="534">
         <v>65.85</v>
       </c>
-      <c r="J44" s="544">
+      <c r="J44" s="539">
         <v>65.85</v>
       </c>
-      <c r="K44" s="536">
+      <c r="K44" s="540">
         <v>60.98</v>
       </c>
-      <c r="L44" s="545">
+      <c r="L44" s="535">
         <v>56.1</v>
       </c>
-      <c r="M44" s="539">
+      <c r="M44" s="536">
         <v>48.78</v>
       </c>
-      <c r="N44" s="540">
+      <c r="N44" s="542">
         <v>46.34</v>
       </c>
       <c r="O44" s="537">
         <v>48.78</v>
       </c>
-      <c r="P44" s="534">
+      <c r="P44" s="538">
         <v>43.9</v>
       </c>
-      <c r="Q44" s="538">
+      <c r="Q44" s="541">
         <v>39.02</v>
       </c>
-      <c r="R44" s="541">
+      <c r="R44" s="543">
         <v>43.9</v>
       </c>
-      <c r="S44" s="542">
+      <c r="S44" s="544">
         <v>43.9</v>
       </c>
-      <c r="T44" s="543">
+      <c r="T44" s="545">
         <v>34.15</v>
       </c>
     </row>
@@ -11945,41 +11945,41 @@
       <c r="F45" t="str"/>
       <c r="G45" t="str"/>
       <c r="H45" t="str"/>
-      <c r="I45" s="553">
+      <c r="I45" s="550">
         <v>3.79</v>
       </c>
-      <c r="J45" s="554">
+      <c r="J45" s="551">
         <v>5.59</v>
       </c>
-      <c r="K45" s="549">
+      <c r="K45" s="547">
         <v>5.07</v>
       </c>
-      <c r="L45" s="556">
+      <c r="L45" s="552">
         <v>5.23</v>
       </c>
       <c r="M45" s="557">
         <v>5.01</v>
       </c>
-      <c r="N45" s="550">
+      <c r="N45" s="553">
         <v>4.05</v>
       </c>
-      <c r="O45" s="551">
+      <c r="O45" s="548">
         <v>4.42</v>
       </c>
-      <c r="P45" s="552">
+      <c r="P45" s="549">
         <v>3.76</v>
       </c>
       <c r="Q45" s="546">
         <v>1.74</v>
       </c>
-      <c r="R45" s="547">
+      <c r="R45" s="554">
         <v>1.6</v>
       </c>
-      <c r="S45" s="548">
+      <c r="S45" s="555">
         <v>0.99</v>
       </c>
-      <c r="T45" s="555">
-        <v>-3.44</v>
+      <c r="T45" s="556">
+        <v>-5.5</v>
       </c>
     </row>
   </sheetData>

--- a/youzi/越王大道/index.xlsx
+++ b/youzi/越王大道/index.xlsx
@@ -39,13 +39,247 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFC4E7CC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF70C483"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAE202D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8236"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAB1E2C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF218E3B"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FFED979F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB8E1C1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA91E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDA3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAB1F2C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BDC2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC32938"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAC1F2C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF3F4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2FAA4B"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -57,25 +291,1951 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA91E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAB1E2C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC4E7CC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF70C483"/>
+        <fgColor rgb="FFEFA4AB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE2E4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8ACF9A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCF0F1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC02836"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD33140"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDE4150"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD53241"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBE8EA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC959E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3D4D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED9BA3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFACDDB7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7DCA8F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9808A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7130"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC42A38"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0ACB3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B2B8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF95D3A3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF67C07B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCA2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC969F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDB3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3B9BF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFDFD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9DFE1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDA3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEE9FA6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBB2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB92533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25866"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD2303F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBEDEE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7B33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A702F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E7F35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8437"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BFC4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBEAEC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDE4251"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6AC27E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE3E5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8437"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23943D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCFDFC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23943D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23953E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5BBC71"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218D3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A712F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208838"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF46B35F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A443"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7B34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC3E6CB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7FCA90"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5FBD75"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8337"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23943D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBC2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF63BF78"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC52A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8638"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8638"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7E35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23933D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8738"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7A33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8136"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7CC98E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5EBD74"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF53B86A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B2B8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6DC381"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2DFBC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2DFBC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2FA94B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF46B35F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8738"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF84CD95"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6CC280"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77580"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A644"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8638"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF249A3F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFCFC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22903C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7CC98E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77883"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBF2736"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF95D3A3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6CDD1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9DCDF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8337"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9858F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BAC0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF99D5A7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF30AA4C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B3B9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFBFB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDE4251"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196F2F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD43140"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24983F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208839"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC929B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4C4C8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF54B96B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF37AD52"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2EA94A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46672"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDE4554"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2CA848"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6727D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A544"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8538"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBB2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7832"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF37AD52"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6D0D3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3949"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCEEEF"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -87,49 +2247,85 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFB8E1C1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED979F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8236"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6F4E9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE35E6B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE35E6B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC32A38"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD63242"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCDEAD4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7ECA8F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -141,55 +2337,991 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDA3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFBB2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE04D5B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8537"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B4BA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6FBF7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22923D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8638"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC12937"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB72432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3847"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4957"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF269F42"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC92C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA9DBB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8ED19D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE5E7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8538"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC52A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF64BF79"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3848"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A042"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC939B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC72B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B3B9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD1303F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9DEE0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEE9DA4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259E41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196D2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7E35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8136"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC12937"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC32938"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D3D7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAD1F2D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE3E6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB3E0BD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF44B25D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9838D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE4F4E8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7BC98D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7BC98D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBC2635"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7BC98D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBC2635"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD63242"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0DEBA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE4F4E8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A142"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAD1F2D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE04F5D"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -207,3162 +3339,36 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC32938"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAB1F2C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BDC2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF3F4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE2E4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC02836"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2FAA4B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDE4150"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCF0F1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFA4AB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD33140"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE6E8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3D4D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7DCA8F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD53241"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE35F6B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC42A38"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFACDDB7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7130"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBE8EA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9808A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED9BA3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF95D3A3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDB3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B2B8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCA2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC969F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77580"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF67C07B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25866"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9DFE1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEE9FA6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBB2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3B9BF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDA3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD2303F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFDFD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BFC4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E7F35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7B33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8437"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBEDEE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A702F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCFDFC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6AC27E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE3E5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDE4251"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBEAEC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23943D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23943D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8437"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23953E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5BBC71"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB72432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A712F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218D3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC3E6CB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208838"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7B34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF46B35F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A443"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBC2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5FBD75"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC52A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF63BF78"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7FCA90"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23943D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF40B15A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8638"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8638"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8738"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7E35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23933D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7A33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8136"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2DFBC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5EBD74"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8738"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF84CD95"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7CC98E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF46B35F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6DC381"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B2B8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2DFBC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2FA94B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF53B86A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A644"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8638"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFCFC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77580"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6CC280"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF249A3F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77883"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF95D3A3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBF2736"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7CC98E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22903C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6CDD1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BAC0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9DCDF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9858F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B3B9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF99D5A7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8337"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFBFB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7531"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196F2F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD43140"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDE4251"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC929B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208839"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4C4C8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF37AD52"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF54B96B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFACDDB7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46672"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7732"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2CA848"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDE4554"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A544"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8538"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6727D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBB2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6D0D3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7832"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF37AD52"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3949"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC32A38"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE35E6B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCEEEF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6F4E9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE35E6B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAE202D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7ECA8F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8537"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE04D5B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD63242"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B4BA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCDEAD4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBB2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22923D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6FBF7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8638"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC12937"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB72432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3847"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF269F42"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC92C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC52A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE5E7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA9DBB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF64BF79"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8ED19D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8538"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3848"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A042"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD1303F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9DEE0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC72B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC939B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEE9DA4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B3B9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196D2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259E41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8136"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7E35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAD1F2D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D3D7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC12937"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB3E0BD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE3E6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC32938"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC32938"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBC2635"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9838D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE4F4E8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE4F4E8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7BC98D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBC2635"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD63242"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A142"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0DEBA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7BC98D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7BC98D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8437"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE04F5D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAD1F2D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAC1F2C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFE35D6A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFED9BA2"/>
         <bgColor/>
       </patternFill>
@@ -3370,12 +3376,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -9306,7 +9306,7 @@
       <c r="C2" t="str">
         <v>002570</v>
       </c>
-      <c r="D2" s="3" t="str">
+      <c r="D2" s="5" t="str">
         <v>净卖: -1602.12万</v>
       </c>
       <c r="E2">
@@ -9321,41 +9321,41 @@
       <c r="H2">
         <v>0.15</v>
       </c>
-      <c r="I2" s="4">
+      <c r="I2" s="13">
         <v>9.77</v>
       </c>
-      <c r="J2" s="5">
+      <c r="J2" s="9">
         <v>9.62</v>
       </c>
-      <c r="K2" s="6">
+      <c r="K2" s="1">
         <v>-1.35</v>
       </c>
-      <c r="L2" s="1">
+      <c r="L2" s="10">
         <v>-7.07</v>
       </c>
-      <c r="M2" s="7">
+      <c r="M2" s="2">
         <v>-3.31</v>
       </c>
-      <c r="N2" s="10">
+      <c r="N2" s="11">
         <v>2.56</v>
       </c>
-      <c r="O2" s="8">
+      <c r="O2" s="7">
         <v>9.32</v>
       </c>
-      <c r="P2" s="9">
+      <c r="P2" s="12">
         <v>-1.65</v>
       </c>
-      <c r="Q2" s="11">
+      <c r="Q2" s="3">
         <v>-11.43</v>
       </c>
-      <c r="R2" s="13">
+      <c r="R2" s="6">
         <v>-9.47</v>
       </c>
-      <c r="S2" s="12">
+      <c r="S2" s="8">
         <v>-8.12</v>
       </c>
-      <c r="T2" s="2">
-        <v>-25.41</v>
+      <c r="T2" s="4">
+        <v>-26.77</v>
       </c>
     </row>
     <row r="3">
@@ -9368,7 +9368,7 @@
       <c r="C3" t="str">
         <v>002915</v>
       </c>
-      <c r="D3" s="17" t="str">
+      <c r="D3" s="22" t="str">
         <v>净买: 2039.94万</v>
       </c>
       <c r="E3">
@@ -9383,41 +9383,41 @@
       <c r="H3">
         <v>0.12</v>
       </c>
-      <c r="I3" s="18">
+      <c r="I3" s="26">
         <v>5.12</v>
       </c>
-      <c r="J3" s="24">
+      <c r="J3" s="18">
         <v>15.65</v>
       </c>
-      <c r="K3" s="15">
+      <c r="K3" s="14">
         <v>27.2</v>
       </c>
-      <c r="L3" s="25">
+      <c r="L3" s="15">
         <v>27.56</v>
       </c>
-      <c r="M3" s="16">
+      <c r="M3" s="23">
         <v>40.3</v>
       </c>
-      <c r="N3" s="26">
+      <c r="N3" s="19">
         <v>27.68</v>
       </c>
-      <c r="O3" s="19">
+      <c r="O3" s="16">
         <v>30.06</v>
       </c>
       <c r="P3" s="20">
         <v>28.1</v>
       </c>
-      <c r="Q3" s="21">
+      <c r="Q3" s="17">
         <v>36.9</v>
       </c>
-      <c r="R3" s="22">
+      <c r="R3" s="21">
         <v>34.52</v>
       </c>
-      <c r="S3" s="23">
+      <c r="S3" s="24">
         <v>21.07</v>
       </c>
-      <c r="T3" s="14">
-        <v>27.98</v>
+      <c r="T3" s="25">
+        <v>23.75</v>
       </c>
     </row>
     <row r="4">
@@ -9430,7 +9430,7 @@
       <c r="C4" t="str">
         <v>002229</v>
       </c>
-      <c r="D4" s="37" t="str">
+      <c r="D4" s="31" t="str">
         <v>净买: 2135.02万</v>
       </c>
       <c r="E4">
@@ -9448,38 +9448,38 @@
       <c r="I4" s="32">
         <v>1.62</v>
       </c>
-      <c r="J4" s="38">
+      <c r="J4" s="37">
         <v>11.75</v>
       </c>
-      <c r="K4" s="29">
+      <c r="K4" s="27">
         <v>21.04</v>
       </c>
-      <c r="L4" s="33">
+      <c r="L4" s="28">
         <v>28.15</v>
       </c>
-      <c r="M4" s="34">
+      <c r="M4" s="38">
         <v>15.34</v>
       </c>
-      <c r="N4" s="36">
+      <c r="N4" s="39">
         <v>13.65</v>
       </c>
-      <c r="O4" s="39">
+      <c r="O4" s="33">
         <v>13.02</v>
       </c>
-      <c r="P4" s="30">
+      <c r="P4" s="34">
         <v>7.32</v>
       </c>
-      <c r="Q4" s="27">
+      <c r="Q4" s="35">
         <v>9.5</v>
       </c>
-      <c r="R4" s="31">
+      <c r="R4" s="30">
         <v>9.57</v>
       </c>
-      <c r="S4" s="35">
+      <c r="S4" s="36">
         <v>14.22</v>
       </c>
-      <c r="T4" s="28">
-        <v>33.29</v>
+      <c r="T4" s="29">
+        <v>18.79</v>
       </c>
     </row>
     <row r="5">
@@ -9492,7 +9492,7 @@
       <c r="C5" t="str">
         <v>002915</v>
       </c>
-      <c r="D5" s="52" t="str">
+      <c r="D5" s="42" t="str">
         <v>净卖: -2747.73万</v>
       </c>
       <c r="E5">
@@ -9507,41 +9507,41 @@
       <c r="H5">
         <v>9.98</v>
       </c>
-      <c r="I5" s="40">
+      <c r="I5" s="46">
         <v>0</v>
       </c>
-      <c r="J5" s="41">
+      <c r="J5" s="40">
         <v>0.28</v>
       </c>
-      <c r="K5" s="42">
+      <c r="K5" s="47">
         <v>10.29</v>
       </c>
       <c r="L5" s="48">
         <v>0.37</v>
       </c>
-      <c r="M5" s="49">
+      <c r="M5" s="43">
         <v>2.25</v>
       </c>
-      <c r="N5" s="43">
+      <c r="N5" s="44">
         <v>0.7</v>
       </c>
-      <c r="O5" s="44">
+      <c r="O5" s="49">
         <v>7.63</v>
       </c>
       <c r="P5" s="50">
         <v>5.76</v>
       </c>
-      <c r="Q5" s="45">
+      <c r="Q5" s="41">
         <v>-4.82</v>
       </c>
-      <c r="R5" s="46">
+      <c r="R5" s="51">
         <v>4.68</v>
       </c>
-      <c r="S5" s="47">
+      <c r="S5" s="52">
         <v>11</v>
       </c>
-      <c r="T5" s="51">
-        <v>0.61</v>
+      <c r="T5" s="45">
+        <v>-2.71</v>
       </c>
     </row>
     <row r="6">
@@ -9554,7 +9554,7 @@
       <c r="C6" t="str">
         <v>002177</v>
       </c>
-      <c r="D6" s="64" t="str">
+      <c r="D6" s="59" t="str">
         <v>净买: 3117.92万</v>
       </c>
       <c r="E6">
@@ -9569,41 +9569,41 @@
       <c r="H6">
         <v>5.02</v>
       </c>
-      <c r="I6" s="53">
+      <c r="I6" s="56">
         <v>4.78</v>
       </c>
-      <c r="J6" s="55">
+      <c r="J6" s="60">
         <v>10.79</v>
       </c>
-      <c r="K6" s="59">
+      <c r="K6" s="65">
         <v>7.24</v>
       </c>
-      <c r="L6" s="56">
+      <c r="L6" s="57">
         <v>12.3</v>
       </c>
-      <c r="M6" s="57">
+      <c r="M6" s="53">
         <v>5.6</v>
       </c>
-      <c r="N6" s="65">
+      <c r="N6" s="58">
         <v>2.46</v>
       </c>
-      <c r="O6" s="60">
+      <c r="O6" s="61">
         <v>-1.91</v>
       </c>
-      <c r="P6" s="61">
+      <c r="P6" s="64">
         <v>-9.56</v>
       </c>
-      <c r="Q6" s="54">
+      <c r="Q6" s="62">
         <v>-3.01</v>
       </c>
-      <c r="R6" s="62">
+      <c r="R6" s="54">
         <v>0.55</v>
       </c>
       <c r="S6" s="63">
         <v>3.14</v>
       </c>
-      <c r="T6" s="58">
-        <v>3.96</v>
+      <c r="T6" s="55">
+        <v>2.6</v>
       </c>
     </row>
     <row r="7">
@@ -9616,7 +9616,7 @@
       <c r="C7" t="str">
         <v>002177</v>
       </c>
-      <c r="D7" s="68" t="str">
+      <c r="D7" s="67" t="str">
         <v>净卖: -2852.77万</v>
       </c>
       <c r="E7">
@@ -9631,41 +9631,41 @@
       <c r="H7">
         <v>-4.04</v>
       </c>
-      <c r="I7" s="66">
+      <c r="I7" s="68">
         <v>10.19</v>
       </c>
-      <c r="J7" s="71">
+      <c r="J7" s="76">
         <v>6.66</v>
       </c>
-      <c r="K7" s="72">
+      <c r="K7" s="69">
         <v>11.68</v>
       </c>
-      <c r="L7" s="69">
+      <c r="L7" s="78">
         <v>5.03</v>
       </c>
       <c r="M7" s="70">
         <v>1.9</v>
       </c>
-      <c r="N7" s="67">
+      <c r="N7" s="71">
         <v>-2.45</v>
       </c>
-      <c r="O7" s="75">
+      <c r="O7" s="72">
         <v>-10.05</v>
       </c>
-      <c r="P7" s="76">
+      <c r="P7" s="74">
         <v>-3.53</v>
       </c>
-      <c r="Q7" s="77">
+      <c r="Q7" s="73">
         <v>0</v>
       </c>
-      <c r="R7" s="73">
+      <c r="R7" s="77">
         <v>2.58</v>
       </c>
-      <c r="S7" s="78">
+      <c r="S7" s="75">
         <v>-5.3</v>
       </c>
-      <c r="T7" s="74">
-        <v>3.4</v>
+      <c r="T7" s="66">
+        <v>2.04</v>
       </c>
     </row>
     <row r="8">
@@ -9678,7 +9678,7 @@
       <c r="C8" t="str">
         <v>002882</v>
       </c>
-      <c r="D8" s="90" t="str">
+      <c r="D8" s="91" t="str">
         <v>净卖: -1459.92万</v>
       </c>
       <c r="E8">
@@ -9693,41 +9693,41 @@
       <c r="H8">
         <v>-0.92</v>
       </c>
-      <c r="I8" s="91">
+      <c r="I8" s="88">
         <v>11.01</v>
       </c>
       <c r="J8" s="79">
         <v>11.21</v>
       </c>
-      <c r="K8" s="85">
+      <c r="K8" s="80">
         <v>1.71</v>
       </c>
-      <c r="L8" s="80">
+      <c r="L8" s="89">
         <v>4.11</v>
       </c>
-      <c r="M8" s="88">
+      <c r="M8" s="81">
         <v>0.04</v>
       </c>
-      <c r="N8" s="81">
+      <c r="N8" s="82">
         <v>0.78</v>
       </c>
-      <c r="O8" s="82">
+      <c r="O8" s="85">
         <v>2.37</v>
       </c>
-      <c r="P8" s="86">
+      <c r="P8" s="83">
         <v>5.12</v>
       </c>
-      <c r="Q8" s="87">
+      <c r="Q8" s="90">
         <v>5.93</v>
       </c>
-      <c r="R8" s="83">
+      <c r="R8" s="86">
         <v>8.07</v>
       </c>
       <c r="S8" s="84">
         <v>18.88</v>
       </c>
-      <c r="T8" s="89">
-        <v>12.56</v>
+      <c r="T8" s="87">
+        <v>8.3</v>
       </c>
     </row>
     <row r="9">
@@ -9740,7 +9740,7 @@
       <c r="C9" t="str">
         <v>003029</v>
       </c>
-      <c r="D9" s="96" t="str">
+      <c r="D9" s="101" t="str">
         <v>净卖: -276.02万</v>
       </c>
       <c r="E9">
@@ -9755,41 +9755,41 @@
       <c r="H9">
         <v>10.01</v>
       </c>
-      <c r="I9" s="92">
+      <c r="I9" s="102">
         <v>0</v>
       </c>
-      <c r="J9" s="101">
+      <c r="J9" s="103">
         <v>10.01</v>
       </c>
-      <c r="K9" s="93">
+      <c r="K9" s="104">
         <v>1.58</v>
       </c>
-      <c r="L9" s="102">
+      <c r="L9" s="92">
         <v>0.44</v>
       </c>
-      <c r="M9" s="103">
+      <c r="M9" s="94">
         <v>-9.6</v>
       </c>
-      <c r="N9" s="98">
+      <c r="N9" s="97">
         <v>-14.15</v>
       </c>
-      <c r="O9" s="99">
+      <c r="O9" s="95">
         <v>-11.05</v>
       </c>
-      <c r="P9" s="97">
+      <c r="P9" s="93">
         <v>-8.72</v>
       </c>
-      <c r="Q9" s="104">
+      <c r="Q9" s="96">
         <v>-7.3</v>
       </c>
-      <c r="R9" s="94">
+      <c r="R9" s="98">
         <v>-8.31</v>
       </c>
-      <c r="S9" s="100">
+      <c r="S9" s="99">
         <v>-7.9</v>
       </c>
-      <c r="T9" s="95">
-        <v>-33.7</v>
+      <c r="T9" s="100">
+        <v>-33.45</v>
       </c>
     </row>
     <row r="10">
@@ -9802,7 +9802,7 @@
       <c r="C10" t="str">
         <v>002017</v>
       </c>
-      <c r="D10" s="111" t="str">
+      <c r="D10" s="107" t="str">
         <v>净买: 6518.56万</v>
       </c>
       <c r="E10">
@@ -9820,38 +9820,38 @@
       <c r="I10" s="108">
         <v>4.66</v>
       </c>
-      <c r="J10" s="105">
+      <c r="J10" s="113">
         <v>-0.06</v>
       </c>
-      <c r="K10" s="112">
+      <c r="K10" s="114">
         <v>-6.53</v>
       </c>
-      <c r="L10" s="116">
+      <c r="L10" s="115">
         <v>-5.79</v>
       </c>
-      <c r="M10" s="113">
+      <c r="M10" s="111">
         <v>-7.89</v>
       </c>
-      <c r="N10" s="106">
+      <c r="N10" s="109">
         <v>-3.46</v>
       </c>
-      <c r="O10" s="107">
+      <c r="O10" s="110">
         <v>0.68</v>
       </c>
-      <c r="P10" s="109">
+      <c r="P10" s="105">
         <v>0.51</v>
       </c>
-      <c r="Q10" s="114">
+      <c r="Q10" s="116">
         <v>-6.47</v>
       </c>
-      <c r="R10" s="115">
+      <c r="R10" s="117">
         <v>-3.8</v>
       </c>
-      <c r="S10" s="110">
+      <c r="S10" s="112">
         <v>-6.53</v>
       </c>
-      <c r="T10" s="117">
-        <v>8.46</v>
+      <c r="T10" s="106">
+        <v>5.22</v>
       </c>
     </row>
     <row r="11">
@@ -9864,7 +9864,7 @@
       <c r="C11" t="str">
         <v>002670</v>
       </c>
-      <c r="D11" s="124" t="str">
+      <c r="D11" s="120" t="str">
         <v>净卖: -2720.58万</v>
       </c>
       <c r="E11">
@@ -9879,41 +9879,41 @@
       <c r="H11">
         <v>-0.81</v>
       </c>
-      <c r="I11" s="130">
+      <c r="I11" s="126">
         <v>-5.23</v>
       </c>
-      <c r="J11" s="121">
+      <c r="J11" s="130">
         <v>-1.39</v>
       </c>
-      <c r="K11" s="118">
+      <c r="K11" s="121">
         <v>-9.57</v>
       </c>
-      <c r="L11" s="119">
+      <c r="L11" s="118">
         <v>-7.18</v>
       </c>
       <c r="M11" s="122">
         <v>-7.62</v>
       </c>
-      <c r="N11" s="125">
+      <c r="N11" s="127">
         <v>-8.69</v>
       </c>
-      <c r="O11" s="129">
+      <c r="O11" s="128">
         <v>-7.37</v>
       </c>
-      <c r="P11" s="123">
+      <c r="P11" s="129">
         <v>-8.56</v>
       </c>
-      <c r="Q11" s="120">
+      <c r="Q11" s="119">
         <v>-8.63</v>
       </c>
-      <c r="R11" s="126">
+      <c r="R11" s="123">
         <v>-4.28</v>
       </c>
-      <c r="S11" s="127">
+      <c r="S11" s="124">
         <v>-8.56</v>
       </c>
-      <c r="T11" s="128">
-        <v>-16.81</v>
+      <c r="T11" s="125">
+        <v>-21.98</v>
       </c>
     </row>
     <row r="12">
@@ -9926,7 +9926,7 @@
       <c r="C12" t="str">
         <v>002579</v>
       </c>
-      <c r="D12" s="135" t="str">
+      <c r="D12" s="139" t="str">
         <v>净买: 4403.72万</v>
       </c>
       <c r="E12">
@@ -9941,41 +9941,41 @@
       <c r="H12">
         <v>-2.68</v>
       </c>
-      <c r="I12" s="136">
+      <c r="I12" s="132">
         <v>13.04</v>
       </c>
-      <c r="J12" s="143">
+      <c r="J12" s="133">
         <v>12.54</v>
       </c>
-      <c r="K12" s="131">
+      <c r="K12" s="140">
         <v>7.97</v>
       </c>
-      <c r="L12" s="133">
+      <c r="L12" s="141">
         <v>12.54</v>
       </c>
-      <c r="M12" s="134">
+      <c r="M12" s="143">
         <v>7.1</v>
       </c>
-      <c r="N12" s="137">
+      <c r="N12" s="142">
         <v>-3.62</v>
       </c>
-      <c r="O12" s="138">
+      <c r="O12" s="131">
         <v>-2.97</v>
       </c>
-      <c r="P12" s="140">
+      <c r="P12" s="134">
         <v>-5.36</v>
       </c>
-      <c r="Q12" s="132">
+      <c r="Q12" s="135">
         <v>-3.7</v>
       </c>
-      <c r="R12" s="141">
+      <c r="R12" s="137">
         <v>-10.07</v>
       </c>
-      <c r="S12" s="139">
+      <c r="S12" s="138">
         <v>-6.59</v>
       </c>
-      <c r="T12" s="142">
-        <v>-4.42</v>
+      <c r="T12" s="136">
+        <v>-8.04</v>
       </c>
     </row>
     <row r="13">
@@ -9988,7 +9988,7 @@
       <c r="C13" t="str">
         <v>002229</v>
       </c>
-      <c r="D13" s="145" t="str">
+      <c r="D13" s="148" t="str">
         <v>净卖: -4629.75万</v>
       </c>
       <c r="E13">
@@ -10003,41 +10003,41 @@
       <c r="H13">
         <v>3.11</v>
       </c>
-      <c r="I13" s="146">
+      <c r="I13" s="150">
         <v>-7.78</v>
       </c>
-      <c r="J13" s="151">
+      <c r="J13" s="153">
         <v>-8.44</v>
       </c>
       <c r="K13" s="154">
         <v>-11.23</v>
       </c>
-      <c r="L13" s="147">
+      <c r="L13" s="149">
         <v>-12.22</v>
       </c>
-      <c r="M13" s="155">
+      <c r="M13" s="145">
         <v>-10.66</v>
       </c>
-      <c r="N13" s="152">
+      <c r="N13" s="155">
         <v>-6.65</v>
       </c>
-      <c r="O13" s="144">
+      <c r="O13" s="151">
         <v>-7.74</v>
       </c>
-      <c r="P13" s="148">
+      <c r="P13" s="156">
         <v>-7.69</v>
       </c>
-      <c r="Q13" s="149">
+      <c r="Q13" s="144">
         <v>-11.37</v>
       </c>
-      <c r="R13" s="150">
+      <c r="R13" s="146">
         <v>-10.8</v>
       </c>
-      <c r="S13" s="156">
+      <c r="S13" s="152">
         <v>-13.68</v>
       </c>
-      <c r="T13" s="153">
-        <v>-10.66</v>
+      <c r="T13" s="147">
+        <v>-20.38</v>
       </c>
     </row>
     <row r="14">
@@ -10050,7 +10050,7 @@
       <c r="C14" t="str">
         <v>000657</v>
       </c>
-      <c r="D14" s="160" t="str">
+      <c r="D14" s="163" t="str">
         <v>净卖: -6184.73万</v>
       </c>
       <c r="E14">
@@ -10065,41 +10065,41 @@
       <c r="H14">
         <v>-2</v>
       </c>
-      <c r="I14" s="161">
+      <c r="I14" s="169">
         <v>-8.16</v>
       </c>
-      <c r="J14" s="169">
+      <c r="J14" s="159">
         <v>-13.48</v>
       </c>
-      <c r="K14" s="162">
+      <c r="K14" s="157">
         <v>-14.93</v>
       </c>
-      <c r="L14" s="165">
+      <c r="L14" s="158">
         <v>-15.36</v>
       </c>
-      <c r="M14" s="166">
+      <c r="M14" s="160">
         <v>-15.2</v>
       </c>
-      <c r="N14" s="167">
+      <c r="N14" s="164">
         <v>-13.43</v>
       </c>
-      <c r="O14" s="168">
+      <c r="O14" s="161">
         <v>-13.1</v>
       </c>
-      <c r="P14" s="163">
+      <c r="P14" s="168">
         <v>-11.6</v>
       </c>
-      <c r="Q14" s="157">
+      <c r="Q14" s="165">
         <v>-10.74</v>
       </c>
-      <c r="R14" s="164">
+      <c r="R14" s="162">
         <v>-10.9</v>
       </c>
-      <c r="S14" s="159">
+      <c r="S14" s="166">
         <v>-8.81</v>
       </c>
-      <c r="T14" s="158">
-        <v>210.47</v>
+      <c r="T14" s="167">
+        <v>196.35</v>
       </c>
     </row>
     <row r="15">
@@ -10112,7 +10112,7 @@
       <c r="C15" t="str">
         <v>002670</v>
       </c>
-      <c r="D15" s="175" t="str">
+      <c r="D15" s="173" t="str">
         <v>净卖: -7597.74万</v>
       </c>
       <c r="E15">
@@ -10127,41 +10127,41 @@
       <c r="H15">
         <v>0.45</v>
       </c>
-      <c r="I15" s="179">
+      <c r="I15" s="174">
         <v>1.89</v>
       </c>
-      <c r="J15" s="170">
+      <c r="J15" s="177">
         <v>-1.79</v>
       </c>
-      <c r="K15" s="180">
+      <c r="K15" s="178">
         <v>-1.79</v>
       </c>
-      <c r="L15" s="176">
+      <c r="L15" s="170">
         <v>-3.03</v>
       </c>
-      <c r="M15" s="181">
+      <c r="M15" s="179">
         <v>-4.83</v>
       </c>
       <c r="N15" s="171">
         <v>-3.73</v>
       </c>
-      <c r="O15" s="178">
+      <c r="O15" s="175">
         <v>-3.38</v>
       </c>
-      <c r="P15" s="177">
+      <c r="P15" s="180">
         <v>-4.28</v>
       </c>
-      <c r="Q15" s="172">
+      <c r="Q15" s="181">
         <v>-7.71</v>
       </c>
-      <c r="R15" s="182">
+      <c r="R15" s="172">
         <v>-3.98</v>
       </c>
-      <c r="S15" s="173">
+      <c r="S15" s="182">
         <v>-2.84</v>
       </c>
-      <c r="T15" s="174">
-        <v>-34.28</v>
+      <c r="T15" s="176">
+        <v>-38.36</v>
       </c>
     </row>
     <row r="16">
@@ -10174,7 +10174,7 @@
       <c r="C16" t="str">
         <v>688039</v>
       </c>
-      <c r="D16" s="195" t="str">
+      <c r="D16" s="194" t="str">
         <v>净买: 3066.00万</v>
       </c>
       <c r="E16">
@@ -10189,41 +10189,41 @@
       <c r="H16">
         <v>7.16</v>
       </c>
-      <c r="I16" s="185">
+      <c r="I16" s="192">
         <v>11.98</v>
       </c>
-      <c r="J16" s="193">
+      <c r="J16" s="195">
         <v>16.69</v>
       </c>
-      <c r="K16" s="188">
+      <c r="K16" s="184">
         <v>3.41</v>
       </c>
-      <c r="L16" s="186">
+      <c r="L16" s="193">
         <v>0.07</v>
       </c>
-      <c r="M16" s="189">
+      <c r="M16" s="185">
         <v>-5.26</v>
       </c>
-      <c r="N16" s="190">
+      <c r="N16" s="183">
         <v>-3.41</v>
       </c>
-      <c r="O16" s="183">
+      <c r="O16" s="186">
         <v>-5.04</v>
       </c>
       <c r="P16" s="187">
         <v>-10.52</v>
       </c>
-      <c r="Q16" s="184">
+      <c r="Q16" s="188">
         <v>-7.78</v>
       </c>
-      <c r="R16" s="191">
+      <c r="R16" s="189">
         <v>-6.1</v>
       </c>
-      <c r="S16" s="194">
+      <c r="S16" s="190">
         <v>-7.34</v>
       </c>
-      <c r="T16" s="192">
-        <v>-21.69</v>
+      <c r="T16" s="191">
+        <v>-25.31</v>
       </c>
     </row>
     <row r="17">
@@ -10236,7 +10236,7 @@
       <c r="C17" t="str">
         <v>600408</v>
       </c>
-      <c r="D17" s="197" t="str">
+      <c r="D17" s="198" t="str">
         <v>净买: 1877.05万</v>
       </c>
       <c r="E17">
@@ -10251,41 +10251,41 @@
       <c r="H17">
         <v>-4.45</v>
       </c>
-      <c r="I17" s="204">
+      <c r="I17" s="205">
         <v>15.2</v>
       </c>
-      <c r="J17" s="198">
+      <c r="J17" s="199">
         <v>26.72</v>
       </c>
-      <c r="K17" s="201">
+      <c r="K17" s="200">
         <v>39.46</v>
       </c>
-      <c r="L17" s="196">
+      <c r="L17" s="201">
         <v>53.43</v>
       </c>
-      <c r="M17" s="199">
+      <c r="M17" s="208">
         <v>68.87</v>
       </c>
-      <c r="N17" s="205">
+      <c r="N17" s="206">
         <v>52.7</v>
       </c>
-      <c r="O17" s="206">
+      <c r="O17" s="196">
         <v>37.5</v>
       </c>
-      <c r="P17" s="207">
+      <c r="P17" s="197">
         <v>24.26</v>
       </c>
-      <c r="Q17" s="200">
+      <c r="Q17" s="207">
         <v>14.95</v>
       </c>
-      <c r="R17" s="208">
+      <c r="R17" s="202">
         <v>10.54</v>
       </c>
-      <c r="S17" s="202">
+      <c r="S17" s="203">
         <v>11.52</v>
       </c>
-      <c r="T17" s="203">
-        <v>-21.81</v>
+      <c r="T17" s="204">
+        <v>-23.04</v>
       </c>
     </row>
     <row r="18">
@@ -10298,7 +10298,7 @@
       <c r="C18" t="str">
         <v>601566</v>
       </c>
-      <c r="D18" s="211" t="str">
+      <c r="D18" s="217" t="str">
         <v>净买: 5226.66万</v>
       </c>
       <c r="E18">
@@ -10313,41 +10313,41 @@
       <c r="H18">
         <v>10.02</v>
       </c>
-      <c r="I18" s="214">
+      <c r="I18" s="220">
         <v>0</v>
       </c>
-      <c r="J18" s="221">
+      <c r="J18" s="218">
         <v>9.97</v>
       </c>
-      <c r="K18" s="218">
+      <c r="K18" s="211">
         <v>20.95</v>
       </c>
-      <c r="L18" s="215">
+      <c r="L18" s="221">
         <v>33.02</v>
       </c>
-      <c r="M18" s="219">
+      <c r="M18" s="215">
         <v>19.73</v>
       </c>
-      <c r="N18" s="212">
+      <c r="N18" s="216">
         <v>7.73</v>
       </c>
-      <c r="O18" s="209">
+      <c r="O18" s="212">
         <v>3.32</v>
       </c>
-      <c r="P18" s="220">
+      <c r="P18" s="213">
         <v>-5.35</v>
       </c>
-      <c r="Q18" s="216">
+      <c r="Q18" s="209">
         <v>-6.94</v>
       </c>
-      <c r="R18" s="213">
+      <c r="R18" s="210">
         <v>-3.03</v>
       </c>
-      <c r="S18" s="210">
+      <c r="S18" s="219">
         <v>-2.46</v>
       </c>
-      <c r="T18" s="217">
-        <v>-21.17</v>
+      <c r="T18" s="214">
+        <v>-22.54</v>
       </c>
     </row>
     <row r="19">
@@ -10360,7 +10360,7 @@
       <c r="C19" t="str">
         <v>002029</v>
       </c>
-      <c r="D19" s="232" t="str">
+      <c r="D19" s="224" t="str">
         <v>净卖: -1276.40万</v>
       </c>
       <c r="E19">
@@ -10375,41 +10375,41 @@
       <c r="H19">
         <v>0</v>
       </c>
-      <c r="I19" s="224">
+      <c r="I19" s="232">
         <v>9.97</v>
       </c>
-      <c r="J19" s="227">
+      <c r="J19" s="233">
         <v>1.88</v>
       </c>
-      <c r="K19" s="228">
+      <c r="K19" s="230">
         <v>-2.35</v>
       </c>
-      <c r="L19" s="233">
+      <c r="L19" s="225">
         <v>-9.97</v>
       </c>
-      <c r="M19" s="234">
+      <c r="M19" s="226">
         <v>-11.67</v>
       </c>
-      <c r="N19" s="229">
+      <c r="N19" s="227">
         <v>-8</v>
       </c>
       <c r="O19" s="222">
         <v>1.22</v>
       </c>
-      <c r="P19" s="225">
+      <c r="P19" s="223">
         <v>0.85</v>
       </c>
-      <c r="Q19" s="226">
+      <c r="Q19" s="228">
         <v>3.01</v>
       </c>
-      <c r="R19" s="223">
+      <c r="R19" s="229">
         <v>1.69</v>
       </c>
-      <c r="S19" s="230">
+      <c r="S19" s="234">
         <v>0.09</v>
       </c>
       <c r="T19" s="231">
-        <v>-9.22</v>
+        <v>-4.8</v>
       </c>
     </row>
     <row r="20">
@@ -10422,7 +10422,7 @@
       <c r="C20" t="str">
         <v>601566</v>
       </c>
-      <c r="D20" s="243" t="str">
+      <c r="D20" s="241" t="str">
         <v>净卖: -2737.55万</v>
       </c>
       <c r="E20">
@@ -10440,28 +10440,28 @@
       <c r="I20" s="240">
         <v>5.75</v>
       </c>
-      <c r="J20" s="244">
+      <c r="J20" s="235">
         <v>16.3</v>
       </c>
-      <c r="K20" s="245">
+      <c r="K20" s="236">
         <v>4.67</v>
       </c>
-      <c r="L20" s="235">
+      <c r="L20" s="237">
         <v>-5.81</v>
       </c>
-      <c r="M20" s="236">
+      <c r="M20" s="238">
         <v>-9.67</v>
       </c>
-      <c r="N20" s="237">
+      <c r="N20" s="244">
         <v>-17.25</v>
       </c>
-      <c r="O20" s="241">
+      <c r="O20" s="242">
         <v>-18.64</v>
       </c>
-      <c r="P20" s="238">
+      <c r="P20" s="245">
         <v>-15.22</v>
       </c>
-      <c r="Q20" s="242">
+      <c r="Q20" s="243">
         <v>-14.72</v>
       </c>
       <c r="R20" s="239">
@@ -10471,7 +10471,7 @@
         <v>-6.19</v>
       </c>
       <c r="T20" s="247">
-        <v>-31.08</v>
+        <v>-32.28</v>
       </c>
     </row>
     <row r="21">
@@ -10484,7 +10484,7 @@
       <c r="C21" t="str">
         <v>601566</v>
       </c>
-      <c r="D21" s="252" t="str">
+      <c r="D21" s="257" t="str">
         <v>净卖: -5218.09万</v>
       </c>
       <c r="E21">
@@ -10499,41 +10499,41 @@
       <c r="H21">
         <v>7.11</v>
       </c>
-      <c r="I21" s="248">
+      <c r="I21" s="258">
         <v>2.68</v>
       </c>
-      <c r="J21" s="249">
+      <c r="J21" s="248">
         <v>-7.59</v>
       </c>
-      <c r="K21" s="250">
+      <c r="K21" s="255">
         <v>-16.84</v>
       </c>
-      <c r="L21" s="255">
+      <c r="L21" s="251">
         <v>-20.25</v>
       </c>
-      <c r="M21" s="256">
+      <c r="M21" s="259">
         <v>-26.94</v>
       </c>
-      <c r="N21" s="257">
+      <c r="N21" s="256">
         <v>-28.17</v>
       </c>
-      <c r="O21" s="253">
+      <c r="O21" s="249">
         <v>-25.15</v>
       </c>
-      <c r="P21" s="254">
+      <c r="P21" s="260">
         <v>-24.71</v>
       </c>
-      <c r="Q21" s="258">
+      <c r="Q21" s="250">
         <v>-21.25</v>
       </c>
-      <c r="R21" s="259">
+      <c r="R21" s="252">
         <v>-17.18</v>
       </c>
-      <c r="S21" s="260">
+      <c r="S21" s="253">
         <v>-25.43</v>
       </c>
-      <c r="T21" s="251">
-        <v>-39.15</v>
+      <c r="T21" s="254">
+        <v>-40.21</v>
       </c>
     </row>
     <row r="22">
@@ -10561,41 +10561,41 @@
       <c r="H22">
         <v>-1.6</v>
       </c>
-      <c r="I22" s="267">
+      <c r="I22" s="263">
         <v>1.46</v>
       </c>
-      <c r="J22" s="268">
+      <c r="J22" s="272">
         <v>-4.63</v>
       </c>
-      <c r="K22" s="269">
+      <c r="K22" s="265">
         <v>-3.97</v>
       </c>
-      <c r="L22" s="273">
+      <c r="L22" s="269">
         <v>-13.57</v>
       </c>
-      <c r="M22" s="272">
+      <c r="M22" s="273">
         <v>-21.09</v>
       </c>
-      <c r="N22" s="263">
+      <c r="N22" s="264">
         <v>-19.75</v>
       </c>
-      <c r="O22" s="261">
+      <c r="O22" s="266">
         <v>-18.25</v>
       </c>
-      <c r="P22" s="264">
+      <c r="P22" s="267">
         <v>-20.84</v>
       </c>
-      <c r="Q22" s="265">
+      <c r="Q22" s="268">
         <v>-21.42</v>
       </c>
-      <c r="R22" s="270">
+      <c r="R22" s="261">
         <v>-23.17</v>
       </c>
-      <c r="S22" s="262">
+      <c r="S22" s="270">
         <v>-24.43</v>
       </c>
-      <c r="T22" s="266">
-        <v>-32.03</v>
+      <c r="T22" s="262">
+        <v>-32.4</v>
       </c>
     </row>
     <row r="23">
@@ -10608,7 +10608,7 @@
       <c r="C23" t="str">
         <v>603696</v>
       </c>
-      <c r="D23" s="276" t="str">
+      <c r="D23" s="285" t="str">
         <v>净买: 3978.78万</v>
       </c>
       <c r="E23">
@@ -10623,25 +10623,25 @@
       <c r="H23">
         <v>9.98</v>
       </c>
-      <c r="I23" s="285">
+      <c r="I23" s="282">
         <v>0</v>
       </c>
       <c r="J23" s="277">
         <v>10.01</v>
       </c>
-      <c r="K23" s="282">
+      <c r="K23" s="283">
         <v>21.01</v>
       </c>
-      <c r="L23" s="278">
+      <c r="L23" s="286">
         <v>33.13</v>
       </c>
-      <c r="M23" s="286">
+      <c r="M23" s="284">
         <v>46.43</v>
       </c>
-      <c r="N23" s="279">
+      <c r="N23" s="278">
         <v>43.01</v>
       </c>
-      <c r="O23" s="283">
+      <c r="O23" s="279">
         <v>28.71</v>
       </c>
       <c r="P23" s="280">
@@ -10650,14 +10650,14 @@
       <c r="Q23" s="274">
         <v>27.91</v>
       </c>
-      <c r="R23" s="284">
+      <c r="R23" s="281">
         <v>40.71</v>
       </c>
       <c r="S23" s="275">
         <v>26.66</v>
       </c>
-      <c r="T23" s="281">
-        <v>-1.93</v>
+      <c r="T23" s="276">
+        <v>-4.85</v>
       </c>
     </row>
     <row r="24">
@@ -10670,7 +10670,7 @@
       <c r="C24" t="str">
         <v>002682</v>
       </c>
-      <c r="D24" s="293" t="str">
+      <c r="D24" s="299" t="str">
         <v>净买: 2499.06万</v>
       </c>
       <c r="E24">
@@ -10685,41 +10685,41 @@
       <c r="H24">
         <v>5.99</v>
       </c>
-      <c r="I24" s="290">
+      <c r="I24" s="295">
         <v>3.77</v>
       </c>
-      <c r="J24" s="299">
+      <c r="J24" s="292">
         <v>14.2</v>
       </c>
-      <c r="K24" s="287">
+      <c r="K24" s="296">
         <v>25.65</v>
       </c>
-      <c r="L24" s="298">
+      <c r="L24" s="293">
         <v>38.26</v>
       </c>
-      <c r="M24" s="294">
+      <c r="M24" s="297">
         <v>52.03</v>
       </c>
-      <c r="N24" s="295">
+      <c r="N24" s="287">
         <v>42.9</v>
       </c>
-      <c r="O24" s="291">
+      <c r="O24" s="288">
         <v>57.25</v>
       </c>
-      <c r="P24" s="288">
+      <c r="P24" s="294">
         <v>72.9</v>
       </c>
-      <c r="Q24" s="296">
+      <c r="Q24" s="289">
         <v>55.65</v>
       </c>
-      <c r="R24" s="289">
+      <c r="R24" s="290">
         <v>40.14</v>
       </c>
-      <c r="S24" s="292">
+      <c r="S24" s="291">
         <v>42.75</v>
       </c>
-      <c r="T24" s="297">
-        <v>-13.91</v>
+      <c r="T24" s="298">
+        <v>-17.25</v>
       </c>
     </row>
     <row r="25">
@@ -10732,7 +10732,7 @@
       <c r="C25" t="str">
         <v>603696</v>
       </c>
-      <c r="D25" s="306" t="str">
+      <c r="D25" s="309" t="str">
         <v>净卖: -1913.63万</v>
       </c>
       <c r="E25">
@@ -10747,41 +10747,41 @@
       <c r="H25">
         <v>-2.03</v>
       </c>
-      <c r="I25" s="312">
+      <c r="I25" s="310">
         <v>12.28</v>
       </c>
-      <c r="J25" s="305">
+      <c r="J25" s="301">
         <v>23.53</v>
       </c>
-      <c r="K25" s="309">
+      <c r="K25" s="302">
         <v>35.87</v>
       </c>
-      <c r="L25" s="300">
+      <c r="L25" s="311">
         <v>32.7</v>
       </c>
-      <c r="M25" s="307">
+      <c r="M25" s="305">
         <v>19.43</v>
       </c>
-      <c r="N25" s="308">
+      <c r="N25" s="303">
         <v>15.74</v>
       </c>
-      <c r="O25" s="310">
+      <c r="O25" s="306">
         <v>18.69</v>
       </c>
-      <c r="P25" s="301">
+      <c r="P25" s="307">
         <v>30.57</v>
       </c>
-      <c r="Q25" s="302">
+      <c r="Q25" s="308">
         <v>17.53</v>
       </c>
-      <c r="R25" s="311">
+      <c r="R25" s="300">
         <v>10.73</v>
       </c>
-      <c r="S25" s="303">
+      <c r="S25" s="312">
         <v>16.49</v>
       </c>
       <c r="T25" s="304">
-        <v>-9</v>
+        <v>-11.71</v>
       </c>
     </row>
     <row r="26">
@@ -10794,7 +10794,7 @@
       <c r="C26" t="str">
         <v>603696</v>
       </c>
-      <c r="D26" s="319" t="str">
+      <c r="D26" s="320" t="str">
         <v>净卖: -3631.64万</v>
       </c>
       <c r="E26">
@@ -10809,41 +10809,41 @@
       <c r="H26">
         <v>9.08</v>
       </c>
-      <c r="I26" s="320">
+      <c r="I26" s="321">
         <v>-10.47</v>
       </c>
-      <c r="J26" s="321">
+      <c r="J26" s="322">
         <v>-19.42</v>
       </c>
       <c r="K26" s="313">
         <v>-21.91</v>
       </c>
-      <c r="L26" s="314">
+      <c r="L26" s="316">
         <v>-19.92</v>
       </c>
-      <c r="M26" s="324">
+      <c r="M26" s="314">
         <v>-11.91</v>
       </c>
-      <c r="N26" s="325">
+      <c r="N26" s="323">
         <v>-20.7</v>
       </c>
-      <c r="O26" s="322">
+      <c r="O26" s="317">
         <v>-25.29</v>
       </c>
-      <c r="P26" s="315">
+      <c r="P26" s="318">
         <v>-21.4</v>
       </c>
-      <c r="Q26" s="323">
+      <c r="Q26" s="319">
         <v>-13.54</v>
       </c>
-      <c r="R26" s="316">
+      <c r="R26" s="324">
         <v>-4.9</v>
       </c>
-      <c r="S26" s="317">
+      <c r="S26" s="315">
         <v>4.59</v>
       </c>
-      <c r="T26" s="318">
-        <v>-38.6</v>
+      <c r="T26" s="325">
+        <v>-40.43</v>
       </c>
     </row>
     <row r="27">
@@ -10856,7 +10856,7 @@
       <c r="C27" t="str">
         <v>002682</v>
       </c>
-      <c r="D27" s="338" t="str">
+      <c r="D27" s="337" t="str">
         <v>净卖: -4674.28万</v>
       </c>
       <c r="E27">
@@ -10871,41 +10871,41 @@
       <c r="H27">
         <v>-4.33</v>
       </c>
-      <c r="I27" s="336">
+      <c r="I27" s="338">
         <v>14.93</v>
       </c>
-      <c r="J27" s="333">
+      <c r="J27" s="326">
         <v>3.47</v>
       </c>
-      <c r="K27" s="326">
+      <c r="K27" s="328">
         <v>-6.84</v>
       </c>
-      <c r="L27" s="327">
+      <c r="L27" s="329">
         <v>-5.11</v>
       </c>
-      <c r="M27" s="334">
+      <c r="M27" s="332">
         <v>-10.89</v>
       </c>
-      <c r="N27" s="337">
+      <c r="N27" s="327">
         <v>-19.36</v>
       </c>
-      <c r="O27" s="330">
+      <c r="O27" s="333">
         <v>-21</v>
       </c>
-      <c r="P27" s="335">
+      <c r="P27" s="334">
         <v>-20.33</v>
       </c>
-      <c r="Q27" s="331">
+      <c r="Q27" s="335">
         <v>-12.43</v>
       </c>
-      <c r="R27" s="328">
+      <c r="R27" s="330">
         <v>-14.26</v>
       </c>
-      <c r="S27" s="329">
+      <c r="S27" s="336">
         <v>-7.8</v>
       </c>
-      <c r="T27" s="332">
-        <v>-42.77</v>
+      <c r="T27" s="331">
+        <v>-44.99</v>
       </c>
     </row>
     <row r="28">
@@ -10918,7 +10918,7 @@
       <c r="C28" t="str">
         <v>600693</v>
       </c>
-      <c r="D28" s="340" t="str">
+      <c r="D28" s="339" t="str">
         <v>净买: 4441.53万</v>
       </c>
       <c r="E28">
@@ -10933,41 +10933,41 @@
       <c r="H28">
         <v>1.81</v>
       </c>
-      <c r="I28" s="348">
+      <c r="I28" s="340">
         <v>8.04</v>
       </c>
-      <c r="J28" s="341">
+      <c r="J28" s="349">
         <v>15.95</v>
       </c>
-      <c r="K28" s="342">
+      <c r="K28" s="343">
         <v>10.22</v>
       </c>
-      <c r="L28" s="345">
+      <c r="L28" s="341">
         <v>13.45</v>
       </c>
-      <c r="M28" s="339">
+      <c r="M28" s="350">
         <v>12.33</v>
       </c>
-      <c r="N28" s="343">
+      <c r="N28" s="351">
         <v>23.53</v>
       </c>
-      <c r="O28" s="349">
+      <c r="O28" s="347">
         <v>28.54</v>
       </c>
-      <c r="P28" s="350">
+      <c r="P28" s="342">
         <v>41.4</v>
       </c>
-      <c r="Q28" s="344">
+      <c r="Q28" s="348">
         <v>37.84</v>
       </c>
-      <c r="R28" s="351">
+      <c r="R28" s="344">
         <v>44.23</v>
       </c>
-      <c r="S28" s="346">
+      <c r="S28" s="345">
         <v>30.52</v>
       </c>
-      <c r="T28" s="347">
-        <v>-22.87</v>
+      <c r="T28" s="346">
+        <v>-30.92</v>
       </c>
     </row>
     <row r="29">
@@ -10980,7 +10980,7 @@
       <c r="C29" t="str">
         <v>603696</v>
       </c>
-      <c r="D29" s="361" t="str">
+      <c r="D29" s="360" t="str">
         <v>净卖: -3147.63万</v>
       </c>
       <c r="E29">
@@ -10995,41 +10995,41 @@
       <c r="H29">
         <v>2.92</v>
       </c>
-      <c r="I29" s="359">
+      <c r="I29" s="361">
         <v>-12.53</v>
       </c>
-      <c r="J29" s="354">
+      <c r="J29" s="363">
         <v>-17.6</v>
       </c>
-      <c r="K29" s="355">
+      <c r="K29" s="354">
         <v>-13.3</v>
       </c>
-      <c r="L29" s="362">
+      <c r="L29" s="358">
         <v>-4.64</v>
       </c>
-      <c r="M29" s="363">
+      <c r="M29" s="364">
         <v>4.89</v>
       </c>
-      <c r="N29" s="364">
+      <c r="N29" s="359">
         <v>15.36</v>
       </c>
-      <c r="O29" s="356">
+      <c r="O29" s="355">
         <v>13.73</v>
       </c>
-      <c r="P29" s="352">
+      <c r="P29" s="356">
         <v>12.4</v>
       </c>
-      <c r="Q29" s="357">
+      <c r="Q29" s="362">
         <v>1.16</v>
       </c>
-      <c r="R29" s="358">
+      <c r="R29" s="352">
         <v>-8.97</v>
       </c>
-      <c r="S29" s="353">
+      <c r="S29" s="357">
         <v>-12.96</v>
       </c>
-      <c r="T29" s="360">
-        <v>-32.27</v>
+      <c r="T29" s="353">
+        <v>-34.29</v>
       </c>
     </row>
     <row r="30">
@@ -11042,7 +11042,7 @@
       <c r="C30" t="str">
         <v>600693</v>
       </c>
-      <c r="D30" s="368" t="str">
+      <c r="D30" s="371" t="str">
         <v>净卖: -5308.96万</v>
       </c>
       <c r="E30">
@@ -11057,41 +11057,41 @@
       <c r="H30">
         <v>2.51</v>
       </c>
-      <c r="I30" s="372">
+      <c r="I30" s="367">
         <v>0.41</v>
       </c>
-      <c r="J30" s="373">
+      <c r="J30" s="372">
         <v>-0.58</v>
       </c>
-      <c r="K30" s="377">
+      <c r="K30" s="368">
         <v>9.33</v>
       </c>
-      <c r="L30" s="374">
+      <c r="L30" s="370">
         <v>13.77</v>
       </c>
-      <c r="M30" s="365">
+      <c r="M30" s="373">
         <v>25.15</v>
       </c>
-      <c r="N30" s="366">
+      <c r="N30" s="377">
         <v>22</v>
       </c>
-      <c r="O30" s="375">
+      <c r="O30" s="369">
         <v>27.65</v>
       </c>
-      <c r="P30" s="371">
+      <c r="P30" s="365">
         <v>15.52</v>
       </c>
-      <c r="Q30" s="376">
+      <c r="Q30" s="374">
         <v>3.97</v>
       </c>
-      <c r="R30" s="369">
+      <c r="R30" s="375">
         <v>3.97</v>
       </c>
-      <c r="S30" s="367">
+      <c r="S30" s="376">
         <v>7.29</v>
       </c>
-      <c r="T30" s="370">
-        <v>-31.74</v>
+      <c r="T30" s="366">
+        <v>-38.86</v>
       </c>
     </row>
     <row r="31">
@@ -11119,41 +11119,41 @@
       <c r="H31">
         <v>1.88</v>
       </c>
-      <c r="I31" s="390">
+      <c r="I31" s="384">
         <v>8.08</v>
       </c>
-      <c r="J31" s="378">
+      <c r="J31" s="385">
         <v>17.78</v>
       </c>
-      <c r="K31" s="379">
+      <c r="K31" s="386">
         <v>12.93</v>
       </c>
-      <c r="L31" s="384">
+      <c r="L31" s="387">
         <v>4.39</v>
       </c>
-      <c r="M31" s="385">
+      <c r="M31" s="379">
         <v>5.54</v>
       </c>
-      <c r="N31" s="387">
+      <c r="N31" s="390">
         <v>1.85</v>
       </c>
-      <c r="O31" s="388">
+      <c r="O31" s="380">
         <v>-1.15</v>
       </c>
-      <c r="P31" s="380">
+      <c r="P31" s="381">
         <v>-3</v>
       </c>
-      <c r="Q31" s="382">
+      <c r="Q31" s="389">
         <v>-7.85</v>
       </c>
-      <c r="R31" s="381">
+      <c r="R31" s="382">
         <v>-11.09</v>
       </c>
-      <c r="S31" s="389">
+      <c r="S31" s="378">
         <v>-10.16</v>
       </c>
-      <c r="T31" s="386">
-        <v>-29.1</v>
+      <c r="T31" s="388">
+        <v>-32.1</v>
       </c>
     </row>
     <row r="32">
@@ -11166,7 +11166,7 @@
       <c r="C32" t="str">
         <v>600280</v>
       </c>
-      <c r="D32" s="401" t="str">
+      <c r="D32" s="403" t="str">
         <v>净卖: -2545.17万</v>
       </c>
       <c r="E32">
@@ -11181,41 +11181,41 @@
       <c r="H32">
         <v>-3.92</v>
       </c>
-      <c r="I32" s="398">
+      <c r="I32" s="396">
         <v>-0.2</v>
       </c>
-      <c r="J32" s="403">
+      <c r="J32" s="401">
         <v>-7.76</v>
       </c>
-      <c r="K32" s="394">
+      <c r="K32" s="397">
         <v>-6.73</v>
       </c>
-      <c r="L32" s="402">
+      <c r="L32" s="391">
         <v>-10</v>
       </c>
-      <c r="M32" s="391">
+      <c r="M32" s="394">
         <v>-12.65</v>
       </c>
-      <c r="N32" s="399">
+      <c r="N32" s="392">
         <v>-14.29</v>
       </c>
-      <c r="O32" s="395">
+      <c r="O32" s="398">
         <v>-18.57</v>
       </c>
-      <c r="P32" s="400">
+      <c r="P32" s="399">
         <v>-21.43</v>
       </c>
-      <c r="Q32" s="396">
+      <c r="Q32" s="395">
         <v>-20.61</v>
       </c>
-      <c r="R32" s="392">
+      <c r="R32" s="400">
         <v>-16.33</v>
       </c>
       <c r="S32" s="393">
         <v>-15.92</v>
       </c>
-      <c r="T32" s="397">
-        <v>-37.35</v>
+      <c r="T32" s="402">
+        <v>-40</v>
       </c>
     </row>
     <row r="33">
@@ -11228,7 +11228,7 @@
       <c r="C33" t="str">
         <v>002759</v>
       </c>
-      <c r="D33" s="407" t="str">
+      <c r="D33" s="412" t="str">
         <v>净买: 8490.49万</v>
       </c>
       <c r="E33">
@@ -11243,41 +11243,41 @@
       <c r="H33">
         <v>-3.82</v>
       </c>
-      <c r="I33" s="408">
+      <c r="I33" s="416">
         <v>11.08</v>
       </c>
-      <c r="J33" s="416">
+      <c r="J33" s="409">
         <v>22.19</v>
       </c>
       <c r="K33" s="413">
         <v>22.69</v>
       </c>
-      <c r="L33" s="409">
+      <c r="L33" s="404">
         <v>13.63</v>
       </c>
-      <c r="M33" s="404">
+      <c r="M33" s="414">
         <v>14.61</v>
       </c>
-      <c r="N33" s="414">
+      <c r="N33" s="406">
         <v>26.07</v>
       </c>
-      <c r="O33" s="415">
+      <c r="O33" s="405">
         <v>26.51</v>
       </c>
-      <c r="P33" s="410">
+      <c r="P33" s="415">
         <v>18.86</v>
       </c>
-      <c r="Q33" s="411">
+      <c r="Q33" s="410">
         <v>15.77</v>
       </c>
-      <c r="R33" s="412">
+      <c r="R33" s="407">
         <v>13.87</v>
       </c>
-      <c r="S33" s="406">
+      <c r="S33" s="411">
         <v>15.03</v>
       </c>
-      <c r="T33" s="405">
-        <v>-13.9</v>
+      <c r="T33" s="408">
+        <v>-17.53</v>
       </c>
     </row>
     <row r="34">
@@ -11290,7 +11290,7 @@
       <c r="C34" t="str">
         <v>002792</v>
       </c>
-      <c r="D34" s="420" t="str">
+      <c r="D34" s="426" t="str">
         <v>净买: 8322.30万</v>
       </c>
       <c r="E34">
@@ -11305,31 +11305,31 @@
       <c r="H34">
         <v>0.05</v>
       </c>
-      <c r="I34" s="421">
+      <c r="I34" s="427">
         <v>7.5</v>
       </c>
-      <c r="J34" s="422">
+      <c r="J34" s="421">
         <v>15.33</v>
       </c>
-      <c r="K34" s="423">
+      <c r="K34" s="428">
         <v>19.23</v>
       </c>
-      <c r="L34" s="424">
+      <c r="L34" s="418">
         <v>31.17</v>
       </c>
-      <c r="M34" s="418">
+      <c r="M34" s="419">
         <v>44.28</v>
       </c>
-      <c r="N34" s="426">
+      <c r="N34" s="420">
         <v>53.02</v>
       </c>
-      <c r="O34" s="419">
+      <c r="O34" s="422">
         <v>68.33</v>
       </c>
-      <c r="P34" s="427">
+      <c r="P34" s="423">
         <v>76.16</v>
       </c>
-      <c r="Q34" s="428">
+      <c r="Q34" s="424">
         <v>58.53</v>
       </c>
       <c r="R34" s="429">
@@ -11339,7 +11339,7 @@
         <v>30.19</v>
       </c>
       <c r="T34" s="417">
-        <v>28.85</v>
+        <v>14.85</v>
       </c>
     </row>
     <row r="35">
@@ -11352,7 +11352,7 @@
       <c r="C35" t="str">
         <v>002792</v>
       </c>
-      <c r="D35" s="441" t="str">
+      <c r="D35" s="431" t="str">
         <v>净卖: -7684.69万</v>
       </c>
       <c r="E35">
@@ -11367,41 +11367,41 @@
       <c r="H35">
         <v>2.25</v>
       </c>
-      <c r="I35" s="436">
+      <c r="I35" s="437">
         <v>4.92</v>
       </c>
-      <c r="J35" s="433">
+      <c r="J35" s="432">
         <v>8.47</v>
       </c>
-      <c r="K35" s="442">
+      <c r="K35" s="433">
         <v>19.33</v>
       </c>
-      <c r="L35" s="437">
+      <c r="L35" s="434">
         <v>31.26</v>
       </c>
-      <c r="M35" s="434">
+      <c r="M35" s="435">
         <v>39.21</v>
       </c>
-      <c r="N35" s="430">
+      <c r="N35" s="436">
         <v>53.14</v>
       </c>
-      <c r="O35" s="431">
+      <c r="O35" s="442">
         <v>60.26</v>
       </c>
-      <c r="P35" s="432">
+      <c r="P35" s="438">
         <v>44.23</v>
       </c>
-      <c r="Q35" s="435">
+      <c r="Q35" s="439">
         <v>29.8</v>
       </c>
-      <c r="R35" s="438">
+      <c r="R35" s="440">
         <v>18.44</v>
       </c>
-      <c r="S35" s="439">
+      <c r="S35" s="430">
         <v>17.43</v>
       </c>
-      <c r="T35" s="440">
-        <v>17.22</v>
+      <c r="T35" s="441">
+        <v>4.49</v>
       </c>
     </row>
     <row r="36">
@@ -11414,7 +11414,7 @@
       <c r="C36" t="str">
         <v>002759</v>
       </c>
-      <c r="D36" s="447" t="str">
+      <c r="D36" s="455" t="str">
         <v>净买: 1.00亿</v>
       </c>
       <c r="E36">
@@ -11429,41 +11429,41 @@
       <c r="H36">
         <v>3.06</v>
       </c>
-      <c r="I36" s="448">
+      <c r="I36" s="445">
         <v>6.73</v>
       </c>
-      <c r="J36" s="450">
+      <c r="J36" s="453">
         <v>7.11</v>
       </c>
-      <c r="K36" s="451">
+      <c r="K36" s="448">
         <v>0.63</v>
       </c>
-      <c r="L36" s="452">
+      <c r="L36" s="446">
         <v>-1.99</v>
       </c>
-      <c r="M36" s="453">
+      <c r="M36" s="454">
         <v>-3.59</v>
       </c>
-      <c r="N36" s="454">
+      <c r="N36" s="447">
         <v>-2.61</v>
       </c>
-      <c r="O36" s="455">
+      <c r="O36" s="449">
         <v>-7.82</v>
       </c>
-      <c r="P36" s="443">
+      <c r="P36" s="450">
         <v>-11.35</v>
       </c>
-      <c r="Q36" s="445">
+      <c r="Q36" s="443">
         <v>-5.64</v>
       </c>
       <c r="R36" s="444">
         <v>-13.61</v>
       </c>
-      <c r="S36" s="449">
+      <c r="S36" s="451">
         <v>-12.5</v>
       </c>
-      <c r="T36" s="446">
-        <v>-27.11</v>
+      <c r="T36" s="452">
+        <v>-30.18</v>
       </c>
     </row>
     <row r="37">
@@ -11476,7 +11476,7 @@
       <c r="C37" t="str">
         <v>600776</v>
       </c>
-      <c r="D37" s="463" t="str">
+      <c r="D37" s="465" t="str">
         <v>净买: 5452.75万</v>
       </c>
       <c r="E37">
@@ -11491,41 +11491,41 @@
       <c r="H37">
         <v>10.02</v>
       </c>
-      <c r="I37" s="464">
+      <c r="I37" s="458">
         <v>0</v>
       </c>
-      <c r="J37" s="468">
+      <c r="J37" s="459">
         <v>10</v>
       </c>
-      <c r="K37" s="456">
+      <c r="K37" s="460">
         <v>16.57</v>
       </c>
-      <c r="L37" s="457">
+      <c r="L37" s="461">
         <v>4.91</v>
       </c>
-      <c r="M37" s="465">
+      <c r="M37" s="466">
         <v>-5.58</v>
       </c>
-      <c r="N37" s="466">
+      <c r="N37" s="467">
         <v>-15.01</v>
       </c>
-      <c r="O37" s="467">
+      <c r="O37" s="463">
         <v>-17.91</v>
       </c>
-      <c r="P37" s="458">
+      <c r="P37" s="468">
         <v>-16.93</v>
       </c>
-      <c r="Q37" s="459">
+      <c r="Q37" s="456">
         <v>-15.19</v>
       </c>
-      <c r="R37" s="460">
+      <c r="R37" s="462">
         <v>-10.99</v>
       </c>
-      <c r="S37" s="461">
+      <c r="S37" s="457">
         <v>-15.27</v>
       </c>
-      <c r="T37" s="462">
-        <v>-26.75</v>
+      <c r="T37" s="464">
+        <v>-26.53</v>
       </c>
     </row>
     <row r="38">
@@ -11553,41 +11553,41 @@
       <c r="H38">
         <v>-1.64</v>
       </c>
-      <c r="I38" s="474">
+      <c r="I38" s="475">
         <v>11.84</v>
       </c>
-      <c r="J38" s="475">
+      <c r="J38" s="478">
         <v>23.02</v>
       </c>
-      <c r="K38" s="472">
+      <c r="K38" s="476">
         <v>10.78</v>
       </c>
-      <c r="L38" s="476">
+      <c r="L38" s="481">
         <v>2.42</v>
       </c>
-      <c r="M38" s="478">
+      <c r="M38" s="479">
         <v>0</v>
       </c>
-      <c r="N38" s="479">
+      <c r="N38" s="472">
         <v>1.86</v>
       </c>
-      <c r="O38" s="473">
+      <c r="O38" s="469">
         <v>2.67</v>
       </c>
-      <c r="P38" s="469">
+      <c r="P38" s="473">
         <v>5.99</v>
       </c>
-      <c r="Q38" s="470">
+      <c r="Q38" s="480">
         <v>0.81</v>
       </c>
-      <c r="R38" s="471">
+      <c r="R38" s="470">
         <v>6.95</v>
       </c>
-      <c r="S38" s="480">
+      <c r="S38" s="474">
         <v>6.25</v>
       </c>
-      <c r="T38" s="481">
-        <v>40.55</v>
+      <c r="T38" s="471">
+        <v>36.98</v>
       </c>
     </row>
     <row r="39">
@@ -11600,7 +11600,7 @@
       <c r="C39" t="str">
         <v>600410</v>
       </c>
-      <c r="D39" s="487" t="str">
+      <c r="D39" s="489" t="str">
         <v>净买: 1.26亿</v>
       </c>
       <c r="E39">
@@ -11615,22 +11615,22 @@
       <c r="H39">
         <v>10</v>
       </c>
-      <c r="I39" s="488">
+      <c r="I39" s="494">
         <v>0</v>
       </c>
-      <c r="J39" s="482">
+      <c r="J39" s="484">
         <v>-9.95</v>
       </c>
-      <c r="K39" s="486">
+      <c r="K39" s="490">
         <v>-16.75</v>
       </c>
-      <c r="L39" s="483">
+      <c r="L39" s="487">
         <v>-18.71</v>
       </c>
-      <c r="M39" s="484">
+      <c r="M39" s="488">
         <v>-17.2</v>
       </c>
-      <c r="N39" s="489">
+      <c r="N39" s="491">
         <v>-16.54</v>
       </c>
       <c r="O39" s="492">
@@ -11639,17 +11639,17 @@
       <c r="P39" s="493">
         <v>-18.06</v>
       </c>
-      <c r="Q39" s="490">
+      <c r="Q39" s="482">
         <v>-13.06</v>
       </c>
-      <c r="R39" s="494">
+      <c r="R39" s="485">
         <v>-13.64</v>
       </c>
-      <c r="S39" s="491">
+      <c r="S39" s="486">
         <v>-10.2</v>
       </c>
-      <c r="T39" s="485">
-        <v>14.25</v>
+      <c r="T39" s="483">
+        <v>11.34</v>
       </c>
     </row>
     <row r="40">
@@ -11662,7 +11662,7 @@
       <c r="C40" t="str">
         <v>600776</v>
       </c>
-      <c r="D40" s="500" t="str">
+      <c r="D40" s="501" t="str">
         <v>净卖: -233.39万</v>
       </c>
       <c r="E40">
@@ -11677,41 +11677,41 @@
       <c r="H40">
         <v>-10</v>
       </c>
-      <c r="I40" s="495">
+      <c r="I40" s="505">
         <v>0</v>
       </c>
-      <c r="J40" s="501">
+      <c r="J40" s="498">
         <v>-9.98</v>
       </c>
-      <c r="K40" s="496">
+      <c r="K40" s="502">
         <v>-13.06</v>
       </c>
-      <c r="L40" s="497">
+      <c r="L40" s="506">
         <v>-12.02</v>
       </c>
-      <c r="M40" s="502">
+      <c r="M40" s="495">
         <v>-10.17</v>
       </c>
-      <c r="N40" s="505">
+      <c r="N40" s="503">
         <v>-5.72</v>
       </c>
-      <c r="O40" s="503">
+      <c r="O40" s="496">
         <v>-10.26</v>
       </c>
       <c r="P40" s="504">
         <v>-9.89</v>
       </c>
-      <c r="Q40" s="498">
+      <c r="Q40" s="499">
         <v>-11.26</v>
       </c>
-      <c r="R40" s="506">
+      <c r="R40" s="507">
         <v>-11.78</v>
       </c>
-      <c r="S40" s="499">
+      <c r="S40" s="500">
         <v>-12.49</v>
       </c>
-      <c r="T40" s="507">
-        <v>-22.42</v>
+      <c r="T40" s="497">
+        <v>-22.19</v>
       </c>
     </row>
     <row r="41">
@@ -11724,7 +11724,7 @@
       <c r="C41" t="str">
         <v>600410</v>
       </c>
-      <c r="D41" s="516" t="str">
+      <c r="D41" s="514" t="str">
         <v>净卖: -1.30亿</v>
       </c>
       <c r="E41">
@@ -11739,41 +11739,41 @@
       <c r="H41">
         <v>-1.97</v>
       </c>
-      <c r="I41" s="508">
+      <c r="I41" s="515">
         <v>-8.15</v>
       </c>
-      <c r="J41" s="512">
+      <c r="J41" s="519">
         <v>-15.08</v>
       </c>
-      <c r="K41" s="514">
+      <c r="K41" s="520">
         <v>-17.08</v>
       </c>
-      <c r="L41" s="509">
+      <c r="L41" s="516">
         <v>-15.54</v>
       </c>
-      <c r="M41" s="517">
+      <c r="M41" s="510">
         <v>-14.87</v>
       </c>
-      <c r="N41" s="518">
+      <c r="N41" s="508">
         <v>-12.11</v>
       </c>
-      <c r="O41" s="510">
+      <c r="O41" s="511">
         <v>-16.42</v>
       </c>
-      <c r="P41" s="515">
+      <c r="P41" s="517">
         <v>-11.32</v>
       </c>
-      <c r="Q41" s="513">
+      <c r="Q41" s="512">
         <v>-11.9</v>
       </c>
-      <c r="R41" s="519">
+      <c r="R41" s="513">
         <v>-8.4</v>
       </c>
-      <c r="S41" s="511">
+      <c r="S41" s="518">
         <v>-12.24</v>
       </c>
-      <c r="T41" s="520">
-        <v>16.54</v>
+      <c r="T41" s="509">
+        <v>13.58</v>
       </c>
     </row>
     <row r="42">
@@ -11786,7 +11786,7 @@
       <c r="C42" t="str">
         <v>002792</v>
       </c>
-      <c r="D42" s="533" t="str">
+      <c r="D42" s="531" t="str">
         <v>净买: 5153.68万</v>
       </c>
       <c r="E42">
@@ -11801,41 +11801,41 @@
       <c r="H42">
         <v>0.55</v>
       </c>
-      <c r="I42" s="521">
+      <c r="I42" s="526">
         <v>9.39</v>
       </c>
-      <c r="J42" s="530">
+      <c r="J42" s="524">
         <v>15.85</v>
       </c>
-      <c r="K42" s="527">
+      <c r="K42" s="532">
         <v>10.51</v>
       </c>
-      <c r="L42" s="522">
+      <c r="L42" s="533">
         <v>6.31</v>
       </c>
-      <c r="M42" s="523">
+      <c r="M42" s="525">
         <v>1.07</v>
       </c>
-      <c r="N42" s="525">
+      <c r="N42" s="529">
         <v>-1.76</v>
       </c>
-      <c r="O42" s="526">
+      <c r="O42" s="527">
         <v>0.67</v>
       </c>
-      <c r="P42" s="528">
+      <c r="P42" s="521">
         <v>10.74</v>
       </c>
-      <c r="Q42" s="531">
+      <c r="Q42" s="528">
         <v>10.74</v>
       </c>
-      <c r="R42" s="524">
+      <c r="R42" s="522">
         <v>7.46</v>
       </c>
-      <c r="S42" s="532">
+      <c r="S42" s="523">
         <v>7.34</v>
       </c>
-      <c r="T42" s="529">
-        <v>7.32</v>
+      <c r="T42" s="530">
+        <v>-4.34</v>
       </c>
     </row>
     <row r="43">
@@ -11897,41 +11897,41 @@
       <c r="F44" t="str"/>
       <c r="G44" t="str"/>
       <c r="H44" t="str"/>
-      <c r="I44" s="534">
+      <c r="I44" s="539">
         <v>65.85</v>
       </c>
-      <c r="J44" s="539">
+      <c r="J44" s="541">
         <v>65.85</v>
       </c>
-      <c r="K44" s="540">
+      <c r="K44" s="542">
         <v>60.98</v>
       </c>
-      <c r="L44" s="535">
+      <c r="L44" s="534">
         <v>56.1</v>
       </c>
-      <c r="M44" s="536">
+      <c r="M44" s="535">
         <v>48.78</v>
       </c>
-      <c r="N44" s="542">
+      <c r="N44" s="543">
         <v>46.34</v>
       </c>
-      <c r="O44" s="537">
+      <c r="O44" s="544">
         <v>48.78</v>
       </c>
       <c r="P44" s="538">
         <v>43.9</v>
       </c>
-      <c r="Q44" s="541">
+      <c r="Q44" s="545">
         <v>39.02</v>
       </c>
-      <c r="R44" s="543">
+      <c r="R44" s="540">
         <v>43.9</v>
       </c>
-      <c r="S44" s="544">
+      <c r="S44" s="536">
         <v>43.9</v>
       </c>
-      <c r="T44" s="545">
-        <v>34.15</v>
+      <c r="T44" s="537">
+        <v>29.27</v>
       </c>
     </row>
     <row r="45">
@@ -11945,41 +11945,41 @@
       <c r="F45" t="str"/>
       <c r="G45" t="str"/>
       <c r="H45" t="str"/>
-      <c r="I45" s="550">
+      <c r="I45" s="549">
         <v>3.79</v>
       </c>
-      <c r="J45" s="551">
+      <c r="J45" s="546">
         <v>5.59</v>
       </c>
-      <c r="K45" s="547">
+      <c r="K45" s="553">
         <v>5.07</v>
       </c>
-      <c r="L45" s="552">
+      <c r="L45" s="554">
         <v>5.23</v>
       </c>
-      <c r="M45" s="557">
+      <c r="M45" s="550">
         <v>5.01</v>
       </c>
-      <c r="N45" s="553">
+      <c r="N45" s="552">
         <v>4.05</v>
       </c>
-      <c r="O45" s="548">
+      <c r="O45" s="555">
         <v>4.42</v>
       </c>
-      <c r="P45" s="549">
+      <c r="P45" s="547">
         <v>3.76</v>
       </c>
-      <c r="Q45" s="546">
+      <c r="Q45" s="548">
         <v>1.74</v>
       </c>
-      <c r="R45" s="554">
+      <c r="R45" s="551">
         <v>1.6</v>
       </c>
-      <c r="S45" s="555">
+      <c r="S45" s="556">
         <v>0.99</v>
       </c>
-      <c r="T45" s="556">
-        <v>-5.5</v>
+      <c r="T45" s="557">
+        <v>-9.52</v>
       </c>
     </row>
   </sheetData>

--- a/youzi/越王大道/index.xlsx
+++ b/youzi/越王大道/index.xlsx
@@ -39,19 +39,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF70C483"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED979F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA91E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218E3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAE202D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB8E1C1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAB1E2C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFC4E7CC"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF70C483"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FF1E8236"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -69,151 +117,721 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDA3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BDC2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAC1F2C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC32938"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAB1F2C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC02836"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD33140"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDE4150"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCF0F1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFA4AB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2FAA4B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF1A7230"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFDF3F4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE2E4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBE8EA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87A84"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC42A38"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED9BA3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7130"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3D4D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD53241"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9808A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFACDDB7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7DCA8F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF67C07B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCA2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF95D3A3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC969F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDB3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B2B8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB9199"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFDFD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9DFE1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDA3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3B9BF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25866"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEE9FA6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBB2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD2303F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BFC4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8437"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A702F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E7F35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBEDEE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7B33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBEAEC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE3E5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23953E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23943D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8437"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5BBC71"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDE4251"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCFDFC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFAE202D"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1E8236"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAB1E2C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218E3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED979F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB8E1C1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA91E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFDC3545"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDA3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAB1F2C"/>
+        <fgColor rgb="FF23943D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6AC27E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC3E6CB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A712F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218D3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208838"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7B34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF46B35F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A443"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7FCA90"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC52A39"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -225,7 +843,2335 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF3BDC2"/>
+        <fgColor rgb="FF63BF78"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5FBD75"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23943D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBC2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24983F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8638"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8738"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8638"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7E35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23933D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7A33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8136"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF46B35F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2DFBC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8738"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF84CD95"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6DC381"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF53B86A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2DFBC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7CC98E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B2B8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2FA94B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5EBD74"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A644"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77580"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFCFC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6CC280"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8638"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF249A3F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7CC98E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22903C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBF2736"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77883"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF95D3A3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BAC0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDE4150"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B3B9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6CDD1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF99D5A7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9DCDF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFBFB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8337"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9858F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24983F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196F2F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD43140"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDE4251"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208839"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC929B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF54B96B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF37AD52"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4C4C8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6EC382"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46672"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDE4554"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2CA848"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8538"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A544"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6727D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBB2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6D0D3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3949"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7832"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF37AD52"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAE202D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC32A38"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE35E6B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE35E6B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCEEEF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6F4E9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBB2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCDEAD4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE04D5B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7ECA8F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8537"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD63242"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B4BA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8638"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22923D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6FBF7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC12937"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87E88"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB72432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3847"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE5E7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA9DBB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8ED19D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC92C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF64BF79"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8538"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF269F42"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC52A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3848"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A042"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEE9DA4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD1303F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9DEE0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC72B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B3B9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC939B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCC2D3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259E41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196D2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB52331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8136"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7E35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC12937"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -243,6 +3189,174 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF26A042"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAD1F2D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D3D7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE3E6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB3E0BD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBC2635"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9838D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7BC98D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBC2635"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7BC98D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0DEBA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7631"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD63242"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE4F4E8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE4F4E8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7BC98D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A142"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED9BA2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE04F5D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE35D6A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFAC1F2C"/>
         <bgColor/>
       </patternFill>
@@ -261,3121 +3375,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF3F4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2FAA4B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFA4AB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE2E4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8ACF9A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCF0F1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC02836"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD33140"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDE4150"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD53241"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBE8EA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC959E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3D4D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED9BA3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFACDDB7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7DCA8F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9808A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7130"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC42A38"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0ACB3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B2B8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF95D3A3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF67C07B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCA2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC969F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDB3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3B9BF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFDFD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9DFE1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDA3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEE9FA6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBB2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB92533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25866"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD2303F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBEDEE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7B33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A702F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E7F35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8437"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BFC4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBEAEC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDE4251"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6AC27E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE3E5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8437"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23943D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCFDFC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23943D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23953E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5BBC71"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218D3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A712F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208838"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF46B35F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A443"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7B34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC3E6CB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7FCA90"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5FBD75"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8337"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23943D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBC2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF63BF78"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC52A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8638"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8638"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7E35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23933D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8738"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7A33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8136"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7CC98E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5EBD74"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF53B86A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B2B8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6DC381"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2DFBC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2DFBC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2FA94B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF46B35F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8738"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF84CD95"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6CC280"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77580"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A644"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8638"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF249A3F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFCFC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22903C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7CC98E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77883"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBF2736"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF95D3A3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6CDD1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9DCDF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8337"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9858F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BAC0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF99D5A7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF30AA4C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B3B9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFBFB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDE4251"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196F2F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD43140"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208839"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC929B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4C4C8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF54B96B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF37AD52"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2EA94A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46672"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDE4554"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2CA848"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6727D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A544"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8538"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBB2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7832"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF37AD52"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6D0D3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3949"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCEEEF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAE202D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6F4E9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE35E6B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE35E6B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC32A38"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD63242"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCDEAD4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7ECA8F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBB2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE04D5B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8537"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B4BA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6FBF7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22923D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8638"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC12937"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB72432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3847"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4957"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF269F42"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC92C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA9DBB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8ED19D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE5E7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8538"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC52A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF64BF79"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3848"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A042"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC939B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC72B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B3B9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD1303F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9DEE0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEE9DA4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259E41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196D2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7E35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8136"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC12937"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC32938"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D3D7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFAD1F2D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE3E6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB3E0BD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF44B25D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9838D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE4F4E8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7BC98D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7BC98D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBC2635"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7BC98D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBC2635"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD63242"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0DEBA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE4F4E8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A142"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAD1F2D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE04F5D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAC1F2C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE35D6A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED9BA2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -9306,7 +9306,7 @@
       <c r="C2" t="str">
         <v>002570</v>
       </c>
-      <c r="D2" s="5" t="str">
+      <c r="D2" s="13" t="str">
         <v>净卖: -1602.12万</v>
       </c>
       <c r="E2">
@@ -9321,41 +9321,41 @@
       <c r="H2">
         <v>0.15</v>
       </c>
-      <c r="I2" s="13">
+      <c r="I2" s="4">
         <v>9.77</v>
       </c>
       <c r="J2" s="9">
         <v>9.62</v>
       </c>
-      <c r="K2" s="1">
+      <c r="K2" s="10">
         <v>-1.35</v>
       </c>
-      <c r="L2" s="10">
+      <c r="L2" s="5">
         <v>-7.07</v>
       </c>
-      <c r="M2" s="2">
+      <c r="M2" s="1">
         <v>-3.31</v>
       </c>
-      <c r="N2" s="11">
+      <c r="N2" s="2">
         <v>2.56</v>
       </c>
-      <c r="O2" s="7">
+      <c r="O2" s="6">
         <v>9.32</v>
       </c>
-      <c r="P2" s="12">
+      <c r="P2" s="7">
         <v>-1.65</v>
       </c>
       <c r="Q2" s="3">
         <v>-11.43</v>
       </c>
-      <c r="R2" s="6">
+      <c r="R2" s="8">
         <v>-9.47</v>
       </c>
-      <c r="S2" s="8">
+      <c r="S2" s="11">
         <v>-8.12</v>
       </c>
-      <c r="T2" s="4">
-        <v>-26.77</v>
+      <c r="T2" s="12">
+        <v>-26.17</v>
       </c>
     </row>
     <row r="3">
@@ -9368,7 +9368,7 @@
       <c r="C3" t="str">
         <v>002915</v>
       </c>
-      <c r="D3" s="22" t="str">
+      <c r="D3" s="17" t="str">
         <v>净买: 2039.94万</v>
       </c>
       <c r="E3">
@@ -9383,41 +9383,41 @@
       <c r="H3">
         <v>0.12</v>
       </c>
-      <c r="I3" s="26">
+      <c r="I3" s="21">
         <v>5.12</v>
       </c>
-      <c r="J3" s="18">
+      <c r="J3" s="25">
         <v>15.65</v>
       </c>
-      <c r="K3" s="14">
+      <c r="K3" s="26">
         <v>27.2</v>
       </c>
-      <c r="L3" s="15">
+      <c r="L3" s="18">
         <v>27.56</v>
       </c>
-      <c r="M3" s="23">
+      <c r="M3" s="22">
         <v>40.3</v>
       </c>
-      <c r="N3" s="19">
+      <c r="N3" s="14">
         <v>27.68</v>
       </c>
-      <c r="O3" s="16">
+      <c r="O3" s="23">
         <v>30.06</v>
       </c>
-      <c r="P3" s="20">
+      <c r="P3" s="19">
         <v>28.1</v>
       </c>
-      <c r="Q3" s="17">
+      <c r="Q3" s="15">
         <v>36.9</v>
       </c>
-      <c r="R3" s="21">
+      <c r="R3" s="20">
         <v>34.52</v>
       </c>
-      <c r="S3" s="24">
+      <c r="S3" s="16">
         <v>21.07</v>
       </c>
-      <c r="T3" s="25">
-        <v>23.75</v>
+      <c r="T3" s="24">
+        <v>15.24</v>
       </c>
     </row>
     <row r="4">
@@ -9430,7 +9430,7 @@
       <c r="C4" t="str">
         <v>002229</v>
       </c>
-      <c r="D4" s="31" t="str">
+      <c r="D4" s="29" t="str">
         <v>净买: 2135.02万</v>
       </c>
       <c r="E4">
@@ -9445,41 +9445,41 @@
       <c r="H4">
         <v>8.23</v>
       </c>
-      <c r="I4" s="32">
+      <c r="I4" s="27">
         <v>1.62</v>
       </c>
-      <c r="J4" s="37">
+      <c r="J4" s="28">
         <v>11.75</v>
       </c>
-      <c r="K4" s="27">
+      <c r="K4" s="34">
         <v>21.04</v>
       </c>
-      <c r="L4" s="28">
+      <c r="L4" s="35">
         <v>28.15</v>
       </c>
       <c r="M4" s="38">
         <v>15.34</v>
       </c>
-      <c r="N4" s="39">
+      <c r="N4" s="30">
         <v>13.65</v>
       </c>
-      <c r="O4" s="33">
+      <c r="O4" s="36">
         <v>13.02</v>
       </c>
-      <c r="P4" s="34">
+      <c r="P4" s="37">
         <v>7.32</v>
       </c>
-      <c r="Q4" s="35">
+      <c r="Q4" s="31">
         <v>9.5</v>
       </c>
-      <c r="R4" s="30">
+      <c r="R4" s="39">
         <v>9.57</v>
       </c>
-      <c r="S4" s="36">
+      <c r="S4" s="32">
         <v>14.22</v>
       </c>
-      <c r="T4" s="29">
-        <v>18.79</v>
+      <c r="T4" s="33">
+        <v>16.68</v>
       </c>
     </row>
     <row r="5">
@@ -9492,7 +9492,7 @@
       <c r="C5" t="str">
         <v>002915</v>
       </c>
-      <c r="D5" s="42" t="str">
+      <c r="D5" s="46" t="str">
         <v>净卖: -2747.73万</v>
       </c>
       <c r="E5">
@@ -9507,41 +9507,41 @@
       <c r="H5">
         <v>9.98</v>
       </c>
-      <c r="I5" s="46">
+      <c r="I5" s="40">
         <v>0</v>
       </c>
-      <c r="J5" s="40">
+      <c r="J5" s="51">
         <v>0.28</v>
       </c>
-      <c r="K5" s="47">
+      <c r="K5" s="44">
         <v>10.29</v>
       </c>
-      <c r="L5" s="48">
+      <c r="L5" s="47">
         <v>0.37</v>
       </c>
-      <c r="M5" s="43">
+      <c r="M5" s="48">
         <v>2.25</v>
       </c>
-      <c r="N5" s="44">
+      <c r="N5" s="52">
         <v>0.7</v>
       </c>
-      <c r="O5" s="49">
+      <c r="O5" s="41">
         <v>7.63</v>
       </c>
-      <c r="P5" s="50">
+      <c r="P5" s="42">
         <v>5.76</v>
       </c>
-      <c r="Q5" s="41">
+      <c r="Q5" s="49">
         <v>-4.82</v>
       </c>
-      <c r="R5" s="51">
+      <c r="R5" s="45">
         <v>4.68</v>
       </c>
-      <c r="S5" s="52">
+      <c r="S5" s="43">
         <v>11</v>
       </c>
-      <c r="T5" s="45">
-        <v>-2.71</v>
+      <c r="T5" s="50">
+        <v>-9.41</v>
       </c>
     </row>
     <row r="6">
@@ -9554,7 +9554,7 @@
       <c r="C6" t="str">
         <v>002177</v>
       </c>
-      <c r="D6" s="59" t="str">
+      <c r="D6" s="62" t="str">
         <v>净买: 3117.92万</v>
       </c>
       <c r="E6">
@@ -9569,41 +9569,41 @@
       <c r="H6">
         <v>5.02</v>
       </c>
-      <c r="I6" s="56">
+      <c r="I6" s="58">
         <v>4.78</v>
       </c>
-      <c r="J6" s="60">
+      <c r="J6" s="61">
         <v>10.79</v>
       </c>
-      <c r="K6" s="65">
+      <c r="K6" s="55">
         <v>7.24</v>
       </c>
-      <c r="L6" s="57">
+      <c r="L6" s="63">
         <v>12.3</v>
       </c>
-      <c r="M6" s="53">
+      <c r="M6" s="59">
         <v>5.6</v>
       </c>
-      <c r="N6" s="58">
+      <c r="N6" s="56">
         <v>2.46</v>
       </c>
-      <c r="O6" s="61">
+      <c r="O6" s="64">
         <v>-1.91</v>
       </c>
-      <c r="P6" s="64">
+      <c r="P6" s="57">
         <v>-9.56</v>
       </c>
-      <c r="Q6" s="62">
+      <c r="Q6" s="65">
         <v>-3.01</v>
       </c>
-      <c r="R6" s="54">
+      <c r="R6" s="53">
         <v>0.55</v>
       </c>
-      <c r="S6" s="63">
+      <c r="S6" s="60">
         <v>3.14</v>
       </c>
-      <c r="T6" s="55">
-        <v>2.6</v>
+      <c r="T6" s="54">
+        <v>3.28</v>
       </c>
     </row>
     <row r="7">
@@ -9616,7 +9616,7 @@
       <c r="C7" t="str">
         <v>002177</v>
       </c>
-      <c r="D7" s="67" t="str">
+      <c r="D7" s="74" t="str">
         <v>净卖: -2852.77万</v>
       </c>
       <c r="E7">
@@ -9634,38 +9634,38 @@
       <c r="I7" s="68">
         <v>10.19</v>
       </c>
-      <c r="J7" s="76">
+      <c r="J7" s="69">
         <v>6.66</v>
       </c>
-      <c r="K7" s="69">
+      <c r="K7" s="75">
         <v>11.68</v>
       </c>
-      <c r="L7" s="78">
+      <c r="L7" s="72">
         <v>5.03</v>
       </c>
-      <c r="M7" s="70">
+      <c r="M7" s="76">
         <v>1.9</v>
       </c>
-      <c r="N7" s="71">
+      <c r="N7" s="70">
         <v>-2.45</v>
       </c>
-      <c r="O7" s="72">
+      <c r="O7" s="77">
         <v>-10.05</v>
       </c>
-      <c r="P7" s="74">
+      <c r="P7" s="66">
         <v>-3.53</v>
       </c>
       <c r="Q7" s="73">
         <v>0</v>
       </c>
-      <c r="R7" s="77">
+      <c r="R7" s="71">
         <v>2.58</v>
       </c>
-      <c r="S7" s="75">
+      <c r="S7" s="67">
         <v>-5.3</v>
       </c>
-      <c r="T7" s="66">
-        <v>2.04</v>
+      <c r="T7" s="78">
+        <v>2.72</v>
       </c>
     </row>
     <row r="8">
@@ -9678,7 +9678,7 @@
       <c r="C8" t="str">
         <v>002882</v>
       </c>
-      <c r="D8" s="91" t="str">
+      <c r="D8" s="83" t="str">
         <v>净卖: -1459.92万</v>
       </c>
       <c r="E8">
@@ -9693,41 +9693,41 @@
       <c r="H8">
         <v>-0.92</v>
       </c>
-      <c r="I8" s="88">
+      <c r="I8" s="84">
         <v>11.01</v>
       </c>
-      <c r="J8" s="79">
+      <c r="J8" s="90">
         <v>11.21</v>
       </c>
-      <c r="K8" s="80">
+      <c r="K8" s="85">
         <v>1.71</v>
       </c>
-      <c r="L8" s="89">
+      <c r="L8" s="86">
         <v>4.11</v>
       </c>
-      <c r="M8" s="81">
+      <c r="M8" s="79">
         <v>0.04</v>
       </c>
-      <c r="N8" s="82">
+      <c r="N8" s="80">
         <v>0.78</v>
       </c>
-      <c r="O8" s="85">
+      <c r="O8" s="87">
         <v>2.37</v>
       </c>
-      <c r="P8" s="83">
+      <c r="P8" s="81">
         <v>5.12</v>
       </c>
-      <c r="Q8" s="90">
+      <c r="Q8" s="91">
         <v>5.93</v>
       </c>
-      <c r="R8" s="86">
+      <c r="R8" s="88">
         <v>8.07</v>
       </c>
-      <c r="S8" s="84">
+      <c r="S8" s="89">
         <v>18.88</v>
       </c>
-      <c r="T8" s="87">
-        <v>8.3</v>
+      <c r="T8" s="82">
+        <v>6.24</v>
       </c>
     </row>
     <row r="9">
@@ -9740,7 +9740,7 @@
       <c r="C9" t="str">
         <v>003029</v>
       </c>
-      <c r="D9" s="101" t="str">
+      <c r="D9" s="94" t="str">
         <v>净卖: -276.02万</v>
       </c>
       <c r="E9">
@@ -9755,41 +9755,41 @@
       <c r="H9">
         <v>10.01</v>
       </c>
-      <c r="I9" s="102">
+      <c r="I9" s="101">
         <v>0</v>
       </c>
-      <c r="J9" s="103">
+      <c r="J9" s="92">
         <v>10.01</v>
       </c>
-      <c r="K9" s="104">
+      <c r="K9" s="93">
         <v>1.58</v>
       </c>
-      <c r="L9" s="92">
+      <c r="L9" s="102">
         <v>0.44</v>
       </c>
-      <c r="M9" s="94">
+      <c r="M9" s="97">
         <v>-9.6</v>
       </c>
-      <c r="N9" s="97">
+      <c r="N9" s="103">
         <v>-14.15</v>
       </c>
-      <c r="O9" s="95">
+      <c r="O9" s="98">
         <v>-11.05</v>
       </c>
-      <c r="P9" s="93">
+      <c r="P9" s="104">
         <v>-8.72</v>
       </c>
-      <c r="Q9" s="96">
+      <c r="Q9" s="99">
         <v>-7.3</v>
       </c>
-      <c r="R9" s="98">
+      <c r="R9" s="100">
         <v>-8.31</v>
       </c>
-      <c r="S9" s="99">
+      <c r="S9" s="95">
         <v>-7.9</v>
       </c>
-      <c r="T9" s="100">
-        <v>-33.45</v>
+      <c r="T9" s="96">
+        <v>-32.79</v>
       </c>
     </row>
     <row r="10">
@@ -9802,7 +9802,7 @@
       <c r="C10" t="str">
         <v>002017</v>
       </c>
-      <c r="D10" s="107" t="str">
+      <c r="D10" s="115" t="str">
         <v>净买: 6518.56万</v>
       </c>
       <c r="E10">
@@ -9817,41 +9817,41 @@
       <c r="H10">
         <v>5.13</v>
       </c>
-      <c r="I10" s="108">
+      <c r="I10" s="112">
         <v>4.66</v>
       </c>
       <c r="J10" s="113">
         <v>-0.06</v>
       </c>
-      <c r="K10" s="114">
+      <c r="K10" s="116">
         <v>-6.53</v>
       </c>
-      <c r="L10" s="115">
+      <c r="L10" s="109">
         <v>-5.79</v>
       </c>
-      <c r="M10" s="111">
+      <c r="M10" s="110">
         <v>-7.89</v>
       </c>
-      <c r="N10" s="109">
+      <c r="N10" s="117">
         <v>-3.46</v>
       </c>
-      <c r="O10" s="110">
+      <c r="O10" s="106">
         <v>0.68</v>
       </c>
       <c r="P10" s="105">
         <v>0.51</v>
       </c>
-      <c r="Q10" s="116">
+      <c r="Q10" s="107">
         <v>-6.47</v>
       </c>
-      <c r="R10" s="117">
+      <c r="R10" s="111">
         <v>-3.8</v>
       </c>
-      <c r="S10" s="112">
+      <c r="S10" s="108">
         <v>-6.53</v>
       </c>
-      <c r="T10" s="106">
-        <v>5.22</v>
+      <c r="T10" s="114">
+        <v>9.31</v>
       </c>
     </row>
     <row r="11">
@@ -9864,7 +9864,7 @@
       <c r="C11" t="str">
         <v>002670</v>
       </c>
-      <c r="D11" s="120" t="str">
+      <c r="D11" s="129" t="str">
         <v>净卖: -2720.58万</v>
       </c>
       <c r="E11">
@@ -9879,41 +9879,41 @@
       <c r="H11">
         <v>-0.81</v>
       </c>
-      <c r="I11" s="126">
+      <c r="I11" s="130">
         <v>-5.23</v>
       </c>
-      <c r="J11" s="130">
+      <c r="J11" s="118">
         <v>-1.39</v>
       </c>
-      <c r="K11" s="121">
+      <c r="K11" s="119">
         <v>-9.57</v>
       </c>
-      <c r="L11" s="118">
+      <c r="L11" s="120">
         <v>-7.18</v>
       </c>
-      <c r="M11" s="122">
+      <c r="M11" s="121">
         <v>-7.62</v>
       </c>
-      <c r="N11" s="127">
+      <c r="N11" s="125">
         <v>-8.69</v>
       </c>
-      <c r="O11" s="128">
+      <c r="O11" s="122">
         <v>-7.37</v>
       </c>
-      <c r="P11" s="129">
+      <c r="P11" s="126">
         <v>-8.56</v>
       </c>
-      <c r="Q11" s="119">
+      <c r="Q11" s="127">
         <v>-8.63</v>
       </c>
-      <c r="R11" s="123">
+      <c r="R11" s="128">
         <v>-4.28</v>
       </c>
-      <c r="S11" s="124">
+      <c r="S11" s="123">
         <v>-8.56</v>
       </c>
-      <c r="T11" s="125">
-        <v>-21.98</v>
+      <c r="T11" s="124">
+        <v>-21.1</v>
       </c>
     </row>
     <row r="12">
@@ -9926,7 +9926,7 @@
       <c r="C12" t="str">
         <v>002579</v>
       </c>
-      <c r="D12" s="139" t="str">
+      <c r="D12" s="134" t="str">
         <v>净买: 4403.72万</v>
       </c>
       <c r="E12">
@@ -9941,41 +9941,41 @@
       <c r="H12">
         <v>-2.68</v>
       </c>
-      <c r="I12" s="132">
+      <c r="I12" s="138">
         <v>13.04</v>
       </c>
-      <c r="J12" s="133">
+      <c r="J12" s="142">
         <v>12.54</v>
       </c>
-      <c r="K12" s="140">
+      <c r="K12" s="139">
         <v>7.97</v>
       </c>
-      <c r="L12" s="141">
+      <c r="L12" s="143">
         <v>12.54</v>
       </c>
-      <c r="M12" s="143">
+      <c r="M12" s="133">
         <v>7.1</v>
       </c>
-      <c r="N12" s="142">
+      <c r="N12" s="135">
         <v>-3.62</v>
       </c>
       <c r="O12" s="131">
         <v>-2.97</v>
       </c>
-      <c r="P12" s="134">
+      <c r="P12" s="132">
         <v>-5.36</v>
       </c>
-      <c r="Q12" s="135">
+      <c r="Q12" s="136">
         <v>-3.7</v>
       </c>
-      <c r="R12" s="137">
+      <c r="R12" s="140">
         <v>-10.07</v>
       </c>
-      <c r="S12" s="138">
+      <c r="S12" s="137">
         <v>-6.59</v>
       </c>
-      <c r="T12" s="136">
-        <v>-8.04</v>
+      <c r="T12" s="141">
+        <v>-6.23</v>
       </c>
     </row>
     <row r="13">
@@ -9988,7 +9988,7 @@
       <c r="C13" t="str">
         <v>002229</v>
       </c>
-      <c r="D13" s="148" t="str">
+      <c r="D13" s="156" t="str">
         <v>净卖: -4629.75万</v>
       </c>
       <c r="E13">
@@ -10003,41 +10003,41 @@
       <c r="H13">
         <v>3.11</v>
       </c>
-      <c r="I13" s="150">
+      <c r="I13" s="151">
         <v>-7.78</v>
       </c>
-      <c r="J13" s="153">
+      <c r="J13" s="152">
         <v>-8.44</v>
       </c>
-      <c r="K13" s="154">
+      <c r="K13" s="146">
         <v>-11.23</v>
       </c>
-      <c r="L13" s="149">
+      <c r="L13" s="144">
         <v>-12.22</v>
       </c>
-      <c r="M13" s="145">
+      <c r="M13" s="153">
         <v>-10.66</v>
       </c>
-      <c r="N13" s="155">
+      <c r="N13" s="154">
         <v>-6.65</v>
       </c>
-      <c r="O13" s="151">
+      <c r="O13" s="147">
         <v>-7.74</v>
       </c>
-      <c r="P13" s="156">
+      <c r="P13" s="148">
         <v>-7.69</v>
       </c>
-      <c r="Q13" s="144">
+      <c r="Q13" s="145">
         <v>-11.37</v>
       </c>
-      <c r="R13" s="146">
+      <c r="R13" s="149">
         <v>-10.8</v>
       </c>
-      <c r="S13" s="152">
+      <c r="S13" s="155">
         <v>-13.68</v>
       </c>
-      <c r="T13" s="147">
-        <v>-20.38</v>
+      <c r="T13" s="150">
+        <v>-21.79</v>
       </c>
     </row>
     <row r="14">
@@ -10050,7 +10050,7 @@
       <c r="C14" t="str">
         <v>000657</v>
       </c>
-      <c r="D14" s="163" t="str">
+      <c r="D14" s="158" t="str">
         <v>净卖: -6184.73万</v>
       </c>
       <c r="E14">
@@ -10065,28 +10065,28 @@
       <c r="H14">
         <v>-2</v>
       </c>
-      <c r="I14" s="169">
+      <c r="I14" s="159">
         <v>-8.16</v>
       </c>
-      <c r="J14" s="159">
+      <c r="J14" s="168">
         <v>-13.48</v>
       </c>
-      <c r="K14" s="157">
+      <c r="K14" s="169">
         <v>-14.93</v>
       </c>
-      <c r="L14" s="158">
+      <c r="L14" s="163">
         <v>-15.36</v>
       </c>
       <c r="M14" s="160">
         <v>-15.2</v>
       </c>
-      <c r="N14" s="164">
+      <c r="N14" s="166">
         <v>-13.43</v>
       </c>
-      <c r="O14" s="161">
+      <c r="O14" s="164">
         <v>-13.1</v>
       </c>
-      <c r="P14" s="168">
+      <c r="P14" s="161">
         <v>-11.6</v>
       </c>
       <c r="Q14" s="165">
@@ -10095,11 +10095,11 @@
       <c r="R14" s="162">
         <v>-10.9</v>
       </c>
-      <c r="S14" s="166">
+      <c r="S14" s="157">
         <v>-8.81</v>
       </c>
       <c r="T14" s="167">
-        <v>196.35</v>
+        <v>189.1</v>
       </c>
     </row>
     <row r="15">
@@ -10112,7 +10112,7 @@
       <c r="C15" t="str">
         <v>002670</v>
       </c>
-      <c r="D15" s="173" t="str">
+      <c r="D15" s="174" t="str">
         <v>净卖: -7597.74万</v>
       </c>
       <c r="E15">
@@ -10127,41 +10127,41 @@
       <c r="H15">
         <v>0.45</v>
       </c>
-      <c r="I15" s="174">
+      <c r="I15" s="180">
         <v>1.89</v>
       </c>
-      <c r="J15" s="177">
+      <c r="J15" s="171">
         <v>-1.79</v>
       </c>
       <c r="K15" s="178">
         <v>-1.79</v>
       </c>
-      <c r="L15" s="170">
+      <c r="L15" s="179">
         <v>-3.03</v>
       </c>
-      <c r="M15" s="179">
+      <c r="M15" s="181">
         <v>-4.83</v>
       </c>
-      <c r="N15" s="171">
+      <c r="N15" s="182">
         <v>-3.73</v>
       </c>
       <c r="O15" s="175">
         <v>-3.38</v>
       </c>
-      <c r="P15" s="180">
+      <c r="P15" s="170">
         <v>-4.28</v>
       </c>
-      <c r="Q15" s="181">
+      <c r="Q15" s="172">
         <v>-7.71</v>
       </c>
-      <c r="R15" s="172">
+      <c r="R15" s="176">
         <v>-3.98</v>
       </c>
-      <c r="S15" s="182">
+      <c r="S15" s="173">
         <v>-2.84</v>
       </c>
-      <c r="T15" s="176">
-        <v>-38.36</v>
+      <c r="T15" s="177">
+        <v>-37.66</v>
       </c>
     </row>
     <row r="16">
@@ -10189,41 +10189,41 @@
       <c r="H16">
         <v>7.16</v>
       </c>
-      <c r="I16" s="192">
+      <c r="I16" s="195">
         <v>11.98</v>
       </c>
-      <c r="J16" s="195">
+      <c r="J16" s="183">
         <v>16.69</v>
       </c>
-      <c r="K16" s="184">
+      <c r="K16" s="187">
         <v>3.41</v>
       </c>
-      <c r="L16" s="193">
+      <c r="L16" s="188">
         <v>0.07</v>
       </c>
-      <c r="M16" s="185">
+      <c r="M16" s="189">
         <v>-5.26</v>
       </c>
-      <c r="N16" s="183">
+      <c r="N16" s="190">
         <v>-3.41</v>
       </c>
-      <c r="O16" s="186">
+      <c r="O16" s="184">
         <v>-5.04</v>
       </c>
-      <c r="P16" s="187">
+      <c r="P16" s="185">
         <v>-10.52</v>
       </c>
-      <c r="Q16" s="188">
+      <c r="Q16" s="191">
         <v>-7.78</v>
       </c>
-      <c r="R16" s="189">
+      <c r="R16" s="193">
         <v>-6.1</v>
       </c>
-      <c r="S16" s="190">
+      <c r="S16" s="186">
         <v>-7.34</v>
       </c>
-      <c r="T16" s="191">
-        <v>-25.31</v>
+      <c r="T16" s="192">
+        <v>-23.78</v>
       </c>
     </row>
     <row r="17">
@@ -10236,7 +10236,7 @@
       <c r="C17" t="str">
         <v>600408</v>
       </c>
-      <c r="D17" s="198" t="str">
+      <c r="D17" s="206" t="str">
         <v>净买: 1877.05万</v>
       </c>
       <c r="E17">
@@ -10251,41 +10251,41 @@
       <c r="H17">
         <v>-4.45</v>
       </c>
-      <c r="I17" s="205">
+      <c r="I17" s="198">
         <v>15.2</v>
       </c>
-      <c r="J17" s="199">
+      <c r="J17" s="204">
         <v>26.72</v>
       </c>
-      <c r="K17" s="200">
+      <c r="K17" s="205">
         <v>39.46</v>
       </c>
       <c r="L17" s="201">
         <v>53.43</v>
       </c>
-      <c r="M17" s="208">
+      <c r="M17" s="199">
         <v>68.87</v>
       </c>
-      <c r="N17" s="206">
+      <c r="N17" s="207">
         <v>52.7</v>
       </c>
-      <c r="O17" s="196">
+      <c r="O17" s="208">
         <v>37.5</v>
       </c>
-      <c r="P17" s="197">
+      <c r="P17" s="200">
         <v>24.26</v>
       </c>
-      <c r="Q17" s="207">
+      <c r="Q17" s="196">
         <v>14.95</v>
       </c>
       <c r="R17" s="202">
         <v>10.54</v>
       </c>
-      <c r="S17" s="203">
+      <c r="S17" s="197">
         <v>11.52</v>
       </c>
-      <c r="T17" s="204">
-        <v>-23.04</v>
+      <c r="T17" s="203">
+        <v>-21.08</v>
       </c>
     </row>
     <row r="18">
@@ -10298,7 +10298,7 @@
       <c r="C18" t="str">
         <v>601566</v>
       </c>
-      <c r="D18" s="217" t="str">
+      <c r="D18" s="210" t="str">
         <v>净买: 5226.66万</v>
       </c>
       <c r="E18">
@@ -10313,41 +10313,41 @@
       <c r="H18">
         <v>10.02</v>
       </c>
-      <c r="I18" s="220">
+      <c r="I18" s="211">
         <v>0</v>
       </c>
-      <c r="J18" s="218">
+      <c r="J18" s="217">
         <v>9.97</v>
       </c>
-      <c r="K18" s="211">
+      <c r="K18" s="218">
         <v>20.95</v>
       </c>
-      <c r="L18" s="221">
+      <c r="L18" s="215">
         <v>33.02</v>
       </c>
-      <c r="M18" s="215">
+      <c r="M18" s="212">
         <v>19.73</v>
       </c>
-      <c r="N18" s="216">
+      <c r="N18" s="219">
         <v>7.73</v>
       </c>
-      <c r="O18" s="212">
+      <c r="O18" s="220">
         <v>3.32</v>
       </c>
       <c r="P18" s="213">
         <v>-5.35</v>
       </c>
-      <c r="Q18" s="209">
+      <c r="Q18" s="216">
         <v>-6.94</v>
       </c>
-      <c r="R18" s="210">
+      <c r="R18" s="214">
         <v>-3.03</v>
       </c>
-      <c r="S18" s="219">
+      <c r="S18" s="221">
         <v>-2.46</v>
       </c>
-      <c r="T18" s="214">
-        <v>-22.54</v>
+      <c r="T18" s="209">
+        <v>-21.03</v>
       </c>
     </row>
     <row r="19">
@@ -10360,7 +10360,7 @@
       <c r="C19" t="str">
         <v>002029</v>
       </c>
-      <c r="D19" s="224" t="str">
+      <c r="D19" s="231" t="str">
         <v>净卖: -1276.40万</v>
       </c>
       <c r="E19">
@@ -10375,41 +10375,41 @@
       <c r="H19">
         <v>0</v>
       </c>
-      <c r="I19" s="232">
+      <c r="I19" s="227">
         <v>9.97</v>
       </c>
-      <c r="J19" s="233">
+      <c r="J19" s="224">
         <v>1.88</v>
       </c>
-      <c r="K19" s="230">
+      <c r="K19" s="228">
         <v>-2.35</v>
       </c>
-      <c r="L19" s="225">
+      <c r="L19" s="232">
         <v>-9.97</v>
       </c>
-      <c r="M19" s="226">
+      <c r="M19" s="225">
         <v>-11.67</v>
       </c>
-      <c r="N19" s="227">
+      <c r="N19" s="233">
         <v>-8</v>
       </c>
-      <c r="O19" s="222">
+      <c r="O19" s="226">
         <v>1.22</v>
       </c>
-      <c r="P19" s="223">
+      <c r="P19" s="229">
         <v>0.85</v>
       </c>
-      <c r="Q19" s="228">
+      <c r="Q19" s="234">
         <v>3.01</v>
       </c>
-      <c r="R19" s="229">
+      <c r="R19" s="222">
         <v>1.69</v>
       </c>
-      <c r="S19" s="234">
+      <c r="S19" s="230">
         <v>0.09</v>
       </c>
-      <c r="T19" s="231">
-        <v>-4.8</v>
+      <c r="T19" s="223">
+        <v>4.7</v>
       </c>
     </row>
     <row r="20">
@@ -10422,7 +10422,7 @@
       <c r="C20" t="str">
         <v>601566</v>
       </c>
-      <c r="D20" s="241" t="str">
+      <c r="D20" s="236" t="str">
         <v>净卖: -2737.55万</v>
       </c>
       <c r="E20">
@@ -10437,41 +10437,41 @@
       <c r="H20">
         <v>4.01</v>
       </c>
-      <c r="I20" s="240">
+      <c r="I20" s="245">
         <v>5.75</v>
       </c>
-      <c r="J20" s="235">
+      <c r="J20" s="246">
         <v>16.3</v>
       </c>
-      <c r="K20" s="236">
+      <c r="K20" s="247">
         <v>4.67</v>
       </c>
       <c r="L20" s="237">
         <v>-5.81</v>
       </c>
-      <c r="M20" s="238">
+      <c r="M20" s="242">
         <v>-9.67</v>
       </c>
-      <c r="N20" s="244">
+      <c r="N20" s="243">
         <v>-17.25</v>
       </c>
-      <c r="O20" s="242">
+      <c r="O20" s="238">
         <v>-18.64</v>
       </c>
-      <c r="P20" s="245">
+      <c r="P20" s="239">
         <v>-15.22</v>
       </c>
-      <c r="Q20" s="243">
+      <c r="Q20" s="244">
         <v>-14.72</v>
       </c>
-      <c r="R20" s="239">
+      <c r="R20" s="240">
         <v>-10.8</v>
       </c>
-      <c r="S20" s="246">
+      <c r="S20" s="235">
         <v>-6.19</v>
       </c>
-      <c r="T20" s="247">
-        <v>-32.28</v>
+      <c r="T20" s="241">
+        <v>-30.95</v>
       </c>
     </row>
     <row r="21">
@@ -10484,7 +10484,7 @@
       <c r="C21" t="str">
         <v>601566</v>
       </c>
-      <c r="D21" s="257" t="str">
+      <c r="D21" s="258" t="str">
         <v>净卖: -5218.09万</v>
       </c>
       <c r="E21">
@@ -10499,41 +10499,41 @@
       <c r="H21">
         <v>7.11</v>
       </c>
-      <c r="I21" s="258">
+      <c r="I21" s="259">
         <v>2.68</v>
       </c>
-      <c r="J21" s="248">
+      <c r="J21" s="255">
         <v>-7.59</v>
       </c>
-      <c r="K21" s="255">
+      <c r="K21" s="256">
         <v>-16.84</v>
       </c>
-      <c r="L21" s="251">
+      <c r="L21" s="250">
         <v>-20.25</v>
       </c>
-      <c r="M21" s="259">
+      <c r="M21" s="251">
         <v>-26.94</v>
       </c>
-      <c r="N21" s="256">
+      <c r="N21" s="252">
         <v>-28.17</v>
       </c>
-      <c r="O21" s="249">
+      <c r="O21" s="253">
         <v>-25.15</v>
       </c>
       <c r="P21" s="260">
         <v>-24.71</v>
       </c>
-      <c r="Q21" s="250">
+      <c r="Q21" s="248">
         <v>-21.25</v>
       </c>
-      <c r="R21" s="252">
+      <c r="R21" s="249">
         <v>-17.18</v>
       </c>
-      <c r="S21" s="253">
+      <c r="S21" s="254">
         <v>-25.43</v>
       </c>
-      <c r="T21" s="254">
-        <v>-40.21</v>
+      <c r="T21" s="257">
+        <v>-39.04</v>
       </c>
     </row>
     <row r="22">
@@ -10546,7 +10546,7 @@
       <c r="C22" t="str">
         <v>600756</v>
       </c>
-      <c r="D22" s="271" t="str">
+      <c r="D22" s="266" t="str">
         <v>净卖: -2369.10万</v>
       </c>
       <c r="E22">
@@ -10561,41 +10561,41 @@
       <c r="H22">
         <v>-1.6</v>
       </c>
-      <c r="I22" s="263">
+      <c r="I22" s="273">
         <v>1.46</v>
       </c>
-      <c r="J22" s="272">
+      <c r="J22" s="271">
         <v>-4.63</v>
       </c>
-      <c r="K22" s="265">
+      <c r="K22" s="267">
         <v>-3.97</v>
       </c>
-      <c r="L22" s="269">
+      <c r="L22" s="268">
         <v>-13.57</v>
       </c>
-      <c r="M22" s="273">
+      <c r="M22" s="269">
         <v>-21.09</v>
       </c>
-      <c r="N22" s="264">
+      <c r="N22" s="272">
         <v>-19.75</v>
       </c>
-      <c r="O22" s="266">
+      <c r="O22" s="264">
         <v>-18.25</v>
       </c>
-      <c r="P22" s="267">
+      <c r="P22" s="261">
         <v>-20.84</v>
       </c>
-      <c r="Q22" s="268">
+      <c r="Q22" s="262">
         <v>-21.42</v>
       </c>
-      <c r="R22" s="261">
+      <c r="R22" s="265">
         <v>-23.17</v>
       </c>
       <c r="S22" s="270">
         <v>-24.43</v>
       </c>
-      <c r="T22" s="262">
-        <v>-32.4</v>
+      <c r="T22" s="263">
+        <v>-31.82</v>
       </c>
     </row>
     <row r="23">
@@ -10608,7 +10608,7 @@
       <c r="C23" t="str">
         <v>603696</v>
       </c>
-      <c r="D23" s="285" t="str">
+      <c r="D23" s="280" t="str">
         <v>净买: 3978.78万</v>
       </c>
       <c r="E23">
@@ -10623,41 +10623,41 @@
       <c r="H23">
         <v>9.98</v>
       </c>
-      <c r="I23" s="282">
+      <c r="I23" s="285">
         <v>0</v>
       </c>
-      <c r="J23" s="277">
+      <c r="J23" s="281">
         <v>10.01</v>
       </c>
-      <c r="K23" s="283">
+      <c r="K23" s="275">
         <v>21.01</v>
       </c>
-      <c r="L23" s="286">
+      <c r="L23" s="282">
         <v>33.13</v>
       </c>
-      <c r="M23" s="284">
+      <c r="M23" s="283">
         <v>46.43</v>
       </c>
-      <c r="N23" s="278">
+      <c r="N23" s="286">
         <v>43.01</v>
       </c>
-      <c r="O23" s="279">
+      <c r="O23" s="276">
         <v>28.71</v>
       </c>
-      <c r="P23" s="280">
+      <c r="P23" s="274">
         <v>24.74</v>
       </c>
-      <c r="Q23" s="274">
+      <c r="Q23" s="279">
         <v>27.91</v>
       </c>
-      <c r="R23" s="281">
+      <c r="R23" s="284">
         <v>40.71</v>
       </c>
-      <c r="S23" s="275">
+      <c r="S23" s="277">
         <v>26.66</v>
       </c>
-      <c r="T23" s="276">
-        <v>-4.85</v>
+      <c r="T23" s="278">
+        <v>-3.36</v>
       </c>
     </row>
     <row r="24">
@@ -10670,7 +10670,7 @@
       <c r="C24" t="str">
         <v>002682</v>
       </c>
-      <c r="D24" s="299" t="str">
+      <c r="D24" s="295" t="str">
         <v>净买: 2499.06万</v>
       </c>
       <c r="E24">
@@ -10685,41 +10685,41 @@
       <c r="H24">
         <v>5.99</v>
       </c>
-      <c r="I24" s="295">
+      <c r="I24" s="290">
         <v>3.77</v>
       </c>
-      <c r="J24" s="292">
+      <c r="J24" s="299">
         <v>14.2</v>
       </c>
       <c r="K24" s="296">
         <v>25.65</v>
       </c>
-      <c r="L24" s="293">
+      <c r="L24" s="287">
         <v>38.26</v>
       </c>
-      <c r="M24" s="297">
+      <c r="M24" s="292">
         <v>52.03</v>
       </c>
-      <c r="N24" s="287">
+      <c r="N24" s="288">
         <v>42.9</v>
       </c>
-      <c r="O24" s="288">
+      <c r="O24" s="293">
         <v>57.25</v>
       </c>
-      <c r="P24" s="294">
+      <c r="P24" s="289">
         <v>72.9</v>
       </c>
-      <c r="Q24" s="289">
+      <c r="Q24" s="297">
         <v>55.65</v>
       </c>
-      <c r="R24" s="290">
+      <c r="R24" s="291">
         <v>40.14</v>
       </c>
-      <c r="S24" s="291">
+      <c r="S24" s="298">
         <v>42.75</v>
       </c>
-      <c r="T24" s="298">
-        <v>-17.25</v>
+      <c r="T24" s="294">
+        <v>-16.38</v>
       </c>
     </row>
     <row r="25">
@@ -10732,7 +10732,7 @@
       <c r="C25" t="str">
         <v>603696</v>
       </c>
-      <c r="D25" s="309" t="str">
+      <c r="D25" s="301" t="str">
         <v>净卖: -1913.63万</v>
       </c>
       <c r="E25">
@@ -10750,38 +10750,38 @@
       <c r="I25" s="310">
         <v>12.28</v>
       </c>
-      <c r="J25" s="301">
+      <c r="J25" s="307">
         <v>23.53</v>
       </c>
-      <c r="K25" s="302">
+      <c r="K25" s="311">
         <v>35.87</v>
       </c>
-      <c r="L25" s="311">
+      <c r="L25" s="302">
         <v>32.7</v>
       </c>
-      <c r="M25" s="305">
+      <c r="M25" s="308">
         <v>19.43</v>
       </c>
       <c r="N25" s="303">
         <v>15.74</v>
       </c>
-      <c r="O25" s="306">
+      <c r="O25" s="304">
         <v>18.69</v>
       </c>
-      <c r="P25" s="307">
+      <c r="P25" s="305">
         <v>30.57</v>
       </c>
-      <c r="Q25" s="308">
+      <c r="Q25" s="309">
         <v>17.53</v>
       </c>
-      <c r="R25" s="300">
+      <c r="R25" s="306">
         <v>10.73</v>
       </c>
       <c r="S25" s="312">
         <v>16.49</v>
       </c>
-      <c r="T25" s="304">
-        <v>-11.71</v>
+      <c r="T25" s="300">
+        <v>-10.32</v>
       </c>
     </row>
     <row r="26">
@@ -10794,7 +10794,7 @@
       <c r="C26" t="str">
         <v>603696</v>
       </c>
-      <c r="D26" s="320" t="str">
+      <c r="D26" s="314" t="str">
         <v>净卖: -3631.64万</v>
       </c>
       <c r="E26">
@@ -10809,41 +10809,41 @@
       <c r="H26">
         <v>9.08</v>
       </c>
-      <c r="I26" s="321">
+      <c r="I26" s="317">
         <v>-10.47</v>
       </c>
-      <c r="J26" s="322">
+      <c r="J26" s="315">
         <v>-19.42</v>
       </c>
-      <c r="K26" s="313">
+      <c r="K26" s="318">
         <v>-21.91</v>
       </c>
-      <c r="L26" s="316">
+      <c r="L26" s="323">
         <v>-19.92</v>
       </c>
-      <c r="M26" s="314">
+      <c r="M26" s="316">
         <v>-11.91</v>
       </c>
-      <c r="N26" s="323">
+      <c r="N26" s="324">
         <v>-20.7</v>
       </c>
-      <c r="O26" s="317">
+      <c r="O26" s="319">
         <v>-25.29</v>
       </c>
-      <c r="P26" s="318">
+      <c r="P26" s="320">
         <v>-21.4</v>
       </c>
-      <c r="Q26" s="319">
+      <c r="Q26" s="325">
         <v>-13.54</v>
       </c>
-      <c r="R26" s="324">
+      <c r="R26" s="321">
         <v>-4.9</v>
       </c>
-      <c r="S26" s="315">
+      <c r="S26" s="313">
         <v>4.59</v>
       </c>
-      <c r="T26" s="325">
-        <v>-40.43</v>
+      <c r="T26" s="322">
+        <v>-39.49</v>
       </c>
     </row>
     <row r="27">
@@ -10856,7 +10856,7 @@
       <c r="C27" t="str">
         <v>002682</v>
       </c>
-      <c r="D27" s="337" t="str">
+      <c r="D27" s="331" t="str">
         <v>净卖: -4674.28万</v>
       </c>
       <c r="E27">
@@ -10871,41 +10871,41 @@
       <c r="H27">
         <v>-4.33</v>
       </c>
-      <c r="I27" s="338">
+      <c r="I27" s="332">
         <v>14.93</v>
       </c>
-      <c r="J27" s="326">
+      <c r="J27" s="336">
         <v>3.47</v>
       </c>
-      <c r="K27" s="328">
+      <c r="K27" s="327">
         <v>-6.84</v>
       </c>
-      <c r="L27" s="329">
+      <c r="L27" s="330">
         <v>-5.11</v>
       </c>
-      <c r="M27" s="332">
+      <c r="M27" s="333">
         <v>-10.89</v>
       </c>
-      <c r="N27" s="327">
+      <c r="N27" s="334">
         <v>-19.36</v>
       </c>
-      <c r="O27" s="333">
+      <c r="O27" s="328">
         <v>-21</v>
       </c>
-      <c r="P27" s="334">
+      <c r="P27" s="337">
         <v>-20.33</v>
       </c>
-      <c r="Q27" s="335">
+      <c r="Q27" s="338">
         <v>-12.43</v>
       </c>
-      <c r="R27" s="330">
+      <c r="R27" s="335">
         <v>-14.26</v>
       </c>
-      <c r="S27" s="336">
+      <c r="S27" s="326">
         <v>-7.8</v>
       </c>
-      <c r="T27" s="331">
-        <v>-44.99</v>
+      <c r="T27" s="329">
+        <v>-44.41</v>
       </c>
     </row>
     <row r="28">
@@ -10918,7 +10918,7 @@
       <c r="C28" t="str">
         <v>600693</v>
       </c>
-      <c r="D28" s="339" t="str">
+      <c r="D28" s="343" t="str">
         <v>净买: 4441.53万</v>
       </c>
       <c r="E28">
@@ -10933,16 +10933,16 @@
       <c r="H28">
         <v>1.81</v>
       </c>
-      <c r="I28" s="340">
+      <c r="I28" s="341">
         <v>8.04</v>
       </c>
-      <c r="J28" s="349">
+      <c r="J28" s="348">
         <v>15.95</v>
       </c>
-      <c r="K28" s="343">
+      <c r="K28" s="349">
         <v>10.22</v>
       </c>
-      <c r="L28" s="341">
+      <c r="L28" s="344">
         <v>13.45</v>
       </c>
       <c r="M28" s="350">
@@ -10951,23 +10951,23 @@
       <c r="N28" s="351">
         <v>23.53</v>
       </c>
-      <c r="O28" s="347">
+      <c r="O28" s="339">
         <v>28.54</v>
       </c>
       <c r="P28" s="342">
         <v>41.4</v>
       </c>
-      <c r="Q28" s="348">
+      <c r="Q28" s="340">
         <v>37.84</v>
       </c>
-      <c r="R28" s="344">
+      <c r="R28" s="345">
         <v>44.23</v>
       </c>
-      <c r="S28" s="345">
+      <c r="S28" s="346">
         <v>30.52</v>
       </c>
-      <c r="T28" s="346">
-        <v>-30.92</v>
+      <c r="T28" s="347">
+        <v>-23.99</v>
       </c>
     </row>
     <row r="29">
@@ -10980,7 +10980,7 @@
       <c r="C29" t="str">
         <v>603696</v>
       </c>
-      <c r="D29" s="360" t="str">
+      <c r="D29" s="354" t="str">
         <v>净卖: -3147.63万</v>
       </c>
       <c r="E29">
@@ -10995,41 +10995,41 @@
       <c r="H29">
         <v>2.92</v>
       </c>
-      <c r="I29" s="361">
+      <c r="I29" s="357">
         <v>-12.53</v>
       </c>
-      <c r="J29" s="363">
+      <c r="J29" s="358">
         <v>-17.6</v>
       </c>
-      <c r="K29" s="354">
+      <c r="K29" s="359">
         <v>-13.3</v>
       </c>
-      <c r="L29" s="358">
+      <c r="L29" s="364">
         <v>-4.64</v>
       </c>
-      <c r="M29" s="364">
+      <c r="M29" s="360">
         <v>4.89</v>
       </c>
-      <c r="N29" s="359">
+      <c r="N29" s="352">
         <v>15.36</v>
       </c>
-      <c r="O29" s="355">
+      <c r="O29" s="353">
         <v>13.73</v>
       </c>
-      <c r="P29" s="356">
+      <c r="P29" s="361">
         <v>12.4</v>
       </c>
-      <c r="Q29" s="362">
+      <c r="Q29" s="355">
         <v>1.16</v>
       </c>
-      <c r="R29" s="352">
+      <c r="R29" s="362">
         <v>-8.97</v>
       </c>
-      <c r="S29" s="357">
+      <c r="S29" s="356">
         <v>-12.96</v>
       </c>
-      <c r="T29" s="353">
-        <v>-34.29</v>
+      <c r="T29" s="363">
+        <v>-33.26</v>
       </c>
     </row>
     <row r="30">
@@ -11042,7 +11042,7 @@
       <c r="C30" t="str">
         <v>600693</v>
       </c>
-      <c r="D30" s="371" t="str">
+      <c r="D30" s="367" t="str">
         <v>净卖: -5308.96万</v>
       </c>
       <c r="E30">
@@ -11057,41 +11057,41 @@
       <c r="H30">
         <v>2.51</v>
       </c>
-      <c r="I30" s="367">
+      <c r="I30" s="376">
         <v>0.41</v>
       </c>
-      <c r="J30" s="372">
+      <c r="J30" s="377">
         <v>-0.58</v>
       </c>
-      <c r="K30" s="368">
+      <c r="K30" s="365">
         <v>9.33</v>
       </c>
-      <c r="L30" s="370">
+      <c r="L30" s="372">
         <v>13.77</v>
       </c>
-      <c r="M30" s="373">
+      <c r="M30" s="368">
         <v>25.15</v>
       </c>
-      <c r="N30" s="377">
+      <c r="N30" s="369">
         <v>22</v>
       </c>
-      <c r="O30" s="369">
+      <c r="O30" s="370">
         <v>27.65</v>
       </c>
-      <c r="P30" s="365">
+      <c r="P30" s="373">
         <v>15.52</v>
       </c>
       <c r="Q30" s="374">
         <v>3.97</v>
       </c>
-      <c r="R30" s="375">
+      <c r="R30" s="371">
         <v>3.97</v>
       </c>
-      <c r="S30" s="376">
+      <c r="S30" s="366">
         <v>7.29</v>
       </c>
-      <c r="T30" s="366">
-        <v>-38.86</v>
+      <c r="T30" s="375">
+        <v>-32.73</v>
       </c>
     </row>
     <row r="31">
@@ -11104,7 +11104,7 @@
       <c r="C31" t="str">
         <v>600280</v>
       </c>
-      <c r="D31" s="383" t="str">
+      <c r="D31" s="378" t="str">
         <v>净买: 2343.21万</v>
       </c>
       <c r="E31">
@@ -11119,41 +11119,41 @@
       <c r="H31">
         <v>1.88</v>
       </c>
-      <c r="I31" s="384">
+      <c r="I31" s="379">
         <v>8.08</v>
       </c>
-      <c r="J31" s="385">
+      <c r="J31" s="383">
         <v>17.78</v>
       </c>
-      <c r="K31" s="386">
+      <c r="K31" s="384">
         <v>12.93</v>
       </c>
-      <c r="L31" s="387">
+      <c r="L31" s="385">
         <v>4.39</v>
       </c>
-      <c r="M31" s="379">
+      <c r="M31" s="388">
         <v>5.54</v>
       </c>
-      <c r="N31" s="390">
+      <c r="N31" s="389">
         <v>1.85</v>
       </c>
       <c r="O31" s="380">
         <v>-1.15</v>
       </c>
-      <c r="P31" s="381">
+      <c r="P31" s="386">
         <v>-3</v>
       </c>
-      <c r="Q31" s="389">
+      <c r="Q31" s="387">
         <v>-7.85</v>
       </c>
-      <c r="R31" s="382">
+      <c r="R31" s="381">
         <v>-11.09</v>
       </c>
-      <c r="S31" s="378">
+      <c r="S31" s="382">
         <v>-10.16</v>
       </c>
-      <c r="T31" s="388">
-        <v>-32.1</v>
+      <c r="T31" s="390">
+        <v>-30.02</v>
       </c>
     </row>
     <row r="32">
@@ -11166,7 +11166,7 @@
       <c r="C32" t="str">
         <v>600280</v>
       </c>
-      <c r="D32" s="403" t="str">
+      <c r="D32" s="393" t="str">
         <v>净卖: -2545.17万</v>
       </c>
       <c r="E32">
@@ -11181,41 +11181,41 @@
       <c r="H32">
         <v>-3.92</v>
       </c>
-      <c r="I32" s="396">
+      <c r="I32" s="398">
         <v>-0.2</v>
       </c>
-      <c r="J32" s="401">
+      <c r="J32" s="392">
         <v>-7.76</v>
       </c>
-      <c r="K32" s="397">
+      <c r="K32" s="394">
         <v>-6.73</v>
       </c>
-      <c r="L32" s="391">
+      <c r="L32" s="401">
         <v>-10</v>
       </c>
-      <c r="M32" s="394">
+      <c r="M32" s="402">
         <v>-12.65</v>
       </c>
-      <c r="N32" s="392">
+      <c r="N32" s="395">
         <v>-14.29</v>
       </c>
-      <c r="O32" s="398">
+      <c r="O32" s="396">
         <v>-18.57</v>
       </c>
-      <c r="P32" s="399">
+      <c r="P32" s="403">
         <v>-21.43</v>
       </c>
-      <c r="Q32" s="395">
+      <c r="Q32" s="399">
         <v>-20.61</v>
       </c>
-      <c r="R32" s="400">
+      <c r="R32" s="397">
         <v>-16.33</v>
       </c>
-      <c r="S32" s="393">
+      <c r="S32" s="400">
         <v>-15.92</v>
       </c>
-      <c r="T32" s="402">
-        <v>-40</v>
+      <c r="T32" s="391">
+        <v>-38.16</v>
       </c>
     </row>
     <row r="33">
@@ -11228,7 +11228,7 @@
       <c r="C33" t="str">
         <v>002759</v>
       </c>
-      <c r="D33" s="412" t="str">
+      <c r="D33" s="410" t="str">
         <v>净买: 8490.49万</v>
       </c>
       <c r="E33">
@@ -11243,41 +11243,41 @@
       <c r="H33">
         <v>-3.82</v>
       </c>
-      <c r="I33" s="416">
+      <c r="I33" s="415">
         <v>11.08</v>
       </c>
-      <c r="J33" s="409">
+      <c r="J33" s="406">
         <v>22.19</v>
       </c>
-      <c r="K33" s="413">
+      <c r="K33" s="411">
         <v>22.69</v>
       </c>
-      <c r="L33" s="404">
+      <c r="L33" s="407">
         <v>13.63</v>
       </c>
-      <c r="M33" s="414">
+      <c r="M33" s="412">
         <v>14.61</v>
       </c>
-      <c r="N33" s="406">
+      <c r="N33" s="413">
         <v>26.07</v>
       </c>
-      <c r="O33" s="405">
+      <c r="O33" s="414">
         <v>26.51</v>
       </c>
-      <c r="P33" s="415">
+      <c r="P33" s="416">
         <v>18.86</v>
       </c>
-      <c r="Q33" s="410">
+      <c r="Q33" s="408">
         <v>15.77</v>
       </c>
-      <c r="R33" s="407">
+      <c r="R33" s="404">
         <v>13.87</v>
       </c>
-      <c r="S33" s="411">
+      <c r="S33" s="405">
         <v>15.03</v>
       </c>
-      <c r="T33" s="408">
-        <v>-17.53</v>
+      <c r="T33" s="409">
+        <v>-15.08</v>
       </c>
     </row>
     <row r="34">
@@ -11290,7 +11290,7 @@
       <c r="C34" t="str">
         <v>002792</v>
       </c>
-      <c r="D34" s="426" t="str">
+      <c r="D34" s="417" t="str">
         <v>净买: 8322.30万</v>
       </c>
       <c r="E34">
@@ -11305,41 +11305,41 @@
       <c r="H34">
         <v>0.05</v>
       </c>
-      <c r="I34" s="427">
+      <c r="I34" s="426">
         <v>7.5</v>
       </c>
-      <c r="J34" s="421">
+      <c r="J34" s="423">
         <v>15.33</v>
       </c>
-      <c r="K34" s="428">
+      <c r="K34" s="427">
         <v>19.23</v>
       </c>
-      <c r="L34" s="418">
+      <c r="L34" s="424">
         <v>31.17</v>
       </c>
-      <c r="M34" s="419">
+      <c r="M34" s="418">
         <v>44.28</v>
       </c>
-      <c r="N34" s="420">
+      <c r="N34" s="425">
         <v>53.02</v>
       </c>
-      <c r="O34" s="422">
+      <c r="O34" s="419">
         <v>68.33</v>
       </c>
-      <c r="P34" s="423">
+      <c r="P34" s="420">
         <v>76.16</v>
       </c>
-      <c r="Q34" s="424">
+      <c r="Q34" s="421">
         <v>58.53</v>
       </c>
-      <c r="R34" s="429">
+      <c r="R34" s="422">
         <v>42.67</v>
       </c>
-      <c r="S34" s="425">
+      <c r="S34" s="428">
         <v>30.19</v>
       </c>
-      <c r="T34" s="417">
-        <v>14.85</v>
+      <c r="T34" s="429">
+        <v>13.42</v>
       </c>
     </row>
     <row r="35">
@@ -11352,7 +11352,7 @@
       <c r="C35" t="str">
         <v>002792</v>
       </c>
-      <c r="D35" s="431" t="str">
+      <c r="D35" s="432" t="str">
         <v>净卖: -7684.69万</v>
       </c>
       <c r="E35">
@@ -11367,41 +11367,41 @@
       <c r="H35">
         <v>2.25</v>
       </c>
-      <c r="I35" s="437">
+      <c r="I35" s="436">
         <v>4.92</v>
       </c>
-      <c r="J35" s="432">
+      <c r="J35" s="431">
         <v>8.47</v>
       </c>
-      <c r="K35" s="433">
+      <c r="K35" s="437">
         <v>19.33</v>
       </c>
-      <c r="L35" s="434">
+      <c r="L35" s="439">
         <v>31.26</v>
       </c>
-      <c r="M35" s="435">
+      <c r="M35" s="440">
         <v>39.21</v>
       </c>
-      <c r="N35" s="436">
+      <c r="N35" s="433">
         <v>53.14</v>
       </c>
-      <c r="O35" s="442">
+      <c r="O35" s="441">
         <v>60.26</v>
       </c>
-      <c r="P35" s="438">
+      <c r="P35" s="434">
         <v>44.23</v>
       </c>
-      <c r="Q35" s="439">
+      <c r="Q35" s="435">
         <v>29.8</v>
       </c>
-      <c r="R35" s="440">
+      <c r="R35" s="442">
         <v>18.44</v>
       </c>
-      <c r="S35" s="430">
+      <c r="S35" s="438">
         <v>17.43</v>
       </c>
-      <c r="T35" s="441">
-        <v>4.49</v>
+      <c r="T35" s="430">
+        <v>3.18</v>
       </c>
     </row>
     <row r="36">
@@ -11414,7 +11414,7 @@
       <c r="C36" t="str">
         <v>002759</v>
       </c>
-      <c r="D36" s="455" t="str">
+      <c r="D36" s="450" t="str">
         <v>净买: 1.00亿</v>
       </c>
       <c r="E36">
@@ -11429,41 +11429,41 @@
       <c r="H36">
         <v>3.06</v>
       </c>
-      <c r="I36" s="445">
+      <c r="I36" s="447">
         <v>6.73</v>
       </c>
-      <c r="J36" s="453">
+      <c r="J36" s="455">
         <v>7.11</v>
       </c>
-      <c r="K36" s="448">
+      <c r="K36" s="443">
         <v>0.63</v>
       </c>
-      <c r="L36" s="446">
+      <c r="L36" s="444">
         <v>-1.99</v>
       </c>
-      <c r="M36" s="454">
+      <c r="M36" s="448">
         <v>-3.59</v>
       </c>
-      <c r="N36" s="447">
+      <c r="N36" s="445">
         <v>-2.61</v>
       </c>
-      <c r="O36" s="449">
+      <c r="O36" s="451">
         <v>-7.82</v>
       </c>
-      <c r="P36" s="450">
+      <c r="P36" s="452">
         <v>-11.35</v>
       </c>
-      <c r="Q36" s="443">
+      <c r="Q36" s="453">
         <v>-5.64</v>
       </c>
-      <c r="R36" s="444">
+      <c r="R36" s="454">
         <v>-13.61</v>
       </c>
-      <c r="S36" s="451">
+      <c r="S36" s="449">
         <v>-12.5</v>
       </c>
-      <c r="T36" s="452">
-        <v>-30.18</v>
+      <c r="T36" s="446">
+        <v>-28.11</v>
       </c>
     </row>
     <row r="37">
@@ -11476,7 +11476,7 @@
       <c r="C37" t="str">
         <v>600776</v>
       </c>
-      <c r="D37" s="465" t="str">
+      <c r="D37" s="464" t="str">
         <v>净买: 5452.75万</v>
       </c>
       <c r="E37">
@@ -11491,41 +11491,41 @@
       <c r="H37">
         <v>10.02</v>
       </c>
-      <c r="I37" s="458">
+      <c r="I37" s="461">
         <v>0</v>
       </c>
-      <c r="J37" s="459">
+      <c r="J37" s="458">
         <v>10</v>
       </c>
-      <c r="K37" s="460">
+      <c r="K37" s="465">
         <v>16.57</v>
       </c>
-      <c r="L37" s="461">
+      <c r="L37" s="466">
         <v>4.91</v>
       </c>
-      <c r="M37" s="466">
+      <c r="M37" s="467">
         <v>-5.58</v>
       </c>
-      <c r="N37" s="467">
+      <c r="N37" s="456">
         <v>-15.01</v>
       </c>
-      <c r="O37" s="463">
+      <c r="O37" s="462">
         <v>-17.91</v>
       </c>
-      <c r="P37" s="468">
+      <c r="P37" s="459">
         <v>-16.93</v>
       </c>
-      <c r="Q37" s="456">
+      <c r="Q37" s="463">
         <v>-15.19</v>
       </c>
-      <c r="R37" s="462">
+      <c r="R37" s="468">
         <v>-10.99</v>
       </c>
-      <c r="S37" s="457">
+      <c r="S37" s="460">
         <v>-15.27</v>
       </c>
-      <c r="T37" s="464">
-        <v>-26.53</v>
+      <c r="T37" s="457">
+        <v>-25.23</v>
       </c>
     </row>
     <row r="38">
@@ -11538,7 +11538,7 @@
       <c r="C38" t="str">
         <v>600410</v>
       </c>
-      <c r="D38" s="477" t="str">
+      <c r="D38" s="474" t="str">
         <v>净买: 1.26亿</v>
       </c>
       <c r="E38">
@@ -11556,38 +11556,38 @@
       <c r="I38" s="475">
         <v>11.84</v>
       </c>
-      <c r="J38" s="478">
+      <c r="J38" s="481">
         <v>23.02</v>
       </c>
       <c r="K38" s="476">
         <v>10.78</v>
       </c>
-      <c r="L38" s="481">
+      <c r="L38" s="469">
         <v>2.42</v>
       </c>
       <c r="M38" s="479">
         <v>0</v>
       </c>
-      <c r="N38" s="472">
+      <c r="N38" s="477">
         <v>1.86</v>
       </c>
-      <c r="O38" s="469">
+      <c r="O38" s="480">
         <v>2.67</v>
       </c>
-      <c r="P38" s="473">
+      <c r="P38" s="470">
         <v>5.99</v>
       </c>
-      <c r="Q38" s="480">
+      <c r="Q38" s="471">
         <v>0.81</v>
       </c>
-      <c r="R38" s="470">
+      <c r="R38" s="472">
         <v>6.95</v>
       </c>
-      <c r="S38" s="474">
+      <c r="S38" s="473">
         <v>6.25</v>
       </c>
-      <c r="T38" s="471">
-        <v>36.98</v>
+      <c r="T38" s="478">
+        <v>30.98</v>
       </c>
     </row>
     <row r="39">
@@ -11600,7 +11600,7 @@
       <c r="C39" t="str">
         <v>600410</v>
       </c>
-      <c r="D39" s="489" t="str">
+      <c r="D39" s="484" t="str">
         <v>净买: 1.26亿</v>
       </c>
       <c r="E39">
@@ -11615,41 +11615,41 @@
       <c r="H39">
         <v>10</v>
       </c>
-      <c r="I39" s="494">
+      <c r="I39" s="485">
         <v>0</v>
       </c>
-      <c r="J39" s="484">
+      <c r="J39" s="488">
         <v>-9.95</v>
       </c>
-      <c r="K39" s="490">
+      <c r="K39" s="494">
         <v>-16.75</v>
       </c>
-      <c r="L39" s="487">
+      <c r="L39" s="486">
         <v>-18.71</v>
       </c>
-      <c r="M39" s="488">
+      <c r="M39" s="482">
         <v>-17.2</v>
       </c>
-      <c r="N39" s="491">
+      <c r="N39" s="487">
         <v>-16.54</v>
       </c>
-      <c r="O39" s="492">
+      <c r="O39" s="491">
         <v>-13.84</v>
       </c>
-      <c r="P39" s="493">
+      <c r="P39" s="492">
         <v>-18.06</v>
       </c>
-      <c r="Q39" s="482">
+      <c r="Q39" s="489">
         <v>-13.06</v>
       </c>
-      <c r="R39" s="485">
+      <c r="R39" s="493">
         <v>-13.64</v>
       </c>
-      <c r="S39" s="486">
+      <c r="S39" s="490">
         <v>-10.2</v>
       </c>
       <c r="T39" s="483">
-        <v>11.34</v>
+        <v>6.47</v>
       </c>
     </row>
     <row r="40">
@@ -11662,7 +11662,7 @@
       <c r="C40" t="str">
         <v>600776</v>
       </c>
-      <c r="D40" s="501" t="str">
+      <c r="D40" s="505" t="str">
         <v>净卖: -233.39万</v>
       </c>
       <c r="E40">
@@ -11677,41 +11677,41 @@
       <c r="H40">
         <v>-10</v>
       </c>
-      <c r="I40" s="505">
+      <c r="I40" s="503">
         <v>0</v>
       </c>
-      <c r="J40" s="498">
+      <c r="J40" s="506">
         <v>-9.98</v>
       </c>
-      <c r="K40" s="502">
+      <c r="K40" s="507">
         <v>-13.06</v>
       </c>
-      <c r="L40" s="506">
+      <c r="L40" s="495">
         <v>-12.02</v>
       </c>
-      <c r="M40" s="495">
+      <c r="M40" s="500">
         <v>-10.17</v>
       </c>
-      <c r="N40" s="503">
+      <c r="N40" s="496">
         <v>-5.72</v>
       </c>
-      <c r="O40" s="496">
+      <c r="O40" s="498">
         <v>-10.26</v>
       </c>
       <c r="P40" s="504">
         <v>-9.89</v>
       </c>
-      <c r="Q40" s="499">
+      <c r="Q40" s="501">
         <v>-11.26</v>
       </c>
-      <c r="R40" s="507">
+      <c r="R40" s="499">
         <v>-11.78</v>
       </c>
-      <c r="S40" s="500">
+      <c r="S40" s="502">
         <v>-12.49</v>
       </c>
       <c r="T40" s="497">
-        <v>-22.19</v>
+        <v>-20.81</v>
       </c>
     </row>
     <row r="41">
@@ -11724,7 +11724,7 @@
       <c r="C41" t="str">
         <v>600410</v>
       </c>
-      <c r="D41" s="514" t="str">
+      <c r="D41" s="510" t="str">
         <v>净卖: -1.30亿</v>
       </c>
       <c r="E41">
@@ -11739,41 +11739,41 @@
       <c r="H41">
         <v>-1.97</v>
       </c>
-      <c r="I41" s="515">
+      <c r="I41" s="517">
         <v>-8.15</v>
       </c>
-      <c r="J41" s="519">
+      <c r="J41" s="518">
         <v>-15.08</v>
       </c>
-      <c r="K41" s="520">
+      <c r="K41" s="519">
         <v>-17.08</v>
       </c>
-      <c r="L41" s="516">
+      <c r="L41" s="511">
         <v>-15.54</v>
       </c>
-      <c r="M41" s="510">
+      <c r="M41" s="512">
         <v>-14.87</v>
       </c>
       <c r="N41" s="508">
         <v>-12.11</v>
       </c>
-      <c r="O41" s="511">
+      <c r="O41" s="509">
         <v>-16.42</v>
       </c>
-      <c r="P41" s="517">
+      <c r="P41" s="513">
         <v>-11.32</v>
       </c>
-      <c r="Q41" s="512">
+      <c r="Q41" s="515">
         <v>-11.9</v>
       </c>
-      <c r="R41" s="513">
+      <c r="R41" s="520">
         <v>-8.4</v>
       </c>
-      <c r="S41" s="518">
+      <c r="S41" s="514">
         <v>-12.24</v>
       </c>
-      <c r="T41" s="509">
-        <v>13.58</v>
+      <c r="T41" s="516">
+        <v>8.6</v>
       </c>
     </row>
     <row r="42">
@@ -11801,41 +11801,41 @@
       <c r="H42">
         <v>0.55</v>
       </c>
-      <c r="I42" s="526">
+      <c r="I42" s="527">
         <v>9.39</v>
       </c>
-      <c r="J42" s="524">
+      <c r="J42" s="523">
         <v>15.85</v>
       </c>
       <c r="K42" s="532">
         <v>10.51</v>
       </c>
-      <c r="L42" s="533">
+      <c r="L42" s="528">
         <v>6.31</v>
       </c>
-      <c r="M42" s="525">
+      <c r="M42" s="529">
         <v>1.07</v>
       </c>
-      <c r="N42" s="529">
+      <c r="N42" s="533">
         <v>-1.76</v>
       </c>
-      <c r="O42" s="527">
+      <c r="O42" s="530">
         <v>0.67</v>
       </c>
       <c r="P42" s="521">
         <v>10.74</v>
       </c>
-      <c r="Q42" s="528">
+      <c r="Q42" s="524">
         <v>10.74</v>
       </c>
       <c r="R42" s="522">
         <v>7.46</v>
       </c>
-      <c r="S42" s="523">
+      <c r="S42" s="525">
         <v>7.34</v>
       </c>
-      <c r="T42" s="530">
-        <v>-4.34</v>
+      <c r="T42" s="526">
+        <v>-5.54</v>
       </c>
     </row>
     <row r="43">
@@ -11897,41 +11897,41 @@
       <c r="F44" t="str"/>
       <c r="G44" t="str"/>
       <c r="H44" t="str"/>
-      <c r="I44" s="539">
+      <c r="I44" s="537">
         <v>65.85</v>
       </c>
-      <c r="J44" s="541">
+      <c r="J44" s="534">
         <v>65.85</v>
       </c>
-      <c r="K44" s="542">
+      <c r="K44" s="541">
         <v>60.98</v>
       </c>
-      <c r="L44" s="534">
+      <c r="L44" s="535">
         <v>56.1</v>
       </c>
-      <c r="M44" s="535">
+      <c r="M44" s="542">
         <v>48.78</v>
       </c>
-      <c r="N44" s="543">
+      <c r="N44" s="539">
         <v>46.34</v>
       </c>
-      <c r="O44" s="544">
+      <c r="O44" s="543">
         <v>48.78</v>
       </c>
-      <c r="P44" s="538">
+      <c r="P44" s="544">
         <v>43.9</v>
       </c>
       <c r="Q44" s="545">
         <v>39.02</v>
       </c>
-      <c r="R44" s="540">
+      <c r="R44" s="538">
         <v>43.9</v>
       </c>
       <c r="S44" s="536">
         <v>43.9</v>
       </c>
-      <c r="T44" s="537">
-        <v>29.27</v>
+      <c r="T44" s="540">
+        <v>31.71</v>
       </c>
     </row>
     <row r="45">
@@ -11945,41 +11945,41 @@
       <c r="F45" t="str"/>
       <c r="G45" t="str"/>
       <c r="H45" t="str"/>
-      <c r="I45" s="549">
+      <c r="I45" s="554">
         <v>3.79</v>
       </c>
       <c r="J45" s="546">
         <v>5.59</v>
       </c>
-      <c r="K45" s="553">
+      <c r="K45" s="549">
         <v>5.07</v>
       </c>
-      <c r="L45" s="554">
+      <c r="L45" s="550">
         <v>5.23</v>
       </c>
-      <c r="M45" s="550">
+      <c r="M45" s="555">
         <v>5.01</v>
       </c>
-      <c r="N45" s="552">
+      <c r="N45" s="556">
         <v>4.05</v>
       </c>
-      <c r="O45" s="555">
+      <c r="O45" s="547">
         <v>4.42</v>
       </c>
-      <c r="P45" s="547">
+      <c r="P45" s="557">
         <v>3.76</v>
       </c>
-      <c r="Q45" s="548">
+      <c r="Q45" s="551">
         <v>1.74</v>
       </c>
-      <c r="R45" s="551">
+      <c r="R45" s="552">
         <v>1.6</v>
       </c>
-      <c r="S45" s="556">
+      <c r="S45" s="548">
         <v>0.99</v>
       </c>
-      <c r="T45" s="557">
-        <v>-9.52</v>
+      <c r="T45" s="553">
+        <v>-9.26</v>
       </c>
     </row>
   </sheetData>

--- a/youzi/越王大道/index.xlsx
+++ b/youzi/越王大道/index.xlsx
@@ -39,19 +39,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFAE202D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF70C483"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFB8E1C1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAB1E2C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC4E7CC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218E3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFED979F"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FF1A7230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8236"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -63,7 +117,2107 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF218E3B"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDA3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAC1F2C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BDC2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAB1F2C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC32938"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2FAA4B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDE4150"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCF0F1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF3F4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFA4AB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE2E4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC02836"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD33140"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9808A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC42A38"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD53241"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFACDDB7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7DCA8F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3D4D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7130"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED9BA3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBE8EA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE7F5EA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDB3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B2B8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF95D3A3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF67C07B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCA2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC969F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25866"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDA3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4756"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFDFD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9DFE1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3B9BF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEE9FA6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD2303F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBB2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E7F35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBEDEE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A702F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8437"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BFC4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7B33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23943D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBEAEC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23943D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8437"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE3E5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23953E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDE4251"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCFDFC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6AC27E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCD2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5BBC71"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7B34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A443"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218D3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208838"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF46B35F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC3E6CB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A712F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF63BF78"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC52A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7FCA90"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBC2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23943D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5FBD75"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23933D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8638"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8738"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7E35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8638"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7A33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8136"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5EBD74"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B2B8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2FA94B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF46B35F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8738"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2DFBC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6DC381"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF53B86A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2DFBC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7CC98E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF84CD95"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8638"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A644"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77580"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFCFC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF249A3F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6CC280"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBF2736"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77883"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22903C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF95D3A3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7CC98E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8337"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6CDD1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9DCDF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BAC0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE04C5A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B3B9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9858F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFBFB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF99D5A7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196F2F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24983F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD43140"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDE4251"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC929B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208839"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF37AD52"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4C4C8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF54B96B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF41B15A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46672"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2CA848"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDE4554"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8538"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6727D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A544"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBB2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7832"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6D0D3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF37AD52"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3949"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -75,37 +2229,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFB8E1C1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAB1E2C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC4E7CC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8236"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FFE35E6B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE35E6B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6F4E9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC32A38"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -129,7 +2289,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCEEEF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE04D5B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD63242"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -147,61 +2337,139 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDA3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BDC2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFF2B4BA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBB2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8537"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCDEAD4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7ECA8F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6FBF7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8638"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22923D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -219,6 +2487,864 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC12937"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCC2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF76C788"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3847"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB72432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8ED19D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF269F42"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE5E7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC92C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA9DBB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC52A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8538"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF64BF79"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A042"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3848"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC939B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD1303F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEE9DA4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9DEE0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B3B9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC72B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4BB563"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259E41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196D2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7E35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9DD7AA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8136"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAD1F2D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB3E0BD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE3E6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC12937"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D3D7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC32938"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE4F4E8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7BC98D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9838D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0DEBA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE4F4E8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7BC98D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBC2635"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD63242"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A142"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7BC98D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBC2635"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE04F5D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAD1F2D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFAC1F2C"/>
         <bgColor/>
       </patternFill>
@@ -231,3091 +3357,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC32938"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAB1F2C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC02836"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD33140"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDE4150"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCF0F1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFA4AB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2FAA4B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF3F4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE2E4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBE8EA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87A84"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC42A38"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED9BA3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7130"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3D4D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD53241"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9808A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFACDDB7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7DCA8F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF67C07B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCA2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF95D3A3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC969F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDB3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B2B8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB9199"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFDFD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9DFE1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDA3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3B9BF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25866"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEE9FA6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBB2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD2303F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BFC4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8437"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A702F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E7F35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBEDEE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7B33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBEAEC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE3E5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23953E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23943D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8437"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5BBC71"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDE4251"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCFDFC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAE202D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23943D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6AC27E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC3E6CB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A712F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218D3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208838"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7B34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF46B35F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A443"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7FCA90"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC52A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF63BF78"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5FBD75"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23943D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBC2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8638"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8738"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8638"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7E35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23933D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7A33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8136"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF46B35F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2DFBC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8738"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF84CD95"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6DC381"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF53B86A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2DFBC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7CC98E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B2B8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2FA94B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5EBD74"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A644"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77580"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFCFC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6CC280"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8638"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF249A3F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7CC98E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22903C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBF2736"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77883"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF95D3A3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BAC0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDE4150"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B3B9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6CDD1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF99D5A7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9DCDF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFBFB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8337"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9858F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196F2F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD43140"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDE4251"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208839"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC929B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF54B96B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF37AD52"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4C4C8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6EC382"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46672"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDE4554"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2CA848"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8538"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A544"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6727D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBB2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6D0D3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3949"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7832"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF37AD52"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAE202D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC32A38"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE35E6B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE35E6B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCEEEF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6F4E9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBB2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCDEAD4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE04D5B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7ECA8F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8537"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD63242"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B4BA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8638"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22923D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6FBF7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC12937"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87E88"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB72432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3847"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE5E7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA9DBB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8ED19D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC92C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF64BF79"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8538"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF269F42"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC52A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3848"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A042"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEE9DA4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD1303F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9DEE0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC72B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B3B9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC939B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCC2D3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259E41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196D2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB52331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8136"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7E35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC12937"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC32938"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A042"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAD1F2D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D3D7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE3E6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB3E0BD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBC2635"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9838D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7BC98D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBC2635"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7BC98D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0DEBA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7631"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD63242"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE4F4E8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE4F4E8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7BC98D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A142"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFE35D6A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -3334,48 +3376,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE04F5D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE35D6A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAC1F2C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAD1F2D"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -9306,7 +9306,7 @@
       <c r="C2" t="str">
         <v>002570</v>
       </c>
-      <c r="D2" s="13" t="str">
+      <c r="D2" s="6" t="str">
         <v>净卖: -1602.12万</v>
       </c>
       <c r="E2">
@@ -9321,41 +9321,41 @@
       <c r="H2">
         <v>0.15</v>
       </c>
-      <c r="I2" s="4">
+      <c r="I2" s="13">
         <v>9.77</v>
       </c>
-      <c r="J2" s="9">
+      <c r="J2" s="7">
         <v>9.62</v>
       </c>
-      <c r="K2" s="10">
+      <c r="K2" s="8">
         <v>-1.35</v>
       </c>
-      <c r="L2" s="5">
+      <c r="L2" s="9">
         <v>-7.07</v>
       </c>
-      <c r="M2" s="1">
+      <c r="M2" s="2">
         <v>-3.31</v>
       </c>
-      <c r="N2" s="2">
+      <c r="N2" s="10">
         <v>2.56</v>
       </c>
-      <c r="O2" s="6">
+      <c r="O2" s="1">
         <v>9.32</v>
       </c>
-      <c r="P2" s="7">
+      <c r="P2" s="3">
         <v>-1.65</v>
       </c>
-      <c r="Q2" s="3">
+      <c r="Q2" s="4">
         <v>-11.43</v>
       </c>
-      <c r="R2" s="8">
+      <c r="R2" s="11">
         <v>-9.47</v>
       </c>
-      <c r="S2" s="11">
+      <c r="S2" s="12">
         <v>-8.12</v>
       </c>
-      <c r="T2" s="12">
-        <v>-26.17</v>
+      <c r="T2" s="5">
+        <v>-27.22</v>
       </c>
     </row>
     <row r="3">
@@ -9368,7 +9368,7 @@
       <c r="C3" t="str">
         <v>002915</v>
       </c>
-      <c r="D3" s="17" t="str">
+      <c r="D3" s="19" t="str">
         <v>净买: 2039.94万</v>
       </c>
       <c r="E3">
@@ -9383,41 +9383,41 @@
       <c r="H3">
         <v>0.12</v>
       </c>
-      <c r="I3" s="21">
+      <c r="I3" s="24">
         <v>5.12</v>
       </c>
-      <c r="J3" s="25">
+      <c r="J3" s="20">
         <v>15.65</v>
       </c>
-      <c r="K3" s="26">
+      <c r="K3" s="21">
         <v>27.2</v>
       </c>
       <c r="L3" s="18">
         <v>27.56</v>
       </c>
-      <c r="M3" s="22">
+      <c r="M3" s="14">
         <v>40.3</v>
       </c>
-      <c r="N3" s="14">
+      <c r="N3" s="22">
         <v>27.68</v>
       </c>
-      <c r="O3" s="23">
+      <c r="O3" s="15">
         <v>30.06</v>
       </c>
-      <c r="P3" s="19">
+      <c r="P3" s="16">
         <v>28.1</v>
       </c>
-      <c r="Q3" s="15">
+      <c r="Q3" s="25">
         <v>36.9</v>
       </c>
-      <c r="R3" s="20">
+      <c r="R3" s="17">
         <v>34.52</v>
       </c>
-      <c r="S3" s="16">
+      <c r="S3" s="23">
         <v>21.07</v>
       </c>
-      <c r="T3" s="24">
-        <v>15.24</v>
+      <c r="T3" s="26">
+        <v>10</v>
       </c>
     </row>
     <row r="4">
@@ -9430,7 +9430,7 @@
       <c r="C4" t="str">
         <v>002229</v>
       </c>
-      <c r="D4" s="29" t="str">
+      <c r="D4" s="36" t="str">
         <v>净买: 2135.02万</v>
       </c>
       <c r="E4">
@@ -9445,41 +9445,41 @@
       <c r="H4">
         <v>8.23</v>
       </c>
-      <c r="I4" s="27">
+      <c r="I4" s="34">
         <v>1.62</v>
       </c>
-      <c r="J4" s="28">
+      <c r="J4" s="29">
         <v>11.75</v>
       </c>
-      <c r="K4" s="34">
+      <c r="K4" s="30">
         <v>21.04</v>
       </c>
-      <c r="L4" s="35">
+      <c r="L4" s="31">
         <v>28.15</v>
       </c>
-      <c r="M4" s="38">
+      <c r="M4" s="37">
         <v>15.34</v>
       </c>
-      <c r="N4" s="30">
+      <c r="N4" s="32">
         <v>13.65</v>
       </c>
-      <c r="O4" s="36">
+      <c r="O4" s="38">
         <v>13.02</v>
       </c>
-      <c r="P4" s="37">
+      <c r="P4" s="39">
         <v>7.32</v>
       </c>
-      <c r="Q4" s="31">
+      <c r="Q4" s="33">
         <v>9.5</v>
       </c>
-      <c r="R4" s="39">
+      <c r="R4" s="35">
         <v>9.57</v>
       </c>
-      <c r="S4" s="32">
+      <c r="S4" s="27">
         <v>14.22</v>
       </c>
-      <c r="T4" s="33">
-        <v>16.68</v>
+      <c r="T4" s="28">
+        <v>14.57</v>
       </c>
     </row>
     <row r="5">
@@ -9492,7 +9492,7 @@
       <c r="C5" t="str">
         <v>002915</v>
       </c>
-      <c r="D5" s="46" t="str">
+      <c r="D5" s="43" t="str">
         <v>净卖: -2747.73万</v>
       </c>
       <c r="E5">
@@ -9507,41 +9507,41 @@
       <c r="H5">
         <v>9.98</v>
       </c>
-      <c r="I5" s="40">
+      <c r="I5" s="44">
         <v>0</v>
       </c>
-      <c r="J5" s="51">
+      <c r="J5" s="48">
         <v>0.28</v>
       </c>
-      <c r="K5" s="44">
+      <c r="K5" s="47">
         <v>10.29</v>
       </c>
-      <c r="L5" s="47">
+      <c r="L5" s="45">
         <v>0.37</v>
       </c>
-      <c r="M5" s="48">
+      <c r="M5" s="49">
         <v>2.25</v>
       </c>
-      <c r="N5" s="52">
+      <c r="N5" s="50">
         <v>0.7</v>
       </c>
-      <c r="O5" s="41">
+      <c r="O5" s="51">
         <v>7.63</v>
       </c>
-      <c r="P5" s="42">
+      <c r="P5" s="52">
         <v>5.76</v>
       </c>
-      <c r="Q5" s="49">
+      <c r="Q5" s="40">
         <v>-4.82</v>
       </c>
-      <c r="R5" s="45">
+      <c r="R5" s="41">
         <v>4.68</v>
       </c>
-      <c r="S5" s="43">
+      <c r="S5" s="42">
         <v>11</v>
       </c>
-      <c r="T5" s="50">
-        <v>-9.41</v>
+      <c r="T5" s="46">
+        <v>-13.52</v>
       </c>
     </row>
     <row r="6">
@@ -9569,41 +9569,41 @@
       <c r="H6">
         <v>5.02</v>
       </c>
-      <c r="I6" s="58">
+      <c r="I6" s="60">
         <v>4.78</v>
       </c>
-      <c r="J6" s="61">
+      <c r="J6" s="63">
         <v>10.79</v>
       </c>
       <c r="K6" s="55">
         <v>7.24</v>
       </c>
-      <c r="L6" s="63">
+      <c r="L6" s="57">
         <v>12.3</v>
       </c>
-      <c r="M6" s="59">
+      <c r="M6" s="56">
         <v>5.6</v>
       </c>
-      <c r="N6" s="56">
+      <c r="N6" s="64">
         <v>2.46</v>
       </c>
-      <c r="O6" s="64">
+      <c r="O6" s="58">
         <v>-1.91</v>
       </c>
-      <c r="P6" s="57">
+      <c r="P6" s="61">
         <v>-9.56</v>
       </c>
-      <c r="Q6" s="65">
+      <c r="Q6" s="59">
         <v>-3.01</v>
       </c>
-      <c r="R6" s="53">
+      <c r="R6" s="65">
         <v>0.55</v>
       </c>
-      <c r="S6" s="60">
+      <c r="S6" s="53">
         <v>3.14</v>
       </c>
       <c r="T6" s="54">
-        <v>3.28</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -9616,7 +9616,7 @@
       <c r="C7" t="str">
         <v>002177</v>
       </c>
-      <c r="D7" s="74" t="str">
+      <c r="D7" s="67" t="str">
         <v>净卖: -2852.77万</v>
       </c>
       <c r="E7">
@@ -9631,41 +9631,41 @@
       <c r="H7">
         <v>-4.04</v>
       </c>
-      <c r="I7" s="68">
+      <c r="I7" s="74">
         <v>10.19</v>
       </c>
-      <c r="J7" s="69">
+      <c r="J7" s="75">
         <v>6.66</v>
       </c>
-      <c r="K7" s="75">
+      <c r="K7" s="72">
         <v>11.68</v>
       </c>
-      <c r="L7" s="72">
+      <c r="L7" s="68">
         <v>5.03</v>
       </c>
-      <c r="M7" s="76">
+      <c r="M7" s="69">
         <v>1.9</v>
       </c>
       <c r="N7" s="70">
         <v>-2.45</v>
       </c>
-      <c r="O7" s="77">
+      <c r="O7" s="78">
         <v>-10.05</v>
       </c>
-      <c r="P7" s="66">
+      <c r="P7" s="71">
         <v>-3.53</v>
       </c>
-      <c r="Q7" s="73">
+      <c r="Q7" s="76">
         <v>0</v>
       </c>
-      <c r="R7" s="71">
+      <c r="R7" s="77">
         <v>2.58</v>
       </c>
-      <c r="S7" s="67">
+      <c r="S7" s="73">
         <v>-5.3</v>
       </c>
-      <c r="T7" s="78">
-        <v>2.72</v>
+      <c r="T7" s="66">
+        <v>-0.54</v>
       </c>
     </row>
     <row r="8">
@@ -9696,38 +9696,38 @@
       <c r="I8" s="84">
         <v>11.01</v>
       </c>
-      <c r="J8" s="90">
+      <c r="J8" s="82">
         <v>11.21</v>
       </c>
-      <c r="K8" s="85">
+      <c r="K8" s="87">
         <v>1.71</v>
       </c>
-      <c r="L8" s="86">
+      <c r="L8" s="79">
         <v>4.11</v>
       </c>
-      <c r="M8" s="79">
+      <c r="M8" s="85">
         <v>0.04</v>
       </c>
-      <c r="N8" s="80">
+      <c r="N8" s="86">
         <v>0.78</v>
       </c>
-      <c r="O8" s="87">
+      <c r="O8" s="88">
         <v>2.37</v>
       </c>
-      <c r="P8" s="81">
+      <c r="P8" s="80">
         <v>5.12</v>
       </c>
-      <c r="Q8" s="91">
+      <c r="Q8" s="89">
         <v>5.93</v>
       </c>
-      <c r="R8" s="88">
+      <c r="R8" s="90">
         <v>8.07</v>
       </c>
-      <c r="S8" s="89">
+      <c r="S8" s="91">
         <v>18.88</v>
       </c>
-      <c r="T8" s="82">
-        <v>6.24</v>
+      <c r="T8" s="81">
+        <v>4.54</v>
       </c>
     </row>
     <row r="9">
@@ -9740,7 +9740,7 @@
       <c r="C9" t="str">
         <v>003029</v>
       </c>
-      <c r="D9" s="94" t="str">
+      <c r="D9" s="96" t="str">
         <v>净卖: -276.02万</v>
       </c>
       <c r="E9">
@@ -9758,38 +9758,38 @@
       <c r="I9" s="101">
         <v>0</v>
       </c>
-      <c r="J9" s="92">
+      <c r="J9" s="99">
         <v>10.01</v>
       </c>
-      <c r="K9" s="93">
+      <c r="K9" s="102">
         <v>1.58</v>
       </c>
-      <c r="L9" s="102">
+      <c r="L9" s="94">
         <v>0.44</v>
       </c>
-      <c r="M9" s="97">
+      <c r="M9" s="95">
         <v>-9.6</v>
       </c>
-      <c r="N9" s="103">
+      <c r="N9" s="97">
         <v>-14.15</v>
       </c>
       <c r="O9" s="98">
         <v>-11.05</v>
       </c>
-      <c r="P9" s="104">
+      <c r="P9" s="103">
         <v>-8.72</v>
       </c>
-      <c r="Q9" s="99">
+      <c r="Q9" s="104">
         <v>-7.3</v>
       </c>
-      <c r="R9" s="100">
+      <c r="R9" s="92">
         <v>-8.31</v>
       </c>
-      <c r="S9" s="95">
+      <c r="S9" s="100">
         <v>-7.9</v>
       </c>
-      <c r="T9" s="96">
-        <v>-32.79</v>
+      <c r="T9" s="93">
+        <v>-35.34</v>
       </c>
     </row>
     <row r="10">
@@ -9802,7 +9802,7 @@
       <c r="C10" t="str">
         <v>002017</v>
       </c>
-      <c r="D10" s="115" t="str">
+      <c r="D10" s="111" t="str">
         <v>净买: 6518.56万</v>
       </c>
       <c r="E10">
@@ -9823,35 +9823,35 @@
       <c r="J10" s="113">
         <v>-0.06</v>
       </c>
-      <c r="K10" s="116">
+      <c r="K10" s="105">
         <v>-6.53</v>
       </c>
-      <c r="L10" s="109">
+      <c r="L10" s="114">
         <v>-5.79</v>
       </c>
-      <c r="M10" s="110">
+      <c r="M10" s="108">
         <v>-7.89</v>
       </c>
-      <c r="N10" s="117">
+      <c r="N10" s="115">
         <v>-3.46</v>
       </c>
-      <c r="O10" s="106">
+      <c r="O10" s="109">
         <v>0.68</v>
       </c>
-      <c r="P10" s="105">
+      <c r="P10" s="106">
         <v>0.51</v>
       </c>
-      <c r="Q10" s="107">
+      <c r="Q10" s="110">
         <v>-6.47</v>
       </c>
-      <c r="R10" s="111">
+      <c r="R10" s="117">
         <v>-3.8</v>
       </c>
-      <c r="S10" s="108">
+      <c r="S10" s="107">
         <v>-6.53</v>
       </c>
-      <c r="T10" s="114">
-        <v>9.31</v>
+      <c r="T10" s="116">
+        <v>6.36</v>
       </c>
     </row>
     <row r="11">
@@ -9879,41 +9879,41 @@
       <c r="H11">
         <v>-0.81</v>
       </c>
-      <c r="I11" s="130">
+      <c r="I11" s="122">
         <v>-5.23</v>
       </c>
-      <c r="J11" s="118">
+      <c r="J11" s="126">
         <v>-1.39</v>
       </c>
-      <c r="K11" s="119">
+      <c r="K11" s="130">
         <v>-9.57</v>
       </c>
-      <c r="L11" s="120">
+      <c r="L11" s="123">
         <v>-7.18</v>
       </c>
-      <c r="M11" s="121">
+      <c r="M11" s="124">
         <v>-7.62</v>
       </c>
-      <c r="N11" s="125">
+      <c r="N11" s="118">
         <v>-8.69</v>
       </c>
-      <c r="O11" s="122">
+      <c r="O11" s="127">
         <v>-7.37</v>
       </c>
-      <c r="P11" s="126">
+      <c r="P11" s="119">
         <v>-8.56</v>
       </c>
-      <c r="Q11" s="127">
+      <c r="Q11" s="120">
         <v>-8.63</v>
       </c>
-      <c r="R11" s="128">
+      <c r="R11" s="125">
         <v>-4.28</v>
       </c>
-      <c r="S11" s="123">
+      <c r="S11" s="121">
         <v>-8.56</v>
       </c>
-      <c r="T11" s="124">
-        <v>-21.1</v>
+      <c r="T11" s="128">
+        <v>-21.54</v>
       </c>
     </row>
     <row r="12">
@@ -9926,7 +9926,7 @@
       <c r="C12" t="str">
         <v>002579</v>
       </c>
-      <c r="D12" s="134" t="str">
+      <c r="D12" s="139" t="str">
         <v>净买: 4403.72万</v>
       </c>
       <c r="E12">
@@ -9941,41 +9941,41 @@
       <c r="H12">
         <v>-2.68</v>
       </c>
-      <c r="I12" s="138">
+      <c r="I12" s="131">
         <v>13.04</v>
       </c>
-      <c r="J12" s="142">
+      <c r="J12" s="140">
         <v>12.54</v>
       </c>
-      <c r="K12" s="139">
+      <c r="K12" s="141">
         <v>7.97</v>
       </c>
-      <c r="L12" s="143">
+      <c r="L12" s="132">
         <v>12.54</v>
       </c>
-      <c r="M12" s="133">
+      <c r="M12" s="136">
         <v>7.1</v>
       </c>
-      <c r="N12" s="135">
+      <c r="N12" s="133">
         <v>-3.62</v>
       </c>
-      <c r="O12" s="131">
+      <c r="O12" s="137">
         <v>-2.97</v>
       </c>
-      <c r="P12" s="132">
+      <c r="P12" s="138">
         <v>-5.36</v>
       </c>
-      <c r="Q12" s="136">
+      <c r="Q12" s="143">
         <v>-3.7</v>
       </c>
-      <c r="R12" s="140">
+      <c r="R12" s="134">
         <v>-10.07</v>
       </c>
-      <c r="S12" s="137">
+      <c r="S12" s="142">
         <v>-6.59</v>
       </c>
-      <c r="T12" s="141">
-        <v>-6.23</v>
+      <c r="T12" s="135">
+        <v>-11.67</v>
       </c>
     </row>
     <row r="13">
@@ -9988,7 +9988,7 @@
       <c r="C13" t="str">
         <v>002229</v>
       </c>
-      <c r="D13" s="156" t="str">
+      <c r="D13" s="145" t="str">
         <v>净卖: -4629.75万</v>
       </c>
       <c r="E13">
@@ -10003,41 +10003,41 @@
       <c r="H13">
         <v>3.11</v>
       </c>
-      <c r="I13" s="151">
+      <c r="I13" s="150">
         <v>-7.78</v>
       </c>
       <c r="J13" s="152">
         <v>-8.44</v>
       </c>
-      <c r="K13" s="146">
+      <c r="K13" s="153">
         <v>-11.23</v>
       </c>
-      <c r="L13" s="144">
+      <c r="L13" s="154">
         <v>-12.22</v>
       </c>
-      <c r="M13" s="153">
+      <c r="M13" s="156">
         <v>-10.66</v>
       </c>
-      <c r="N13" s="154">
+      <c r="N13" s="146">
         <v>-6.65</v>
       </c>
-      <c r="O13" s="147">
+      <c r="O13" s="155">
         <v>-7.74</v>
       </c>
-      <c r="P13" s="148">
+      <c r="P13" s="151">
         <v>-7.69</v>
       </c>
-      <c r="Q13" s="145">
+      <c r="Q13" s="147">
         <v>-11.37</v>
       </c>
-      <c r="R13" s="149">
+      <c r="R13" s="148">
         <v>-10.8</v>
       </c>
-      <c r="S13" s="155">
+      <c r="S13" s="149">
         <v>-13.68</v>
       </c>
-      <c r="T13" s="150">
-        <v>-21.79</v>
+      <c r="T13" s="144">
+        <v>-23.21</v>
       </c>
     </row>
     <row r="14">
@@ -10050,7 +10050,7 @@
       <c r="C14" t="str">
         <v>000657</v>
       </c>
-      <c r="D14" s="158" t="str">
+      <c r="D14" s="166" t="str">
         <v>净卖: -6184.73万</v>
       </c>
       <c r="E14">
@@ -10065,41 +10065,41 @@
       <c r="H14">
         <v>-2</v>
       </c>
-      <c r="I14" s="159">
+      <c r="I14" s="165">
         <v>-8.16</v>
       </c>
-      <c r="J14" s="168">
+      <c r="J14" s="157">
         <v>-13.48</v>
       </c>
-      <c r="K14" s="169">
+      <c r="K14" s="158">
         <v>-14.93</v>
       </c>
-      <c r="L14" s="163">
+      <c r="L14" s="161">
         <v>-15.36</v>
       </c>
-      <c r="M14" s="160">
+      <c r="M14" s="162">
         <v>-15.2</v>
       </c>
-      <c r="N14" s="166">
+      <c r="N14" s="159">
         <v>-13.43</v>
       </c>
-      <c r="O14" s="164">
+      <c r="O14" s="167">
         <v>-13.1</v>
       </c>
-      <c r="P14" s="161">
+      <c r="P14" s="168">
         <v>-11.6</v>
       </c>
-      <c r="Q14" s="165">
+      <c r="Q14" s="169">
         <v>-10.74</v>
       </c>
-      <c r="R14" s="162">
+      <c r="R14" s="163">
         <v>-10.9</v>
       </c>
-      <c r="S14" s="157">
+      <c r="S14" s="160">
         <v>-8.81</v>
       </c>
-      <c r="T14" s="167">
-        <v>189.1</v>
+      <c r="T14" s="164">
+        <v>179.81</v>
       </c>
     </row>
     <row r="15">
@@ -10112,7 +10112,7 @@
       <c r="C15" t="str">
         <v>002670</v>
       </c>
-      <c r="D15" s="174" t="str">
+      <c r="D15" s="170" t="str">
         <v>净卖: -7597.74万</v>
       </c>
       <c r="E15">
@@ -10127,41 +10127,41 @@
       <c r="H15">
         <v>0.45</v>
       </c>
-      <c r="I15" s="180">
+      <c r="I15" s="172">
         <v>1.89</v>
       </c>
-      <c r="J15" s="171">
+      <c r="J15" s="180">
         <v>-1.79</v>
       </c>
-      <c r="K15" s="178">
+      <c r="K15" s="176">
         <v>-1.79</v>
       </c>
-      <c r="L15" s="179">
+      <c r="L15" s="181">
         <v>-3.03</v>
       </c>
-      <c r="M15" s="181">
+      <c r="M15" s="173">
         <v>-4.83</v>
       </c>
-      <c r="N15" s="182">
+      <c r="N15" s="171">
         <v>-3.73</v>
       </c>
-      <c r="O15" s="175">
+      <c r="O15" s="177">
         <v>-3.38</v>
       </c>
-      <c r="P15" s="170">
+      <c r="P15" s="174">
         <v>-4.28</v>
       </c>
-      <c r="Q15" s="172">
+      <c r="Q15" s="175">
         <v>-7.71</v>
       </c>
-      <c r="R15" s="176">
+      <c r="R15" s="178">
         <v>-3.98</v>
       </c>
-      <c r="S15" s="173">
+      <c r="S15" s="182">
         <v>-2.84</v>
       </c>
-      <c r="T15" s="177">
-        <v>-37.66</v>
+      <c r="T15" s="179">
+        <v>-38.01</v>
       </c>
     </row>
     <row r="16">
@@ -10174,7 +10174,7 @@
       <c r="C16" t="str">
         <v>688039</v>
       </c>
-      <c r="D16" s="194" t="str">
+      <c r="D16" s="193" t="str">
         <v>净买: 3066.00万</v>
       </c>
       <c r="E16">
@@ -10189,41 +10189,41 @@
       <c r="H16">
         <v>7.16</v>
       </c>
-      <c r="I16" s="195">
+      <c r="I16" s="188">
         <v>11.98</v>
       </c>
-      <c r="J16" s="183">
+      <c r="J16" s="184">
         <v>16.69</v>
       </c>
-      <c r="K16" s="187">
+      <c r="K16" s="189">
         <v>3.41</v>
       </c>
-      <c r="L16" s="188">
+      <c r="L16" s="190">
         <v>0.07</v>
       </c>
-      <c r="M16" s="189">
+      <c r="M16" s="194">
         <v>-5.26</v>
       </c>
-      <c r="N16" s="190">
+      <c r="N16" s="195">
         <v>-3.41</v>
       </c>
-      <c r="O16" s="184">
+      <c r="O16" s="185">
         <v>-5.04</v>
       </c>
-      <c r="P16" s="185">
+      <c r="P16" s="191">
         <v>-10.52</v>
       </c>
-      <c r="Q16" s="191">
+      <c r="Q16" s="183">
         <v>-7.78</v>
       </c>
-      <c r="R16" s="193">
+      <c r="R16" s="192">
         <v>-6.1</v>
       </c>
       <c r="S16" s="186">
         <v>-7.34</v>
       </c>
-      <c r="T16" s="192">
-        <v>-23.78</v>
+      <c r="T16" s="187">
+        <v>-26.68</v>
       </c>
     </row>
     <row r="17">
@@ -10236,7 +10236,7 @@
       <c r="C17" t="str">
         <v>600408</v>
       </c>
-      <c r="D17" s="206" t="str">
+      <c r="D17" s="202" t="str">
         <v>净买: 1877.05万</v>
       </c>
       <c r="E17">
@@ -10251,41 +10251,41 @@
       <c r="H17">
         <v>-4.45</v>
       </c>
-      <c r="I17" s="198">
+      <c r="I17" s="203">
         <v>15.2</v>
       </c>
-      <c r="J17" s="204">
+      <c r="J17" s="200">
         <v>26.72</v>
       </c>
       <c r="K17" s="205">
         <v>39.46</v>
       </c>
-      <c r="L17" s="201">
+      <c r="L17" s="206">
         <v>53.43</v>
       </c>
-      <c r="M17" s="199">
+      <c r="M17" s="207">
         <v>68.87</v>
       </c>
-      <c r="N17" s="207">
+      <c r="N17" s="196">
         <v>52.7</v>
       </c>
-      <c r="O17" s="208">
+      <c r="O17" s="204">
         <v>37.5</v>
       </c>
-      <c r="P17" s="200">
+      <c r="P17" s="201">
         <v>24.26</v>
       </c>
-      <c r="Q17" s="196">
+      <c r="Q17" s="197">
         <v>14.95</v>
       </c>
-      <c r="R17" s="202">
+      <c r="R17" s="208">
         <v>10.54</v>
       </c>
-      <c r="S17" s="197">
+      <c r="S17" s="198">
         <v>11.52</v>
       </c>
-      <c r="T17" s="203">
-        <v>-21.08</v>
+      <c r="T17" s="199">
+        <v>-19.61</v>
       </c>
     </row>
     <row r="18">
@@ -10298,7 +10298,7 @@
       <c r="C18" t="str">
         <v>601566</v>
       </c>
-      <c r="D18" s="210" t="str">
+      <c r="D18" s="217" t="str">
         <v>净买: 5226.66万</v>
       </c>
       <c r="E18">
@@ -10313,41 +10313,41 @@
       <c r="H18">
         <v>10.02</v>
       </c>
-      <c r="I18" s="211">
+      <c r="I18" s="218">
         <v>0</v>
       </c>
-      <c r="J18" s="217">
+      <c r="J18" s="219">
         <v>9.97</v>
       </c>
-      <c r="K18" s="218">
+      <c r="K18" s="220">
         <v>20.95</v>
       </c>
-      <c r="L18" s="215">
+      <c r="L18" s="211">
         <v>33.02</v>
       </c>
-      <c r="M18" s="212">
+      <c r="M18" s="215">
         <v>19.73</v>
       </c>
-      <c r="N18" s="219">
+      <c r="N18" s="212">
         <v>7.73</v>
       </c>
-      <c r="O18" s="220">
+      <c r="O18" s="213">
         <v>3.32</v>
       </c>
-      <c r="P18" s="213">
+      <c r="P18" s="209">
         <v>-5.35</v>
       </c>
-      <c r="Q18" s="216">
+      <c r="Q18" s="214">
         <v>-6.94</v>
       </c>
-      <c r="R18" s="214">
+      <c r="R18" s="221">
         <v>-3.03</v>
       </c>
-      <c r="S18" s="221">
+      <c r="S18" s="216">
         <v>-2.46</v>
       </c>
-      <c r="T18" s="209">
-        <v>-21.03</v>
+      <c r="T18" s="210">
+        <v>-22.18</v>
       </c>
     </row>
     <row r="19">
@@ -10360,7 +10360,7 @@
       <c r="C19" t="str">
         <v>002029</v>
       </c>
-      <c r="D19" s="231" t="str">
+      <c r="D19" s="232" t="str">
         <v>净卖: -1276.40万</v>
       </c>
       <c r="E19">
@@ -10375,41 +10375,41 @@
       <c r="H19">
         <v>0</v>
       </c>
-      <c r="I19" s="227">
+      <c r="I19" s="224">
         <v>9.97</v>
       </c>
-      <c r="J19" s="224">
+      <c r="J19" s="228">
         <v>1.88</v>
       </c>
-      <c r="K19" s="228">
+      <c r="K19" s="233">
         <v>-2.35</v>
       </c>
-      <c r="L19" s="232">
+      <c r="L19" s="234">
         <v>-9.97</v>
       </c>
-      <c r="M19" s="225">
+      <c r="M19" s="229">
         <v>-11.67</v>
       </c>
-      <c r="N19" s="233">
+      <c r="N19" s="222">
         <v>-8</v>
       </c>
-      <c r="O19" s="226">
+      <c r="O19" s="223">
         <v>1.22</v>
       </c>
-      <c r="P19" s="229">
+      <c r="P19" s="225">
         <v>0.85</v>
       </c>
-      <c r="Q19" s="234">
+      <c r="Q19" s="230">
         <v>3.01</v>
       </c>
-      <c r="R19" s="222">
+      <c r="R19" s="226">
         <v>1.69</v>
       </c>
-      <c r="S19" s="230">
+      <c r="S19" s="231">
         <v>0.09</v>
       </c>
-      <c r="T19" s="223">
-        <v>4.7</v>
+      <c r="T19" s="227">
+        <v>4.42</v>
       </c>
     </row>
     <row r="20">
@@ -10422,7 +10422,7 @@
       <c r="C20" t="str">
         <v>601566</v>
       </c>
-      <c r="D20" s="236" t="str">
+      <c r="D20" s="239" t="str">
         <v>净卖: -2737.55万</v>
       </c>
       <c r="E20">
@@ -10437,41 +10437,41 @@
       <c r="H20">
         <v>4.01</v>
       </c>
-      <c r="I20" s="245">
+      <c r="I20" s="243">
         <v>5.75</v>
       </c>
       <c r="J20" s="246">
         <v>16.3</v>
       </c>
-      <c r="K20" s="247">
+      <c r="K20" s="244">
         <v>4.67</v>
       </c>
-      <c r="L20" s="237">
+      <c r="L20" s="240">
         <v>-5.81</v>
       </c>
-      <c r="M20" s="242">
+      <c r="M20" s="235">
         <v>-9.67</v>
       </c>
-      <c r="N20" s="243">
+      <c r="N20" s="241">
         <v>-17.25</v>
       </c>
-      <c r="O20" s="238">
+      <c r="O20" s="245">
         <v>-18.64</v>
       </c>
-      <c r="P20" s="239">
+      <c r="P20" s="236">
         <v>-15.22</v>
       </c>
-      <c r="Q20" s="244">
+      <c r="Q20" s="242">
         <v>-14.72</v>
       </c>
-      <c r="R20" s="240">
+      <c r="R20" s="247">
         <v>-10.8</v>
       </c>
-      <c r="S20" s="235">
+      <c r="S20" s="237">
         <v>-6.19</v>
       </c>
-      <c r="T20" s="241">
-        <v>-30.95</v>
+      <c r="T20" s="238">
+        <v>-31.96</v>
       </c>
     </row>
     <row r="21">
@@ -10484,7 +10484,7 @@
       <c r="C21" t="str">
         <v>601566</v>
       </c>
-      <c r="D21" s="258" t="str">
+      <c r="D21" s="257" t="str">
         <v>净卖: -5218.09万</v>
       </c>
       <c r="E21">
@@ -10499,41 +10499,41 @@
       <c r="H21">
         <v>7.11</v>
       </c>
-      <c r="I21" s="259">
+      <c r="I21" s="249">
         <v>2.68</v>
       </c>
-      <c r="J21" s="255">
+      <c r="J21" s="250">
         <v>-7.59</v>
       </c>
-      <c r="K21" s="256">
+      <c r="K21" s="253">
         <v>-16.84</v>
       </c>
-      <c r="L21" s="250">
+      <c r="L21" s="256">
         <v>-20.25</v>
       </c>
-      <c r="M21" s="251">
+      <c r="M21" s="258">
         <v>-26.94</v>
       </c>
-      <c r="N21" s="252">
+      <c r="N21" s="254">
         <v>-28.17</v>
       </c>
-      <c r="O21" s="253">
+      <c r="O21" s="259">
         <v>-25.15</v>
       </c>
-      <c r="P21" s="260">
+      <c r="P21" s="251">
         <v>-24.71</v>
       </c>
-      <c r="Q21" s="248">
+      <c r="Q21" s="255">
         <v>-21.25</v>
       </c>
-      <c r="R21" s="249">
+      <c r="R21" s="260">
         <v>-17.18</v>
       </c>
-      <c r="S21" s="254">
+      <c r="S21" s="252">
         <v>-25.43</v>
       </c>
-      <c r="T21" s="257">
-        <v>-39.04</v>
+      <c r="T21" s="248">
+        <v>-39.93</v>
       </c>
     </row>
     <row r="22">
@@ -10546,7 +10546,7 @@
       <c r="C22" t="str">
         <v>600756</v>
       </c>
-      <c r="D22" s="266" t="str">
+      <c r="D22" s="271" t="str">
         <v>净卖: -2369.10万</v>
       </c>
       <c r="E22">
@@ -10561,41 +10561,41 @@
       <c r="H22">
         <v>-1.6</v>
       </c>
-      <c r="I22" s="273">
+      <c r="I22" s="265">
         <v>1.46</v>
       </c>
-      <c r="J22" s="271">
+      <c r="J22" s="263">
         <v>-4.63</v>
       </c>
-      <c r="K22" s="267">
+      <c r="K22" s="266">
         <v>-3.97</v>
       </c>
-      <c r="L22" s="268">
+      <c r="L22" s="272">
         <v>-13.57</v>
       </c>
-      <c r="M22" s="269">
+      <c r="M22" s="273">
         <v>-21.09</v>
       </c>
-      <c r="N22" s="272">
+      <c r="N22" s="264">
         <v>-19.75</v>
       </c>
-      <c r="O22" s="264">
+      <c r="O22" s="261">
         <v>-18.25</v>
       </c>
-      <c r="P22" s="261">
+      <c r="P22" s="268">
         <v>-20.84</v>
       </c>
-      <c r="Q22" s="262">
+      <c r="Q22" s="269">
         <v>-21.42</v>
       </c>
-      <c r="R22" s="265">
+      <c r="R22" s="270">
         <v>-23.17</v>
       </c>
-      <c r="S22" s="270">
+      <c r="S22" s="267">
         <v>-24.43</v>
       </c>
-      <c r="T22" s="263">
-        <v>-31.82</v>
+      <c r="T22" s="262">
+        <v>-32.78</v>
       </c>
     </row>
     <row r="23">
@@ -10608,7 +10608,7 @@
       <c r="C23" t="str">
         <v>603696</v>
       </c>
-      <c r="D23" s="280" t="str">
+      <c r="D23" s="276" t="str">
         <v>净买: 3978.78万</v>
       </c>
       <c r="E23">
@@ -10623,41 +10623,41 @@
       <c r="H23">
         <v>9.98</v>
       </c>
-      <c r="I23" s="285">
+      <c r="I23" s="277">
         <v>0</v>
       </c>
-      <c r="J23" s="281">
+      <c r="J23" s="279">
         <v>10.01</v>
       </c>
-      <c r="K23" s="275">
+      <c r="K23" s="278">
         <v>21.01</v>
       </c>
-      <c r="L23" s="282">
+      <c r="L23" s="274">
         <v>33.13</v>
       </c>
       <c r="M23" s="283">
         <v>46.43</v>
       </c>
-      <c r="N23" s="286">
+      <c r="N23" s="284">
         <v>43.01</v>
       </c>
-      <c r="O23" s="276">
+      <c r="O23" s="285">
         <v>28.71</v>
       </c>
-      <c r="P23" s="274">
+      <c r="P23" s="280">
         <v>24.74</v>
       </c>
-      <c r="Q23" s="279">
+      <c r="Q23" s="286">
         <v>27.91</v>
       </c>
-      <c r="R23" s="284">
+      <c r="R23" s="275">
         <v>40.71</v>
       </c>
-      <c r="S23" s="277">
+      <c r="S23" s="281">
         <v>26.66</v>
       </c>
-      <c r="T23" s="278">
-        <v>-3.36</v>
+      <c r="T23" s="282">
+        <v>-4.41</v>
       </c>
     </row>
     <row r="24">
@@ -10670,7 +10670,7 @@
       <c r="C24" t="str">
         <v>002682</v>
       </c>
-      <c r="D24" s="295" t="str">
+      <c r="D24" s="293" t="str">
         <v>净买: 2499.06万</v>
       </c>
       <c r="E24">
@@ -10685,41 +10685,41 @@
       <c r="H24">
         <v>5.99</v>
       </c>
-      <c r="I24" s="290">
+      <c r="I24" s="296">
         <v>3.77</v>
       </c>
-      <c r="J24" s="299">
+      <c r="J24" s="287">
         <v>14.2</v>
       </c>
-      <c r="K24" s="296">
+      <c r="K24" s="288">
         <v>25.65</v>
       </c>
-      <c r="L24" s="287">
+      <c r="L24" s="294">
         <v>38.26</v>
       </c>
-      <c r="M24" s="292">
+      <c r="M24" s="295">
         <v>52.03</v>
       </c>
-      <c r="N24" s="288">
+      <c r="N24" s="297">
         <v>42.9</v>
       </c>
-      <c r="O24" s="293">
+      <c r="O24" s="298">
         <v>57.25</v>
       </c>
       <c r="P24" s="289">
         <v>72.9</v>
       </c>
-      <c r="Q24" s="297">
+      <c r="Q24" s="299">
         <v>55.65</v>
       </c>
-      <c r="R24" s="291">
+      <c r="R24" s="290">
         <v>40.14</v>
       </c>
-      <c r="S24" s="298">
+      <c r="S24" s="291">
         <v>42.75</v>
       </c>
-      <c r="T24" s="294">
-        <v>-16.38</v>
+      <c r="T24" s="292">
+        <v>-16.23</v>
       </c>
     </row>
     <row r="25">
@@ -10732,7 +10732,7 @@
       <c r="C25" t="str">
         <v>603696</v>
       </c>
-      <c r="D25" s="301" t="str">
+      <c r="D25" s="307" t="str">
         <v>净卖: -1913.63万</v>
       </c>
       <c r="E25">
@@ -10747,41 +10747,41 @@
       <c r="H25">
         <v>-2.03</v>
       </c>
-      <c r="I25" s="310">
+      <c r="I25" s="302">
         <v>12.28</v>
       </c>
-      <c r="J25" s="307">
+      <c r="J25" s="303">
         <v>23.53</v>
       </c>
-      <c r="K25" s="311">
+      <c r="K25" s="304">
         <v>35.87</v>
       </c>
-      <c r="L25" s="302">
+      <c r="L25" s="312">
         <v>32.7</v>
       </c>
       <c r="M25" s="308">
         <v>19.43</v>
       </c>
-      <c r="N25" s="303">
+      <c r="N25" s="309">
         <v>15.74</v>
       </c>
-      <c r="O25" s="304">
+      <c r="O25" s="310">
         <v>18.69</v>
       </c>
-      <c r="P25" s="305">
+      <c r="P25" s="306">
         <v>30.57</v>
       </c>
-      <c r="Q25" s="309">
+      <c r="Q25" s="300">
         <v>17.53</v>
       </c>
-      <c r="R25" s="306">
+      <c r="R25" s="305">
         <v>10.73</v>
       </c>
-      <c r="S25" s="312">
+      <c r="S25" s="301">
         <v>16.49</v>
       </c>
-      <c r="T25" s="300">
-        <v>-10.32</v>
+      <c r="T25" s="311">
+        <v>-11.3</v>
       </c>
     </row>
     <row r="26">
@@ -10794,7 +10794,7 @@
       <c r="C26" t="str">
         <v>603696</v>
       </c>
-      <c r="D26" s="314" t="str">
+      <c r="D26" s="317" t="str">
         <v>净卖: -3631.64万</v>
       </c>
       <c r="E26">
@@ -10809,41 +10809,41 @@
       <c r="H26">
         <v>9.08</v>
       </c>
-      <c r="I26" s="317">
+      <c r="I26" s="318">
         <v>-10.47</v>
       </c>
-      <c r="J26" s="315">
+      <c r="J26" s="313">
         <v>-19.42</v>
       </c>
-      <c r="K26" s="318">
+      <c r="K26" s="314">
         <v>-21.91</v>
       </c>
       <c r="L26" s="323">
         <v>-19.92</v>
       </c>
-      <c r="M26" s="316">
+      <c r="M26" s="324">
         <v>-11.91</v>
       </c>
-      <c r="N26" s="324">
+      <c r="N26" s="325">
         <v>-20.7</v>
       </c>
-      <c r="O26" s="319">
+      <c r="O26" s="321">
         <v>-25.29</v>
       </c>
-      <c r="P26" s="320">
+      <c r="P26" s="315">
         <v>-21.4</v>
       </c>
-      <c r="Q26" s="325">
+      <c r="Q26" s="322">
         <v>-13.54</v>
       </c>
-      <c r="R26" s="321">
+      <c r="R26" s="316">
         <v>-4.9</v>
       </c>
-      <c r="S26" s="313">
+      <c r="S26" s="319">
         <v>4.59</v>
       </c>
-      <c r="T26" s="322">
-        <v>-39.49</v>
+      <c r="T26" s="320">
+        <v>-40.16</v>
       </c>
     </row>
     <row r="27">
@@ -10856,7 +10856,7 @@
       <c r="C27" t="str">
         <v>002682</v>
       </c>
-      <c r="D27" s="331" t="str">
+      <c r="D27" s="336" t="str">
         <v>净卖: -4674.28万</v>
       </c>
       <c r="E27">
@@ -10871,41 +10871,41 @@
       <c r="H27">
         <v>-4.33</v>
       </c>
-      <c r="I27" s="332">
+      <c r="I27" s="333">
         <v>14.93</v>
       </c>
-      <c r="J27" s="336">
+      <c r="J27" s="334">
         <v>3.47</v>
       </c>
-      <c r="K27" s="327">
+      <c r="K27" s="337">
         <v>-6.84</v>
       </c>
-      <c r="L27" s="330">
+      <c r="L27" s="338">
         <v>-5.11</v>
       </c>
-      <c r="M27" s="333">
+      <c r="M27" s="335">
         <v>-10.89</v>
       </c>
-      <c r="N27" s="334">
+      <c r="N27" s="326">
         <v>-19.36</v>
       </c>
       <c r="O27" s="328">
         <v>-21</v>
       </c>
-      <c r="P27" s="337">
+      <c r="P27" s="327">
         <v>-20.33</v>
       </c>
-      <c r="Q27" s="338">
+      <c r="Q27" s="329">
         <v>-12.43</v>
       </c>
-      <c r="R27" s="335">
+      <c r="R27" s="330">
         <v>-14.26</v>
       </c>
-      <c r="S27" s="326">
+      <c r="S27" s="331">
         <v>-7.8</v>
       </c>
-      <c r="T27" s="329">
-        <v>-44.41</v>
+      <c r="T27" s="332">
+        <v>-44.32</v>
       </c>
     </row>
     <row r="28">
@@ -10918,7 +10918,7 @@
       <c r="C28" t="str">
         <v>600693</v>
       </c>
-      <c r="D28" s="343" t="str">
+      <c r="D28" s="340" t="str">
         <v>净买: 4441.53万</v>
       </c>
       <c r="E28">
@@ -10933,41 +10933,41 @@
       <c r="H28">
         <v>1.81</v>
       </c>
-      <c r="I28" s="341">
+      <c r="I28" s="351">
         <v>8.04</v>
       </c>
-      <c r="J28" s="348">
+      <c r="J28" s="339">
         <v>15.95</v>
       </c>
-      <c r="K28" s="349">
+      <c r="K28" s="345">
         <v>10.22</v>
       </c>
-      <c r="L28" s="344">
+      <c r="L28" s="346">
         <v>13.45</v>
       </c>
-      <c r="M28" s="350">
+      <c r="M28" s="349">
         <v>12.33</v>
       </c>
-      <c r="N28" s="351">
+      <c r="N28" s="341">
         <v>23.53</v>
       </c>
-      <c r="O28" s="339">
+      <c r="O28" s="342">
         <v>28.54</v>
       </c>
-      <c r="P28" s="342">
+      <c r="P28" s="343">
         <v>41.4</v>
       </c>
-      <c r="Q28" s="340">
+      <c r="Q28" s="347">
         <v>37.84</v>
       </c>
-      <c r="R28" s="345">
+      <c r="R28" s="344">
         <v>44.23</v>
       </c>
-      <c r="S28" s="346">
+      <c r="S28" s="350">
         <v>30.52</v>
       </c>
-      <c r="T28" s="347">
-        <v>-23.99</v>
+      <c r="T28" s="348">
+        <v>-24.85</v>
       </c>
     </row>
     <row r="29">
@@ -10980,7 +10980,7 @@
       <c r="C29" t="str">
         <v>603696</v>
       </c>
-      <c r="D29" s="354" t="str">
+      <c r="D29" s="357" t="str">
         <v>净卖: -3147.63万</v>
       </c>
       <c r="E29">
@@ -10995,41 +10995,41 @@
       <c r="H29">
         <v>2.92</v>
       </c>
-      <c r="I29" s="357">
+      <c r="I29" s="353">
         <v>-12.53</v>
       </c>
       <c r="J29" s="358">
         <v>-17.6</v>
       </c>
-      <c r="K29" s="359">
+      <c r="K29" s="360">
         <v>-13.3</v>
       </c>
-      <c r="L29" s="364">
+      <c r="L29" s="363">
         <v>-4.64</v>
       </c>
-      <c r="M29" s="360">
+      <c r="M29" s="364">
         <v>4.89</v>
       </c>
-      <c r="N29" s="352">
+      <c r="N29" s="359">
         <v>15.36</v>
       </c>
-      <c r="O29" s="353">
+      <c r="O29" s="354">
         <v>13.73</v>
       </c>
-      <c r="P29" s="361">
+      <c r="P29" s="355">
         <v>12.4</v>
       </c>
-      <c r="Q29" s="355">
+      <c r="Q29" s="361">
         <v>1.16</v>
       </c>
-      <c r="R29" s="362">
+      <c r="R29" s="352">
         <v>-8.97</v>
       </c>
-      <c r="S29" s="356">
+      <c r="S29" s="362">
         <v>-12.96</v>
       </c>
-      <c r="T29" s="363">
-        <v>-33.26</v>
+      <c r="T29" s="356">
+        <v>-33.99</v>
       </c>
     </row>
     <row r="30">
@@ -11042,7 +11042,7 @@
       <c r="C30" t="str">
         <v>600693</v>
       </c>
-      <c r="D30" s="367" t="str">
+      <c r="D30" s="373" t="str">
         <v>净卖: -5308.96万</v>
       </c>
       <c r="E30">
@@ -11057,41 +11057,41 @@
       <c r="H30">
         <v>2.51</v>
       </c>
-      <c r="I30" s="376">
+      <c r="I30" s="377">
         <v>0.41</v>
       </c>
-      <c r="J30" s="377">
+      <c r="J30" s="370">
         <v>-0.58</v>
       </c>
       <c r="K30" s="365">
         <v>9.33</v>
       </c>
-      <c r="L30" s="372">
+      <c r="L30" s="374">
         <v>13.77</v>
       </c>
-      <c r="M30" s="368">
+      <c r="M30" s="371">
         <v>25.15</v>
       </c>
-      <c r="N30" s="369">
+      <c r="N30" s="368">
         <v>22</v>
       </c>
-      <c r="O30" s="370">
+      <c r="O30" s="375">
         <v>27.65</v>
       </c>
-      <c r="P30" s="373">
+      <c r="P30" s="369">
         <v>15.52</v>
       </c>
-      <c r="Q30" s="374">
+      <c r="Q30" s="366">
         <v>3.97</v>
       </c>
-      <c r="R30" s="371">
+      <c r="R30" s="367">
         <v>3.97</v>
       </c>
-      <c r="S30" s="366">
+      <c r="S30" s="372">
         <v>7.29</v>
       </c>
-      <c r="T30" s="375">
-        <v>-32.73</v>
+      <c r="T30" s="376">
+        <v>-33.49</v>
       </c>
     </row>
     <row r="31">
@@ -11104,7 +11104,7 @@
       <c r="C31" t="str">
         <v>600280</v>
       </c>
-      <c r="D31" s="378" t="str">
+      <c r="D31" s="382" t="str">
         <v>净买: 2343.21万</v>
       </c>
       <c r="E31">
@@ -11119,41 +11119,41 @@
       <c r="H31">
         <v>1.88</v>
       </c>
-      <c r="I31" s="379">
+      <c r="I31" s="385">
         <v>8.08</v>
       </c>
       <c r="J31" s="383">
         <v>17.78</v>
       </c>
-      <c r="K31" s="384">
+      <c r="K31" s="379">
         <v>12.93</v>
       </c>
-      <c r="L31" s="385">
+      <c r="L31" s="380">
         <v>4.39</v>
       </c>
-      <c r="M31" s="388">
+      <c r="M31" s="381">
         <v>5.54</v>
       </c>
-      <c r="N31" s="389">
+      <c r="N31" s="384">
         <v>1.85</v>
       </c>
-      <c r="O31" s="380">
+      <c r="O31" s="387">
         <v>-1.15</v>
       </c>
-      <c r="P31" s="386">
+      <c r="P31" s="388">
         <v>-3</v>
       </c>
-      <c r="Q31" s="387">
+      <c r="Q31" s="386">
         <v>-7.85</v>
       </c>
-      <c r="R31" s="381">
+      <c r="R31" s="389">
         <v>-11.09</v>
       </c>
-      <c r="S31" s="382">
+      <c r="S31" s="390">
         <v>-10.16</v>
       </c>
-      <c r="T31" s="390">
-        <v>-30.02</v>
+      <c r="T31" s="378">
+        <v>-30.25</v>
       </c>
     </row>
     <row r="32">
@@ -11166,7 +11166,7 @@
       <c r="C32" t="str">
         <v>600280</v>
       </c>
-      <c r="D32" s="393" t="str">
+      <c r="D32" s="395" t="str">
         <v>净卖: -2545.17万</v>
       </c>
       <c r="E32">
@@ -11181,41 +11181,41 @@
       <c r="H32">
         <v>-3.92</v>
       </c>
-      <c r="I32" s="398">
+      <c r="I32" s="396">
         <v>-0.2</v>
       </c>
-      <c r="J32" s="392">
+      <c r="J32" s="397">
         <v>-7.76</v>
       </c>
-      <c r="K32" s="394">
+      <c r="K32" s="399">
         <v>-6.73</v>
       </c>
-      <c r="L32" s="401">
+      <c r="L32" s="403">
         <v>-10</v>
       </c>
-      <c r="M32" s="402">
+      <c r="M32" s="391">
         <v>-12.65</v>
       </c>
-      <c r="N32" s="395">
+      <c r="N32" s="393">
         <v>-14.29</v>
       </c>
-      <c r="O32" s="396">
+      <c r="O32" s="400">
         <v>-18.57</v>
       </c>
-      <c r="P32" s="403">
+      <c r="P32" s="394">
         <v>-21.43</v>
       </c>
-      <c r="Q32" s="399">
+      <c r="Q32" s="392">
         <v>-20.61</v>
       </c>
-      <c r="R32" s="397">
+      <c r="R32" s="401">
         <v>-16.33</v>
       </c>
-      <c r="S32" s="400">
+      <c r="S32" s="402">
         <v>-15.92</v>
       </c>
-      <c r="T32" s="391">
-        <v>-38.16</v>
+      <c r="T32" s="398">
+        <v>-38.37</v>
       </c>
     </row>
     <row r="33">
@@ -11228,7 +11228,7 @@
       <c r="C33" t="str">
         <v>002759</v>
       </c>
-      <c r="D33" s="410" t="str">
+      <c r="D33" s="407" t="str">
         <v>净买: 8490.49万</v>
       </c>
       <c r="E33">
@@ -11243,31 +11243,31 @@
       <c r="H33">
         <v>-3.82</v>
       </c>
-      <c r="I33" s="415">
+      <c r="I33" s="408">
         <v>11.08</v>
       </c>
-      <c r="J33" s="406">
+      <c r="J33" s="411">
         <v>22.19</v>
       </c>
-      <c r="K33" s="411">
+      <c r="K33" s="409">
         <v>22.69</v>
       </c>
-      <c r="L33" s="407">
+      <c r="L33" s="412">
         <v>13.63</v>
       </c>
-      <c r="M33" s="412">
+      <c r="M33" s="416">
         <v>14.61</v>
       </c>
       <c r="N33" s="413">
         <v>26.07</v>
       </c>
-      <c r="O33" s="414">
+      <c r="O33" s="410">
         <v>26.51</v>
       </c>
-      <c r="P33" s="416">
+      <c r="P33" s="414">
         <v>18.86</v>
       </c>
-      <c r="Q33" s="408">
+      <c r="Q33" s="415">
         <v>15.77</v>
       </c>
       <c r="R33" s="404">
@@ -11276,8 +11276,8 @@
       <c r="S33" s="405">
         <v>15.03</v>
       </c>
-      <c r="T33" s="409">
-        <v>-15.08</v>
+      <c r="T33" s="406">
+        <v>-16.07</v>
       </c>
     </row>
     <row r="34">
@@ -11290,7 +11290,7 @@
       <c r="C34" t="str">
         <v>002792</v>
       </c>
-      <c r="D34" s="417" t="str">
+      <c r="D34" s="429" t="str">
         <v>净买: 8322.30万</v>
       </c>
       <c r="E34">
@@ -11305,41 +11305,41 @@
       <c r="H34">
         <v>0.05</v>
       </c>
-      <c r="I34" s="426">
+      <c r="I34" s="417">
         <v>7.5</v>
       </c>
-      <c r="J34" s="423">
+      <c r="J34" s="422">
         <v>15.33</v>
       </c>
-      <c r="K34" s="427">
+      <c r="K34" s="423">
         <v>19.23</v>
       </c>
       <c r="L34" s="424">
         <v>31.17</v>
       </c>
-      <c r="M34" s="418">
+      <c r="M34" s="420">
         <v>44.28</v>
       </c>
-      <c r="N34" s="425">
+      <c r="N34" s="427">
         <v>53.02</v>
       </c>
-      <c r="O34" s="419">
+      <c r="O34" s="425">
         <v>68.33</v>
       </c>
-      <c r="P34" s="420">
+      <c r="P34" s="428">
         <v>76.16</v>
       </c>
       <c r="Q34" s="421">
         <v>58.53</v>
       </c>
-      <c r="R34" s="422">
+      <c r="R34" s="426">
         <v>42.67</v>
       </c>
-      <c r="S34" s="428">
+      <c r="S34" s="418">
         <v>30.19</v>
       </c>
-      <c r="T34" s="429">
-        <v>13.42</v>
+      <c r="T34" s="419">
+        <v>6.42</v>
       </c>
     </row>
     <row r="35">
@@ -11352,7 +11352,7 @@
       <c r="C35" t="str">
         <v>002792</v>
       </c>
-      <c r="D35" s="432" t="str">
+      <c r="D35" s="435" t="str">
         <v>净卖: -7684.69万</v>
       </c>
       <c r="E35">
@@ -11367,41 +11367,41 @@
       <c r="H35">
         <v>2.25</v>
       </c>
-      <c r="I35" s="436">
+      <c r="I35" s="439">
         <v>4.92</v>
       </c>
-      <c r="J35" s="431">
+      <c r="J35" s="442">
         <v>8.47</v>
       </c>
-      <c r="K35" s="437">
+      <c r="K35" s="436">
         <v>19.33</v>
       </c>
-      <c r="L35" s="439">
+      <c r="L35" s="430">
         <v>31.26</v>
       </c>
-      <c r="M35" s="440">
+      <c r="M35" s="437">
         <v>39.21</v>
       </c>
-      <c r="N35" s="433">
+      <c r="N35" s="431">
         <v>53.14</v>
       </c>
-      <c r="O35" s="441">
+      <c r="O35" s="440">
         <v>60.26</v>
       </c>
-      <c r="P35" s="434">
+      <c r="P35" s="438">
         <v>44.23</v>
       </c>
-      <c r="Q35" s="435">
+      <c r="Q35" s="441">
         <v>29.8</v>
       </c>
-      <c r="R35" s="442">
+      <c r="R35" s="432">
         <v>18.44</v>
       </c>
-      <c r="S35" s="438">
+      <c r="S35" s="433">
         <v>17.43</v>
       </c>
-      <c r="T35" s="430">
-        <v>3.18</v>
+      <c r="T35" s="434">
+        <v>-3.18</v>
       </c>
     </row>
     <row r="36">
@@ -11414,7 +11414,7 @@
       <c r="C36" t="str">
         <v>002759</v>
       </c>
-      <c r="D36" s="450" t="str">
+      <c r="D36" s="454" t="str">
         <v>净买: 1.00亿</v>
       </c>
       <c r="E36">
@@ -11432,38 +11432,38 @@
       <c r="I36" s="447">
         <v>6.73</v>
       </c>
-      <c r="J36" s="455">
+      <c r="J36" s="451">
         <v>7.11</v>
       </c>
-      <c r="K36" s="443">
+      <c r="K36" s="446">
         <v>0.63</v>
       </c>
-      <c r="L36" s="444">
+      <c r="L36" s="448">
         <v>-1.99</v>
       </c>
-      <c r="M36" s="448">
+      <c r="M36" s="455">
         <v>-3.59</v>
       </c>
-      <c r="N36" s="445">
+      <c r="N36" s="443">
         <v>-2.61</v>
       </c>
-      <c r="O36" s="451">
+      <c r="O36" s="452">
         <v>-7.82</v>
       </c>
-      <c r="P36" s="452">
+      <c r="P36" s="449">
         <v>-11.35</v>
       </c>
-      <c r="Q36" s="453">
+      <c r="Q36" s="444">
         <v>-5.64</v>
       </c>
-      <c r="R36" s="454">
+      <c r="R36" s="453">
         <v>-13.61</v>
       </c>
-      <c r="S36" s="449">
+      <c r="S36" s="450">
         <v>-12.5</v>
       </c>
-      <c r="T36" s="446">
-        <v>-28.11</v>
+      <c r="T36" s="445">
+        <v>-28.94</v>
       </c>
     </row>
     <row r="37">
@@ -11476,7 +11476,7 @@
       <c r="C37" t="str">
         <v>600776</v>
       </c>
-      <c r="D37" s="464" t="str">
+      <c r="D37" s="463" t="str">
         <v>净买: 5452.75万</v>
       </c>
       <c r="E37">
@@ -11491,41 +11491,41 @@
       <c r="H37">
         <v>10.02</v>
       </c>
-      <c r="I37" s="461">
+      <c r="I37" s="456">
         <v>0</v>
       </c>
-      <c r="J37" s="458">
+      <c r="J37" s="464">
         <v>10</v>
       </c>
-      <c r="K37" s="465">
+      <c r="K37" s="457">
         <v>16.57</v>
       </c>
-      <c r="L37" s="466">
+      <c r="L37" s="465">
         <v>4.91</v>
       </c>
-      <c r="M37" s="467">
+      <c r="M37" s="459">
         <v>-5.58</v>
       </c>
-      <c r="N37" s="456">
+      <c r="N37" s="466">
         <v>-15.01</v>
       </c>
-      <c r="O37" s="462">
+      <c r="O37" s="458">
         <v>-17.91</v>
       </c>
-      <c r="P37" s="459">
+      <c r="P37" s="467">
         <v>-16.93</v>
       </c>
-      <c r="Q37" s="463">
+      <c r="Q37" s="460">
         <v>-15.19</v>
       </c>
-      <c r="R37" s="468">
+      <c r="R37" s="461">
         <v>-10.99</v>
       </c>
-      <c r="S37" s="460">
+      <c r="S37" s="468">
         <v>-15.27</v>
       </c>
-      <c r="T37" s="457">
-        <v>-25.23</v>
+      <c r="T37" s="462">
+        <v>-23.45</v>
       </c>
     </row>
     <row r="38">
@@ -11538,7 +11538,7 @@
       <c r="C38" t="str">
         <v>600410</v>
       </c>
-      <c r="D38" s="474" t="str">
+      <c r="D38" s="475" t="str">
         <v>净买: 1.26亿</v>
       </c>
       <c r="E38">
@@ -11553,41 +11553,41 @@
       <c r="H38">
         <v>-1.64</v>
       </c>
-      <c r="I38" s="475">
+      <c r="I38" s="481">
         <v>11.84</v>
       </c>
-      <c r="J38" s="481">
+      <c r="J38" s="476">
         <v>23.02</v>
       </c>
-      <c r="K38" s="476">
+      <c r="K38" s="472">
         <v>10.78</v>
       </c>
-      <c r="L38" s="469">
+      <c r="L38" s="473">
         <v>2.42</v>
       </c>
-      <c r="M38" s="479">
+      <c r="M38" s="477">
         <v>0</v>
       </c>
-      <c r="N38" s="477">
+      <c r="N38" s="478">
         <v>1.86</v>
       </c>
-      <c r="O38" s="480">
+      <c r="O38" s="469">
         <v>2.67</v>
       </c>
       <c r="P38" s="470">
         <v>5.99</v>
       </c>
-      <c r="Q38" s="471">
+      <c r="Q38" s="474">
         <v>0.81</v>
       </c>
-      <c r="R38" s="472">
+      <c r="R38" s="479">
         <v>6.95</v>
       </c>
-      <c r="S38" s="473">
+      <c r="S38" s="471">
         <v>6.25</v>
       </c>
-      <c r="T38" s="478">
-        <v>30.98</v>
+      <c r="T38" s="480">
+        <v>17.88</v>
       </c>
     </row>
     <row r="39">
@@ -11600,7 +11600,7 @@
       <c r="C39" t="str">
         <v>600410</v>
       </c>
-      <c r="D39" s="484" t="str">
+      <c r="D39" s="494" t="str">
         <v>净买: 1.26亿</v>
       </c>
       <c r="E39">
@@ -11615,41 +11615,41 @@
       <c r="H39">
         <v>10</v>
       </c>
-      <c r="I39" s="485">
+      <c r="I39" s="482">
         <v>0</v>
       </c>
-      <c r="J39" s="488">
+      <c r="J39" s="483">
         <v>-9.95</v>
       </c>
-      <c r="K39" s="494">
+      <c r="K39" s="484">
         <v>-16.75</v>
       </c>
       <c r="L39" s="486">
         <v>-18.71</v>
       </c>
-      <c r="M39" s="482">
+      <c r="M39" s="490">
         <v>-17.2</v>
       </c>
       <c r="N39" s="487">
         <v>-16.54</v>
       </c>
-      <c r="O39" s="491">
+      <c r="O39" s="492">
         <v>-13.84</v>
       </c>
-      <c r="P39" s="492">
+      <c r="P39" s="485">
         <v>-18.06</v>
       </c>
-      <c r="Q39" s="489">
+      <c r="Q39" s="493">
         <v>-13.06</v>
       </c>
-      <c r="R39" s="493">
+      <c r="R39" s="491">
         <v>-13.64</v>
       </c>
-      <c r="S39" s="490">
+      <c r="S39" s="488">
         <v>-10.2</v>
       </c>
-      <c r="T39" s="483">
-        <v>6.47</v>
+      <c r="T39" s="489">
+        <v>-4.18</v>
       </c>
     </row>
     <row r="40">
@@ -11662,7 +11662,7 @@
       <c r="C40" t="str">
         <v>600776</v>
       </c>
-      <c r="D40" s="505" t="str">
+      <c r="D40" s="506" t="str">
         <v>净卖: -233.39万</v>
       </c>
       <c r="E40">
@@ -11677,41 +11677,41 @@
       <c r="H40">
         <v>-10</v>
       </c>
-      <c r="I40" s="503">
+      <c r="I40" s="507">
         <v>0</v>
       </c>
-      <c r="J40" s="506">
+      <c r="J40" s="503">
         <v>-9.98</v>
       </c>
-      <c r="K40" s="507">
+      <c r="K40" s="495">
         <v>-13.06</v>
       </c>
-      <c r="L40" s="495">
+      <c r="L40" s="497">
         <v>-12.02</v>
       </c>
-      <c r="M40" s="500">
+      <c r="M40" s="498">
         <v>-10.17</v>
       </c>
-      <c r="N40" s="496">
+      <c r="N40" s="499">
         <v>-5.72</v>
       </c>
-      <c r="O40" s="498">
+      <c r="O40" s="496">
         <v>-10.26</v>
       </c>
-      <c r="P40" s="504">
+      <c r="P40" s="505">
         <v>-9.89</v>
       </c>
-      <c r="Q40" s="501">
+      <c r="Q40" s="504">
         <v>-11.26</v>
       </c>
-      <c r="R40" s="499">
+      <c r="R40" s="500">
         <v>-11.78</v>
       </c>
-      <c r="S40" s="502">
+      <c r="S40" s="501">
         <v>-12.49</v>
       </c>
-      <c r="T40" s="497">
-        <v>-20.81</v>
+      <c r="T40" s="502">
+        <v>-18.92</v>
       </c>
     </row>
     <row r="41">
@@ -11724,7 +11724,7 @@
       <c r="C41" t="str">
         <v>600410</v>
       </c>
-      <c r="D41" s="510" t="str">
+      <c r="D41" s="512" t="str">
         <v>净卖: -1.30亿</v>
       </c>
       <c r="E41">
@@ -11742,38 +11742,38 @@
       <c r="I41" s="517">
         <v>-8.15</v>
       </c>
-      <c r="J41" s="518">
+      <c r="J41" s="509">
         <v>-15.08</v>
       </c>
-      <c r="K41" s="519">
+      <c r="K41" s="513">
         <v>-17.08</v>
       </c>
-      <c r="L41" s="511">
+      <c r="L41" s="518">
         <v>-15.54</v>
       </c>
-      <c r="M41" s="512">
+      <c r="M41" s="510">
         <v>-14.87</v>
       </c>
-      <c r="N41" s="508">
+      <c r="N41" s="519">
         <v>-12.11</v>
       </c>
-      <c r="O41" s="509">
+      <c r="O41" s="520">
         <v>-16.42</v>
       </c>
-      <c r="P41" s="513">
+      <c r="P41" s="508">
         <v>-11.32</v>
       </c>
-      <c r="Q41" s="515">
+      <c r="Q41" s="514">
         <v>-11.9</v>
       </c>
-      <c r="R41" s="520">
+      <c r="R41" s="511">
         <v>-8.4</v>
       </c>
-      <c r="S41" s="514">
+      <c r="S41" s="515">
         <v>-12.24</v>
       </c>
       <c r="T41" s="516">
-        <v>8.6</v>
+        <v>-2.26</v>
       </c>
     </row>
     <row r="42">
@@ -11786,7 +11786,7 @@
       <c r="C42" t="str">
         <v>002792</v>
       </c>
-      <c r="D42" s="531" t="str">
+      <c r="D42" s="533" t="str">
         <v>净买: 5153.68万</v>
       </c>
       <c r="E42">
@@ -11801,41 +11801,41 @@
       <c r="H42">
         <v>0.55</v>
       </c>
-      <c r="I42" s="527">
+      <c r="I42" s="521">
         <v>9.39</v>
       </c>
-      <c r="J42" s="523">
+      <c r="J42" s="526">
         <v>15.85</v>
       </c>
-      <c r="K42" s="532">
+      <c r="K42" s="524">
         <v>10.51</v>
       </c>
-      <c r="L42" s="528">
+      <c r="L42" s="530">
         <v>6.31</v>
       </c>
-      <c r="M42" s="529">
+      <c r="M42" s="531">
         <v>1.07</v>
       </c>
-      <c r="N42" s="533">
+      <c r="N42" s="522">
         <v>-1.76</v>
       </c>
-      <c r="O42" s="530">
+      <c r="O42" s="523">
         <v>0.67</v>
       </c>
-      <c r="P42" s="521">
+      <c r="P42" s="527">
         <v>10.74</v>
       </c>
-      <c r="Q42" s="524">
+      <c r="Q42" s="528">
         <v>10.74</v>
       </c>
-      <c r="R42" s="522">
+      <c r="R42" s="525">
         <v>7.46</v>
       </c>
-      <c r="S42" s="525">
+      <c r="S42" s="532">
         <v>7.34</v>
       </c>
-      <c r="T42" s="526">
-        <v>-5.54</v>
+      <c r="T42" s="529">
+        <v>-11.37</v>
       </c>
     </row>
     <row r="43">
@@ -11897,41 +11897,41 @@
       <c r="F44" t="str"/>
       <c r="G44" t="str"/>
       <c r="H44" t="str"/>
-      <c r="I44" s="537">
+      <c r="I44" s="541">
         <v>65.85</v>
       </c>
-      <c r="J44" s="534">
+      <c r="J44" s="545">
         <v>65.85</v>
       </c>
-      <c r="K44" s="541">
+      <c r="K44" s="542">
         <v>60.98</v>
       </c>
-      <c r="L44" s="535">
+      <c r="L44" s="537">
         <v>56.1</v>
       </c>
-      <c r="M44" s="542">
+      <c r="M44" s="534">
         <v>48.78</v>
       </c>
-      <c r="N44" s="539">
+      <c r="N44" s="538">
         <v>46.34</v>
       </c>
-      <c r="O44" s="543">
+      <c r="O44" s="539">
         <v>48.78</v>
       </c>
-      <c r="P44" s="544">
+      <c r="P44" s="535">
         <v>43.9</v>
       </c>
-      <c r="Q44" s="545">
+      <c r="Q44" s="543">
         <v>39.02</v>
       </c>
-      <c r="R44" s="538">
+      <c r="R44" s="544">
         <v>43.9</v>
       </c>
-      <c r="S44" s="536">
+      <c r="S44" s="540">
         <v>43.9</v>
       </c>
-      <c r="T44" s="540">
-        <v>31.71</v>
+      <c r="T44" s="536">
+        <v>19.51</v>
       </c>
     </row>
     <row r="45">
@@ -11945,41 +11945,41 @@
       <c r="F45" t="str"/>
       <c r="G45" t="str"/>
       <c r="H45" t="str"/>
-      <c r="I45" s="554">
+      <c r="I45" s="552">
         <v>3.79</v>
       </c>
-      <c r="J45" s="546">
+      <c r="J45" s="556">
         <v>5.59</v>
       </c>
-      <c r="K45" s="549">
+      <c r="K45" s="557">
         <v>5.07</v>
       </c>
-      <c r="L45" s="550">
+      <c r="L45" s="546">
         <v>5.23</v>
       </c>
-      <c r="M45" s="555">
+      <c r="M45" s="553">
         <v>5.01</v>
       </c>
-      <c r="N45" s="556">
+      <c r="N45" s="548">
         <v>4.05</v>
       </c>
-      <c r="O45" s="547">
+      <c r="O45" s="549">
         <v>4.42</v>
       </c>
-      <c r="P45" s="557">
+      <c r="P45" s="550">
         <v>3.76</v>
       </c>
-      <c r="Q45" s="551">
+      <c r="Q45" s="547">
         <v>1.74</v>
       </c>
-      <c r="R45" s="552">
+      <c r="R45" s="554">
         <v>1.6</v>
       </c>
-      <c r="S45" s="548">
+      <c r="S45" s="555">
         <v>0.99</v>
       </c>
-      <c r="T45" s="553">
-        <v>-9.26</v>
+      <c r="T45" s="551">
+        <v>-11.85</v>
       </c>
     </row>
   </sheetData>
